--- a/docs/Spartum_Gantt.xlsx
+++ b/docs/Spartum_Gantt.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Planificación Mes 3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Planificación Mes 1'!$A$1:$AD$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planificación Mes 2'!$A$1:$AD$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Planificación Mes 3'!$A$1:$W$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Planificación Mes 1'!$A$1:$AD$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planificación Mes 2'!$A$1:$AD$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Planificación Mes 3'!$A$1:$W$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,18 +63,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -286,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -343,28 +333,31 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -730,13 +723,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008CB5B7"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD36"/>
+  <dimension ref="A1:AD58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
     <col width="3.7" customWidth="1" min="3" max="3"/>
     <col width="3.7" customWidth="1" min="4" max="4"/>
@@ -1148,7 +1141,7 @@
       </c>
       <c r="AD7" s="13" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Núcleo del proyecto</t>
@@ -1156,7 +1149,7 @@
       </c>
       <c r="B8" s="21" t="n"/>
       <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
+      <c r="D8" s="22" t="n"/>
       <c r="E8" s="22" t="n"/>
       <c r="F8" s="22" t="n"/>
       <c r="G8" s="22" t="n"/>
@@ -1188,20 +1181,20 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Acceso, registro y sesión</t>
+    <row r="9" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B9" s="22" t="n"/>
       <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="24" t="n"/>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
-      <c r="I9" s="24" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
       <c r="J9" s="22" t="n"/>
       <c r="K9" s="22" t="n"/>
       <c r="L9" s="22" t="n"/>
@@ -1228,23 +1221,23 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Recuperación de cuenta y tickets</t>
+    <row r="10" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B10" s="22" t="n"/>
       <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
+      <c r="D10" s="21" t="n"/>
       <c r="E10" s="22" t="n"/>
       <c r="F10" s="22" t="n"/>
       <c r="G10" s="22" t="n"/>
       <c r="H10" s="22" t="n"/>
       <c r="I10" s="22" t="n"/>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="25" t="n"/>
-      <c r="L10" s="25" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="22" t="n"/>
+      <c r="L10" s="22" t="n"/>
       <c r="M10" s="22" t="n"/>
       <c r="N10" s="22" t="n"/>
       <c r="O10" s="22" t="n"/>
@@ -1268,27 +1261,27 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Perfil, contraseña y baja</t>
+          <t>Acceso, registro y sesión</t>
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
       <c r="C11" s="22" t="n"/>
       <c r="D11" s="22" t="n"/>
-      <c r="E11" s="22" t="n"/>
-      <c r="F11" s="22" t="n"/>
+      <c r="E11" s="25" t="n"/>
+      <c r="F11" s="25" t="n"/>
       <c r="G11" s="22" t="n"/>
       <c r="H11" s="22" t="n"/>
       <c r="I11" s="22" t="n"/>
       <c r="J11" s="22" t="n"/>
       <c r="K11" s="22" t="n"/>
       <c r="L11" s="22" t="n"/>
-      <c r="M11" s="26" t="n"/>
-      <c r="N11" s="26" t="n"/>
-      <c r="O11" s="26" t="n"/>
-      <c r="P11" s="26" t="n"/>
+      <c r="M11" s="22" t="n"/>
+      <c r="N11" s="22" t="n"/>
+      <c r="O11" s="22" t="n"/>
+      <c r="P11" s="22" t="n"/>
       <c r="Q11" s="22" t="n"/>
       <c r="R11" s="22" t="n"/>
       <c r="S11" s="22" t="n"/>
@@ -1308,10 +1301,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Actividades y horario</t>
+    <row r="12" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
@@ -1321,7 +1314,7 @@
       <c r="F12" s="22" t="n"/>
       <c r="G12" s="22" t="n"/>
       <c r="H12" s="22" t="n"/>
-      <c r="I12" s="22" t="n"/>
+      <c r="I12" s="25" t="n"/>
       <c r="J12" s="22" t="n"/>
       <c r="K12" s="22" t="n"/>
       <c r="L12" s="22" t="n"/>
@@ -1329,9 +1322,9 @@
       <c r="N12" s="22" t="n"/>
       <c r="O12" s="22" t="n"/>
       <c r="P12" s="22" t="n"/>
-      <c r="Q12" s="27" t="n"/>
-      <c r="R12" s="27" t="n"/>
-      <c r="S12" s="27" t="n"/>
+      <c r="Q12" s="22" t="n"/>
+      <c r="R12" s="22" t="n"/>
+      <c r="S12" s="22" t="n"/>
       <c r="T12" s="22" t="n"/>
       <c r="U12" s="22" t="n"/>
       <c r="V12" s="22" t="n"/>
@@ -1342,16 +1335,16 @@
       <c r="AA12" s="22" t="n"/>
       <c r="AB12" s="22" t="n"/>
       <c r="AC12" s="22" t="n"/>
-      <c r="AD12" s="28" t="inlineStr">
-        <is>
-          <t>en curso</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Inscripciones y reservas</t>
+      <c r="AD12" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
@@ -1361,7 +1354,7 @@
       <c r="F13" s="22" t="n"/>
       <c r="G13" s="22" t="n"/>
       <c r="H13" s="22" t="n"/>
-      <c r="I13" s="22" t="n"/>
+      <c r="I13" s="25" t="n"/>
       <c r="J13" s="22" t="n"/>
       <c r="K13" s="22" t="n"/>
       <c r="L13" s="22" t="n"/>
@@ -1372,26 +1365,26 @@
       <c r="Q13" s="22" t="n"/>
       <c r="R13" s="22" t="n"/>
       <c r="S13" s="22" t="n"/>
-      <c r="T13" s="21" t="n"/>
-      <c r="U13" s="21" t="n"/>
-      <c r="V13" s="21" t="n"/>
-      <c r="W13" s="21" t="n"/>
-      <c r="X13" s="21" t="n"/>
+      <c r="T13" s="22" t="n"/>
+      <c r="U13" s="22" t="n"/>
+      <c r="V13" s="22" t="n"/>
+      <c r="W13" s="22" t="n"/>
+      <c r="X13" s="22" t="n"/>
       <c r="Y13" s="22" t="n"/>
       <c r="Z13" s="22" t="n"/>
       <c r="AA13" s="22" t="n"/>
       <c r="AB13" s="22" t="n"/>
       <c r="AC13" s="22" t="n"/>
-      <c r="AD13" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
+      <c r="AD13" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Suscripciones</t>
+          <t>Recuperación de cuenta y tickets</t>
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
@@ -1402,8 +1395,8 @@
       <c r="G14" s="22" t="n"/>
       <c r="H14" s="22" t="n"/>
       <c r="I14" s="22" t="n"/>
-      <c r="J14" s="22" t="n"/>
-      <c r="K14" s="22" t="n"/>
+      <c r="J14" s="26" t="n"/>
+      <c r="K14" s="26" t="n"/>
       <c r="L14" s="22" t="n"/>
       <c r="M14" s="22" t="n"/>
       <c r="N14" s="22" t="n"/>
@@ -1417,21 +1410,21 @@
       <c r="V14" s="22" t="n"/>
       <c r="W14" s="22" t="n"/>
       <c r="X14" s="22" t="n"/>
-      <c r="Y14" s="24" t="n"/>
-      <c r="Z14" s="24" t="n"/>
+      <c r="Y14" s="22" t="n"/>
+      <c r="Z14" s="22" t="n"/>
       <c r="AA14" s="22" t="n"/>
       <c r="AB14" s="22" t="n"/>
       <c r="AC14" s="22" t="n"/>
-      <c r="AD14" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Pagos con Stripe</t>
+      <c r="AD14" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
@@ -1444,7 +1437,7 @@
       <c r="I15" s="22" t="n"/>
       <c r="J15" s="22" t="n"/>
       <c r="K15" s="22" t="n"/>
-      <c r="L15" s="22" t="n"/>
+      <c r="L15" s="26" t="n"/>
       <c r="M15" s="22" t="n"/>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
@@ -1459,19 +1452,19 @@
       <c r="X15" s="22" t="n"/>
       <c r="Y15" s="22" t="n"/>
       <c r="Z15" s="22" t="n"/>
-      <c r="AA15" s="25" t="n"/>
-      <c r="AB15" s="25" t="n"/>
-      <c r="AC15" s="25" t="n"/>
-      <c r="AD15" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Panel de administración</t>
+      <c r="AA15" s="22" t="n"/>
+      <c r="AB15" s="22" t="n"/>
+      <c r="AC15" s="22" t="n"/>
+      <c r="AD15" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
@@ -1484,7 +1477,7 @@
       <c r="I16" s="22" t="n"/>
       <c r="J16" s="22" t="n"/>
       <c r="K16" s="22" t="n"/>
-      <c r="L16" s="22" t="n"/>
+      <c r="L16" s="26" t="n"/>
       <c r="M16" s="22" t="n"/>
       <c r="N16" s="22" t="n"/>
       <c r="O16" s="22" t="n"/>
@@ -1502,16 +1495,16 @@
       <c r="AA16" s="22" t="n"/>
       <c r="AB16" s="22" t="n"/>
       <c r="AC16" s="22" t="n"/>
-      <c r="AD16" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
+      <c r="AD16" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>Gestión de clientes</t>
+          <t>Perfil, contraseña y baja</t>
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
@@ -1525,7 +1518,7 @@
       <c r="J17" s="22" t="n"/>
       <c r="K17" s="22" t="n"/>
       <c r="L17" s="22" t="n"/>
-      <c r="M17" s="22" t="n"/>
+      <c r="M17" s="27" t="n"/>
       <c r="N17" s="22" t="n"/>
       <c r="O17" s="22" t="n"/>
       <c r="P17" s="22" t="n"/>
@@ -1542,16 +1535,16 @@
       <c r="AA17" s="22" t="n"/>
       <c r="AB17" s="22" t="n"/>
       <c r="AC17" s="22" t="n"/>
-      <c r="AD17" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Monitores y solicitudes</t>
+      <c r="AD17" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B18" s="22" t="n"/>
@@ -1568,7 +1561,7 @@
       <c r="M18" s="22" t="n"/>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
-      <c r="P18" s="22" t="n"/>
+      <c r="P18" s="27" t="n"/>
       <c r="Q18" s="22" t="n"/>
       <c r="R18" s="22" t="n"/>
       <c r="S18" s="22" t="n"/>
@@ -1582,16 +1575,16 @@
       <c r="AA18" s="22" t="n"/>
       <c r="AB18" s="22" t="n"/>
       <c r="AC18" s="22" t="n"/>
-      <c r="AD18" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>Salas y materiales</t>
+      <c r="AD18" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B19" s="22" t="n"/>
@@ -1608,7 +1601,7 @@
       <c r="M19" s="22" t="n"/>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
-      <c r="P19" s="22" t="n"/>
+      <c r="P19" s="27" t="n"/>
       <c r="Q19" s="22" t="n"/>
       <c r="R19" s="22" t="n"/>
       <c r="S19" s="22" t="n"/>
@@ -1622,16 +1615,16 @@
       <c r="AA19" s="22" t="n"/>
       <c r="AB19" s="22" t="n"/>
       <c r="AC19" s="22" t="n"/>
-      <c r="AD19" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
+      <c r="AD19" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Fisioterapia y citas</t>
+          <t>Actividades y horario</t>
         </is>
       </c>
       <c r="B20" s="22" t="n"/>
@@ -1649,8 +1642,8 @@
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="22" t="n"/>
-      <c r="R20" s="22" t="n"/>
+      <c r="Q20" s="28" t="n"/>
+      <c r="R20" s="28" t="n"/>
       <c r="S20" s="22" t="n"/>
       <c r="T20" s="22" t="n"/>
       <c r="U20" s="22" t="n"/>
@@ -1664,14 +1657,14 @@
       <c r="AC20" s="22" t="n"/>
       <c r="AD20" s="29" t="inlineStr">
         <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>Comentarios, feedback y seguridad</t>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B21" s="22" t="n"/>
@@ -1691,7 +1684,7 @@
       <c r="P21" s="22" t="n"/>
       <c r="Q21" s="22" t="n"/>
       <c r="R21" s="22" t="n"/>
-      <c r="S21" s="22" t="n"/>
+      <c r="S21" s="28" t="n"/>
       <c r="T21" s="22" t="n"/>
       <c r="U21" s="22" t="n"/>
       <c r="V21" s="22" t="n"/>
@@ -1702,16 +1695,16 @@
       <c r="AA21" s="22" t="n"/>
       <c r="AB21" s="22" t="n"/>
       <c r="AC21" s="22" t="n"/>
-      <c r="AD21" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Interfaz Tailwind, correo y cierre</t>
+      <c r="AD21" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
@@ -1731,7 +1724,7 @@
       <c r="P22" s="22" t="n"/>
       <c r="Q22" s="22" t="n"/>
       <c r="R22" s="22" t="n"/>
-      <c r="S22" s="22" t="n"/>
+      <c r="S22" s="28" t="n"/>
       <c r="T22" s="22" t="n"/>
       <c r="U22" s="22" t="n"/>
       <c r="V22" s="22" t="n"/>
@@ -1742,459 +1735,1403 @@
       <c r="AA22" s="22" t="n"/>
       <c r="AB22" s="22" t="n"/>
       <c r="AC22" s="22" t="n"/>
-      <c r="AD22" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="30" t="n"/>
-      <c r="B23" s="31" t="n"/>
-      <c r="C23" s="31" t="n"/>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="31" t="n"/>
-      <c r="F23" s="31" t="n"/>
-      <c r="G23" s="31" t="n"/>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="31" t="n"/>
-      <c r="J23" s="31" t="n"/>
-      <c r="K23" s="31" t="n"/>
-      <c r="L23" s="31" t="n"/>
-      <c r="M23" s="31" t="n"/>
-      <c r="N23" s="31" t="n"/>
-      <c r="O23" s="31" t="n"/>
-      <c r="P23" s="31" t="n"/>
-      <c r="Q23" s="31" t="n"/>
-      <c r="R23" s="31" t="n"/>
-      <c r="S23" s="31" t="n"/>
-      <c r="T23" s="31" t="n"/>
-      <c r="U23" s="31" t="n"/>
-      <c r="V23" s="31" t="n"/>
-      <c r="W23" s="31" t="n"/>
-      <c r="X23" s="31" t="n"/>
-      <c r="Y23" s="31" t="n"/>
-      <c r="Z23" s="31" t="n"/>
-      <c r="AA23" s="31" t="n"/>
-      <c r="AB23" s="31" t="n"/>
-      <c r="AC23" s="31" t="n"/>
-      <c r="AD23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="30" t="n"/>
-      <c r="B24" s="31" t="n"/>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="31" t="n"/>
-      <c r="O24" s="31" t="n"/>
-      <c r="P24" s="31" t="n"/>
-      <c r="Q24" s="31" t="n"/>
-      <c r="R24" s="31" t="n"/>
-      <c r="S24" s="31" t="n"/>
-      <c r="T24" s="31" t="n"/>
-      <c r="U24" s="31" t="n"/>
-      <c r="V24" s="31" t="n"/>
-      <c r="W24" s="31" t="n"/>
-      <c r="X24" s="31" t="n"/>
-      <c r="Y24" s="31" t="n"/>
-      <c r="Z24" s="31" t="n"/>
-      <c r="AA24" s="31" t="n"/>
-      <c r="AB24" s="31" t="n"/>
-      <c r="AC24" s="31" t="n"/>
-      <c r="AD24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="30" t="n"/>
-      <c r="B25" s="31" t="n"/>
-      <c r="C25" s="31" t="n"/>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="31" t="n"/>
-      <c r="F25" s="31" t="n"/>
-      <c r="G25" s="31" t="n"/>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="31" t="n"/>
-      <c r="J25" s="31" t="n"/>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n"/>
-      <c r="N25" s="31" t="n"/>
-      <c r="O25" s="31" t="n"/>
-      <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="31" t="n"/>
-      <c r="R25" s="31" t="n"/>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="31" t="n"/>
-      <c r="U25" s="31" t="n"/>
-      <c r="V25" s="31" t="n"/>
-      <c r="W25" s="31" t="n"/>
-      <c r="X25" s="31" t="n"/>
-      <c r="Y25" s="31" t="n"/>
-      <c r="Z25" s="31" t="n"/>
-      <c r="AA25" s="31" t="n"/>
-      <c r="AB25" s="31" t="n"/>
-      <c r="AC25" s="31" t="n"/>
-      <c r="AD25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="30" t="n"/>
-      <c r="B26" s="31" t="n"/>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="31" t="n"/>
-      <c r="J26" s="31" t="n"/>
-      <c r="K26" s="31" t="n"/>
-      <c r="L26" s="31" t="n"/>
-      <c r="M26" s="31" t="n"/>
-      <c r="N26" s="31" t="n"/>
-      <c r="O26" s="31" t="n"/>
-      <c r="P26" s="31" t="n"/>
-      <c r="Q26" s="31" t="n"/>
-      <c r="R26" s="31" t="n"/>
-      <c r="S26" s="31" t="n"/>
-      <c r="T26" s="31" t="n"/>
-      <c r="U26" s="31" t="n"/>
-      <c r="V26" s="31" t="n"/>
-      <c r="W26" s="31" t="n"/>
-      <c r="X26" s="31" t="n"/>
-      <c r="Y26" s="31" t="n"/>
-      <c r="Z26" s="31" t="n"/>
-      <c r="AA26" s="31" t="n"/>
-      <c r="AB26" s="31" t="n"/>
-      <c r="AC26" s="31" t="n"/>
-      <c r="AD26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="30" t="n"/>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="31" t="n"/>
-      <c r="G27" s="31" t="n"/>
-      <c r="H27" s="31" t="n"/>
-      <c r="I27" s="31" t="n"/>
-      <c r="J27" s="31" t="n"/>
-      <c r="K27" s="31" t="n"/>
-      <c r="L27" s="31" t="n"/>
-      <c r="M27" s="31" t="n"/>
-      <c r="N27" s="31" t="n"/>
-      <c r="O27" s="31" t="n"/>
-      <c r="P27" s="31" t="n"/>
-      <c r="Q27" s="31" t="n"/>
-      <c r="R27" s="31" t="n"/>
-      <c r="S27" s="31" t="n"/>
-      <c r="T27" s="31" t="n"/>
-      <c r="U27" s="31" t="n"/>
-      <c r="V27" s="31" t="n"/>
-      <c r="W27" s="31" t="n"/>
-      <c r="X27" s="31" t="n"/>
-      <c r="Y27" s="31" t="n"/>
-      <c r="Z27" s="31" t="n"/>
-      <c r="AA27" s="31" t="n"/>
-      <c r="AB27" s="31" t="n"/>
-      <c r="AC27" s="31" t="n"/>
-      <c r="AD27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="30" t="n"/>
-      <c r="B28" s="31" t="n"/>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n"/>
-      <c r="G28" s="31" t="n"/>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-      <c r="J28" s="31" t="n"/>
-      <c r="K28" s="31" t="n"/>
-      <c r="L28" s="31" t="n"/>
-      <c r="M28" s="31" t="n"/>
-      <c r="N28" s="31" t="n"/>
-      <c r="O28" s="31" t="n"/>
-      <c r="P28" s="31" t="n"/>
-      <c r="Q28" s="31" t="n"/>
-      <c r="R28" s="31" t="n"/>
-      <c r="S28" s="31" t="n"/>
-      <c r="T28" s="31" t="n"/>
-      <c r="U28" s="31" t="n"/>
-      <c r="V28" s="31" t="n"/>
-      <c r="W28" s="31" t="n"/>
-      <c r="X28" s="31" t="n"/>
-      <c r="Y28" s="31" t="n"/>
-      <c r="Z28" s="31" t="n"/>
-      <c r="AA28" s="31" t="n"/>
-      <c r="AB28" s="31" t="n"/>
-      <c r="AC28" s="31" t="n"/>
-      <c r="AD28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="30" t="n"/>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="31" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="31" t="n"/>
-      <c r="J29" s="31" t="n"/>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="31" t="n"/>
-      <c r="M29" s="31" t="n"/>
-      <c r="N29" s="31" t="n"/>
-      <c r="O29" s="31" t="n"/>
-      <c r="P29" s="31" t="n"/>
-      <c r="Q29" s="31" t="n"/>
-      <c r="R29" s="31" t="n"/>
-      <c r="S29" s="31" t="n"/>
-      <c r="T29" s="31" t="n"/>
-      <c r="U29" s="31" t="n"/>
-      <c r="V29" s="31" t="n"/>
-      <c r="W29" s="31" t="n"/>
-      <c r="X29" s="31" t="n"/>
-      <c r="Y29" s="31" t="n"/>
-      <c r="Z29" s="31" t="n"/>
-      <c r="AA29" s="31" t="n"/>
-      <c r="AB29" s="31" t="n"/>
-      <c r="AC29" s="31" t="n"/>
-      <c r="AD29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="30" t="n"/>
-      <c r="B30" s="31" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="31" t="n"/>
-      <c r="N30" s="31" t="n"/>
-      <c r="O30" s="31" t="n"/>
-      <c r="P30" s="31" t="n"/>
-      <c r="Q30" s="31" t="n"/>
-      <c r="R30" s="31" t="n"/>
-      <c r="S30" s="31" t="n"/>
-      <c r="T30" s="31" t="n"/>
-      <c r="U30" s="31" t="n"/>
-      <c r="V30" s="31" t="n"/>
-      <c r="W30" s="31" t="n"/>
-      <c r="X30" s="31" t="n"/>
-      <c r="Y30" s="31" t="n"/>
-      <c r="Z30" s="31" t="n"/>
-      <c r="AA30" s="31" t="n"/>
-      <c r="AB30" s="31" t="n"/>
-      <c r="AC30" s="31" t="n"/>
-      <c r="AD30" s="31" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="30" t="n"/>
-      <c r="B31" s="31" t="n"/>
-      <c r="C31" s="31" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="31" t="n"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="31" t="n"/>
-      <c r="J31" s="31" t="n"/>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="31" t="n"/>
-      <c r="M31" s="31" t="n"/>
-      <c r="N31" s="31" t="n"/>
-      <c r="O31" s="31" t="n"/>
-      <c r="P31" s="31" t="n"/>
-      <c r="Q31" s="31" t="n"/>
-      <c r="R31" s="31" t="n"/>
-      <c r="S31" s="31" t="n"/>
-      <c r="T31" s="31" t="n"/>
-      <c r="U31" s="31" t="n"/>
-      <c r="V31" s="31" t="n"/>
-      <c r="W31" s="31" t="n"/>
-      <c r="X31" s="31" t="n"/>
-      <c r="Y31" s="31" t="n"/>
-      <c r="Z31" s="31" t="n"/>
-      <c r="AA31" s="31" t="n"/>
-      <c r="AB31" s="31" t="n"/>
-      <c r="AC31" s="31" t="n"/>
-      <c r="AD31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="31" t="n"/>
-      <c r="M32" s="31" t="n"/>
-      <c r="N32" s="31" t="n"/>
-      <c r="O32" s="31" t="n"/>
-      <c r="P32" s="31" t="n"/>
-      <c r="Q32" s="31" t="n"/>
-      <c r="R32" s="31" t="n"/>
-      <c r="S32" s="31" t="n"/>
-      <c r="T32" s="31" t="n"/>
-      <c r="U32" s="31" t="n"/>
-      <c r="V32" s="31" t="n"/>
-      <c r="W32" s="31" t="n"/>
-      <c r="X32" s="31" t="n"/>
-      <c r="Y32" s="31" t="n"/>
-      <c r="Z32" s="31" t="n"/>
-      <c r="AA32" s="31" t="n"/>
-      <c r="AB32" s="31" t="n"/>
-      <c r="AC32" s="31" t="n"/>
-      <c r="AD32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="30" t="n"/>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="31" t="n"/>
-      <c r="G33" s="31" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="31" t="n"/>
-      <c r="J33" s="31" t="n"/>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="31" t="n"/>
-      <c r="M33" s="31" t="n"/>
-      <c r="N33" s="31" t="n"/>
-      <c r="O33" s="31" t="n"/>
-      <c r="P33" s="31" t="n"/>
-      <c r="Q33" s="31" t="n"/>
-      <c r="R33" s="31" t="n"/>
-      <c r="S33" s="31" t="n"/>
-      <c r="T33" s="31" t="n"/>
-      <c r="U33" s="31" t="n"/>
-      <c r="V33" s="31" t="n"/>
-      <c r="W33" s="31" t="n"/>
-      <c r="X33" s="31" t="n"/>
-      <c r="Y33" s="31" t="n"/>
-      <c r="Z33" s="31" t="n"/>
-      <c r="AA33" s="31" t="n"/>
-      <c r="AB33" s="31" t="n"/>
-      <c r="AC33" s="31" t="n"/>
-      <c r="AD33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="30" t="n"/>
-      <c r="B34" s="31" t="n"/>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n"/>
-      <c r="N34" s="31" t="n"/>
-      <c r="O34" s="31" t="n"/>
-      <c r="P34" s="31" t="n"/>
-      <c r="Q34" s="31" t="n"/>
-      <c r="R34" s="31" t="n"/>
-      <c r="S34" s="31" t="n"/>
-      <c r="T34" s="31" t="n"/>
-      <c r="U34" s="31" t="n"/>
-      <c r="V34" s="31" t="n"/>
-      <c r="W34" s="31" t="n"/>
-      <c r="X34" s="31" t="n"/>
-      <c r="Y34" s="31" t="n"/>
-      <c r="Z34" s="31" t="n"/>
-      <c r="AA34" s="31" t="n"/>
-      <c r="AB34" s="31" t="n"/>
-      <c r="AC34" s="31" t="n"/>
-      <c r="AD34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="30" t="n"/>
-      <c r="B35" s="31" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="31" t="n"/>
-      <c r="J35" s="31" t="n"/>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n"/>
-      <c r="N35" s="31" t="n"/>
-      <c r="O35" s="31" t="n"/>
-      <c r="P35" s="31" t="n"/>
-      <c r="Q35" s="31" t="n"/>
-      <c r="R35" s="31" t="n"/>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n"/>
-      <c r="U35" s="31" t="n"/>
-      <c r="V35" s="31" t="n"/>
-      <c r="W35" s="31" t="n"/>
-      <c r="X35" s="31" t="n"/>
-      <c r="Y35" s="31" t="n"/>
-      <c r="Z35" s="31" t="n"/>
-      <c r="AA35" s="31" t="n"/>
-      <c r="AB35" s="31" t="n"/>
-      <c r="AC35" s="31" t="n"/>
-      <c r="AD35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="30" t="n"/>
-      <c r="B36" s="31" t="n"/>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n"/>
-      <c r="N36" s="31" t="n"/>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="31" t="n"/>
-      <c r="R36" s="31" t="n"/>
-      <c r="S36" s="31" t="n"/>
-      <c r="T36" s="31" t="n"/>
-      <c r="U36" s="31" t="n"/>
-      <c r="V36" s="31" t="n"/>
-      <c r="W36" s="31" t="n"/>
-      <c r="X36" s="31" t="n"/>
-      <c r="Y36" s="31" t="n"/>
-      <c r="Z36" s="31" t="n"/>
-      <c r="AA36" s="31" t="n"/>
-      <c r="AB36" s="31" t="n"/>
-      <c r="AC36" s="31" t="n"/>
-      <c r="AD36" s="31" t="n"/>
+      <c r="AD22" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Inscripciones y reservas</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="22" t="n"/>
+      <c r="L23" s="22" t="n"/>
+      <c r="M23" s="22" t="n"/>
+      <c r="N23" s="22" t="n"/>
+      <c r="O23" s="22" t="n"/>
+      <c r="P23" s="22" t="n"/>
+      <c r="Q23" s="22" t="n"/>
+      <c r="R23" s="22" t="n"/>
+      <c r="S23" s="22" t="n"/>
+      <c r="T23" s="21" t="n"/>
+      <c r="U23" s="21" t="n"/>
+      <c r="V23" s="21" t="n"/>
+      <c r="W23" s="21" t="n"/>
+      <c r="X23" s="22" t="n"/>
+      <c r="Y23" s="22" t="n"/>
+      <c r="Z23" s="22" t="n"/>
+      <c r="AA23" s="22" t="n"/>
+      <c r="AB23" s="22" t="n"/>
+      <c r="AC23" s="22" t="n"/>
+      <c r="AD23" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22" t="n"/>
+      <c r="P24" s="22" t="n"/>
+      <c r="Q24" s="22" t="n"/>
+      <c r="R24" s="22" t="n"/>
+      <c r="S24" s="22" t="n"/>
+      <c r="T24" s="22" t="n"/>
+      <c r="U24" s="22" t="n"/>
+      <c r="V24" s="22" t="n"/>
+      <c r="W24" s="22" t="n"/>
+      <c r="X24" s="21" t="n"/>
+      <c r="Y24" s="22" t="n"/>
+      <c r="Z24" s="22" t="n"/>
+      <c r="AA24" s="22" t="n"/>
+      <c r="AB24" s="22" t="n"/>
+      <c r="AC24" s="22" t="n"/>
+      <c r="AD24" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="22" t="n"/>
+      <c r="K25" s="22" t="n"/>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="22" t="n"/>
+      <c r="N25" s="22" t="n"/>
+      <c r="O25" s="22" t="n"/>
+      <c r="P25" s="22" t="n"/>
+      <c r="Q25" s="22" t="n"/>
+      <c r="R25" s="22" t="n"/>
+      <c r="S25" s="22" t="n"/>
+      <c r="T25" s="22" t="n"/>
+      <c r="U25" s="22" t="n"/>
+      <c r="V25" s="22" t="n"/>
+      <c r="W25" s="22" t="n"/>
+      <c r="X25" s="21" t="n"/>
+      <c r="Y25" s="22" t="n"/>
+      <c r="Z25" s="22" t="n"/>
+      <c r="AA25" s="22" t="n"/>
+      <c r="AB25" s="22" t="n"/>
+      <c r="AC25" s="22" t="n"/>
+      <c r="AD25" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>Suscripciones</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="22" t="n"/>
+      <c r="K26" s="22" t="n"/>
+      <c r="L26" s="22" t="n"/>
+      <c r="M26" s="22" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="22" t="n"/>
+      <c r="P26" s="22" t="n"/>
+      <c r="Q26" s="22" t="n"/>
+      <c r="R26" s="22" t="n"/>
+      <c r="S26" s="22" t="n"/>
+      <c r="T26" s="22" t="n"/>
+      <c r="U26" s="22" t="n"/>
+      <c r="V26" s="22" t="n"/>
+      <c r="W26" s="22" t="n"/>
+      <c r="X26" s="22" t="n"/>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="22" t="n"/>
+      <c r="AA26" s="22" t="n"/>
+      <c r="AB26" s="22" t="n"/>
+      <c r="AC26" s="22" t="n"/>
+      <c r="AD26" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="22" t="n"/>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="22" t="n"/>
+      <c r="N27" s="22" t="n"/>
+      <c r="O27" s="22" t="n"/>
+      <c r="P27" s="22" t="n"/>
+      <c r="Q27" s="22" t="n"/>
+      <c r="R27" s="22" t="n"/>
+      <c r="S27" s="22" t="n"/>
+      <c r="T27" s="22" t="n"/>
+      <c r="U27" s="22" t="n"/>
+      <c r="V27" s="22" t="n"/>
+      <c r="W27" s="22" t="n"/>
+      <c r="X27" s="22" t="n"/>
+      <c r="Y27" s="22" t="n"/>
+      <c r="Z27" s="25" t="n"/>
+      <c r="AA27" s="22" t="n"/>
+      <c r="AB27" s="22" t="n"/>
+      <c r="AC27" s="22" t="n"/>
+      <c r="AD27" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="22" t="n"/>
+      <c r="N28" s="22" t="n"/>
+      <c r="O28" s="22" t="n"/>
+      <c r="P28" s="22" t="n"/>
+      <c r="Q28" s="22" t="n"/>
+      <c r="R28" s="22" t="n"/>
+      <c r="S28" s="22" t="n"/>
+      <c r="T28" s="22" t="n"/>
+      <c r="U28" s="22" t="n"/>
+      <c r="V28" s="22" t="n"/>
+      <c r="W28" s="22" t="n"/>
+      <c r="X28" s="22" t="n"/>
+      <c r="Y28" s="22" t="n"/>
+      <c r="Z28" s="25" t="n"/>
+      <c r="AA28" s="22" t="n"/>
+      <c r="AB28" s="22" t="n"/>
+      <c r="AC28" s="22" t="n"/>
+      <c r="AD28" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Pagos con Stripe</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="22" t="n"/>
+      <c r="K29" s="22" t="n"/>
+      <c r="L29" s="22" t="n"/>
+      <c r="M29" s="22" t="n"/>
+      <c r="N29" s="22" t="n"/>
+      <c r="O29" s="22" t="n"/>
+      <c r="P29" s="22" t="n"/>
+      <c r="Q29" s="22" t="n"/>
+      <c r="R29" s="22" t="n"/>
+      <c r="S29" s="22" t="n"/>
+      <c r="T29" s="22" t="n"/>
+      <c r="U29" s="22" t="n"/>
+      <c r="V29" s="22" t="n"/>
+      <c r="W29" s="22" t="n"/>
+      <c r="X29" s="22" t="n"/>
+      <c r="Y29" s="22" t="n"/>
+      <c r="Z29" s="22" t="n"/>
+      <c r="AA29" s="26" t="n"/>
+      <c r="AB29" s="26" t="n"/>
+      <c r="AC29" s="26" t="n"/>
+      <c r="AD29" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="22" t="n"/>
+      <c r="K30" s="22" t="n"/>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="22" t="n"/>
+      <c r="N30" s="22" t="n"/>
+      <c r="O30" s="22" t="n"/>
+      <c r="P30" s="22" t="n"/>
+      <c r="Q30" s="22" t="n"/>
+      <c r="R30" s="22" t="n"/>
+      <c r="S30" s="22" t="n"/>
+      <c r="T30" s="22" t="n"/>
+      <c r="U30" s="22" t="n"/>
+      <c r="V30" s="22" t="n"/>
+      <c r="W30" s="22" t="n"/>
+      <c r="X30" s="22" t="n"/>
+      <c r="Y30" s="22" t="n"/>
+      <c r="Z30" s="22" t="n"/>
+      <c r="AA30" s="22" t="n"/>
+      <c r="AB30" s="22" t="n"/>
+      <c r="AC30" s="22" t="n"/>
+      <c r="AD30" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="22" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="22" t="n"/>
+      <c r="N31" s="22" t="n"/>
+      <c r="O31" s="22" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="22" t="n"/>
+      <c r="R31" s="22" t="n"/>
+      <c r="S31" s="22" t="n"/>
+      <c r="T31" s="22" t="n"/>
+      <c r="U31" s="22" t="n"/>
+      <c r="V31" s="22" t="n"/>
+      <c r="W31" s="22" t="n"/>
+      <c r="X31" s="22" t="n"/>
+      <c r="Y31" s="22" t="n"/>
+      <c r="Z31" s="22" t="n"/>
+      <c r="AA31" s="22" t="n"/>
+      <c r="AB31" s="22" t="n"/>
+      <c r="AC31" s="22" t="n"/>
+      <c r="AD31" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Panel de administración</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="22" t="n"/>
+      <c r="K32" s="22" t="n"/>
+      <c r="L32" s="22" t="n"/>
+      <c r="M32" s="22" t="n"/>
+      <c r="N32" s="22" t="n"/>
+      <c r="O32" s="22" t="n"/>
+      <c r="P32" s="22" t="n"/>
+      <c r="Q32" s="22" t="n"/>
+      <c r="R32" s="22" t="n"/>
+      <c r="S32" s="22" t="n"/>
+      <c r="T32" s="22" t="n"/>
+      <c r="U32" s="22" t="n"/>
+      <c r="V32" s="22" t="n"/>
+      <c r="W32" s="22" t="n"/>
+      <c r="X32" s="22" t="n"/>
+      <c r="Y32" s="22" t="n"/>
+      <c r="Z32" s="22" t="n"/>
+      <c r="AA32" s="22" t="n"/>
+      <c r="AB32" s="22" t="n"/>
+      <c r="AC32" s="22" t="n"/>
+      <c r="AD32" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="22" t="n"/>
+      <c r="K33" s="22" t="n"/>
+      <c r="L33" s="22" t="n"/>
+      <c r="M33" s="22" t="n"/>
+      <c r="N33" s="22" t="n"/>
+      <c r="O33" s="22" t="n"/>
+      <c r="P33" s="22" t="n"/>
+      <c r="Q33" s="22" t="n"/>
+      <c r="R33" s="22" t="n"/>
+      <c r="S33" s="22" t="n"/>
+      <c r="T33" s="22" t="n"/>
+      <c r="U33" s="22" t="n"/>
+      <c r="V33" s="22" t="n"/>
+      <c r="W33" s="22" t="n"/>
+      <c r="X33" s="22" t="n"/>
+      <c r="Y33" s="22" t="n"/>
+      <c r="Z33" s="22" t="n"/>
+      <c r="AA33" s="22" t="n"/>
+      <c r="AB33" s="22" t="n"/>
+      <c r="AC33" s="22" t="n"/>
+      <c r="AD33" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="22" t="n"/>
+      <c r="K34" s="22" t="n"/>
+      <c r="L34" s="22" t="n"/>
+      <c r="M34" s="22" t="n"/>
+      <c r="N34" s="22" t="n"/>
+      <c r="O34" s="22" t="n"/>
+      <c r="P34" s="22" t="n"/>
+      <c r="Q34" s="22" t="n"/>
+      <c r="R34" s="22" t="n"/>
+      <c r="S34" s="22" t="n"/>
+      <c r="T34" s="22" t="n"/>
+      <c r="U34" s="22" t="n"/>
+      <c r="V34" s="22" t="n"/>
+      <c r="W34" s="22" t="n"/>
+      <c r="X34" s="22" t="n"/>
+      <c r="Y34" s="22" t="n"/>
+      <c r="Z34" s="22" t="n"/>
+      <c r="AA34" s="22" t="n"/>
+      <c r="AB34" s="22" t="n"/>
+      <c r="AC34" s="22" t="n"/>
+      <c r="AD34" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>Gestión de clientes</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="22" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="22" t="n"/>
+      <c r="K35" s="22" t="n"/>
+      <c r="L35" s="22" t="n"/>
+      <c r="M35" s="22" t="n"/>
+      <c r="N35" s="22" t="n"/>
+      <c r="O35" s="22" t="n"/>
+      <c r="P35" s="22" t="n"/>
+      <c r="Q35" s="22" t="n"/>
+      <c r="R35" s="22" t="n"/>
+      <c r="S35" s="22" t="n"/>
+      <c r="T35" s="22" t="n"/>
+      <c r="U35" s="22" t="n"/>
+      <c r="V35" s="22" t="n"/>
+      <c r="W35" s="22" t="n"/>
+      <c r="X35" s="22" t="n"/>
+      <c r="Y35" s="22" t="n"/>
+      <c r="Z35" s="22" t="n"/>
+      <c r="AA35" s="22" t="n"/>
+      <c r="AB35" s="22" t="n"/>
+      <c r="AC35" s="22" t="n"/>
+      <c r="AD35" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="22" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="22" t="n"/>
+      <c r="K36" s="22" t="n"/>
+      <c r="L36" s="22" t="n"/>
+      <c r="M36" s="22" t="n"/>
+      <c r="N36" s="22" t="n"/>
+      <c r="O36" s="22" t="n"/>
+      <c r="P36" s="22" t="n"/>
+      <c r="Q36" s="22" t="n"/>
+      <c r="R36" s="22" t="n"/>
+      <c r="S36" s="22" t="n"/>
+      <c r="T36" s="22" t="n"/>
+      <c r="U36" s="22" t="n"/>
+      <c r="V36" s="22" t="n"/>
+      <c r="W36" s="22" t="n"/>
+      <c r="X36" s="22" t="n"/>
+      <c r="Y36" s="22" t="n"/>
+      <c r="Z36" s="22" t="n"/>
+      <c r="AA36" s="22" t="n"/>
+      <c r="AB36" s="22" t="n"/>
+      <c r="AC36" s="22" t="n"/>
+      <c r="AD36" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="n"/>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="22" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="22" t="n"/>
+      <c r="K37" s="22" t="n"/>
+      <c r="L37" s="22" t="n"/>
+      <c r="M37" s="22" t="n"/>
+      <c r="N37" s="22" t="n"/>
+      <c r="O37" s="22" t="n"/>
+      <c r="P37" s="22" t="n"/>
+      <c r="Q37" s="22" t="n"/>
+      <c r="R37" s="22" t="n"/>
+      <c r="S37" s="22" t="n"/>
+      <c r="T37" s="22" t="n"/>
+      <c r="U37" s="22" t="n"/>
+      <c r="V37" s="22" t="n"/>
+      <c r="W37" s="22" t="n"/>
+      <c r="X37" s="22" t="n"/>
+      <c r="Y37" s="22" t="n"/>
+      <c r="Z37" s="22" t="n"/>
+      <c r="AA37" s="22" t="n"/>
+      <c r="AB37" s="22" t="n"/>
+      <c r="AC37" s="22" t="n"/>
+      <c r="AD37" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Monitores y solicitudes</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="22" t="n"/>
+      <c r="K38" s="22" t="n"/>
+      <c r="L38" s="22" t="n"/>
+      <c r="M38" s="22" t="n"/>
+      <c r="N38" s="22" t="n"/>
+      <c r="O38" s="22" t="n"/>
+      <c r="P38" s="22" t="n"/>
+      <c r="Q38" s="22" t="n"/>
+      <c r="R38" s="22" t="n"/>
+      <c r="S38" s="22" t="n"/>
+      <c r="T38" s="22" t="n"/>
+      <c r="U38" s="22" t="n"/>
+      <c r="V38" s="22" t="n"/>
+      <c r="W38" s="22" t="n"/>
+      <c r="X38" s="22" t="n"/>
+      <c r="Y38" s="22" t="n"/>
+      <c r="Z38" s="22" t="n"/>
+      <c r="AA38" s="22" t="n"/>
+      <c r="AB38" s="22" t="n"/>
+      <c r="AC38" s="22" t="n"/>
+      <c r="AD38" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="n"/>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="22" t="n"/>
+      <c r="H39" s="22" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="22" t="n"/>
+      <c r="K39" s="22" t="n"/>
+      <c r="L39" s="22" t="n"/>
+      <c r="M39" s="22" t="n"/>
+      <c r="N39" s="22" t="n"/>
+      <c r="O39" s="22" t="n"/>
+      <c r="P39" s="22" t="n"/>
+      <c r="Q39" s="22" t="n"/>
+      <c r="R39" s="22" t="n"/>
+      <c r="S39" s="22" t="n"/>
+      <c r="T39" s="22" t="n"/>
+      <c r="U39" s="22" t="n"/>
+      <c r="V39" s="22" t="n"/>
+      <c r="W39" s="22" t="n"/>
+      <c r="X39" s="22" t="n"/>
+      <c r="Y39" s="22" t="n"/>
+      <c r="Z39" s="22" t="n"/>
+      <c r="AA39" s="22" t="n"/>
+      <c r="AB39" s="22" t="n"/>
+      <c r="AC39" s="22" t="n"/>
+      <c r="AD39" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
+      <c r="G40" s="22" t="n"/>
+      <c r="H40" s="22" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="22" t="n"/>
+      <c r="K40" s="22" t="n"/>
+      <c r="L40" s="22" t="n"/>
+      <c r="M40" s="22" t="n"/>
+      <c r="N40" s="22" t="n"/>
+      <c r="O40" s="22" t="n"/>
+      <c r="P40" s="22" t="n"/>
+      <c r="Q40" s="22" t="n"/>
+      <c r="R40" s="22" t="n"/>
+      <c r="S40" s="22" t="n"/>
+      <c r="T40" s="22" t="n"/>
+      <c r="U40" s="22" t="n"/>
+      <c r="V40" s="22" t="n"/>
+      <c r="W40" s="22" t="n"/>
+      <c r="X40" s="22" t="n"/>
+      <c r="Y40" s="22" t="n"/>
+      <c r="Z40" s="22" t="n"/>
+      <c r="AA40" s="22" t="n"/>
+      <c r="AB40" s="22" t="n"/>
+      <c r="AC40" s="22" t="n"/>
+      <c r="AD40" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>Salas y materiales</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="n"/>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="22" t="n"/>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="22" t="n"/>
+      <c r="H41" s="22" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="22" t="n"/>
+      <c r="K41" s="22" t="n"/>
+      <c r="L41" s="22" t="n"/>
+      <c r="M41" s="22" t="n"/>
+      <c r="N41" s="22" t="n"/>
+      <c r="O41" s="22" t="n"/>
+      <c r="P41" s="22" t="n"/>
+      <c r="Q41" s="22" t="n"/>
+      <c r="R41" s="22" t="n"/>
+      <c r="S41" s="22" t="n"/>
+      <c r="T41" s="22" t="n"/>
+      <c r="U41" s="22" t="n"/>
+      <c r="V41" s="22" t="n"/>
+      <c r="W41" s="22" t="n"/>
+      <c r="X41" s="22" t="n"/>
+      <c r="Y41" s="22" t="n"/>
+      <c r="Z41" s="22" t="n"/>
+      <c r="AA41" s="22" t="n"/>
+      <c r="AB41" s="22" t="n"/>
+      <c r="AC41" s="22" t="n"/>
+      <c r="AD41" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
+      <c r="G42" s="22" t="n"/>
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="22" t="n"/>
+      <c r="K42" s="22" t="n"/>
+      <c r="L42" s="22" t="n"/>
+      <c r="M42" s="22" t="n"/>
+      <c r="N42" s="22" t="n"/>
+      <c r="O42" s="22" t="n"/>
+      <c r="P42" s="22" t="n"/>
+      <c r="Q42" s="22" t="n"/>
+      <c r="R42" s="22" t="n"/>
+      <c r="S42" s="22" t="n"/>
+      <c r="T42" s="22" t="n"/>
+      <c r="U42" s="22" t="n"/>
+      <c r="V42" s="22" t="n"/>
+      <c r="W42" s="22" t="n"/>
+      <c r="X42" s="22" t="n"/>
+      <c r="Y42" s="22" t="n"/>
+      <c r="Z42" s="22" t="n"/>
+      <c r="AA42" s="22" t="n"/>
+      <c r="AB42" s="22" t="n"/>
+      <c r="AC42" s="22" t="n"/>
+      <c r="AD42" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="22" t="n"/>
+      <c r="G43" s="22" t="n"/>
+      <c r="H43" s="22" t="n"/>
+      <c r="I43" s="22" t="n"/>
+      <c r="J43" s="22" t="n"/>
+      <c r="K43" s="22" t="n"/>
+      <c r="L43" s="22" t="n"/>
+      <c r="M43" s="22" t="n"/>
+      <c r="N43" s="22" t="n"/>
+      <c r="O43" s="22" t="n"/>
+      <c r="P43" s="22" t="n"/>
+      <c r="Q43" s="22" t="n"/>
+      <c r="R43" s="22" t="n"/>
+      <c r="S43" s="22" t="n"/>
+      <c r="T43" s="22" t="n"/>
+      <c r="U43" s="22" t="n"/>
+      <c r="V43" s="22" t="n"/>
+      <c r="W43" s="22" t="n"/>
+      <c r="X43" s="22" t="n"/>
+      <c r="Y43" s="22" t="n"/>
+      <c r="Z43" s="22" t="n"/>
+      <c r="AA43" s="22" t="n"/>
+      <c r="AB43" s="22" t="n"/>
+      <c r="AC43" s="22" t="n"/>
+      <c r="AD43" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Fisioterapia y citas</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="22" t="n"/>
+      <c r="K44" s="22" t="n"/>
+      <c r="L44" s="22" t="n"/>
+      <c r="M44" s="22" t="n"/>
+      <c r="N44" s="22" t="n"/>
+      <c r="O44" s="22" t="n"/>
+      <c r="P44" s="22" t="n"/>
+      <c r="Q44" s="22" t="n"/>
+      <c r="R44" s="22" t="n"/>
+      <c r="S44" s="22" t="n"/>
+      <c r="T44" s="22" t="n"/>
+      <c r="U44" s="22" t="n"/>
+      <c r="V44" s="22" t="n"/>
+      <c r="W44" s="22" t="n"/>
+      <c r="X44" s="22" t="n"/>
+      <c r="Y44" s="22" t="n"/>
+      <c r="Z44" s="22" t="n"/>
+      <c r="AA44" s="22" t="n"/>
+      <c r="AB44" s="22" t="n"/>
+      <c r="AC44" s="22" t="n"/>
+      <c r="AD44" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="22" t="n"/>
+      <c r="H45" s="22" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="22" t="n"/>
+      <c r="K45" s="22" t="n"/>
+      <c r="L45" s="22" t="n"/>
+      <c r="M45" s="22" t="n"/>
+      <c r="N45" s="22" t="n"/>
+      <c r="O45" s="22" t="n"/>
+      <c r="P45" s="22" t="n"/>
+      <c r="Q45" s="22" t="n"/>
+      <c r="R45" s="22" t="n"/>
+      <c r="S45" s="22" t="n"/>
+      <c r="T45" s="22" t="n"/>
+      <c r="U45" s="22" t="n"/>
+      <c r="V45" s="22" t="n"/>
+      <c r="W45" s="22" t="n"/>
+      <c r="X45" s="22" t="n"/>
+      <c r="Y45" s="22" t="n"/>
+      <c r="Z45" s="22" t="n"/>
+      <c r="AA45" s="22" t="n"/>
+      <c r="AB45" s="22" t="n"/>
+      <c r="AC45" s="22" t="n"/>
+      <c r="AD45" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="n"/>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="22" t="n"/>
+      <c r="F46" s="22" t="n"/>
+      <c r="G46" s="22" t="n"/>
+      <c r="H46" s="22" t="n"/>
+      <c r="I46" s="22" t="n"/>
+      <c r="J46" s="22" t="n"/>
+      <c r="K46" s="22" t="n"/>
+      <c r="L46" s="22" t="n"/>
+      <c r="M46" s="22" t="n"/>
+      <c r="N46" s="22" t="n"/>
+      <c r="O46" s="22" t="n"/>
+      <c r="P46" s="22" t="n"/>
+      <c r="Q46" s="22" t="n"/>
+      <c r="R46" s="22" t="n"/>
+      <c r="S46" s="22" t="n"/>
+      <c r="T46" s="22" t="n"/>
+      <c r="U46" s="22" t="n"/>
+      <c r="V46" s="22" t="n"/>
+      <c r="W46" s="22" t="n"/>
+      <c r="X46" s="22" t="n"/>
+      <c r="Y46" s="22" t="n"/>
+      <c r="Z46" s="22" t="n"/>
+      <c r="AA46" s="22" t="n"/>
+      <c r="AB46" s="22" t="n"/>
+      <c r="AC46" s="22" t="n"/>
+      <c r="AD46" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Comentarios, feedback y seguridad</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="n"/>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="22" t="n"/>
+      <c r="F47" s="22" t="n"/>
+      <c r="G47" s="22" t="n"/>
+      <c r="H47" s="22" t="n"/>
+      <c r="I47" s="22" t="n"/>
+      <c r="J47" s="22" t="n"/>
+      <c r="K47" s="22" t="n"/>
+      <c r="L47" s="22" t="n"/>
+      <c r="M47" s="22" t="n"/>
+      <c r="N47" s="22" t="n"/>
+      <c r="O47" s="22" t="n"/>
+      <c r="P47" s="22" t="n"/>
+      <c r="Q47" s="22" t="n"/>
+      <c r="R47" s="22" t="n"/>
+      <c r="S47" s="22" t="n"/>
+      <c r="T47" s="22" t="n"/>
+      <c r="U47" s="22" t="n"/>
+      <c r="V47" s="22" t="n"/>
+      <c r="W47" s="22" t="n"/>
+      <c r="X47" s="22" t="n"/>
+      <c r="Y47" s="22" t="n"/>
+      <c r="Z47" s="22" t="n"/>
+      <c r="AA47" s="22" t="n"/>
+      <c r="AB47" s="22" t="n"/>
+      <c r="AC47" s="22" t="n"/>
+      <c r="AD47" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="n"/>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="22" t="n"/>
+      <c r="F48" s="22" t="n"/>
+      <c r="G48" s="22" t="n"/>
+      <c r="H48" s="22" t="n"/>
+      <c r="I48" s="22" t="n"/>
+      <c r="J48" s="22" t="n"/>
+      <c r="K48" s="22" t="n"/>
+      <c r="L48" s="22" t="n"/>
+      <c r="M48" s="22" t="n"/>
+      <c r="N48" s="22" t="n"/>
+      <c r="O48" s="22" t="n"/>
+      <c r="P48" s="22" t="n"/>
+      <c r="Q48" s="22" t="n"/>
+      <c r="R48" s="22" t="n"/>
+      <c r="S48" s="22" t="n"/>
+      <c r="T48" s="22" t="n"/>
+      <c r="U48" s="22" t="n"/>
+      <c r="V48" s="22" t="n"/>
+      <c r="W48" s="22" t="n"/>
+      <c r="X48" s="22" t="n"/>
+      <c r="Y48" s="22" t="n"/>
+      <c r="Z48" s="22" t="n"/>
+      <c r="AA48" s="22" t="n"/>
+      <c r="AB48" s="22" t="n"/>
+      <c r="AC48" s="22" t="n"/>
+      <c r="AD48" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="n"/>
+      <c r="C49" s="22" t="n"/>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="22" t="n"/>
+      <c r="F49" s="22" t="n"/>
+      <c r="G49" s="22" t="n"/>
+      <c r="H49" s="22" t="n"/>
+      <c r="I49" s="22" t="n"/>
+      <c r="J49" s="22" t="n"/>
+      <c r="K49" s="22" t="n"/>
+      <c r="L49" s="22" t="n"/>
+      <c r="M49" s="22" t="n"/>
+      <c r="N49" s="22" t="n"/>
+      <c r="O49" s="22" t="n"/>
+      <c r="P49" s="22" t="n"/>
+      <c r="Q49" s="22" t="n"/>
+      <c r="R49" s="22" t="n"/>
+      <c r="S49" s="22" t="n"/>
+      <c r="T49" s="22" t="n"/>
+      <c r="U49" s="22" t="n"/>
+      <c r="V49" s="22" t="n"/>
+      <c r="W49" s="22" t="n"/>
+      <c r="X49" s="22" t="n"/>
+      <c r="Y49" s="22" t="n"/>
+      <c r="Z49" s="22" t="n"/>
+      <c r="AA49" s="22" t="n"/>
+      <c r="AB49" s="22" t="n"/>
+      <c r="AC49" s="22" t="n"/>
+      <c r="AD49" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>Interfaz Tailwind, correo y cierre</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="22" t="n"/>
+      <c r="F50" s="22" t="n"/>
+      <c r="G50" s="22" t="n"/>
+      <c r="H50" s="22" t="n"/>
+      <c r="I50" s="22" t="n"/>
+      <c r="J50" s="22" t="n"/>
+      <c r="K50" s="22" t="n"/>
+      <c r="L50" s="22" t="n"/>
+      <c r="M50" s="22" t="n"/>
+      <c r="N50" s="22" t="n"/>
+      <c r="O50" s="22" t="n"/>
+      <c r="P50" s="22" t="n"/>
+      <c r="Q50" s="22" t="n"/>
+      <c r="R50" s="22" t="n"/>
+      <c r="S50" s="22" t="n"/>
+      <c r="T50" s="22" t="n"/>
+      <c r="U50" s="22" t="n"/>
+      <c r="V50" s="22" t="n"/>
+      <c r="W50" s="22" t="n"/>
+      <c r="X50" s="22" t="n"/>
+      <c r="Y50" s="22" t="n"/>
+      <c r="Z50" s="22" t="n"/>
+      <c r="AA50" s="22" t="n"/>
+      <c r="AB50" s="22" t="n"/>
+      <c r="AC50" s="22" t="n"/>
+      <c r="AD50" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="22" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="22" t="n"/>
+      <c r="H51" s="22" t="n"/>
+      <c r="I51" s="22" t="n"/>
+      <c r="J51" s="22" t="n"/>
+      <c r="K51" s="22" t="n"/>
+      <c r="L51" s="22" t="n"/>
+      <c r="M51" s="22" t="n"/>
+      <c r="N51" s="22" t="n"/>
+      <c r="O51" s="22" t="n"/>
+      <c r="P51" s="22" t="n"/>
+      <c r="Q51" s="22" t="n"/>
+      <c r="R51" s="22" t="n"/>
+      <c r="S51" s="22" t="n"/>
+      <c r="T51" s="22" t="n"/>
+      <c r="U51" s="22" t="n"/>
+      <c r="V51" s="22" t="n"/>
+      <c r="W51" s="22" t="n"/>
+      <c r="X51" s="22" t="n"/>
+      <c r="Y51" s="22" t="n"/>
+      <c r="Z51" s="22" t="n"/>
+      <c r="AA51" s="22" t="n"/>
+      <c r="AB51" s="22" t="n"/>
+      <c r="AC51" s="22" t="n"/>
+      <c r="AD51" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="22" t="n"/>
+      <c r="F52" s="22" t="n"/>
+      <c r="G52" s="22" t="n"/>
+      <c r="H52" s="22" t="n"/>
+      <c r="I52" s="22" t="n"/>
+      <c r="J52" s="22" t="n"/>
+      <c r="K52" s="22" t="n"/>
+      <c r="L52" s="22" t="n"/>
+      <c r="M52" s="22" t="n"/>
+      <c r="N52" s="22" t="n"/>
+      <c r="O52" s="22" t="n"/>
+      <c r="P52" s="22" t="n"/>
+      <c r="Q52" s="22" t="n"/>
+      <c r="R52" s="22" t="n"/>
+      <c r="S52" s="22" t="n"/>
+      <c r="T52" s="22" t="n"/>
+      <c r="U52" s="22" t="n"/>
+      <c r="V52" s="22" t="n"/>
+      <c r="W52" s="22" t="n"/>
+      <c r="X52" s="22" t="n"/>
+      <c r="Y52" s="22" t="n"/>
+      <c r="Z52" s="22" t="n"/>
+      <c r="AA52" s="22" t="n"/>
+      <c r="AB52" s="22" t="n"/>
+      <c r="AC52" s="22" t="n"/>
+      <c r="AD52" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="31" t="n"/>
+      <c r="B53" s="32" t="n"/>
+      <c r="C53" s="32" t="n"/>
+      <c r="D53" s="32" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="32" t="n"/>
+      <c r="H53" s="32" t="n"/>
+      <c r="I53" s="32" t="n"/>
+      <c r="J53" s="32" t="n"/>
+      <c r="K53" s="32" t="n"/>
+      <c r="L53" s="32" t="n"/>
+      <c r="M53" s="32" t="n"/>
+      <c r="N53" s="32" t="n"/>
+      <c r="O53" s="32" t="n"/>
+      <c r="P53" s="32" t="n"/>
+      <c r="Q53" s="32" t="n"/>
+      <c r="R53" s="32" t="n"/>
+      <c r="S53" s="32" t="n"/>
+      <c r="T53" s="32" t="n"/>
+      <c r="U53" s="32" t="n"/>
+      <c r="V53" s="32" t="n"/>
+      <c r="W53" s="32" t="n"/>
+      <c r="X53" s="32" t="n"/>
+      <c r="Y53" s="32" t="n"/>
+      <c r="Z53" s="32" t="n"/>
+      <c r="AA53" s="32" t="n"/>
+      <c r="AB53" s="32" t="n"/>
+      <c r="AC53" s="32" t="n"/>
+      <c r="AD53" s="32" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="31" t="n"/>
+      <c r="B54" s="32" t="n"/>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="32" t="n"/>
+      <c r="G54" s="32" t="n"/>
+      <c r="H54" s="32" t="n"/>
+      <c r="I54" s="32" t="n"/>
+      <c r="J54" s="32" t="n"/>
+      <c r="K54" s="32" t="n"/>
+      <c r="L54" s="32" t="n"/>
+      <c r="M54" s="32" t="n"/>
+      <c r="N54" s="32" t="n"/>
+      <c r="O54" s="32" t="n"/>
+      <c r="P54" s="32" t="n"/>
+      <c r="Q54" s="32" t="n"/>
+      <c r="R54" s="32" t="n"/>
+      <c r="S54" s="32" t="n"/>
+      <c r="T54" s="32" t="n"/>
+      <c r="U54" s="32" t="n"/>
+      <c r="V54" s="32" t="n"/>
+      <c r="W54" s="32" t="n"/>
+      <c r="X54" s="32" t="n"/>
+      <c r="Y54" s="32" t="n"/>
+      <c r="Z54" s="32" t="n"/>
+      <c r="AA54" s="32" t="n"/>
+      <c r="AB54" s="32" t="n"/>
+      <c r="AC54" s="32" t="n"/>
+      <c r="AD54" s="32" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="31" t="n"/>
+      <c r="B55" s="32" t="n"/>
+      <c r="C55" s="32" t="n"/>
+      <c r="D55" s="32" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="32" t="n"/>
+      <c r="H55" s="32" t="n"/>
+      <c r="I55" s="32" t="n"/>
+      <c r="J55" s="32" t="n"/>
+      <c r="K55" s="32" t="n"/>
+      <c r="L55" s="32" t="n"/>
+      <c r="M55" s="32" t="n"/>
+      <c r="N55" s="32" t="n"/>
+      <c r="O55" s="32" t="n"/>
+      <c r="P55" s="32" t="n"/>
+      <c r="Q55" s="32" t="n"/>
+      <c r="R55" s="32" t="n"/>
+      <c r="S55" s="32" t="n"/>
+      <c r="T55" s="32" t="n"/>
+      <c r="U55" s="32" t="n"/>
+      <c r="V55" s="32" t="n"/>
+      <c r="W55" s="32" t="n"/>
+      <c r="X55" s="32" t="n"/>
+      <c r="Y55" s="32" t="n"/>
+      <c r="Z55" s="32" t="n"/>
+      <c r="AA55" s="32" t="n"/>
+      <c r="AB55" s="32" t="n"/>
+      <c r="AC55" s="32" t="n"/>
+      <c r="AD55" s="32" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="31" t="n"/>
+      <c r="B56" s="32" t="n"/>
+      <c r="C56" s="32" t="n"/>
+      <c r="D56" s="32" t="n"/>
+      <c r="E56" s="32" t="n"/>
+      <c r="F56" s="32" t="n"/>
+      <c r="G56" s="32" t="n"/>
+      <c r="H56" s="32" t="n"/>
+      <c r="I56" s="32" t="n"/>
+      <c r="J56" s="32" t="n"/>
+      <c r="K56" s="32" t="n"/>
+      <c r="L56" s="32" t="n"/>
+      <c r="M56" s="32" t="n"/>
+      <c r="N56" s="32" t="n"/>
+      <c r="O56" s="32" t="n"/>
+      <c r="P56" s="32" t="n"/>
+      <c r="Q56" s="32" t="n"/>
+      <c r="R56" s="32" t="n"/>
+      <c r="S56" s="32" t="n"/>
+      <c r="T56" s="32" t="n"/>
+      <c r="U56" s="32" t="n"/>
+      <c r="V56" s="32" t="n"/>
+      <c r="W56" s="32" t="n"/>
+      <c r="X56" s="32" t="n"/>
+      <c r="Y56" s="32" t="n"/>
+      <c r="Z56" s="32" t="n"/>
+      <c r="AA56" s="32" t="n"/>
+      <c r="AB56" s="32" t="n"/>
+      <c r="AC56" s="32" t="n"/>
+      <c r="AD56" s="32" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="31" t="n"/>
+      <c r="B57" s="32" t="n"/>
+      <c r="C57" s="32" t="n"/>
+      <c r="D57" s="32" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="32" t="n"/>
+      <c r="H57" s="32" t="n"/>
+      <c r="I57" s="32" t="n"/>
+      <c r="J57" s="32" t="n"/>
+      <c r="K57" s="32" t="n"/>
+      <c r="L57" s="32" t="n"/>
+      <c r="M57" s="32" t="n"/>
+      <c r="N57" s="32" t="n"/>
+      <c r="O57" s="32" t="n"/>
+      <c r="P57" s="32" t="n"/>
+      <c r="Q57" s="32" t="n"/>
+      <c r="R57" s="32" t="n"/>
+      <c r="S57" s="32" t="n"/>
+      <c r="T57" s="32" t="n"/>
+      <c r="U57" s="32" t="n"/>
+      <c r="V57" s="32" t="n"/>
+      <c r="W57" s="32" t="n"/>
+      <c r="X57" s="32" t="n"/>
+      <c r="Y57" s="32" t="n"/>
+      <c r="Z57" s="32" t="n"/>
+      <c r="AA57" s="32" t="n"/>
+      <c r="AB57" s="32" t="n"/>
+      <c r="AC57" s="32" t="n"/>
+      <c r="AD57" s="32" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="31" t="n"/>
+      <c r="B58" s="32" t="n"/>
+      <c r="C58" s="32" t="n"/>
+      <c r="D58" s="32" t="n"/>
+      <c r="E58" s="32" t="n"/>
+      <c r="F58" s="32" t="n"/>
+      <c r="G58" s="32" t="n"/>
+      <c r="H58" s="32" t="n"/>
+      <c r="I58" s="32" t="n"/>
+      <c r="J58" s="32" t="n"/>
+      <c r="K58" s="32" t="n"/>
+      <c r="L58" s="32" t="n"/>
+      <c r="M58" s="32" t="n"/>
+      <c r="N58" s="32" t="n"/>
+      <c r="O58" s="32" t="n"/>
+      <c r="P58" s="32" t="n"/>
+      <c r="Q58" s="32" t="n"/>
+      <c r="R58" s="32" t="n"/>
+      <c r="S58" s="32" t="n"/>
+      <c r="T58" s="32" t="n"/>
+      <c r="U58" s="32" t="n"/>
+      <c r="V58" s="32" t="n"/>
+      <c r="W58" s="32" t="n"/>
+      <c r="X58" s="32" t="n"/>
+      <c r="Y58" s="32" t="n"/>
+      <c r="Z58" s="32" t="n"/>
+      <c r="AA58" s="32" t="n"/>
+      <c r="AB58" s="32" t="n"/>
+      <c r="AC58" s="32" t="n"/>
+      <c r="AD58" s="32" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -2221,13 +3158,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008CB5B7"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD36"/>
+  <dimension ref="A1:AD58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
     <col width="3.7" customWidth="1" min="3" max="3"/>
     <col width="3.7" customWidth="1" min="4" max="4"/>
@@ -2639,7 +3576,7 @@
       </c>
       <c r="AD7" s="13" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Núcleo del proyecto</t>
@@ -2679,10 +3616,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Acceso, registro y sesión</t>
+    <row r="9" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B9" s="22" t="n"/>
@@ -2719,10 +3656,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Recuperación de cuenta y tickets</t>
+    <row r="10" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B10" s="22" t="n"/>
@@ -2759,10 +3696,10 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Perfil, contraseña y baja</t>
+          <t>Acceso, registro y sesión</t>
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
@@ -2799,10 +3736,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Actividades y horario</t>
+    <row r="12" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
@@ -2833,16 +3770,16 @@
       <c r="AA12" s="22" t="n"/>
       <c r="AB12" s="22" t="n"/>
       <c r="AC12" s="22" t="n"/>
-      <c r="AD12" s="28" t="inlineStr">
-        <is>
-          <t>en curso</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Inscripciones y reservas</t>
+      <c r="AD12" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
@@ -2873,16 +3810,16 @@
       <c r="AA13" s="22" t="n"/>
       <c r="AB13" s="22" t="n"/>
       <c r="AC13" s="22" t="n"/>
-      <c r="AD13" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
+      <c r="AD13" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Suscripciones</t>
+          <t>Recuperación de cuenta y tickets</t>
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
@@ -2913,20 +3850,20 @@
       <c r="AA14" s="22" t="n"/>
       <c r="AB14" s="22" t="n"/>
       <c r="AC14" s="22" t="n"/>
-      <c r="AD14" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Pagos con Stripe</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="25" t="n"/>
+      <c r="AD14" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
       <c r="D15" s="22" t="n"/>
       <c r="E15" s="22" t="n"/>
       <c r="F15" s="22" t="n"/>
@@ -2953,22 +3890,22 @@
       <c r="AA15" s="22" t="n"/>
       <c r="AB15" s="22" t="n"/>
       <c r="AC15" s="22" t="n"/>
-      <c r="AD15" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Panel de administración</t>
+      <c r="AD15" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
       <c r="C16" s="22" t="n"/>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="22" t="n"/>
       <c r="F16" s="22" t="n"/>
       <c r="G16" s="22" t="n"/>
       <c r="H16" s="22" t="n"/>
@@ -2993,26 +3930,26 @@
       <c r="AA16" s="22" t="n"/>
       <c r="AB16" s="22" t="n"/>
       <c r="AC16" s="22" t="n"/>
-      <c r="AD16" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
+      <c r="AD16" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>Gestión de clientes</t>
+          <t>Perfil, contraseña y baja</t>
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
       <c r="C17" s="22" t="n"/>
       <c r="D17" s="22" t="n"/>
       <c r="E17" s="22" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="27" t="n"/>
-      <c r="I17" s="27" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
       <c r="J17" s="22" t="n"/>
       <c r="K17" s="22" t="n"/>
       <c r="L17" s="22" t="n"/>
@@ -3033,16 +3970,16 @@
       <c r="AA17" s="22" t="n"/>
       <c r="AB17" s="22" t="n"/>
       <c r="AC17" s="22" t="n"/>
-      <c r="AD17" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Monitores y solicitudes</t>
+      <c r="AD17" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B18" s="22" t="n"/>
@@ -3053,9 +3990,9 @@
       <c r="G18" s="22" t="n"/>
       <c r="H18" s="22" t="n"/>
       <c r="I18" s="22" t="n"/>
-      <c r="J18" s="21" t="n"/>
-      <c r="K18" s="21" t="n"/>
-      <c r="L18" s="21" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="22" t="n"/>
+      <c r="L18" s="22" t="n"/>
       <c r="M18" s="22" t="n"/>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
@@ -3073,16 +4010,16 @@
       <c r="AA18" s="22" t="n"/>
       <c r="AB18" s="22" t="n"/>
       <c r="AC18" s="22" t="n"/>
-      <c r="AD18" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>Salas y materiales</t>
+      <c r="AD18" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B19" s="22" t="n"/>
@@ -3096,10 +4033,10 @@
       <c r="J19" s="22" t="n"/>
       <c r="K19" s="22" t="n"/>
       <c r="L19" s="22" t="n"/>
-      <c r="M19" s="24" t="n"/>
-      <c r="N19" s="24" t="n"/>
-      <c r="O19" s="24" t="n"/>
-      <c r="P19" s="24" t="n"/>
+      <c r="M19" s="22" t="n"/>
+      <c r="N19" s="22" t="n"/>
+      <c r="O19" s="22" t="n"/>
+      <c r="P19" s="22" t="n"/>
       <c r="Q19" s="22" t="n"/>
       <c r="R19" s="22" t="n"/>
       <c r="S19" s="22" t="n"/>
@@ -3113,16 +4050,16 @@
       <c r="AA19" s="22" t="n"/>
       <c r="AB19" s="22" t="n"/>
       <c r="AC19" s="22" t="n"/>
-      <c r="AD19" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
+      <c r="AD19" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Fisioterapia y citas</t>
+          <t>Actividades y horario</t>
         </is>
       </c>
       <c r="B20" s="22" t="n"/>
@@ -3140,9 +4077,9 @@
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="25" t="n"/>
-      <c r="R20" s="25" t="n"/>
-      <c r="S20" s="25" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
+      <c r="S20" s="22" t="n"/>
       <c r="T20" s="22" t="n"/>
       <c r="U20" s="22" t="n"/>
       <c r="V20" s="22" t="n"/>
@@ -3155,14 +4092,14 @@
       <c r="AC20" s="22" t="n"/>
       <c r="AD20" s="29" t="inlineStr">
         <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>Comentarios, feedback y seguridad</t>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B21" s="22" t="n"/>
@@ -3183,26 +4120,26 @@
       <c r="Q21" s="22" t="n"/>
       <c r="R21" s="22" t="n"/>
       <c r="S21" s="22" t="n"/>
-      <c r="T21" s="26" t="n"/>
-      <c r="U21" s="26" t="n"/>
-      <c r="V21" s="26" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
+      <c r="T21" s="22" t="n"/>
+      <c r="U21" s="22" t="n"/>
+      <c r="V21" s="22" t="n"/>
+      <c r="W21" s="22" t="n"/>
+      <c r="X21" s="22" t="n"/>
       <c r="Y21" s="22" t="n"/>
       <c r="Z21" s="22" t="n"/>
       <c r="AA21" s="22" t="n"/>
       <c r="AB21" s="22" t="n"/>
       <c r="AC21" s="22" t="n"/>
-      <c r="AD21" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Interfaz Tailwind, correo y cierre</t>
+      <c r="AD21" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
@@ -3228,464 +4165,1408 @@
       <c r="V22" s="22" t="n"/>
       <c r="W22" s="22" t="n"/>
       <c r="X22" s="22" t="n"/>
-      <c r="Y22" s="27" t="n"/>
-      <c r="Z22" s="27" t="n"/>
-      <c r="AA22" s="27" t="n"/>
-      <c r="AB22" s="27" t="n"/>
-      <c r="AC22" s="27" t="n"/>
-      <c r="AD22" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="30" t="n"/>
-      <c r="B23" s="31" t="n"/>
-      <c r="C23" s="31" t="n"/>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="31" t="n"/>
-      <c r="F23" s="31" t="n"/>
-      <c r="G23" s="31" t="n"/>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="31" t="n"/>
-      <c r="J23" s="31" t="n"/>
-      <c r="K23" s="31" t="n"/>
-      <c r="L23" s="31" t="n"/>
-      <c r="M23" s="31" t="n"/>
-      <c r="N23" s="31" t="n"/>
-      <c r="O23" s="31" t="n"/>
-      <c r="P23" s="31" t="n"/>
-      <c r="Q23" s="31" t="n"/>
-      <c r="R23" s="31" t="n"/>
-      <c r="S23" s="31" t="n"/>
-      <c r="T23" s="31" t="n"/>
-      <c r="U23" s="31" t="n"/>
-      <c r="V23" s="31" t="n"/>
-      <c r="W23" s="31" t="n"/>
-      <c r="X23" s="31" t="n"/>
-      <c r="Y23" s="31" t="n"/>
-      <c r="Z23" s="31" t="n"/>
-      <c r="AA23" s="31" t="n"/>
-      <c r="AB23" s="31" t="n"/>
-      <c r="AC23" s="31" t="n"/>
-      <c r="AD23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="30" t="n"/>
-      <c r="B24" s="31" t="n"/>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="31" t="n"/>
-      <c r="O24" s="31" t="n"/>
-      <c r="P24" s="31" t="n"/>
-      <c r="Q24" s="31" t="n"/>
-      <c r="R24" s="31" t="n"/>
-      <c r="S24" s="31" t="n"/>
-      <c r="T24" s="31" t="n"/>
-      <c r="U24" s="31" t="n"/>
-      <c r="V24" s="31" t="n"/>
-      <c r="W24" s="31" t="n"/>
-      <c r="X24" s="31" t="n"/>
-      <c r="Y24" s="31" t="n"/>
-      <c r="Z24" s="31" t="n"/>
-      <c r="AA24" s="31" t="n"/>
-      <c r="AB24" s="31" t="n"/>
-      <c r="AC24" s="31" t="n"/>
-      <c r="AD24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="30" t="n"/>
-      <c r="B25" s="31" t="n"/>
-      <c r="C25" s="31" t="n"/>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="31" t="n"/>
-      <c r="F25" s="31" t="n"/>
-      <c r="G25" s="31" t="n"/>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="31" t="n"/>
-      <c r="J25" s="31" t="n"/>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n"/>
-      <c r="N25" s="31" t="n"/>
-      <c r="O25" s="31" t="n"/>
-      <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="31" t="n"/>
-      <c r="R25" s="31" t="n"/>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="31" t="n"/>
-      <c r="U25" s="31" t="n"/>
-      <c r="V25" s="31" t="n"/>
-      <c r="W25" s="31" t="n"/>
-      <c r="X25" s="31" t="n"/>
-      <c r="Y25" s="31" t="n"/>
-      <c r="Z25" s="31" t="n"/>
-      <c r="AA25" s="31" t="n"/>
-      <c r="AB25" s="31" t="n"/>
-      <c r="AC25" s="31" t="n"/>
-      <c r="AD25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="30" t="n"/>
-      <c r="B26" s="31" t="n"/>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="31" t="n"/>
-      <c r="J26" s="31" t="n"/>
-      <c r="K26" s="31" t="n"/>
-      <c r="L26" s="31" t="n"/>
-      <c r="M26" s="31" t="n"/>
-      <c r="N26" s="31" t="n"/>
-      <c r="O26" s="31" t="n"/>
-      <c r="P26" s="31" t="n"/>
-      <c r="Q26" s="31" t="n"/>
-      <c r="R26" s="31" t="n"/>
-      <c r="S26" s="31" t="n"/>
-      <c r="T26" s="31" t="n"/>
-      <c r="U26" s="31" t="n"/>
-      <c r="V26" s="31" t="n"/>
-      <c r="W26" s="31" t="n"/>
-      <c r="X26" s="31" t="n"/>
-      <c r="Y26" s="31" t="n"/>
-      <c r="Z26" s="31" t="n"/>
-      <c r="AA26" s="31" t="n"/>
-      <c r="AB26" s="31" t="n"/>
-      <c r="AC26" s="31" t="n"/>
-      <c r="AD26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="30" t="n"/>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="31" t="n"/>
-      <c r="G27" s="31" t="n"/>
-      <c r="H27" s="31" t="n"/>
-      <c r="I27" s="31" t="n"/>
-      <c r="J27" s="31" t="n"/>
-      <c r="K27" s="31" t="n"/>
-      <c r="L27" s="31" t="n"/>
-      <c r="M27" s="31" t="n"/>
-      <c r="N27" s="31" t="n"/>
-      <c r="O27" s="31" t="n"/>
-      <c r="P27" s="31" t="n"/>
-      <c r="Q27" s="31" t="n"/>
-      <c r="R27" s="31" t="n"/>
-      <c r="S27" s="31" t="n"/>
-      <c r="T27" s="31" t="n"/>
-      <c r="U27" s="31" t="n"/>
-      <c r="V27" s="31" t="n"/>
-      <c r="W27" s="31" t="n"/>
-      <c r="X27" s="31" t="n"/>
-      <c r="Y27" s="31" t="n"/>
-      <c r="Z27" s="31" t="n"/>
-      <c r="AA27" s="31" t="n"/>
-      <c r="AB27" s="31" t="n"/>
-      <c r="AC27" s="31" t="n"/>
-      <c r="AD27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="30" t="n"/>
-      <c r="B28" s="31" t="n"/>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n"/>
-      <c r="G28" s="31" t="n"/>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-      <c r="J28" s="31" t="n"/>
-      <c r="K28" s="31" t="n"/>
-      <c r="L28" s="31" t="n"/>
-      <c r="M28" s="31" t="n"/>
-      <c r="N28" s="31" t="n"/>
-      <c r="O28" s="31" t="n"/>
-      <c r="P28" s="31" t="n"/>
-      <c r="Q28" s="31" t="n"/>
-      <c r="R28" s="31" t="n"/>
-      <c r="S28" s="31" t="n"/>
-      <c r="T28" s="31" t="n"/>
-      <c r="U28" s="31" t="n"/>
-      <c r="V28" s="31" t="n"/>
-      <c r="W28" s="31" t="n"/>
-      <c r="X28" s="31" t="n"/>
-      <c r="Y28" s="31" t="n"/>
-      <c r="Z28" s="31" t="n"/>
-      <c r="AA28" s="31" t="n"/>
-      <c r="AB28" s="31" t="n"/>
-      <c r="AC28" s="31" t="n"/>
-      <c r="AD28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="30" t="n"/>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="31" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="31" t="n"/>
-      <c r="J29" s="31" t="n"/>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="31" t="n"/>
-      <c r="M29" s="31" t="n"/>
-      <c r="N29" s="31" t="n"/>
-      <c r="O29" s="31" t="n"/>
-      <c r="P29" s="31" t="n"/>
-      <c r="Q29" s="31" t="n"/>
-      <c r="R29" s="31" t="n"/>
-      <c r="S29" s="31" t="n"/>
-      <c r="T29" s="31" t="n"/>
-      <c r="U29" s="31" t="n"/>
-      <c r="V29" s="31" t="n"/>
-      <c r="W29" s="31" t="n"/>
-      <c r="X29" s="31" t="n"/>
-      <c r="Y29" s="31" t="n"/>
-      <c r="Z29" s="31" t="n"/>
-      <c r="AA29" s="31" t="n"/>
-      <c r="AB29" s="31" t="n"/>
-      <c r="AC29" s="31" t="n"/>
-      <c r="AD29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="30" t="n"/>
-      <c r="B30" s="31" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="31" t="n"/>
-      <c r="N30" s="31" t="n"/>
-      <c r="O30" s="31" t="n"/>
-      <c r="P30" s="31" t="n"/>
-      <c r="Q30" s="31" t="n"/>
-      <c r="R30" s="31" t="n"/>
-      <c r="S30" s="31" t="n"/>
-      <c r="T30" s="31" t="n"/>
-      <c r="U30" s="31" t="n"/>
-      <c r="V30" s="31" t="n"/>
-      <c r="W30" s="31" t="n"/>
-      <c r="X30" s="31" t="n"/>
-      <c r="Y30" s="31" t="n"/>
-      <c r="Z30" s="31" t="n"/>
-      <c r="AA30" s="31" t="n"/>
-      <c r="AB30" s="31" t="n"/>
-      <c r="AC30" s="31" t="n"/>
-      <c r="AD30" s="31" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="30" t="n"/>
-      <c r="B31" s="31" t="n"/>
-      <c r="C31" s="31" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="31" t="n"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="31" t="n"/>
-      <c r="J31" s="31" t="n"/>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="31" t="n"/>
-      <c r="M31" s="31" t="n"/>
-      <c r="N31" s="31" t="n"/>
-      <c r="O31" s="31" t="n"/>
-      <c r="P31" s="31" t="n"/>
-      <c r="Q31" s="31" t="n"/>
-      <c r="R31" s="31" t="n"/>
-      <c r="S31" s="31" t="n"/>
-      <c r="T31" s="31" t="n"/>
-      <c r="U31" s="31" t="n"/>
-      <c r="V31" s="31" t="n"/>
-      <c r="W31" s="31" t="n"/>
-      <c r="X31" s="31" t="n"/>
-      <c r="Y31" s="31" t="n"/>
-      <c r="Z31" s="31" t="n"/>
-      <c r="AA31" s="31" t="n"/>
-      <c r="AB31" s="31" t="n"/>
-      <c r="AC31" s="31" t="n"/>
-      <c r="AD31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="31" t="n"/>
-      <c r="M32" s="31" t="n"/>
-      <c r="N32" s="31" t="n"/>
-      <c r="O32" s="31" t="n"/>
-      <c r="P32" s="31" t="n"/>
-      <c r="Q32" s="31" t="n"/>
-      <c r="R32" s="31" t="n"/>
-      <c r="S32" s="31" t="n"/>
-      <c r="T32" s="31" t="n"/>
-      <c r="U32" s="31" t="n"/>
-      <c r="V32" s="31" t="n"/>
-      <c r="W32" s="31" t="n"/>
-      <c r="X32" s="31" t="n"/>
-      <c r="Y32" s="31" t="n"/>
-      <c r="Z32" s="31" t="n"/>
-      <c r="AA32" s="31" t="n"/>
-      <c r="AB32" s="31" t="n"/>
-      <c r="AC32" s="31" t="n"/>
-      <c r="AD32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="30" t="n"/>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="31" t="n"/>
-      <c r="G33" s="31" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="31" t="n"/>
-      <c r="J33" s="31" t="n"/>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="31" t="n"/>
-      <c r="M33" s="31" t="n"/>
-      <c r="N33" s="31" t="n"/>
-      <c r="O33" s="31" t="n"/>
-      <c r="P33" s="31" t="n"/>
-      <c r="Q33" s="31" t="n"/>
-      <c r="R33" s="31" t="n"/>
-      <c r="S33" s="31" t="n"/>
-      <c r="T33" s="31" t="n"/>
-      <c r="U33" s="31" t="n"/>
-      <c r="V33" s="31" t="n"/>
-      <c r="W33" s="31" t="n"/>
-      <c r="X33" s="31" t="n"/>
-      <c r="Y33" s="31" t="n"/>
-      <c r="Z33" s="31" t="n"/>
-      <c r="AA33" s="31" t="n"/>
-      <c r="AB33" s="31" t="n"/>
-      <c r="AC33" s="31" t="n"/>
-      <c r="AD33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="30" t="n"/>
-      <c r="B34" s="31" t="n"/>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n"/>
-      <c r="N34" s="31" t="n"/>
-      <c r="O34" s="31" t="n"/>
-      <c r="P34" s="31" t="n"/>
-      <c r="Q34" s="31" t="n"/>
-      <c r="R34" s="31" t="n"/>
-      <c r="S34" s="31" t="n"/>
-      <c r="T34" s="31" t="n"/>
-      <c r="U34" s="31" t="n"/>
-      <c r="V34" s="31" t="n"/>
-      <c r="W34" s="31" t="n"/>
-      <c r="X34" s="31" t="n"/>
-      <c r="Y34" s="31" t="n"/>
-      <c r="Z34" s="31" t="n"/>
-      <c r="AA34" s="31" t="n"/>
-      <c r="AB34" s="31" t="n"/>
-      <c r="AC34" s="31" t="n"/>
-      <c r="AD34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="30" t="n"/>
-      <c r="B35" s="31" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="31" t="n"/>
-      <c r="J35" s="31" t="n"/>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n"/>
-      <c r="N35" s="31" t="n"/>
-      <c r="O35" s="31" t="n"/>
-      <c r="P35" s="31" t="n"/>
-      <c r="Q35" s="31" t="n"/>
-      <c r="R35" s="31" t="n"/>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n"/>
-      <c r="U35" s="31" t="n"/>
-      <c r="V35" s="31" t="n"/>
-      <c r="W35" s="31" t="n"/>
-      <c r="X35" s="31" t="n"/>
-      <c r="Y35" s="31" t="n"/>
-      <c r="Z35" s="31" t="n"/>
-      <c r="AA35" s="31" t="n"/>
-      <c r="AB35" s="31" t="n"/>
-      <c r="AC35" s="31" t="n"/>
-      <c r="AD35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="30" t="n"/>
-      <c r="B36" s="31" t="n"/>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n"/>
-      <c r="N36" s="31" t="n"/>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="31" t="n"/>
-      <c r="R36" s="31" t="n"/>
-      <c r="S36" s="31" t="n"/>
-      <c r="T36" s="31" t="n"/>
-      <c r="U36" s="31" t="n"/>
-      <c r="V36" s="31" t="n"/>
-      <c r="W36" s="31" t="n"/>
-      <c r="X36" s="31" t="n"/>
-      <c r="Y36" s="31" t="n"/>
-      <c r="Z36" s="31" t="n"/>
-      <c r="AA36" s="31" t="n"/>
-      <c r="AB36" s="31" t="n"/>
-      <c r="AC36" s="31" t="n"/>
-      <c r="AD36" s="31" t="n"/>
+      <c r="Y22" s="22" t="n"/>
+      <c r="Z22" s="22" t="n"/>
+      <c r="AA22" s="22" t="n"/>
+      <c r="AB22" s="22" t="n"/>
+      <c r="AC22" s="22" t="n"/>
+      <c r="AD22" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Inscripciones y reservas</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="22" t="n"/>
+      <c r="L23" s="22" t="n"/>
+      <c r="M23" s="22" t="n"/>
+      <c r="N23" s="22" t="n"/>
+      <c r="O23" s="22" t="n"/>
+      <c r="P23" s="22" t="n"/>
+      <c r="Q23" s="22" t="n"/>
+      <c r="R23" s="22" t="n"/>
+      <c r="S23" s="22" t="n"/>
+      <c r="T23" s="22" t="n"/>
+      <c r="U23" s="22" t="n"/>
+      <c r="V23" s="22" t="n"/>
+      <c r="W23" s="22" t="n"/>
+      <c r="X23" s="22" t="n"/>
+      <c r="Y23" s="22" t="n"/>
+      <c r="Z23" s="22" t="n"/>
+      <c r="AA23" s="22" t="n"/>
+      <c r="AB23" s="22" t="n"/>
+      <c r="AC23" s="22" t="n"/>
+      <c r="AD23" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22" t="n"/>
+      <c r="P24" s="22" t="n"/>
+      <c r="Q24" s="22" t="n"/>
+      <c r="R24" s="22" t="n"/>
+      <c r="S24" s="22" t="n"/>
+      <c r="T24" s="22" t="n"/>
+      <c r="U24" s="22" t="n"/>
+      <c r="V24" s="22" t="n"/>
+      <c r="W24" s="22" t="n"/>
+      <c r="X24" s="22" t="n"/>
+      <c r="Y24" s="22" t="n"/>
+      <c r="Z24" s="22" t="n"/>
+      <c r="AA24" s="22" t="n"/>
+      <c r="AB24" s="22" t="n"/>
+      <c r="AC24" s="22" t="n"/>
+      <c r="AD24" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="22" t="n"/>
+      <c r="K25" s="22" t="n"/>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="22" t="n"/>
+      <c r="N25" s="22" t="n"/>
+      <c r="O25" s="22" t="n"/>
+      <c r="P25" s="22" t="n"/>
+      <c r="Q25" s="22" t="n"/>
+      <c r="R25" s="22" t="n"/>
+      <c r="S25" s="22" t="n"/>
+      <c r="T25" s="22" t="n"/>
+      <c r="U25" s="22" t="n"/>
+      <c r="V25" s="22" t="n"/>
+      <c r="W25" s="22" t="n"/>
+      <c r="X25" s="22" t="n"/>
+      <c r="Y25" s="22" t="n"/>
+      <c r="Z25" s="22" t="n"/>
+      <c r="AA25" s="22" t="n"/>
+      <c r="AB25" s="22" t="n"/>
+      <c r="AC25" s="22" t="n"/>
+      <c r="AD25" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>Suscripciones</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="22" t="n"/>
+      <c r="K26" s="22" t="n"/>
+      <c r="L26" s="22" t="n"/>
+      <c r="M26" s="22" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="22" t="n"/>
+      <c r="P26" s="22" t="n"/>
+      <c r="Q26" s="22" t="n"/>
+      <c r="R26" s="22" t="n"/>
+      <c r="S26" s="22" t="n"/>
+      <c r="T26" s="22" t="n"/>
+      <c r="U26" s="22" t="n"/>
+      <c r="V26" s="22" t="n"/>
+      <c r="W26" s="22" t="n"/>
+      <c r="X26" s="22" t="n"/>
+      <c r="Y26" s="22" t="n"/>
+      <c r="Z26" s="22" t="n"/>
+      <c r="AA26" s="22" t="n"/>
+      <c r="AB26" s="22" t="n"/>
+      <c r="AC26" s="22" t="n"/>
+      <c r="AD26" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="22" t="n"/>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="22" t="n"/>
+      <c r="N27" s="22" t="n"/>
+      <c r="O27" s="22" t="n"/>
+      <c r="P27" s="22" t="n"/>
+      <c r="Q27" s="22" t="n"/>
+      <c r="R27" s="22" t="n"/>
+      <c r="S27" s="22" t="n"/>
+      <c r="T27" s="22" t="n"/>
+      <c r="U27" s="22" t="n"/>
+      <c r="V27" s="22" t="n"/>
+      <c r="W27" s="22" t="n"/>
+      <c r="X27" s="22" t="n"/>
+      <c r="Y27" s="22" t="n"/>
+      <c r="Z27" s="22" t="n"/>
+      <c r="AA27" s="22" t="n"/>
+      <c r="AB27" s="22" t="n"/>
+      <c r="AC27" s="22" t="n"/>
+      <c r="AD27" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="22" t="n"/>
+      <c r="N28" s="22" t="n"/>
+      <c r="O28" s="22" t="n"/>
+      <c r="P28" s="22" t="n"/>
+      <c r="Q28" s="22" t="n"/>
+      <c r="R28" s="22" t="n"/>
+      <c r="S28" s="22" t="n"/>
+      <c r="T28" s="22" t="n"/>
+      <c r="U28" s="22" t="n"/>
+      <c r="V28" s="22" t="n"/>
+      <c r="W28" s="22" t="n"/>
+      <c r="X28" s="22" t="n"/>
+      <c r="Y28" s="22" t="n"/>
+      <c r="Z28" s="22" t="n"/>
+      <c r="AA28" s="22" t="n"/>
+      <c r="AB28" s="22" t="n"/>
+      <c r="AC28" s="22" t="n"/>
+      <c r="AD28" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Pagos con Stripe</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="22" t="n"/>
+      <c r="K29" s="22" t="n"/>
+      <c r="L29" s="22" t="n"/>
+      <c r="M29" s="22" t="n"/>
+      <c r="N29" s="22" t="n"/>
+      <c r="O29" s="22" t="n"/>
+      <c r="P29" s="22" t="n"/>
+      <c r="Q29" s="22" t="n"/>
+      <c r="R29" s="22" t="n"/>
+      <c r="S29" s="22" t="n"/>
+      <c r="T29" s="22" t="n"/>
+      <c r="U29" s="22" t="n"/>
+      <c r="V29" s="22" t="n"/>
+      <c r="W29" s="22" t="n"/>
+      <c r="X29" s="22" t="n"/>
+      <c r="Y29" s="22" t="n"/>
+      <c r="Z29" s="22" t="n"/>
+      <c r="AA29" s="22" t="n"/>
+      <c r="AB29" s="22" t="n"/>
+      <c r="AC29" s="22" t="n"/>
+      <c r="AD29" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="22" t="n"/>
+      <c r="K30" s="22" t="n"/>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="22" t="n"/>
+      <c r="N30" s="22" t="n"/>
+      <c r="O30" s="22" t="n"/>
+      <c r="P30" s="22" t="n"/>
+      <c r="Q30" s="22" t="n"/>
+      <c r="R30" s="22" t="n"/>
+      <c r="S30" s="22" t="n"/>
+      <c r="T30" s="22" t="n"/>
+      <c r="U30" s="22" t="n"/>
+      <c r="V30" s="22" t="n"/>
+      <c r="W30" s="22" t="n"/>
+      <c r="X30" s="22" t="n"/>
+      <c r="Y30" s="22" t="n"/>
+      <c r="Z30" s="22" t="n"/>
+      <c r="AA30" s="22" t="n"/>
+      <c r="AB30" s="22" t="n"/>
+      <c r="AC30" s="22" t="n"/>
+      <c r="AD30" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="22" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="22" t="n"/>
+      <c r="N31" s="22" t="n"/>
+      <c r="O31" s="22" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="22" t="n"/>
+      <c r="R31" s="22" t="n"/>
+      <c r="S31" s="22" t="n"/>
+      <c r="T31" s="22" t="n"/>
+      <c r="U31" s="22" t="n"/>
+      <c r="V31" s="22" t="n"/>
+      <c r="W31" s="22" t="n"/>
+      <c r="X31" s="22" t="n"/>
+      <c r="Y31" s="22" t="n"/>
+      <c r="Z31" s="22" t="n"/>
+      <c r="AA31" s="22" t="n"/>
+      <c r="AB31" s="22" t="n"/>
+      <c r="AC31" s="22" t="n"/>
+      <c r="AD31" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Panel de administración</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="22" t="n"/>
+      <c r="K32" s="22" t="n"/>
+      <c r="L32" s="22" t="n"/>
+      <c r="M32" s="22" t="n"/>
+      <c r="N32" s="22" t="n"/>
+      <c r="O32" s="22" t="n"/>
+      <c r="P32" s="22" t="n"/>
+      <c r="Q32" s="22" t="n"/>
+      <c r="R32" s="22" t="n"/>
+      <c r="S32" s="22" t="n"/>
+      <c r="T32" s="22" t="n"/>
+      <c r="U32" s="22" t="n"/>
+      <c r="V32" s="22" t="n"/>
+      <c r="W32" s="22" t="n"/>
+      <c r="X32" s="22" t="n"/>
+      <c r="Y32" s="22" t="n"/>
+      <c r="Z32" s="22" t="n"/>
+      <c r="AA32" s="22" t="n"/>
+      <c r="AB32" s="22" t="n"/>
+      <c r="AC32" s="22" t="n"/>
+      <c r="AD32" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="22" t="n"/>
+      <c r="K33" s="22" t="n"/>
+      <c r="L33" s="22" t="n"/>
+      <c r="M33" s="22" t="n"/>
+      <c r="N33" s="22" t="n"/>
+      <c r="O33" s="22" t="n"/>
+      <c r="P33" s="22" t="n"/>
+      <c r="Q33" s="22" t="n"/>
+      <c r="R33" s="22" t="n"/>
+      <c r="S33" s="22" t="n"/>
+      <c r="T33" s="22" t="n"/>
+      <c r="U33" s="22" t="n"/>
+      <c r="V33" s="22" t="n"/>
+      <c r="W33" s="22" t="n"/>
+      <c r="X33" s="22" t="n"/>
+      <c r="Y33" s="22" t="n"/>
+      <c r="Z33" s="22" t="n"/>
+      <c r="AA33" s="22" t="n"/>
+      <c r="AB33" s="22" t="n"/>
+      <c r="AC33" s="22" t="n"/>
+      <c r="AD33" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="22" t="n"/>
+      <c r="K34" s="22" t="n"/>
+      <c r="L34" s="22" t="n"/>
+      <c r="M34" s="22" t="n"/>
+      <c r="N34" s="22" t="n"/>
+      <c r="O34" s="22" t="n"/>
+      <c r="P34" s="22" t="n"/>
+      <c r="Q34" s="22" t="n"/>
+      <c r="R34" s="22" t="n"/>
+      <c r="S34" s="22" t="n"/>
+      <c r="T34" s="22" t="n"/>
+      <c r="U34" s="22" t="n"/>
+      <c r="V34" s="22" t="n"/>
+      <c r="W34" s="22" t="n"/>
+      <c r="X34" s="22" t="n"/>
+      <c r="Y34" s="22" t="n"/>
+      <c r="Z34" s="22" t="n"/>
+      <c r="AA34" s="22" t="n"/>
+      <c r="AB34" s="22" t="n"/>
+      <c r="AC34" s="22" t="n"/>
+      <c r="AD34" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>Gestión de clientes</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="28" t="n"/>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="22" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="22" t="n"/>
+      <c r="K35" s="22" t="n"/>
+      <c r="L35" s="22" t="n"/>
+      <c r="M35" s="22" t="n"/>
+      <c r="N35" s="22" t="n"/>
+      <c r="O35" s="22" t="n"/>
+      <c r="P35" s="22" t="n"/>
+      <c r="Q35" s="22" t="n"/>
+      <c r="R35" s="22" t="n"/>
+      <c r="S35" s="22" t="n"/>
+      <c r="T35" s="22" t="n"/>
+      <c r="U35" s="22" t="n"/>
+      <c r="V35" s="22" t="n"/>
+      <c r="W35" s="22" t="n"/>
+      <c r="X35" s="22" t="n"/>
+      <c r="Y35" s="22" t="n"/>
+      <c r="Z35" s="22" t="n"/>
+      <c r="AA35" s="22" t="n"/>
+      <c r="AB35" s="22" t="n"/>
+      <c r="AC35" s="22" t="n"/>
+      <c r="AD35" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="22" t="n"/>
+      <c r="I36" s="28" t="n"/>
+      <c r="J36" s="22" t="n"/>
+      <c r="K36" s="22" t="n"/>
+      <c r="L36" s="22" t="n"/>
+      <c r="M36" s="22" t="n"/>
+      <c r="N36" s="22" t="n"/>
+      <c r="O36" s="22" t="n"/>
+      <c r="P36" s="22" t="n"/>
+      <c r="Q36" s="22" t="n"/>
+      <c r="R36" s="22" t="n"/>
+      <c r="S36" s="22" t="n"/>
+      <c r="T36" s="22" t="n"/>
+      <c r="U36" s="22" t="n"/>
+      <c r="V36" s="22" t="n"/>
+      <c r="W36" s="22" t="n"/>
+      <c r="X36" s="22" t="n"/>
+      <c r="Y36" s="22" t="n"/>
+      <c r="Z36" s="22" t="n"/>
+      <c r="AA36" s="22" t="n"/>
+      <c r="AB36" s="22" t="n"/>
+      <c r="AC36" s="22" t="n"/>
+      <c r="AD36" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="n"/>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="22" t="n"/>
+      <c r="I37" s="28" t="n"/>
+      <c r="J37" s="22" t="n"/>
+      <c r="K37" s="22" t="n"/>
+      <c r="L37" s="22" t="n"/>
+      <c r="M37" s="22" t="n"/>
+      <c r="N37" s="22" t="n"/>
+      <c r="O37" s="22" t="n"/>
+      <c r="P37" s="22" t="n"/>
+      <c r="Q37" s="22" t="n"/>
+      <c r="R37" s="22" t="n"/>
+      <c r="S37" s="22" t="n"/>
+      <c r="T37" s="22" t="n"/>
+      <c r="U37" s="22" t="n"/>
+      <c r="V37" s="22" t="n"/>
+      <c r="W37" s="22" t="n"/>
+      <c r="X37" s="22" t="n"/>
+      <c r="Y37" s="22" t="n"/>
+      <c r="Z37" s="22" t="n"/>
+      <c r="AA37" s="22" t="n"/>
+      <c r="AB37" s="22" t="n"/>
+      <c r="AC37" s="22" t="n"/>
+      <c r="AD37" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Monitores y solicitudes</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="21" t="n"/>
+      <c r="K38" s="21" t="n"/>
+      <c r="L38" s="22" t="n"/>
+      <c r="M38" s="22" t="n"/>
+      <c r="N38" s="22" t="n"/>
+      <c r="O38" s="22" t="n"/>
+      <c r="P38" s="22" t="n"/>
+      <c r="Q38" s="22" t="n"/>
+      <c r="R38" s="22" t="n"/>
+      <c r="S38" s="22" t="n"/>
+      <c r="T38" s="22" t="n"/>
+      <c r="U38" s="22" t="n"/>
+      <c r="V38" s="22" t="n"/>
+      <c r="W38" s="22" t="n"/>
+      <c r="X38" s="22" t="n"/>
+      <c r="Y38" s="22" t="n"/>
+      <c r="Z38" s="22" t="n"/>
+      <c r="AA38" s="22" t="n"/>
+      <c r="AB38" s="22" t="n"/>
+      <c r="AC38" s="22" t="n"/>
+      <c r="AD38" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="n"/>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="22" t="n"/>
+      <c r="H39" s="22" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="22" t="n"/>
+      <c r="K39" s="22" t="n"/>
+      <c r="L39" s="21" t="n"/>
+      <c r="M39" s="22" t="n"/>
+      <c r="N39" s="22" t="n"/>
+      <c r="O39" s="22" t="n"/>
+      <c r="P39" s="22" t="n"/>
+      <c r="Q39" s="22" t="n"/>
+      <c r="R39" s="22" t="n"/>
+      <c r="S39" s="22" t="n"/>
+      <c r="T39" s="22" t="n"/>
+      <c r="U39" s="22" t="n"/>
+      <c r="V39" s="22" t="n"/>
+      <c r="W39" s="22" t="n"/>
+      <c r="X39" s="22" t="n"/>
+      <c r="Y39" s="22" t="n"/>
+      <c r="Z39" s="22" t="n"/>
+      <c r="AA39" s="22" t="n"/>
+      <c r="AB39" s="22" t="n"/>
+      <c r="AC39" s="22" t="n"/>
+      <c r="AD39" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
+      <c r="G40" s="22" t="n"/>
+      <c r="H40" s="22" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="22" t="n"/>
+      <c r="K40" s="22" t="n"/>
+      <c r="L40" s="21" t="n"/>
+      <c r="M40" s="22" t="n"/>
+      <c r="N40" s="22" t="n"/>
+      <c r="O40" s="22" t="n"/>
+      <c r="P40" s="22" t="n"/>
+      <c r="Q40" s="22" t="n"/>
+      <c r="R40" s="22" t="n"/>
+      <c r="S40" s="22" t="n"/>
+      <c r="T40" s="22" t="n"/>
+      <c r="U40" s="22" t="n"/>
+      <c r="V40" s="22" t="n"/>
+      <c r="W40" s="22" t="n"/>
+      <c r="X40" s="22" t="n"/>
+      <c r="Y40" s="22" t="n"/>
+      <c r="Z40" s="22" t="n"/>
+      <c r="AA40" s="22" t="n"/>
+      <c r="AB40" s="22" t="n"/>
+      <c r="AC40" s="22" t="n"/>
+      <c r="AD40" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>Salas y materiales</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="n"/>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="22" t="n"/>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="22" t="n"/>
+      <c r="H41" s="22" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="22" t="n"/>
+      <c r="K41" s="22" t="n"/>
+      <c r="L41" s="22" t="n"/>
+      <c r="M41" s="25" t="n"/>
+      <c r="N41" s="22" t="n"/>
+      <c r="O41" s="22" t="n"/>
+      <c r="P41" s="22" t="n"/>
+      <c r="Q41" s="22" t="n"/>
+      <c r="R41" s="22" t="n"/>
+      <c r="S41" s="22" t="n"/>
+      <c r="T41" s="22" t="n"/>
+      <c r="U41" s="22" t="n"/>
+      <c r="V41" s="22" t="n"/>
+      <c r="W41" s="22" t="n"/>
+      <c r="X41" s="22" t="n"/>
+      <c r="Y41" s="22" t="n"/>
+      <c r="Z41" s="22" t="n"/>
+      <c r="AA41" s="22" t="n"/>
+      <c r="AB41" s="22" t="n"/>
+      <c r="AC41" s="22" t="n"/>
+      <c r="AD41" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
+      <c r="G42" s="22" t="n"/>
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="22" t="n"/>
+      <c r="K42" s="22" t="n"/>
+      <c r="L42" s="22" t="n"/>
+      <c r="M42" s="22" t="n"/>
+      <c r="N42" s="22" t="n"/>
+      <c r="O42" s="22" t="n"/>
+      <c r="P42" s="25" t="n"/>
+      <c r="Q42" s="22" t="n"/>
+      <c r="R42" s="22" t="n"/>
+      <c r="S42" s="22" t="n"/>
+      <c r="T42" s="22" t="n"/>
+      <c r="U42" s="22" t="n"/>
+      <c r="V42" s="22" t="n"/>
+      <c r="W42" s="22" t="n"/>
+      <c r="X42" s="22" t="n"/>
+      <c r="Y42" s="22" t="n"/>
+      <c r="Z42" s="22" t="n"/>
+      <c r="AA42" s="22" t="n"/>
+      <c r="AB42" s="22" t="n"/>
+      <c r="AC42" s="22" t="n"/>
+      <c r="AD42" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="22" t="n"/>
+      <c r="G43" s="22" t="n"/>
+      <c r="H43" s="22" t="n"/>
+      <c r="I43" s="22" t="n"/>
+      <c r="J43" s="22" t="n"/>
+      <c r="K43" s="22" t="n"/>
+      <c r="L43" s="22" t="n"/>
+      <c r="M43" s="22" t="n"/>
+      <c r="N43" s="22" t="n"/>
+      <c r="O43" s="22" t="n"/>
+      <c r="P43" s="25" t="n"/>
+      <c r="Q43" s="22" t="n"/>
+      <c r="R43" s="22" t="n"/>
+      <c r="S43" s="22" t="n"/>
+      <c r="T43" s="22" t="n"/>
+      <c r="U43" s="22" t="n"/>
+      <c r="V43" s="22" t="n"/>
+      <c r="W43" s="22" t="n"/>
+      <c r="X43" s="22" t="n"/>
+      <c r="Y43" s="22" t="n"/>
+      <c r="Z43" s="22" t="n"/>
+      <c r="AA43" s="22" t="n"/>
+      <c r="AB43" s="22" t="n"/>
+      <c r="AC43" s="22" t="n"/>
+      <c r="AD43" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Fisioterapia y citas</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="22" t="n"/>
+      <c r="K44" s="22" t="n"/>
+      <c r="L44" s="22" t="n"/>
+      <c r="M44" s="22" t="n"/>
+      <c r="N44" s="22" t="n"/>
+      <c r="O44" s="22" t="n"/>
+      <c r="P44" s="22" t="n"/>
+      <c r="Q44" s="26" t="n"/>
+      <c r="R44" s="26" t="n"/>
+      <c r="S44" s="22" t="n"/>
+      <c r="T44" s="22" t="n"/>
+      <c r="U44" s="22" t="n"/>
+      <c r="V44" s="22" t="n"/>
+      <c r="W44" s="22" t="n"/>
+      <c r="X44" s="22" t="n"/>
+      <c r="Y44" s="22" t="n"/>
+      <c r="Z44" s="22" t="n"/>
+      <c r="AA44" s="22" t="n"/>
+      <c r="AB44" s="22" t="n"/>
+      <c r="AC44" s="22" t="n"/>
+      <c r="AD44" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="22" t="n"/>
+      <c r="H45" s="22" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="22" t="n"/>
+      <c r="K45" s="22" t="n"/>
+      <c r="L45" s="22" t="n"/>
+      <c r="M45" s="22" t="n"/>
+      <c r="N45" s="22" t="n"/>
+      <c r="O45" s="22" t="n"/>
+      <c r="P45" s="22" t="n"/>
+      <c r="Q45" s="22" t="n"/>
+      <c r="R45" s="22" t="n"/>
+      <c r="S45" s="26" t="n"/>
+      <c r="T45" s="22" t="n"/>
+      <c r="U45" s="22" t="n"/>
+      <c r="V45" s="22" t="n"/>
+      <c r="W45" s="22" t="n"/>
+      <c r="X45" s="22" t="n"/>
+      <c r="Y45" s="22" t="n"/>
+      <c r="Z45" s="22" t="n"/>
+      <c r="AA45" s="22" t="n"/>
+      <c r="AB45" s="22" t="n"/>
+      <c r="AC45" s="22" t="n"/>
+      <c r="AD45" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="n"/>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="22" t="n"/>
+      <c r="F46" s="22" t="n"/>
+      <c r="G46" s="22" t="n"/>
+      <c r="H46" s="22" t="n"/>
+      <c r="I46" s="22" t="n"/>
+      <c r="J46" s="22" t="n"/>
+      <c r="K46" s="22" t="n"/>
+      <c r="L46" s="22" t="n"/>
+      <c r="M46" s="22" t="n"/>
+      <c r="N46" s="22" t="n"/>
+      <c r="O46" s="22" t="n"/>
+      <c r="P46" s="22" t="n"/>
+      <c r="Q46" s="22" t="n"/>
+      <c r="R46" s="22" t="n"/>
+      <c r="S46" s="26" t="n"/>
+      <c r="T46" s="22" t="n"/>
+      <c r="U46" s="22" t="n"/>
+      <c r="V46" s="22" t="n"/>
+      <c r="W46" s="22" t="n"/>
+      <c r="X46" s="22" t="n"/>
+      <c r="Y46" s="22" t="n"/>
+      <c r="Z46" s="22" t="n"/>
+      <c r="AA46" s="22" t="n"/>
+      <c r="AB46" s="22" t="n"/>
+      <c r="AC46" s="22" t="n"/>
+      <c r="AD46" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Comentarios, feedback y seguridad</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="n"/>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="22" t="n"/>
+      <c r="F47" s="22" t="n"/>
+      <c r="G47" s="22" t="n"/>
+      <c r="H47" s="22" t="n"/>
+      <c r="I47" s="22" t="n"/>
+      <c r="J47" s="22" t="n"/>
+      <c r="K47" s="22" t="n"/>
+      <c r="L47" s="22" t="n"/>
+      <c r="M47" s="22" t="n"/>
+      <c r="N47" s="22" t="n"/>
+      <c r="O47" s="22" t="n"/>
+      <c r="P47" s="22" t="n"/>
+      <c r="Q47" s="22" t="n"/>
+      <c r="R47" s="22" t="n"/>
+      <c r="S47" s="22" t="n"/>
+      <c r="T47" s="27" t="n"/>
+      <c r="U47" s="27" t="n"/>
+      <c r="V47" s="27" t="n"/>
+      <c r="W47" s="27" t="n"/>
+      <c r="X47" s="22" t="n"/>
+      <c r="Y47" s="22" t="n"/>
+      <c r="Z47" s="22" t="n"/>
+      <c r="AA47" s="22" t="n"/>
+      <c r="AB47" s="22" t="n"/>
+      <c r="AC47" s="22" t="n"/>
+      <c r="AD47" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="n"/>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="22" t="n"/>
+      <c r="F48" s="22" t="n"/>
+      <c r="G48" s="22" t="n"/>
+      <c r="H48" s="22" t="n"/>
+      <c r="I48" s="22" t="n"/>
+      <c r="J48" s="22" t="n"/>
+      <c r="K48" s="22" t="n"/>
+      <c r="L48" s="22" t="n"/>
+      <c r="M48" s="22" t="n"/>
+      <c r="N48" s="22" t="n"/>
+      <c r="O48" s="22" t="n"/>
+      <c r="P48" s="22" t="n"/>
+      <c r="Q48" s="22" t="n"/>
+      <c r="R48" s="22" t="n"/>
+      <c r="S48" s="22" t="n"/>
+      <c r="T48" s="22" t="n"/>
+      <c r="U48" s="22" t="n"/>
+      <c r="V48" s="22" t="n"/>
+      <c r="W48" s="22" t="n"/>
+      <c r="X48" s="27" t="n"/>
+      <c r="Y48" s="22" t="n"/>
+      <c r="Z48" s="22" t="n"/>
+      <c r="AA48" s="22" t="n"/>
+      <c r="AB48" s="22" t="n"/>
+      <c r="AC48" s="22" t="n"/>
+      <c r="AD48" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="n"/>
+      <c r="C49" s="22" t="n"/>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="22" t="n"/>
+      <c r="F49" s="22" t="n"/>
+      <c r="G49" s="22" t="n"/>
+      <c r="H49" s="22" t="n"/>
+      <c r="I49" s="22" t="n"/>
+      <c r="J49" s="22" t="n"/>
+      <c r="K49" s="22" t="n"/>
+      <c r="L49" s="22" t="n"/>
+      <c r="M49" s="22" t="n"/>
+      <c r="N49" s="22" t="n"/>
+      <c r="O49" s="22" t="n"/>
+      <c r="P49" s="22" t="n"/>
+      <c r="Q49" s="22" t="n"/>
+      <c r="R49" s="22" t="n"/>
+      <c r="S49" s="22" t="n"/>
+      <c r="T49" s="22" t="n"/>
+      <c r="U49" s="22" t="n"/>
+      <c r="V49" s="22" t="n"/>
+      <c r="W49" s="22" t="n"/>
+      <c r="X49" s="27" t="n"/>
+      <c r="Y49" s="22" t="n"/>
+      <c r="Z49" s="22" t="n"/>
+      <c r="AA49" s="22" t="n"/>
+      <c r="AB49" s="22" t="n"/>
+      <c r="AC49" s="22" t="n"/>
+      <c r="AD49" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>Interfaz Tailwind, correo y cierre</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="22" t="n"/>
+      <c r="F50" s="22" t="n"/>
+      <c r="G50" s="22" t="n"/>
+      <c r="H50" s="22" t="n"/>
+      <c r="I50" s="22" t="n"/>
+      <c r="J50" s="22" t="n"/>
+      <c r="K50" s="22" t="n"/>
+      <c r="L50" s="22" t="n"/>
+      <c r="M50" s="22" t="n"/>
+      <c r="N50" s="22" t="n"/>
+      <c r="O50" s="22" t="n"/>
+      <c r="P50" s="22" t="n"/>
+      <c r="Q50" s="22" t="n"/>
+      <c r="R50" s="22" t="n"/>
+      <c r="S50" s="22" t="n"/>
+      <c r="T50" s="22" t="n"/>
+      <c r="U50" s="22" t="n"/>
+      <c r="V50" s="22" t="n"/>
+      <c r="W50" s="22" t="n"/>
+      <c r="X50" s="22" t="n"/>
+      <c r="Y50" s="28" t="n"/>
+      <c r="Z50" s="28" t="n"/>
+      <c r="AA50" s="22" t="n"/>
+      <c r="AB50" s="22" t="n"/>
+      <c r="AC50" s="22" t="n"/>
+      <c r="AD50" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="22" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="22" t="n"/>
+      <c r="H51" s="22" t="n"/>
+      <c r="I51" s="22" t="n"/>
+      <c r="J51" s="22" t="n"/>
+      <c r="K51" s="22" t="n"/>
+      <c r="L51" s="22" t="n"/>
+      <c r="M51" s="22" t="n"/>
+      <c r="N51" s="22" t="n"/>
+      <c r="O51" s="22" t="n"/>
+      <c r="P51" s="22" t="n"/>
+      <c r="Q51" s="22" t="n"/>
+      <c r="R51" s="22" t="n"/>
+      <c r="S51" s="22" t="n"/>
+      <c r="T51" s="22" t="n"/>
+      <c r="U51" s="22" t="n"/>
+      <c r="V51" s="22" t="n"/>
+      <c r="W51" s="22" t="n"/>
+      <c r="X51" s="22" t="n"/>
+      <c r="Y51" s="22" t="n"/>
+      <c r="Z51" s="22" t="n"/>
+      <c r="AA51" s="28" t="n"/>
+      <c r="AB51" s="28" t="n"/>
+      <c r="AC51" s="28" t="n"/>
+      <c r="AD51" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="22" t="n"/>
+      <c r="F52" s="22" t="n"/>
+      <c r="G52" s="22" t="n"/>
+      <c r="H52" s="22" t="n"/>
+      <c r="I52" s="22" t="n"/>
+      <c r="J52" s="22" t="n"/>
+      <c r="K52" s="22" t="n"/>
+      <c r="L52" s="22" t="n"/>
+      <c r="M52" s="22" t="n"/>
+      <c r="N52" s="22" t="n"/>
+      <c r="O52" s="22" t="n"/>
+      <c r="P52" s="22" t="n"/>
+      <c r="Q52" s="22" t="n"/>
+      <c r="R52" s="22" t="n"/>
+      <c r="S52" s="22" t="n"/>
+      <c r="T52" s="22" t="n"/>
+      <c r="U52" s="22" t="n"/>
+      <c r="V52" s="22" t="n"/>
+      <c r="W52" s="22" t="n"/>
+      <c r="X52" s="22" t="n"/>
+      <c r="Y52" s="22" t="n"/>
+      <c r="Z52" s="22" t="n"/>
+      <c r="AA52" s="28" t="n"/>
+      <c r="AB52" s="28" t="n"/>
+      <c r="AC52" s="28" t="n"/>
+      <c r="AD52" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="31" t="n"/>
+      <c r="B53" s="32" t="n"/>
+      <c r="C53" s="32" t="n"/>
+      <c r="D53" s="32" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="32" t="n"/>
+      <c r="H53" s="32" t="n"/>
+      <c r="I53" s="32" t="n"/>
+      <c r="J53" s="32" t="n"/>
+      <c r="K53" s="32" t="n"/>
+      <c r="L53" s="32" t="n"/>
+      <c r="M53" s="32" t="n"/>
+      <c r="N53" s="32" t="n"/>
+      <c r="O53" s="32" t="n"/>
+      <c r="P53" s="32" t="n"/>
+      <c r="Q53" s="32" t="n"/>
+      <c r="R53" s="32" t="n"/>
+      <c r="S53" s="32" t="n"/>
+      <c r="T53" s="32" t="n"/>
+      <c r="U53" s="32" t="n"/>
+      <c r="V53" s="32" t="n"/>
+      <c r="W53" s="32" t="n"/>
+      <c r="X53" s="32" t="n"/>
+      <c r="Y53" s="32" t="n"/>
+      <c r="Z53" s="32" t="n"/>
+      <c r="AA53" s="32" t="n"/>
+      <c r="AB53" s="32" t="n"/>
+      <c r="AC53" s="32" t="n"/>
+      <c r="AD53" s="32" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="31" t="n"/>
+      <c r="B54" s="32" t="n"/>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="32" t="n"/>
+      <c r="G54" s="32" t="n"/>
+      <c r="H54" s="32" t="n"/>
+      <c r="I54" s="32" t="n"/>
+      <c r="J54" s="32" t="n"/>
+      <c r="K54" s="32" t="n"/>
+      <c r="L54" s="32" t="n"/>
+      <c r="M54" s="32" t="n"/>
+      <c r="N54" s="32" t="n"/>
+      <c r="O54" s="32" t="n"/>
+      <c r="P54" s="32" t="n"/>
+      <c r="Q54" s="32" t="n"/>
+      <c r="R54" s="32" t="n"/>
+      <c r="S54" s="32" t="n"/>
+      <c r="T54" s="32" t="n"/>
+      <c r="U54" s="32" t="n"/>
+      <c r="V54" s="32" t="n"/>
+      <c r="W54" s="32" t="n"/>
+      <c r="X54" s="32" t="n"/>
+      <c r="Y54" s="32" t="n"/>
+      <c r="Z54" s="32" t="n"/>
+      <c r="AA54" s="32" t="n"/>
+      <c r="AB54" s="32" t="n"/>
+      <c r="AC54" s="32" t="n"/>
+      <c r="AD54" s="32" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="31" t="n"/>
+      <c r="B55" s="32" t="n"/>
+      <c r="C55" s="32" t="n"/>
+      <c r="D55" s="32" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="32" t="n"/>
+      <c r="H55" s="32" t="n"/>
+      <c r="I55" s="32" t="n"/>
+      <c r="J55" s="32" t="n"/>
+      <c r="K55" s="32" t="n"/>
+      <c r="L55" s="32" t="n"/>
+      <c r="M55" s="32" t="n"/>
+      <c r="N55" s="32" t="n"/>
+      <c r="O55" s="32" t="n"/>
+      <c r="P55" s="32" t="n"/>
+      <c r="Q55" s="32" t="n"/>
+      <c r="R55" s="32" t="n"/>
+      <c r="S55" s="32" t="n"/>
+      <c r="T55" s="32" t="n"/>
+      <c r="U55" s="32" t="n"/>
+      <c r="V55" s="32" t="n"/>
+      <c r="W55" s="32" t="n"/>
+      <c r="X55" s="32" t="n"/>
+      <c r="Y55" s="32" t="n"/>
+      <c r="Z55" s="32" t="n"/>
+      <c r="AA55" s="32" t="n"/>
+      <c r="AB55" s="32" t="n"/>
+      <c r="AC55" s="32" t="n"/>
+      <c r="AD55" s="32" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="31" t="n"/>
+      <c r="B56" s="32" t="n"/>
+      <c r="C56" s="32" t="n"/>
+      <c r="D56" s="32" t="n"/>
+      <c r="E56" s="32" t="n"/>
+      <c r="F56" s="32" t="n"/>
+      <c r="G56" s="32" t="n"/>
+      <c r="H56" s="32" t="n"/>
+      <c r="I56" s="32" t="n"/>
+      <c r="J56" s="32" t="n"/>
+      <c r="K56" s="32" t="n"/>
+      <c r="L56" s="32" t="n"/>
+      <c r="M56" s="32" t="n"/>
+      <c r="N56" s="32" t="n"/>
+      <c r="O56" s="32" t="n"/>
+      <c r="P56" s="32" t="n"/>
+      <c r="Q56" s="32" t="n"/>
+      <c r="R56" s="32" t="n"/>
+      <c r="S56" s="32" t="n"/>
+      <c r="T56" s="32" t="n"/>
+      <c r="U56" s="32" t="n"/>
+      <c r="V56" s="32" t="n"/>
+      <c r="W56" s="32" t="n"/>
+      <c r="X56" s="32" t="n"/>
+      <c r="Y56" s="32" t="n"/>
+      <c r="Z56" s="32" t="n"/>
+      <c r="AA56" s="32" t="n"/>
+      <c r="AB56" s="32" t="n"/>
+      <c r="AC56" s="32" t="n"/>
+      <c r="AD56" s="32" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="31" t="n"/>
+      <c r="B57" s="32" t="n"/>
+      <c r="C57" s="32" t="n"/>
+      <c r="D57" s="32" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="32" t="n"/>
+      <c r="H57" s="32" t="n"/>
+      <c r="I57" s="32" t="n"/>
+      <c r="J57" s="32" t="n"/>
+      <c r="K57" s="32" t="n"/>
+      <c r="L57" s="32" t="n"/>
+      <c r="M57" s="32" t="n"/>
+      <c r="N57" s="32" t="n"/>
+      <c r="O57" s="32" t="n"/>
+      <c r="P57" s="32" t="n"/>
+      <c r="Q57" s="32" t="n"/>
+      <c r="R57" s="32" t="n"/>
+      <c r="S57" s="32" t="n"/>
+      <c r="T57" s="32" t="n"/>
+      <c r="U57" s="32" t="n"/>
+      <c r="V57" s="32" t="n"/>
+      <c r="W57" s="32" t="n"/>
+      <c r="X57" s="32" t="n"/>
+      <c r="Y57" s="32" t="n"/>
+      <c r="Z57" s="32" t="n"/>
+      <c r="AA57" s="32" t="n"/>
+      <c r="AB57" s="32" t="n"/>
+      <c r="AC57" s="32" t="n"/>
+      <c r="AD57" s="32" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="31" t="n"/>
+      <c r="B58" s="32" t="n"/>
+      <c r="C58" s="32" t="n"/>
+      <c r="D58" s="32" t="n"/>
+      <c r="E58" s="32" t="n"/>
+      <c r="F58" s="32" t="n"/>
+      <c r="G58" s="32" t="n"/>
+      <c r="H58" s="32" t="n"/>
+      <c r="I58" s="32" t="n"/>
+      <c r="J58" s="32" t="n"/>
+      <c r="K58" s="32" t="n"/>
+      <c r="L58" s="32" t="n"/>
+      <c r="M58" s="32" t="n"/>
+      <c r="N58" s="32" t="n"/>
+      <c r="O58" s="32" t="n"/>
+      <c r="P58" s="32" t="n"/>
+      <c r="Q58" s="32" t="n"/>
+      <c r="R58" s="32" t="n"/>
+      <c r="S58" s="32" t="n"/>
+      <c r="T58" s="32" t="n"/>
+      <c r="U58" s="32" t="n"/>
+      <c r="V58" s="32" t="n"/>
+      <c r="W58" s="32" t="n"/>
+      <c r="X58" s="32" t="n"/>
+      <c r="Y58" s="32" t="n"/>
+      <c r="Z58" s="32" t="n"/>
+      <c r="AA58" s="32" t="n"/>
+      <c r="AB58" s="32" t="n"/>
+      <c r="AC58" s="32" t="n"/>
+      <c r="AD58" s="32" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3712,13 +5593,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008CB5B7"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:W58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
     <col width="3.7" customWidth="1" min="3" max="3"/>
     <col width="3.7" customWidth="1" min="4" max="4"/>
@@ -4038,7 +5919,7 @@
       </c>
       <c r="W7" s="13" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1">
+    <row r="8" ht="15" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Núcleo del proyecto</t>
@@ -4071,10 +5952,10 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Acceso, registro y sesión</t>
+    <row r="9" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B9" s="22" t="n"/>
@@ -4104,10 +5985,10 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>Recuperación de cuenta y tickets</t>
+    <row r="10" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B10" s="22" t="n"/>
@@ -4137,10 +6018,10 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Perfil, contraseña y baja</t>
+          <t>Acceso, registro y sesión</t>
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
@@ -4170,10 +6051,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>Actividades y horario</t>
+    <row r="12" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
@@ -4197,16 +6078,16 @@
       <c r="T12" s="22" t="n"/>
       <c r="U12" s="22" t="n"/>
       <c r="V12" s="22" t="n"/>
-      <c r="W12" s="28" t="inlineStr">
-        <is>
-          <t>en curso</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>Inscripciones y reservas</t>
+      <c r="W12" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
@@ -4230,16 +6111,16 @@
       <c r="T13" s="22" t="n"/>
       <c r="U13" s="22" t="n"/>
       <c r="V13" s="22" t="n"/>
-      <c r="W13" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
+      <c r="W13" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Suscripciones</t>
+          <t>Recuperación de cuenta y tickets</t>
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
@@ -4263,16 +6144,16 @@
       <c r="T14" s="22" t="n"/>
       <c r="U14" s="22" t="n"/>
       <c r="V14" s="22" t="n"/>
-      <c r="W14" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>Pagos con Stripe</t>
+      <c r="W14" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
@@ -4296,16 +6177,16 @@
       <c r="T15" s="22" t="n"/>
       <c r="U15" s="22" t="n"/>
       <c r="V15" s="22" t="n"/>
-      <c r="W15" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Panel de administración</t>
+      <c r="W15" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
@@ -4329,16 +6210,16 @@
       <c r="T16" s="22" t="n"/>
       <c r="U16" s="22" t="n"/>
       <c r="V16" s="22" t="n"/>
-      <c r="W16" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
+      <c r="W16" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>Gestión de clientes</t>
+          <t>Perfil, contraseña y baja</t>
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
@@ -4362,16 +6243,16 @@
       <c r="T17" s="22" t="n"/>
       <c r="U17" s="22" t="n"/>
       <c r="V17" s="22" t="n"/>
-      <c r="W17" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Monitores y solicitudes</t>
+      <c r="W17" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B18" s="22" t="n"/>
@@ -4395,16 +6276,16 @@
       <c r="T18" s="22" t="n"/>
       <c r="U18" s="22" t="n"/>
       <c r="V18" s="22" t="n"/>
-      <c r="W18" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>Salas y materiales</t>
+      <c r="W18" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
         </is>
       </c>
       <c r="B19" s="22" t="n"/>
@@ -4428,16 +6309,16 @@
       <c r="T19" s="22" t="n"/>
       <c r="U19" s="22" t="n"/>
       <c r="V19" s="22" t="n"/>
-      <c r="W19" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
+      <c r="W19" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Fisioterapia y citas</t>
+          <t>Actividades y horario</t>
         </is>
       </c>
       <c r="B20" s="22" t="n"/>
@@ -4463,14 +6344,14 @@
       <c r="V20" s="22" t="n"/>
       <c r="W20" s="29" t="inlineStr">
         <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>Comentarios, feedback y seguridad</t>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
         </is>
       </c>
       <c r="B21" s="22" t="n"/>
@@ -4494,23 +6375,23 @@
       <c r="T21" s="22" t="n"/>
       <c r="U21" s="22" t="n"/>
       <c r="V21" s="22" t="n"/>
-      <c r="W21" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Interfaz Tailwind, correo y cierre</t>
-        </is>
-      </c>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="27" t="n"/>
+      <c r="W21" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="E22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
       <c r="G22" s="22" t="n"/>
       <c r="H22" s="22" t="n"/>
       <c r="I22" s="22" t="n"/>
@@ -4527,361 +6408,1151 @@
       <c r="T22" s="22" t="n"/>
       <c r="U22" s="22" t="n"/>
       <c r="V22" s="22" t="n"/>
-      <c r="W22" s="29" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="30" t="n"/>
-      <c r="B23" s="31" t="n"/>
-      <c r="C23" s="31" t="n"/>
-      <c r="D23" s="31" t="n"/>
-      <c r="E23" s="31" t="n"/>
-      <c r="F23" s="31" t="n"/>
-      <c r="G23" s="31" t="n"/>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="31" t="n"/>
-      <c r="J23" s="31" t="n"/>
-      <c r="K23" s="31" t="n"/>
-      <c r="L23" s="31" t="n"/>
-      <c r="M23" s="31" t="n"/>
-      <c r="N23" s="31" t="n"/>
-      <c r="O23" s="31" t="n"/>
-      <c r="P23" s="31" t="n"/>
-      <c r="Q23" s="31" t="n"/>
-      <c r="R23" s="31" t="n"/>
-      <c r="S23" s="31" t="n"/>
-      <c r="T23" s="31" t="n"/>
-      <c r="U23" s="31" t="n"/>
-      <c r="V23" s="31" t="n"/>
-      <c r="W23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="30" t="n"/>
-      <c r="B24" s="31" t="n"/>
-      <c r="C24" s="31" t="n"/>
-      <c r="D24" s="31" t="n"/>
-      <c r="E24" s="31" t="n"/>
-      <c r="F24" s="31" t="n"/>
-      <c r="G24" s="31" t="n"/>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n"/>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="31" t="n"/>
-      <c r="O24" s="31" t="n"/>
-      <c r="P24" s="31" t="n"/>
-      <c r="Q24" s="31" t="n"/>
-      <c r="R24" s="31" t="n"/>
-      <c r="S24" s="31" t="n"/>
-      <c r="T24" s="31" t="n"/>
-      <c r="U24" s="31" t="n"/>
-      <c r="V24" s="31" t="n"/>
-      <c r="W24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="30" t="n"/>
-      <c r="B25" s="31" t="n"/>
-      <c r="C25" s="31" t="n"/>
-      <c r="D25" s="31" t="n"/>
-      <c r="E25" s="31" t="n"/>
-      <c r="F25" s="31" t="n"/>
-      <c r="G25" s="31" t="n"/>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="31" t="n"/>
-      <c r="J25" s="31" t="n"/>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n"/>
-      <c r="N25" s="31" t="n"/>
-      <c r="O25" s="31" t="n"/>
-      <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="31" t="n"/>
-      <c r="R25" s="31" t="n"/>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="31" t="n"/>
-      <c r="U25" s="31" t="n"/>
-      <c r="V25" s="31" t="n"/>
-      <c r="W25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="30" t="n"/>
-      <c r="B26" s="31" t="n"/>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="31" t="n"/>
-      <c r="J26" s="31" t="n"/>
-      <c r="K26" s="31" t="n"/>
-      <c r="L26" s="31" t="n"/>
-      <c r="M26" s="31" t="n"/>
-      <c r="N26" s="31" t="n"/>
-      <c r="O26" s="31" t="n"/>
-      <c r="P26" s="31" t="n"/>
-      <c r="Q26" s="31" t="n"/>
-      <c r="R26" s="31" t="n"/>
-      <c r="S26" s="31" t="n"/>
-      <c r="T26" s="31" t="n"/>
-      <c r="U26" s="31" t="n"/>
-      <c r="V26" s="31" t="n"/>
-      <c r="W26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="30" t="n"/>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="31" t="n"/>
-      <c r="G27" s="31" t="n"/>
-      <c r="H27" s="31" t="n"/>
-      <c r="I27" s="31" t="n"/>
-      <c r="J27" s="31" t="n"/>
-      <c r="K27" s="31" t="n"/>
-      <c r="L27" s="31" t="n"/>
-      <c r="M27" s="31" t="n"/>
-      <c r="N27" s="31" t="n"/>
-      <c r="O27" s="31" t="n"/>
-      <c r="P27" s="31" t="n"/>
-      <c r="Q27" s="31" t="n"/>
-      <c r="R27" s="31" t="n"/>
-      <c r="S27" s="31" t="n"/>
-      <c r="T27" s="31" t="n"/>
-      <c r="U27" s="31" t="n"/>
-      <c r="V27" s="31" t="n"/>
-      <c r="W27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="30" t="n"/>
-      <c r="B28" s="31" t="n"/>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="31" t="n"/>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n"/>
-      <c r="G28" s="31" t="n"/>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-      <c r="J28" s="31" t="n"/>
-      <c r="K28" s="31" t="n"/>
-      <c r="L28" s="31" t="n"/>
-      <c r="M28" s="31" t="n"/>
-      <c r="N28" s="31" t="n"/>
-      <c r="O28" s="31" t="n"/>
-      <c r="P28" s="31" t="n"/>
-      <c r="Q28" s="31" t="n"/>
-      <c r="R28" s="31" t="n"/>
-      <c r="S28" s="31" t="n"/>
-      <c r="T28" s="31" t="n"/>
-      <c r="U28" s="31" t="n"/>
-      <c r="V28" s="31" t="n"/>
-      <c r="W28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="30" t="n"/>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="31" t="n"/>
-      <c r="D29" s="31" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="31" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="31" t="n"/>
-      <c r="J29" s="31" t="n"/>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="31" t="n"/>
-      <c r="M29" s="31" t="n"/>
-      <c r="N29" s="31" t="n"/>
-      <c r="O29" s="31" t="n"/>
-      <c r="P29" s="31" t="n"/>
-      <c r="Q29" s="31" t="n"/>
-      <c r="R29" s="31" t="n"/>
-      <c r="S29" s="31" t="n"/>
-      <c r="T29" s="31" t="n"/>
-      <c r="U29" s="31" t="n"/>
-      <c r="V29" s="31" t="n"/>
-      <c r="W29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="30" t="n"/>
-      <c r="B30" s="31" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="31" t="n"/>
-      <c r="E30" s="31" t="n"/>
-      <c r="F30" s="31" t="n"/>
-      <c r="G30" s="31" t="n"/>
-      <c r="H30" s="31" t="n"/>
-      <c r="I30" s="31" t="n"/>
-      <c r="J30" s="31" t="n"/>
-      <c r="K30" s="31" t="n"/>
-      <c r="L30" s="31" t="n"/>
-      <c r="M30" s="31" t="n"/>
-      <c r="N30" s="31" t="n"/>
-      <c r="O30" s="31" t="n"/>
-      <c r="P30" s="31" t="n"/>
-      <c r="Q30" s="31" t="n"/>
-      <c r="R30" s="31" t="n"/>
-      <c r="S30" s="31" t="n"/>
-      <c r="T30" s="31" t="n"/>
-      <c r="U30" s="31" t="n"/>
-      <c r="V30" s="31" t="n"/>
-      <c r="W30" s="31" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="30" t="n"/>
-      <c r="B31" s="31" t="n"/>
-      <c r="C31" s="31" t="n"/>
-      <c r="D31" s="31" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="31" t="n"/>
-      <c r="G31" s="31" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="31" t="n"/>
-      <c r="J31" s="31" t="n"/>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="31" t="n"/>
-      <c r="M31" s="31" t="n"/>
-      <c r="N31" s="31" t="n"/>
-      <c r="O31" s="31" t="n"/>
-      <c r="P31" s="31" t="n"/>
-      <c r="Q31" s="31" t="n"/>
-      <c r="R31" s="31" t="n"/>
-      <c r="S31" s="31" t="n"/>
-      <c r="T31" s="31" t="n"/>
-      <c r="U31" s="31" t="n"/>
-      <c r="V31" s="31" t="n"/>
-      <c r="W31" s="31" t="n"/>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
-      <c r="G32" s="31" t="n"/>
-      <c r="H32" s="31" t="n"/>
-      <c r="I32" s="31" t="n"/>
-      <c r="J32" s="31" t="n"/>
-      <c r="K32" s="31" t="n"/>
-      <c r="L32" s="31" t="n"/>
-      <c r="M32" s="31" t="n"/>
-      <c r="N32" s="31" t="n"/>
-      <c r="O32" s="31" t="n"/>
-      <c r="P32" s="31" t="n"/>
-      <c r="Q32" s="31" t="n"/>
-      <c r="R32" s="31" t="n"/>
-      <c r="S32" s="31" t="n"/>
-      <c r="T32" s="31" t="n"/>
-      <c r="U32" s="31" t="n"/>
-      <c r="V32" s="31" t="n"/>
-      <c r="W32" s="31" t="n"/>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="30" t="n"/>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="31" t="n"/>
-      <c r="D33" s="31" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="31" t="n"/>
-      <c r="G33" s="31" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="31" t="n"/>
-      <c r="J33" s="31" t="n"/>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="31" t="n"/>
-      <c r="M33" s="31" t="n"/>
-      <c r="N33" s="31" t="n"/>
-      <c r="O33" s="31" t="n"/>
-      <c r="P33" s="31" t="n"/>
-      <c r="Q33" s="31" t="n"/>
-      <c r="R33" s="31" t="n"/>
-      <c r="S33" s="31" t="n"/>
-      <c r="T33" s="31" t="n"/>
-      <c r="U33" s="31" t="n"/>
-      <c r="V33" s="31" t="n"/>
-      <c r="W33" s="31" t="n"/>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="30" t="n"/>
-      <c r="B34" s="31" t="n"/>
-      <c r="C34" s="31" t="n"/>
-      <c r="D34" s="31" t="n"/>
-      <c r="E34" s="31" t="n"/>
-      <c r="F34" s="31" t="n"/>
-      <c r="G34" s="31" t="n"/>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n"/>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n"/>
-      <c r="N34" s="31" t="n"/>
-      <c r="O34" s="31" t="n"/>
-      <c r="P34" s="31" t="n"/>
-      <c r="Q34" s="31" t="n"/>
-      <c r="R34" s="31" t="n"/>
-      <c r="S34" s="31" t="n"/>
-      <c r="T34" s="31" t="n"/>
-      <c r="U34" s="31" t="n"/>
-      <c r="V34" s="31" t="n"/>
-      <c r="W34" s="31" t="n"/>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="30" t="n"/>
-      <c r="B35" s="31" t="n"/>
-      <c r="C35" s="31" t="n"/>
-      <c r="D35" s="31" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="31" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="31" t="n"/>
-      <c r="J35" s="31" t="n"/>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n"/>
-      <c r="N35" s="31" t="n"/>
-      <c r="O35" s="31" t="n"/>
-      <c r="P35" s="31" t="n"/>
-      <c r="Q35" s="31" t="n"/>
-      <c r="R35" s="31" t="n"/>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n"/>
-      <c r="U35" s="31" t="n"/>
-      <c r="V35" s="31" t="n"/>
-      <c r="W35" s="31" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="30" t="n"/>
-      <c r="B36" s="31" t="n"/>
-      <c r="C36" s="31" t="n"/>
-      <c r="D36" s="31" t="n"/>
-      <c r="E36" s="31" t="n"/>
-      <c r="F36" s="31" t="n"/>
-      <c r="G36" s="31" t="n"/>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n"/>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n"/>
-      <c r="N36" s="31" t="n"/>
-      <c r="O36" s="31" t="n"/>
-      <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="31" t="n"/>
-      <c r="R36" s="31" t="n"/>
-      <c r="S36" s="31" t="n"/>
-      <c r="T36" s="31" t="n"/>
-      <c r="U36" s="31" t="n"/>
-      <c r="V36" s="31" t="n"/>
-      <c r="W36" s="31" t="n"/>
+      <c r="W22" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Inscripciones y reservas</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="22" t="n"/>
+      <c r="L23" s="22" t="n"/>
+      <c r="M23" s="22" t="n"/>
+      <c r="N23" s="22" t="n"/>
+      <c r="O23" s="22" t="n"/>
+      <c r="P23" s="22" t="n"/>
+      <c r="Q23" s="22" t="n"/>
+      <c r="R23" s="22" t="n"/>
+      <c r="S23" s="22" t="n"/>
+      <c r="T23" s="22" t="n"/>
+      <c r="U23" s="22" t="n"/>
+      <c r="V23" s="22" t="n"/>
+      <c r="W23" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="E24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="22" t="n"/>
+      <c r="L24" s="22" t="n"/>
+      <c r="M24" s="22" t="n"/>
+      <c r="N24" s="22" t="n"/>
+      <c r="O24" s="22" t="n"/>
+      <c r="P24" s="22" t="n"/>
+      <c r="Q24" s="22" t="n"/>
+      <c r="R24" s="22" t="n"/>
+      <c r="S24" s="22" t="n"/>
+      <c r="T24" s="22" t="n"/>
+      <c r="U24" s="22" t="n"/>
+      <c r="V24" s="22" t="n"/>
+      <c r="W24" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n"/>
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="22" t="n"/>
+      <c r="E25" s="22" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="22" t="n"/>
+      <c r="K25" s="22" t="n"/>
+      <c r="L25" s="22" t="n"/>
+      <c r="M25" s="22" t="n"/>
+      <c r="N25" s="22" t="n"/>
+      <c r="O25" s="22" t="n"/>
+      <c r="P25" s="22" t="n"/>
+      <c r="Q25" s="22" t="n"/>
+      <c r="R25" s="22" t="n"/>
+      <c r="S25" s="22" t="n"/>
+      <c r="T25" s="22" t="n"/>
+      <c r="U25" s="22" t="n"/>
+      <c r="V25" s="22" t="n"/>
+      <c r="W25" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>Suscripciones</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+      <c r="E26" s="22" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="22" t="n"/>
+      <c r="K26" s="22" t="n"/>
+      <c r="L26" s="22" t="n"/>
+      <c r="M26" s="22" t="n"/>
+      <c r="N26" s="22" t="n"/>
+      <c r="O26" s="22" t="n"/>
+      <c r="P26" s="22" t="n"/>
+      <c r="Q26" s="22" t="n"/>
+      <c r="R26" s="22" t="n"/>
+      <c r="S26" s="22" t="n"/>
+      <c r="T26" s="22" t="n"/>
+      <c r="U26" s="22" t="n"/>
+      <c r="V26" s="22" t="n"/>
+      <c r="W26" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+      <c r="E27" s="22" t="n"/>
+      <c r="F27" s="22" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="22" t="n"/>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="22" t="n"/>
+      <c r="N27" s="22" t="n"/>
+      <c r="O27" s="22" t="n"/>
+      <c r="P27" s="22" t="n"/>
+      <c r="Q27" s="22" t="n"/>
+      <c r="R27" s="22" t="n"/>
+      <c r="S27" s="22" t="n"/>
+      <c r="T27" s="22" t="n"/>
+      <c r="U27" s="22" t="n"/>
+      <c r="V27" s="22" t="n"/>
+      <c r="W27" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+      <c r="E28" s="22" t="n"/>
+      <c r="F28" s="22" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="22" t="n"/>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="22" t="n"/>
+      <c r="N28" s="22" t="n"/>
+      <c r="O28" s="22" t="n"/>
+      <c r="P28" s="22" t="n"/>
+      <c r="Q28" s="22" t="n"/>
+      <c r="R28" s="22" t="n"/>
+      <c r="S28" s="22" t="n"/>
+      <c r="T28" s="22" t="n"/>
+      <c r="U28" s="22" t="n"/>
+      <c r="V28" s="22" t="n"/>
+      <c r="W28" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>Pagos con Stripe</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+      <c r="E29" s="22" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="22" t="n"/>
+      <c r="K29" s="22" t="n"/>
+      <c r="L29" s="22" t="n"/>
+      <c r="M29" s="22" t="n"/>
+      <c r="N29" s="22" t="n"/>
+      <c r="O29" s="22" t="n"/>
+      <c r="P29" s="22" t="n"/>
+      <c r="Q29" s="22" t="n"/>
+      <c r="R29" s="22" t="n"/>
+      <c r="S29" s="22" t="n"/>
+      <c r="T29" s="22" t="n"/>
+      <c r="U29" s="22" t="n"/>
+      <c r="V29" s="22" t="n"/>
+      <c r="W29" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="n"/>
+      <c r="C30" s="22" t="n"/>
+      <c r="D30" s="22" t="n"/>
+      <c r="E30" s="22" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="22" t="n"/>
+      <c r="K30" s="22" t="n"/>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="22" t="n"/>
+      <c r="N30" s="22" t="n"/>
+      <c r="O30" s="22" t="n"/>
+      <c r="P30" s="22" t="n"/>
+      <c r="Q30" s="22" t="n"/>
+      <c r="R30" s="22" t="n"/>
+      <c r="S30" s="22" t="n"/>
+      <c r="T30" s="22" t="n"/>
+      <c r="U30" s="22" t="n"/>
+      <c r="V30" s="22" t="n"/>
+      <c r="W30" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+      <c r="E31" s="22" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="22" t="n"/>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="22" t="n"/>
+      <c r="N31" s="22" t="n"/>
+      <c r="O31" s="22" t="n"/>
+      <c r="P31" s="22" t="n"/>
+      <c r="Q31" s="22" t="n"/>
+      <c r="R31" s="22" t="n"/>
+      <c r="S31" s="22" t="n"/>
+      <c r="T31" s="22" t="n"/>
+      <c r="U31" s="22" t="n"/>
+      <c r="V31" s="22" t="n"/>
+      <c r="W31" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>Panel de administración</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+      <c r="E32" s="22" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="22" t="n"/>
+      <c r="K32" s="22" t="n"/>
+      <c r="L32" s="22" t="n"/>
+      <c r="M32" s="22" t="n"/>
+      <c r="N32" s="22" t="n"/>
+      <c r="O32" s="22" t="n"/>
+      <c r="P32" s="22" t="n"/>
+      <c r="Q32" s="22" t="n"/>
+      <c r="R32" s="22" t="n"/>
+      <c r="S32" s="22" t="n"/>
+      <c r="T32" s="22" t="n"/>
+      <c r="U32" s="22" t="n"/>
+      <c r="V32" s="22" t="n"/>
+      <c r="W32" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="n"/>
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="22" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="22" t="n"/>
+      <c r="K33" s="22" t="n"/>
+      <c r="L33" s="22" t="n"/>
+      <c r="M33" s="22" t="n"/>
+      <c r="N33" s="22" t="n"/>
+      <c r="O33" s="22" t="n"/>
+      <c r="P33" s="22" t="n"/>
+      <c r="Q33" s="22" t="n"/>
+      <c r="R33" s="22" t="n"/>
+      <c r="S33" s="22" t="n"/>
+      <c r="T33" s="22" t="n"/>
+      <c r="U33" s="22" t="n"/>
+      <c r="V33" s="22" t="n"/>
+      <c r="W33" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="22" t="n"/>
+      <c r="K34" s="22" t="n"/>
+      <c r="L34" s="22" t="n"/>
+      <c r="M34" s="22" t="n"/>
+      <c r="N34" s="22" t="n"/>
+      <c r="O34" s="22" t="n"/>
+      <c r="P34" s="22" t="n"/>
+      <c r="Q34" s="22" t="n"/>
+      <c r="R34" s="22" t="n"/>
+      <c r="S34" s="22" t="n"/>
+      <c r="T34" s="22" t="n"/>
+      <c r="U34" s="22" t="n"/>
+      <c r="V34" s="22" t="n"/>
+      <c r="W34" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>Gestión de clientes</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="n"/>
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="22" t="n"/>
+      <c r="E35" s="22" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="22" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="22" t="n"/>
+      <c r="K35" s="22" t="n"/>
+      <c r="L35" s="22" t="n"/>
+      <c r="M35" s="22" t="n"/>
+      <c r="N35" s="22" t="n"/>
+      <c r="O35" s="22" t="n"/>
+      <c r="P35" s="22" t="n"/>
+      <c r="Q35" s="22" t="n"/>
+      <c r="R35" s="22" t="n"/>
+      <c r="S35" s="22" t="n"/>
+      <c r="T35" s="22" t="n"/>
+      <c r="U35" s="22" t="n"/>
+      <c r="V35" s="22" t="n"/>
+      <c r="W35" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+      <c r="E36" s="22" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="22" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="22" t="n"/>
+      <c r="K36" s="22" t="n"/>
+      <c r="L36" s="22" t="n"/>
+      <c r="M36" s="22" t="n"/>
+      <c r="N36" s="22" t="n"/>
+      <c r="O36" s="22" t="n"/>
+      <c r="P36" s="22" t="n"/>
+      <c r="Q36" s="22" t="n"/>
+      <c r="R36" s="22" t="n"/>
+      <c r="S36" s="22" t="n"/>
+      <c r="T36" s="22" t="n"/>
+      <c r="U36" s="22" t="n"/>
+      <c r="V36" s="22" t="n"/>
+      <c r="W36" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="n"/>
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="22" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="22" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="22" t="n"/>
+      <c r="K37" s="22" t="n"/>
+      <c r="L37" s="22" t="n"/>
+      <c r="M37" s="22" t="n"/>
+      <c r="N37" s="22" t="n"/>
+      <c r="O37" s="22" t="n"/>
+      <c r="P37" s="22" t="n"/>
+      <c r="Q37" s="22" t="n"/>
+      <c r="R37" s="22" t="n"/>
+      <c r="S37" s="22" t="n"/>
+      <c r="T37" s="22" t="n"/>
+      <c r="U37" s="22" t="n"/>
+      <c r="V37" s="22" t="n"/>
+      <c r="W37" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>Monitores y solicitudes</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="22" t="n"/>
+      <c r="K38" s="22" t="n"/>
+      <c r="L38" s="22" t="n"/>
+      <c r="M38" s="22" t="n"/>
+      <c r="N38" s="22" t="n"/>
+      <c r="O38" s="22" t="n"/>
+      <c r="P38" s="22" t="n"/>
+      <c r="Q38" s="22" t="n"/>
+      <c r="R38" s="22" t="n"/>
+      <c r="S38" s="22" t="n"/>
+      <c r="T38" s="22" t="n"/>
+      <c r="U38" s="22" t="n"/>
+      <c r="V38" s="22" t="n"/>
+      <c r="W38" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="n"/>
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="22" t="n"/>
+      <c r="E39" s="22" t="n"/>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="22" t="n"/>
+      <c r="H39" s="22" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="22" t="n"/>
+      <c r="K39" s="22" t="n"/>
+      <c r="L39" s="22" t="n"/>
+      <c r="M39" s="22" t="n"/>
+      <c r="N39" s="22" t="n"/>
+      <c r="O39" s="22" t="n"/>
+      <c r="P39" s="22" t="n"/>
+      <c r="Q39" s="22" t="n"/>
+      <c r="R39" s="22" t="n"/>
+      <c r="S39" s="22" t="n"/>
+      <c r="T39" s="22" t="n"/>
+      <c r="U39" s="22" t="n"/>
+      <c r="V39" s="22" t="n"/>
+      <c r="W39" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="n"/>
+      <c r="C40" s="22" t="n"/>
+      <c r="D40" s="22" t="n"/>
+      <c r="E40" s="22" t="n"/>
+      <c r="F40" s="22" t="n"/>
+      <c r="G40" s="22" t="n"/>
+      <c r="H40" s="22" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="22" t="n"/>
+      <c r="K40" s="22" t="n"/>
+      <c r="L40" s="22" t="n"/>
+      <c r="M40" s="22" t="n"/>
+      <c r="N40" s="22" t="n"/>
+      <c r="O40" s="22" t="n"/>
+      <c r="P40" s="22" t="n"/>
+      <c r="Q40" s="22" t="n"/>
+      <c r="R40" s="22" t="n"/>
+      <c r="S40" s="22" t="n"/>
+      <c r="T40" s="22" t="n"/>
+      <c r="U40" s="22" t="n"/>
+      <c r="V40" s="22" t="n"/>
+      <c r="W40" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>Salas y materiales</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="n"/>
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="22" t="n"/>
+      <c r="E41" s="22" t="n"/>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="22" t="n"/>
+      <c r="H41" s="22" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="22" t="n"/>
+      <c r="K41" s="22" t="n"/>
+      <c r="L41" s="22" t="n"/>
+      <c r="M41" s="22" t="n"/>
+      <c r="N41" s="22" t="n"/>
+      <c r="O41" s="22" t="n"/>
+      <c r="P41" s="22" t="n"/>
+      <c r="Q41" s="22" t="n"/>
+      <c r="R41" s="22" t="n"/>
+      <c r="S41" s="22" t="n"/>
+      <c r="T41" s="22" t="n"/>
+      <c r="U41" s="22" t="n"/>
+      <c r="V41" s="22" t="n"/>
+      <c r="W41" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
+      <c r="G42" s="22" t="n"/>
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="22" t="n"/>
+      <c r="K42" s="22" t="n"/>
+      <c r="L42" s="22" t="n"/>
+      <c r="M42" s="22" t="n"/>
+      <c r="N42" s="22" t="n"/>
+      <c r="O42" s="22" t="n"/>
+      <c r="P42" s="22" t="n"/>
+      <c r="Q42" s="22" t="n"/>
+      <c r="R42" s="22" t="n"/>
+      <c r="S42" s="22" t="n"/>
+      <c r="T42" s="22" t="n"/>
+      <c r="U42" s="22" t="n"/>
+      <c r="V42" s="22" t="n"/>
+      <c r="W42" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="22" t="n"/>
+      <c r="G43" s="22" t="n"/>
+      <c r="H43" s="22" t="n"/>
+      <c r="I43" s="22" t="n"/>
+      <c r="J43" s="22" t="n"/>
+      <c r="K43" s="22" t="n"/>
+      <c r="L43" s="22" t="n"/>
+      <c r="M43" s="22" t="n"/>
+      <c r="N43" s="22" t="n"/>
+      <c r="O43" s="22" t="n"/>
+      <c r="P43" s="22" t="n"/>
+      <c r="Q43" s="22" t="n"/>
+      <c r="R43" s="22" t="n"/>
+      <c r="S43" s="22" t="n"/>
+      <c r="T43" s="22" t="n"/>
+      <c r="U43" s="22" t="n"/>
+      <c r="V43" s="22" t="n"/>
+      <c r="W43" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Fisioterapia y citas</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n"/>
+      <c r="C44" s="22" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="22" t="n"/>
+      <c r="K44" s="22" t="n"/>
+      <c r="L44" s="22" t="n"/>
+      <c r="M44" s="22" t="n"/>
+      <c r="N44" s="22" t="n"/>
+      <c r="O44" s="22" t="n"/>
+      <c r="P44" s="22" t="n"/>
+      <c r="Q44" s="22" t="n"/>
+      <c r="R44" s="22" t="n"/>
+      <c r="S44" s="22" t="n"/>
+      <c r="T44" s="22" t="n"/>
+      <c r="U44" s="22" t="n"/>
+      <c r="V44" s="22" t="n"/>
+      <c r="W44" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
+      <c r="E45" s="22" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="22" t="n"/>
+      <c r="H45" s="22" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="22" t="n"/>
+      <c r="K45" s="22" t="n"/>
+      <c r="L45" s="22" t="n"/>
+      <c r="M45" s="22" t="n"/>
+      <c r="N45" s="22" t="n"/>
+      <c r="O45" s="22" t="n"/>
+      <c r="P45" s="22" t="n"/>
+      <c r="Q45" s="22" t="n"/>
+      <c r="R45" s="22" t="n"/>
+      <c r="S45" s="22" t="n"/>
+      <c r="T45" s="22" t="n"/>
+      <c r="U45" s="22" t="n"/>
+      <c r="V45" s="22" t="n"/>
+      <c r="W45" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="n"/>
+      <c r="C46" s="22" t="n"/>
+      <c r="D46" s="22" t="n"/>
+      <c r="E46" s="22" t="n"/>
+      <c r="F46" s="22" t="n"/>
+      <c r="G46" s="22" t="n"/>
+      <c r="H46" s="22" t="n"/>
+      <c r="I46" s="22" t="n"/>
+      <c r="J46" s="22" t="n"/>
+      <c r="K46" s="22" t="n"/>
+      <c r="L46" s="22" t="n"/>
+      <c r="M46" s="22" t="n"/>
+      <c r="N46" s="22" t="n"/>
+      <c r="O46" s="22" t="n"/>
+      <c r="P46" s="22" t="n"/>
+      <c r="Q46" s="22" t="n"/>
+      <c r="R46" s="22" t="n"/>
+      <c r="S46" s="22" t="n"/>
+      <c r="T46" s="22" t="n"/>
+      <c r="U46" s="22" t="n"/>
+      <c r="V46" s="22" t="n"/>
+      <c r="W46" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Comentarios, feedback y seguridad</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="n"/>
+      <c r="C47" s="22" t="n"/>
+      <c r="D47" s="22" t="n"/>
+      <c r="E47" s="22" t="n"/>
+      <c r="F47" s="22" t="n"/>
+      <c r="G47" s="22" t="n"/>
+      <c r="H47" s="22" t="n"/>
+      <c r="I47" s="22" t="n"/>
+      <c r="J47" s="22" t="n"/>
+      <c r="K47" s="22" t="n"/>
+      <c r="L47" s="22" t="n"/>
+      <c r="M47" s="22" t="n"/>
+      <c r="N47" s="22" t="n"/>
+      <c r="O47" s="22" t="n"/>
+      <c r="P47" s="22" t="n"/>
+      <c r="Q47" s="22" t="n"/>
+      <c r="R47" s="22" t="n"/>
+      <c r="S47" s="22" t="n"/>
+      <c r="T47" s="22" t="n"/>
+      <c r="U47" s="22" t="n"/>
+      <c r="V47" s="22" t="n"/>
+      <c r="W47" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="n"/>
+      <c r="C48" s="22" t="n"/>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="22" t="n"/>
+      <c r="F48" s="22" t="n"/>
+      <c r="G48" s="22" t="n"/>
+      <c r="H48" s="22" t="n"/>
+      <c r="I48" s="22" t="n"/>
+      <c r="J48" s="22" t="n"/>
+      <c r="K48" s="22" t="n"/>
+      <c r="L48" s="22" t="n"/>
+      <c r="M48" s="22" t="n"/>
+      <c r="N48" s="22" t="n"/>
+      <c r="O48" s="22" t="n"/>
+      <c r="P48" s="22" t="n"/>
+      <c r="Q48" s="22" t="n"/>
+      <c r="R48" s="22" t="n"/>
+      <c r="S48" s="22" t="n"/>
+      <c r="T48" s="22" t="n"/>
+      <c r="U48" s="22" t="n"/>
+      <c r="V48" s="22" t="n"/>
+      <c r="W48" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="n"/>
+      <c r="C49" s="22" t="n"/>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="22" t="n"/>
+      <c r="F49" s="22" t="n"/>
+      <c r="G49" s="22" t="n"/>
+      <c r="H49" s="22" t="n"/>
+      <c r="I49" s="22" t="n"/>
+      <c r="J49" s="22" t="n"/>
+      <c r="K49" s="22" t="n"/>
+      <c r="L49" s="22" t="n"/>
+      <c r="M49" s="22" t="n"/>
+      <c r="N49" s="22" t="n"/>
+      <c r="O49" s="22" t="n"/>
+      <c r="P49" s="22" t="n"/>
+      <c r="Q49" s="22" t="n"/>
+      <c r="R49" s="22" t="n"/>
+      <c r="S49" s="22" t="n"/>
+      <c r="T49" s="22" t="n"/>
+      <c r="U49" s="22" t="n"/>
+      <c r="V49" s="22" t="n"/>
+      <c r="W49" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>Interfaz Tailwind, correo y cierre</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="n"/>
+      <c r="C50" s="22" t="n"/>
+      <c r="D50" s="22" t="n"/>
+      <c r="E50" s="22" t="n"/>
+      <c r="F50" s="22" t="n"/>
+      <c r="G50" s="22" t="n"/>
+      <c r="H50" s="22" t="n"/>
+      <c r="I50" s="22" t="n"/>
+      <c r="J50" s="22" t="n"/>
+      <c r="K50" s="22" t="n"/>
+      <c r="L50" s="22" t="n"/>
+      <c r="M50" s="22" t="n"/>
+      <c r="N50" s="22" t="n"/>
+      <c r="O50" s="22" t="n"/>
+      <c r="P50" s="22" t="n"/>
+      <c r="Q50" s="22" t="n"/>
+      <c r="R50" s="22" t="n"/>
+      <c r="S50" s="22" t="n"/>
+      <c r="T50" s="22" t="n"/>
+      <c r="U50" s="22" t="n"/>
+      <c r="V50" s="22" t="n"/>
+      <c r="W50" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="B51" s="28" t="n"/>
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="22" t="n"/>
+      <c r="E51" s="22" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="22" t="n"/>
+      <c r="H51" s="22" t="n"/>
+      <c r="I51" s="22" t="n"/>
+      <c r="J51" s="22" t="n"/>
+      <c r="K51" s="22" t="n"/>
+      <c r="L51" s="22" t="n"/>
+      <c r="M51" s="22" t="n"/>
+      <c r="N51" s="22" t="n"/>
+      <c r="O51" s="22" t="n"/>
+      <c r="P51" s="22" t="n"/>
+      <c r="Q51" s="22" t="n"/>
+      <c r="R51" s="22" t="n"/>
+      <c r="S51" s="22" t="n"/>
+      <c r="T51" s="22" t="n"/>
+      <c r="U51" s="22" t="n"/>
+      <c r="V51" s="22" t="n"/>
+      <c r="W51" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" outlineLevel="1" ht="15" customHeight="1">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>Testeo</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="n"/>
+      <c r="C52" s="28" t="n"/>
+      <c r="D52" s="28" t="n"/>
+      <c r="E52" s="28" t="n"/>
+      <c r="F52" s="28" t="n"/>
+      <c r="G52" s="22" t="n"/>
+      <c r="H52" s="22" t="n"/>
+      <c r="I52" s="22" t="n"/>
+      <c r="J52" s="22" t="n"/>
+      <c r="K52" s="22" t="n"/>
+      <c r="L52" s="22" t="n"/>
+      <c r="M52" s="22" t="n"/>
+      <c r="N52" s="22" t="n"/>
+      <c r="O52" s="22" t="n"/>
+      <c r="P52" s="22" t="n"/>
+      <c r="Q52" s="22" t="n"/>
+      <c r="R52" s="22" t="n"/>
+      <c r="S52" s="22" t="n"/>
+      <c r="T52" s="22" t="n"/>
+      <c r="U52" s="22" t="n"/>
+      <c r="V52" s="22" t="n"/>
+      <c r="W52" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="31" t="n"/>
+      <c r="B53" s="32" t="n"/>
+      <c r="C53" s="32" t="n"/>
+      <c r="D53" s="32" t="n"/>
+      <c r="E53" s="32" t="n"/>
+      <c r="F53" s="32" t="n"/>
+      <c r="G53" s="32" t="n"/>
+      <c r="H53" s="32" t="n"/>
+      <c r="I53" s="32" t="n"/>
+      <c r="J53" s="32" t="n"/>
+      <c r="K53" s="32" t="n"/>
+      <c r="L53" s="32" t="n"/>
+      <c r="M53" s="32" t="n"/>
+      <c r="N53" s="32" t="n"/>
+      <c r="O53" s="32" t="n"/>
+      <c r="P53" s="32" t="n"/>
+      <c r="Q53" s="32" t="n"/>
+      <c r="R53" s="32" t="n"/>
+      <c r="S53" s="32" t="n"/>
+      <c r="T53" s="32" t="n"/>
+      <c r="U53" s="32" t="n"/>
+      <c r="V53" s="32" t="n"/>
+      <c r="W53" s="32" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="31" t="n"/>
+      <c r="B54" s="32" t="n"/>
+      <c r="C54" s="32" t="n"/>
+      <c r="D54" s="32" t="n"/>
+      <c r="E54" s="32" t="n"/>
+      <c r="F54" s="32" t="n"/>
+      <c r="G54" s="32" t="n"/>
+      <c r="H54" s="32" t="n"/>
+      <c r="I54" s="32" t="n"/>
+      <c r="J54" s="32" t="n"/>
+      <c r="K54" s="32" t="n"/>
+      <c r="L54" s="32" t="n"/>
+      <c r="M54" s="32" t="n"/>
+      <c r="N54" s="32" t="n"/>
+      <c r="O54" s="32" t="n"/>
+      <c r="P54" s="32" t="n"/>
+      <c r="Q54" s="32" t="n"/>
+      <c r="R54" s="32" t="n"/>
+      <c r="S54" s="32" t="n"/>
+      <c r="T54" s="32" t="n"/>
+      <c r="U54" s="32" t="n"/>
+      <c r="V54" s="32" t="n"/>
+      <c r="W54" s="32" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="31" t="n"/>
+      <c r="B55" s="32" t="n"/>
+      <c r="C55" s="32" t="n"/>
+      <c r="D55" s="32" t="n"/>
+      <c r="E55" s="32" t="n"/>
+      <c r="F55" s="32" t="n"/>
+      <c r="G55" s="32" t="n"/>
+      <c r="H55" s="32" t="n"/>
+      <c r="I55" s="32" t="n"/>
+      <c r="J55" s="32" t="n"/>
+      <c r="K55" s="32" t="n"/>
+      <c r="L55" s="32" t="n"/>
+      <c r="M55" s="32" t="n"/>
+      <c r="N55" s="32" t="n"/>
+      <c r="O55" s="32" t="n"/>
+      <c r="P55" s="32" t="n"/>
+      <c r="Q55" s="32" t="n"/>
+      <c r="R55" s="32" t="n"/>
+      <c r="S55" s="32" t="n"/>
+      <c r="T55" s="32" t="n"/>
+      <c r="U55" s="32" t="n"/>
+      <c r="V55" s="32" t="n"/>
+      <c r="W55" s="32" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="31" t="n"/>
+      <c r="B56" s="32" t="n"/>
+      <c r="C56" s="32" t="n"/>
+      <c r="D56" s="32" t="n"/>
+      <c r="E56" s="32" t="n"/>
+      <c r="F56" s="32" t="n"/>
+      <c r="G56" s="32" t="n"/>
+      <c r="H56" s="32" t="n"/>
+      <c r="I56" s="32" t="n"/>
+      <c r="J56" s="32" t="n"/>
+      <c r="K56" s="32" t="n"/>
+      <c r="L56" s="32" t="n"/>
+      <c r="M56" s="32" t="n"/>
+      <c r="N56" s="32" t="n"/>
+      <c r="O56" s="32" t="n"/>
+      <c r="P56" s="32" t="n"/>
+      <c r="Q56" s="32" t="n"/>
+      <c r="R56" s="32" t="n"/>
+      <c r="S56" s="32" t="n"/>
+      <c r="T56" s="32" t="n"/>
+      <c r="U56" s="32" t="n"/>
+      <c r="V56" s="32" t="n"/>
+      <c r="W56" s="32" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="31" t="n"/>
+      <c r="B57" s="32" t="n"/>
+      <c r="C57" s="32" t="n"/>
+      <c r="D57" s="32" t="n"/>
+      <c r="E57" s="32" t="n"/>
+      <c r="F57" s="32" t="n"/>
+      <c r="G57" s="32" t="n"/>
+      <c r="H57" s="32" t="n"/>
+      <c r="I57" s="32" t="n"/>
+      <c r="J57" s="32" t="n"/>
+      <c r="K57" s="32" t="n"/>
+      <c r="L57" s="32" t="n"/>
+      <c r="M57" s="32" t="n"/>
+      <c r="N57" s="32" t="n"/>
+      <c r="O57" s="32" t="n"/>
+      <c r="P57" s="32" t="n"/>
+      <c r="Q57" s="32" t="n"/>
+      <c r="R57" s="32" t="n"/>
+      <c r="S57" s="32" t="n"/>
+      <c r="T57" s="32" t="n"/>
+      <c r="U57" s="32" t="n"/>
+      <c r="V57" s="32" t="n"/>
+      <c r="W57" s="32" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="31" t="n"/>
+      <c r="B58" s="32" t="n"/>
+      <c r="C58" s="32" t="n"/>
+      <c r="D58" s="32" t="n"/>
+      <c r="E58" s="32" t="n"/>
+      <c r="F58" s="32" t="n"/>
+      <c r="G58" s="32" t="n"/>
+      <c r="H58" s="32" t="n"/>
+      <c r="I58" s="32" t="n"/>
+      <c r="J58" s="32" t="n"/>
+      <c r="K58" s="32" t="n"/>
+      <c r="L58" s="32" t="n"/>
+      <c r="M58" s="32" t="n"/>
+      <c r="N58" s="32" t="n"/>
+      <c r="O58" s="32" t="n"/>
+      <c r="P58" s="32" t="n"/>
+      <c r="Q58" s="32" t="n"/>
+      <c r="R58" s="32" t="n"/>
+      <c r="S58" s="32" t="n"/>
+      <c r="T58" s="32" t="n"/>
+      <c r="U58" s="32" t="n"/>
+      <c r="V58" s="32" t="n"/>
+      <c r="W58" s="32" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/docs/Spartum_Gantt.xlsx
+++ b/docs/Spartum_Gantt.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Planificación Mes 3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Planificación Mes 1'!$A$1:$AD$58</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planificación Mes 2'!$A$1:$AD$58</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Planificación Mes 3'!$A$1:$W$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Planificación Mes 1'!$A$1:$AD$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planificación Mes 2'!$A$1:$AD$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Planificación Mes 3'!$A$1:$W$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -72,7 +72,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -146,27 +146,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4883C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDB50D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00BA7827"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D7630D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FAE29C"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
       </patternFill>
     </fill>
     <fill>
@@ -180,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -204,79 +184,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00F4883C"/>
+        <color rgb="00FFC000"/>
       </left>
       <right style="thin">
-        <color rgb="00F4883C"/>
+        <color rgb="00FFC000"/>
       </right>
       <top style="thin">
-        <color rgb="00F4883C"/>
+        <color rgb="00FFC000"/>
       </top>
       <bottom style="thin">
-        <color rgb="00F4883C"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00EDB50D"/>
-      </left>
-      <right style="thin">
-        <color rgb="00EDB50D"/>
-      </right>
-      <top style="thin">
-        <color rgb="00EDB50D"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00EDB50D"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BA7827"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BA7827"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BA7827"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BA7827"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D7630D"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D7630D"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D7630D"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D7630D"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00FAE29C"/>
-      </left>
-      <right style="thin">
-        <color rgb="00FAE29C"/>
-      </right>
-      <top style="thin">
-        <color rgb="00FAE29C"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00FAE29C"/>
+        <color rgb="00FFC000"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -344,14 +268,10 @@
     <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -726,10 +646,10 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD58"/>
+  <dimension ref="A1:AD101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
     <col width="3.7" customWidth="1" min="3" max="3"/>
     <col width="3.7" customWidth="1" min="4" max="4"/>
@@ -1141,15 +1061,15 @@
       </c>
       <c r="AD7" s="13" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Núcleo del proyecto</t>
+          <t>1. Núcleo del proyecto</t>
         </is>
       </c>
       <c r="B8" s="21" t="n"/>
       <c r="C8" s="21" t="n"/>
-      <c r="D8" s="22" t="n"/>
+      <c r="D8" s="21" t="n"/>
       <c r="E8" s="22" t="n"/>
       <c r="F8" s="22" t="n"/>
       <c r="G8" s="22" t="n"/>
@@ -1181,15 +1101,15 @@
         </is>
       </c>
     </row>
-    <row r="9" outlineLevel="1" ht="15" customHeight="1">
+    <row r="9" outlineLevel="1" ht="14" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="n"/>
+          <t>1.1 Estructura MVC y rutas</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n"/>
       <c r="C9" s="22" t="n"/>
-      <c r="D9" s="21" t="n"/>
+      <c r="D9" s="22" t="n"/>
       <c r="E9" s="22" t="n"/>
       <c r="F9" s="22" t="n"/>
       <c r="G9" s="22" t="n"/>
@@ -1221,15 +1141,15 @@
         </is>
       </c>
     </row>
-    <row r="10" outlineLevel="1" ht="15" customHeight="1">
+    <row r="10" outlineLevel="1" ht="14" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>1.2 Modelo de base de datos</t>
         </is>
       </c>
       <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n"/>
       <c r="E10" s="22" t="n"/>
       <c r="F10" s="22" t="n"/>
       <c r="G10" s="22" t="n"/>
@@ -1261,17 +1181,17 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Acceso, registro y sesión</t>
+    <row r="11" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>1.3 Conexión y configuración</t>
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
+      <c r="C11" s="21" t="n"/>
       <c r="D11" s="22" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
+      <c r="E11" s="22" t="n"/>
+      <c r="F11" s="22" t="n"/>
       <c r="G11" s="22" t="n"/>
       <c r="H11" s="22" t="n"/>
       <c r="I11" s="22" t="n"/>
@@ -1301,20 +1221,20 @@
         </is>
       </c>
     </row>
-    <row r="12" outlineLevel="1" ht="15" customHeight="1">
+    <row r="12" outlineLevel="1" ht="14" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>1.4 Testeo</t>
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
       <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n"/>
+      <c r="D12" s="21" t="n"/>
       <c r="E12" s="22" t="n"/>
       <c r="F12" s="22" t="n"/>
       <c r="G12" s="22" t="n"/>
       <c r="H12" s="22" t="n"/>
-      <c r="I12" s="25" t="n"/>
+      <c r="I12" s="22" t="n"/>
       <c r="J12" s="22" t="n"/>
       <c r="K12" s="22" t="n"/>
       <c r="L12" s="22" t="n"/>
@@ -1341,20 +1261,20 @@
         </is>
       </c>
     </row>
-    <row r="13" outlineLevel="1" ht="15" customHeight="1">
+    <row r="13" outlineLevel="1" ht="14" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>1.5 Documentación</t>
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
       <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="D13" s="21" t="n"/>
       <c r="E13" s="22" t="n"/>
       <c r="F13" s="22" t="n"/>
       <c r="G13" s="22" t="n"/>
       <c r="H13" s="22" t="n"/>
-      <c r="I13" s="25" t="n"/>
+      <c r="I13" s="22" t="n"/>
       <c r="J13" s="22" t="n"/>
       <c r="K13" s="22" t="n"/>
       <c r="L13" s="22" t="n"/>
@@ -1381,22 +1301,22 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Recuperación de cuenta y tickets</t>
+          <t>2. Acceso, registro y sesión</t>
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
       <c r="C14" s="22" t="n"/>
       <c r="D14" s="22" t="n"/>
-      <c r="E14" s="22" t="n"/>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="22" t="n"/>
-      <c r="H14" s="22" t="n"/>
-      <c r="I14" s="22" t="n"/>
-      <c r="J14" s="26" t="n"/>
-      <c r="K14" s="26" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="21" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="22" t="n"/>
       <c r="L14" s="22" t="n"/>
       <c r="M14" s="22" t="n"/>
       <c r="N14" s="22" t="n"/>
@@ -1421,23 +1341,23 @@
         </is>
       </c>
     </row>
-    <row r="15" outlineLevel="1" ht="15" customHeight="1">
+    <row r="15" outlineLevel="1" ht="14" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>2.1 Codificación de la sesión</t>
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
       <c r="C15" s="22" t="n"/>
       <c r="D15" s="22" t="n"/>
-      <c r="E15" s="22" t="n"/>
+      <c r="E15" s="21" t="n"/>
       <c r="F15" s="22" t="n"/>
       <c r="G15" s="22" t="n"/>
       <c r="H15" s="22" t="n"/>
       <c r="I15" s="22" t="n"/>
       <c r="J15" s="22" t="n"/>
       <c r="K15" s="22" t="n"/>
-      <c r="L15" s="26" t="n"/>
+      <c r="L15" s="22" t="n"/>
       <c r="M15" s="22" t="n"/>
       <c r="N15" s="22" t="n"/>
       <c r="O15" s="22" t="n"/>
@@ -1461,23 +1381,23 @@
         </is>
       </c>
     </row>
-    <row r="16" outlineLevel="1" ht="15" customHeight="1">
+    <row r="16" outlineLevel="1" ht="14" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>2.2 Creación del formulario</t>
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
       <c r="C16" s="22" t="n"/>
       <c r="D16" s="22" t="n"/>
       <c r="E16" s="22" t="n"/>
-      <c r="F16" s="22" t="n"/>
+      <c r="F16" s="21" t="n"/>
       <c r="G16" s="22" t="n"/>
       <c r="H16" s="22" t="n"/>
       <c r="I16" s="22" t="n"/>
       <c r="J16" s="22" t="n"/>
       <c r="K16" s="22" t="n"/>
-      <c r="L16" s="26" t="n"/>
+      <c r="L16" s="22" t="n"/>
       <c r="M16" s="22" t="n"/>
       <c r="N16" s="22" t="n"/>
       <c r="O16" s="22" t="n"/>
@@ -1501,24 +1421,24 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>Perfil, contraseña y baja</t>
+    <row r="17" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>2.3 Validación del formulario</t>
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
       <c r="C17" s="22" t="n"/>
       <c r="D17" s="22" t="n"/>
       <c r="E17" s="22" t="n"/>
-      <c r="F17" s="22" t="n"/>
+      <c r="F17" s="21" t="n"/>
       <c r="G17" s="22" t="n"/>
       <c r="H17" s="22" t="n"/>
       <c r="I17" s="22" t="n"/>
       <c r="J17" s="22" t="n"/>
       <c r="K17" s="22" t="n"/>
       <c r="L17" s="22" t="n"/>
-      <c r="M17" s="27" t="n"/>
+      <c r="M17" s="22" t="n"/>
       <c r="N17" s="22" t="n"/>
       <c r="O17" s="22" t="n"/>
       <c r="P17" s="22" t="n"/>
@@ -1541,10 +1461,10 @@
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="15" customHeight="1">
+    <row r="18" outlineLevel="1" ht="14" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>2.4 Testeo</t>
         </is>
       </c>
       <c r="B18" s="22" t="n"/>
@@ -1554,14 +1474,14 @@
       <c r="F18" s="22" t="n"/>
       <c r="G18" s="22" t="n"/>
       <c r="H18" s="22" t="n"/>
-      <c r="I18" s="22" t="n"/>
+      <c r="I18" s="21" t="n"/>
       <c r="J18" s="22" t="n"/>
       <c r="K18" s="22" t="n"/>
       <c r="L18" s="22" t="n"/>
       <c r="M18" s="22" t="n"/>
       <c r="N18" s="22" t="n"/>
       <c r="O18" s="22" t="n"/>
-      <c r="P18" s="27" t="n"/>
+      <c r="P18" s="22" t="n"/>
       <c r="Q18" s="22" t="n"/>
       <c r="R18" s="22" t="n"/>
       <c r="S18" s="22" t="n"/>
@@ -1581,10 +1501,10 @@
         </is>
       </c>
     </row>
-    <row r="19" outlineLevel="1" ht="15" customHeight="1">
+    <row r="19" outlineLevel="1" ht="14" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>2.5 Documentación</t>
         </is>
       </c>
       <c r="B19" s="22" t="n"/>
@@ -1594,14 +1514,14 @@
       <c r="F19" s="22" t="n"/>
       <c r="G19" s="22" t="n"/>
       <c r="H19" s="22" t="n"/>
-      <c r="I19" s="22" t="n"/>
+      <c r="I19" s="21" t="n"/>
       <c r="J19" s="22" t="n"/>
       <c r="K19" s="22" t="n"/>
       <c r="L19" s="22" t="n"/>
       <c r="M19" s="22" t="n"/>
       <c r="N19" s="22" t="n"/>
       <c r="O19" s="22" t="n"/>
-      <c r="P19" s="27" t="n"/>
+      <c r="P19" s="22" t="n"/>
       <c r="Q19" s="22" t="n"/>
       <c r="R19" s="22" t="n"/>
       <c r="S19" s="22" t="n"/>
@@ -1621,10 +1541,10 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Actividades y horario</t>
+          <t>3. Recuperación de cuenta y tickets</t>
         </is>
       </c>
       <c r="B20" s="22" t="n"/>
@@ -1635,15 +1555,15 @@
       <c r="G20" s="22" t="n"/>
       <c r="H20" s="22" t="n"/>
       <c r="I20" s="22" t="n"/>
-      <c r="J20" s="22" t="n"/>
-      <c r="K20" s="22" t="n"/>
-      <c r="L20" s="22" t="n"/>
+      <c r="J20" s="21" t="n"/>
+      <c r="K20" s="21" t="n"/>
+      <c r="L20" s="21" t="n"/>
       <c r="M20" s="22" t="n"/>
       <c r="N20" s="22" t="n"/>
       <c r="O20" s="22" t="n"/>
       <c r="P20" s="22" t="n"/>
-      <c r="Q20" s="28" t="n"/>
-      <c r="R20" s="28" t="n"/>
+      <c r="Q20" s="22" t="n"/>
+      <c r="R20" s="22" t="n"/>
       <c r="S20" s="22" t="n"/>
       <c r="T20" s="22" t="n"/>
       <c r="U20" s="22" t="n"/>
@@ -1655,16 +1575,16 @@
       <c r="AA20" s="22" t="n"/>
       <c r="AB20" s="22" t="n"/>
       <c r="AC20" s="22" t="n"/>
-      <c r="AD20" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD20" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" outlineLevel="1" ht="14" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>3.1 Formulario de recuperación</t>
         </is>
       </c>
       <c r="B21" s="22" t="n"/>
@@ -1675,7 +1595,7 @@
       <c r="G21" s="22" t="n"/>
       <c r="H21" s="22" t="n"/>
       <c r="I21" s="22" t="n"/>
-      <c r="J21" s="22" t="n"/>
+      <c r="J21" s="21" t="n"/>
       <c r="K21" s="22" t="n"/>
       <c r="L21" s="22" t="n"/>
       <c r="M21" s="22" t="n"/>
@@ -1684,7 +1604,7 @@
       <c r="P21" s="22" t="n"/>
       <c r="Q21" s="22" t="n"/>
       <c r="R21" s="22" t="n"/>
-      <c r="S21" s="28" t="n"/>
+      <c r="S21" s="22" t="n"/>
       <c r="T21" s="22" t="n"/>
       <c r="U21" s="22" t="n"/>
       <c r="V21" s="22" t="n"/>
@@ -1695,16 +1615,16 @@
       <c r="AA21" s="22" t="n"/>
       <c r="AB21" s="22" t="n"/>
       <c r="AC21" s="22" t="n"/>
-      <c r="AD21" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD21" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1" ht="14" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>3.2 Tickets de la cuenta</t>
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
@@ -1716,7 +1636,7 @@
       <c r="H22" s="22" t="n"/>
       <c r="I22" s="22" t="n"/>
       <c r="J22" s="22" t="n"/>
-      <c r="K22" s="22" t="n"/>
+      <c r="K22" s="21" t="n"/>
       <c r="L22" s="22" t="n"/>
       <c r="M22" s="22" t="n"/>
       <c r="N22" s="22" t="n"/>
@@ -1724,7 +1644,7 @@
       <c r="P22" s="22" t="n"/>
       <c r="Q22" s="22" t="n"/>
       <c r="R22" s="22" t="n"/>
-      <c r="S22" s="28" t="n"/>
+      <c r="S22" s="22" t="n"/>
       <c r="T22" s="22" t="n"/>
       <c r="U22" s="22" t="n"/>
       <c r="V22" s="22" t="n"/>
@@ -1735,16 +1655,16 @@
       <c r="AA22" s="22" t="n"/>
       <c r="AB22" s="22" t="n"/>
       <c r="AC22" s="22" t="n"/>
-      <c r="AD22" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Inscripciones y reservas</t>
+      <c r="AD22" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>3.3 Envío del enlace</t>
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
@@ -1756,7 +1676,7 @@
       <c r="H23" s="22" t="n"/>
       <c r="I23" s="22" t="n"/>
       <c r="J23" s="22" t="n"/>
-      <c r="K23" s="22" t="n"/>
+      <c r="K23" s="21" t="n"/>
       <c r="L23" s="22" t="n"/>
       <c r="M23" s="22" t="n"/>
       <c r="N23" s="22" t="n"/>
@@ -1765,26 +1685,26 @@
       <c r="Q23" s="22" t="n"/>
       <c r="R23" s="22" t="n"/>
       <c r="S23" s="22" t="n"/>
-      <c r="T23" s="21" t="n"/>
-      <c r="U23" s="21" t="n"/>
-      <c r="V23" s="21" t="n"/>
-      <c r="W23" s="21" t="n"/>
+      <c r="T23" s="22" t="n"/>
+      <c r="U23" s="22" t="n"/>
+      <c r="V23" s="22" t="n"/>
+      <c r="W23" s="22" t="n"/>
       <c r="X23" s="22" t="n"/>
       <c r="Y23" s="22" t="n"/>
       <c r="Z23" s="22" t="n"/>
       <c r="AA23" s="22" t="n"/>
       <c r="AB23" s="22" t="n"/>
       <c r="AC23" s="22" t="n"/>
-      <c r="AD23" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD23" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" outlineLevel="1" ht="14" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>3.4 Testeo</t>
         </is>
       </c>
       <c r="B24" s="22" t="n"/>
@@ -1797,7 +1717,7 @@
       <c r="I24" s="22" t="n"/>
       <c r="J24" s="22" t="n"/>
       <c r="K24" s="22" t="n"/>
-      <c r="L24" s="22" t="n"/>
+      <c r="L24" s="21" t="n"/>
       <c r="M24" s="22" t="n"/>
       <c r="N24" s="22" t="n"/>
       <c r="O24" s="22" t="n"/>
@@ -1809,22 +1729,22 @@
       <c r="U24" s="22" t="n"/>
       <c r="V24" s="22" t="n"/>
       <c r="W24" s="22" t="n"/>
-      <c r="X24" s="21" t="n"/>
+      <c r="X24" s="22" t="n"/>
       <c r="Y24" s="22" t="n"/>
       <c r="Z24" s="22" t="n"/>
       <c r="AA24" s="22" t="n"/>
       <c r="AB24" s="22" t="n"/>
       <c r="AC24" s="22" t="n"/>
-      <c r="AD24" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD24" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" outlineLevel="1" ht="14" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>3.5 Documentación</t>
         </is>
       </c>
       <c r="B25" s="22" t="n"/>
@@ -1837,7 +1757,7 @@
       <c r="I25" s="22" t="n"/>
       <c r="J25" s="22" t="n"/>
       <c r="K25" s="22" t="n"/>
-      <c r="L25" s="22" t="n"/>
+      <c r="L25" s="21" t="n"/>
       <c r="M25" s="22" t="n"/>
       <c r="N25" s="22" t="n"/>
       <c r="O25" s="22" t="n"/>
@@ -1849,22 +1769,22 @@
       <c r="U25" s="22" t="n"/>
       <c r="V25" s="22" t="n"/>
       <c r="W25" s="22" t="n"/>
-      <c r="X25" s="21" t="n"/>
+      <c r="X25" s="22" t="n"/>
       <c r="Y25" s="22" t="n"/>
       <c r="Z25" s="22" t="n"/>
       <c r="AA25" s="22" t="n"/>
       <c r="AB25" s="22" t="n"/>
       <c r="AC25" s="22" t="n"/>
-      <c r="AD25" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+      <c r="AD25" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>Suscripciones</t>
+          <t>4. Perfil, contraseña y baja</t>
         </is>
       </c>
       <c r="B26" s="22" t="n"/>
@@ -1878,10 +1798,10 @@
       <c r="J26" s="22" t="n"/>
       <c r="K26" s="22" t="n"/>
       <c r="L26" s="22" t="n"/>
-      <c r="M26" s="22" t="n"/>
-      <c r="N26" s="22" t="n"/>
-      <c r="O26" s="22" t="n"/>
-      <c r="P26" s="22" t="n"/>
+      <c r="M26" s="21" t="n"/>
+      <c r="N26" s="21" t="n"/>
+      <c r="O26" s="21" t="n"/>
+      <c r="P26" s="21" t="n"/>
       <c r="Q26" s="22" t="n"/>
       <c r="R26" s="22" t="n"/>
       <c r="S26" s="22" t="n"/>
@@ -1890,21 +1810,21 @@
       <c r="V26" s="22" t="n"/>
       <c r="W26" s="22" t="n"/>
       <c r="X26" s="22" t="n"/>
-      <c r="Y26" s="25" t="n"/>
+      <c r="Y26" s="22" t="n"/>
       <c r="Z26" s="22" t="n"/>
       <c r="AA26" s="22" t="n"/>
       <c r="AB26" s="22" t="n"/>
       <c r="AC26" s="22" t="n"/>
-      <c r="AD26" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD26" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1" ht="14" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>4.1 Edición del perfil</t>
         </is>
       </c>
       <c r="B27" s="22" t="n"/>
@@ -1918,7 +1838,7 @@
       <c r="J27" s="22" t="n"/>
       <c r="K27" s="22" t="n"/>
       <c r="L27" s="22" t="n"/>
-      <c r="M27" s="22" t="n"/>
+      <c r="M27" s="21" t="n"/>
       <c r="N27" s="22" t="n"/>
       <c r="O27" s="22" t="n"/>
       <c r="P27" s="22" t="n"/>
@@ -1931,20 +1851,20 @@
       <c r="W27" s="22" t="n"/>
       <c r="X27" s="22" t="n"/>
       <c r="Y27" s="22" t="n"/>
-      <c r="Z27" s="25" t="n"/>
+      <c r="Z27" s="22" t="n"/>
       <c r="AA27" s="22" t="n"/>
       <c r="AB27" s="22" t="n"/>
       <c r="AC27" s="22" t="n"/>
-      <c r="AD27" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD27" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" outlineLevel="1" ht="14" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>4.2 Cambio de contraseña</t>
         </is>
       </c>
       <c r="B28" s="22" t="n"/>
@@ -1958,7 +1878,7 @@
       <c r="J28" s="22" t="n"/>
       <c r="K28" s="22" t="n"/>
       <c r="L28" s="22" t="n"/>
-      <c r="M28" s="22" t="n"/>
+      <c r="M28" s="21" t="n"/>
       <c r="N28" s="22" t="n"/>
       <c r="O28" s="22" t="n"/>
       <c r="P28" s="22" t="n"/>
@@ -1971,20 +1891,20 @@
       <c r="W28" s="22" t="n"/>
       <c r="X28" s="22" t="n"/>
       <c r="Y28" s="22" t="n"/>
-      <c r="Z28" s="25" t="n"/>
+      <c r="Z28" s="22" t="n"/>
       <c r="AA28" s="22" t="n"/>
       <c r="AB28" s="22" t="n"/>
       <c r="AC28" s="22" t="n"/>
-      <c r="AD28" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>Pagos con Stripe</t>
+      <c r="AD28" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>4.3 Baja y reactivación</t>
         </is>
       </c>
       <c r="B29" s="22" t="n"/>
@@ -1998,7 +1918,7 @@
       <c r="J29" s="22" t="n"/>
       <c r="K29" s="22" t="n"/>
       <c r="L29" s="22" t="n"/>
-      <c r="M29" s="22" t="n"/>
+      <c r="M29" s="21" t="n"/>
       <c r="N29" s="22" t="n"/>
       <c r="O29" s="22" t="n"/>
       <c r="P29" s="22" t="n"/>
@@ -2012,19 +1932,19 @@
       <c r="X29" s="22" t="n"/>
       <c r="Y29" s="22" t="n"/>
       <c r="Z29" s="22" t="n"/>
-      <c r="AA29" s="26" t="n"/>
-      <c r="AB29" s="26" t="n"/>
-      <c r="AC29" s="26" t="n"/>
-      <c r="AD29" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AA29" s="22" t="n"/>
+      <c r="AB29" s="22" t="n"/>
+      <c r="AC29" s="22" t="n"/>
+      <c r="AD29" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1" ht="14" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>4.4 Testeo</t>
         </is>
       </c>
       <c r="B30" s="22" t="n"/>
@@ -2041,7 +1961,7 @@
       <c r="M30" s="22" t="n"/>
       <c r="N30" s="22" t="n"/>
       <c r="O30" s="22" t="n"/>
-      <c r="P30" s="22" t="n"/>
+      <c r="P30" s="21" t="n"/>
       <c r="Q30" s="22" t="n"/>
       <c r="R30" s="22" t="n"/>
       <c r="S30" s="22" t="n"/>
@@ -2055,16 +1975,16 @@
       <c r="AA30" s="22" t="n"/>
       <c r="AB30" s="22" t="n"/>
       <c r="AC30" s="22" t="n"/>
-      <c r="AD30" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD30" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1" ht="14" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>4.5 Documentación</t>
         </is>
       </c>
       <c r="B31" s="22" t="n"/>
@@ -2081,7 +2001,7 @@
       <c r="M31" s="22" t="n"/>
       <c r="N31" s="22" t="n"/>
       <c r="O31" s="22" t="n"/>
-      <c r="P31" s="22" t="n"/>
+      <c r="P31" s="21" t="n"/>
       <c r="Q31" s="22" t="n"/>
       <c r="R31" s="22" t="n"/>
       <c r="S31" s="22" t="n"/>
@@ -2095,16 +2015,16 @@
       <c r="AA31" s="22" t="n"/>
       <c r="AB31" s="22" t="n"/>
       <c r="AC31" s="22" t="n"/>
-      <c r="AD31" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+      <c r="AD31" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>Panel de administración</t>
+          <t>5. Actividades y horario</t>
         </is>
       </c>
       <c r="B32" s="22" t="n"/>
@@ -2122,9 +2042,9 @@
       <c r="N32" s="22" t="n"/>
       <c r="O32" s="22" t="n"/>
       <c r="P32" s="22" t="n"/>
-      <c r="Q32" s="22" t="n"/>
-      <c r="R32" s="22" t="n"/>
-      <c r="S32" s="22" t="n"/>
+      <c r="Q32" s="21" t="n"/>
+      <c r="R32" s="21" t="n"/>
+      <c r="S32" s="21" t="n"/>
       <c r="T32" s="22" t="n"/>
       <c r="U32" s="22" t="n"/>
       <c r="V32" s="22" t="n"/>
@@ -2135,16 +2055,16 @@
       <c r="AA32" s="22" t="n"/>
       <c r="AB32" s="22" t="n"/>
       <c r="AC32" s="22" t="n"/>
-      <c r="AD32" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD32" s="25" t="inlineStr">
+        <is>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1" ht="14" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>5.1 Listado de actividades</t>
         </is>
       </c>
       <c r="B33" s="22" t="n"/>
@@ -2162,7 +2082,7 @@
       <c r="N33" s="22" t="n"/>
       <c r="O33" s="22" t="n"/>
       <c r="P33" s="22" t="n"/>
-      <c r="Q33" s="22" t="n"/>
+      <c r="Q33" s="21" t="n"/>
       <c r="R33" s="22" t="n"/>
       <c r="S33" s="22" t="n"/>
       <c r="T33" s="22" t="n"/>
@@ -2175,16 +2095,16 @@
       <c r="AA33" s="22" t="n"/>
       <c r="AB33" s="22" t="n"/>
       <c r="AC33" s="22" t="n"/>
-      <c r="AD33" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD33" s="25" t="inlineStr">
+        <is>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1" ht="14" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>5.2 Horario del centro</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
@@ -2203,7 +2123,7 @@
       <c r="O34" s="22" t="n"/>
       <c r="P34" s="22" t="n"/>
       <c r="Q34" s="22" t="n"/>
-      <c r="R34" s="22" t="n"/>
+      <c r="R34" s="21" t="n"/>
       <c r="S34" s="22" t="n"/>
       <c r="T34" s="22" t="n"/>
       <c r="U34" s="22" t="n"/>
@@ -2215,16 +2135,16 @@
       <c r="AA34" s="22" t="n"/>
       <c r="AB34" s="22" t="n"/>
       <c r="AC34" s="22" t="n"/>
-      <c r="AD34" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>Gestión de clientes</t>
+      <c r="AD34" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>5.3 Alta y edición</t>
         </is>
       </c>
       <c r="B35" s="22" t="n"/>
@@ -2243,7 +2163,7 @@
       <c r="O35" s="22" t="n"/>
       <c r="P35" s="22" t="n"/>
       <c r="Q35" s="22" t="n"/>
-      <c r="R35" s="22" t="n"/>
+      <c r="R35" s="21" t="n"/>
       <c r="S35" s="22" t="n"/>
       <c r="T35" s="22" t="n"/>
       <c r="U35" s="22" t="n"/>
@@ -2255,16 +2175,16 @@
       <c r="AA35" s="22" t="n"/>
       <c r="AB35" s="22" t="n"/>
       <c r="AC35" s="22" t="n"/>
-      <c r="AD35" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD35" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" outlineLevel="1" ht="14" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>5.4 Testeo</t>
         </is>
       </c>
       <c r="B36" s="22" t="n"/>
@@ -2284,7 +2204,7 @@
       <c r="P36" s="22" t="n"/>
       <c r="Q36" s="22" t="n"/>
       <c r="R36" s="22" t="n"/>
-      <c r="S36" s="22" t="n"/>
+      <c r="S36" s="21" t="n"/>
       <c r="T36" s="22" t="n"/>
       <c r="U36" s="22" t="n"/>
       <c r="V36" s="22" t="n"/>
@@ -2295,16 +2215,16 @@
       <c r="AA36" s="22" t="n"/>
       <c r="AB36" s="22" t="n"/>
       <c r="AC36" s="22" t="n"/>
-      <c r="AD36" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD36" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1" ht="14" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>5.5 Documentación</t>
         </is>
       </c>
       <c r="B37" s="22" t="n"/>
@@ -2324,7 +2244,7 @@
       <c r="P37" s="22" t="n"/>
       <c r="Q37" s="22" t="n"/>
       <c r="R37" s="22" t="n"/>
-      <c r="S37" s="22" t="n"/>
+      <c r="S37" s="21" t="n"/>
       <c r="T37" s="22" t="n"/>
       <c r="U37" s="22" t="n"/>
       <c r="V37" s="22" t="n"/>
@@ -2335,16 +2255,16 @@
       <c r="AA37" s="22" t="n"/>
       <c r="AB37" s="22" t="n"/>
       <c r="AC37" s="22" t="n"/>
-      <c r="AD37" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
+      <c r="AD37" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>Monitores y solicitudes</t>
+          <t>6. Inscripciones y reservas</t>
         </is>
       </c>
       <c r="B38" s="22" t="n"/>
@@ -2365,26 +2285,26 @@
       <c r="Q38" s="22" t="n"/>
       <c r="R38" s="22" t="n"/>
       <c r="S38" s="22" t="n"/>
-      <c r="T38" s="22" t="n"/>
-      <c r="U38" s="22" t="n"/>
-      <c r="V38" s="22" t="n"/>
-      <c r="W38" s="22" t="n"/>
-      <c r="X38" s="22" t="n"/>
+      <c r="T38" s="21" t="n"/>
+      <c r="U38" s="21" t="n"/>
+      <c r="V38" s="21" t="n"/>
+      <c r="W38" s="21" t="n"/>
+      <c r="X38" s="21" t="n"/>
       <c r="Y38" s="22" t="n"/>
       <c r="Z38" s="22" t="n"/>
       <c r="AA38" s="22" t="n"/>
       <c r="AB38" s="22" t="n"/>
       <c r="AC38" s="22" t="n"/>
-      <c r="AD38" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD38" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" outlineLevel="1" ht="14" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>6.1 Formulario de inscripción</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -2405,7 +2325,7 @@
       <c r="Q39" s="22" t="n"/>
       <c r="R39" s="22" t="n"/>
       <c r="S39" s="22" t="n"/>
-      <c r="T39" s="22" t="n"/>
+      <c r="T39" s="21" t="n"/>
       <c r="U39" s="22" t="n"/>
       <c r="V39" s="22" t="n"/>
       <c r="W39" s="22" t="n"/>
@@ -2415,16 +2335,16 @@
       <c r="AA39" s="22" t="n"/>
       <c r="AB39" s="22" t="n"/>
       <c r="AC39" s="22" t="n"/>
-      <c r="AD39" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD39" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" outlineLevel="1" ht="14" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>6.2 Control de plazas</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -2448,23 +2368,23 @@
       <c r="T40" s="22" t="n"/>
       <c r="U40" s="22" t="n"/>
       <c r="V40" s="22" t="n"/>
-      <c r="W40" s="22" t="n"/>
+      <c r="W40" s="21" t="n"/>
       <c r="X40" s="22" t="n"/>
       <c r="Y40" s="22" t="n"/>
       <c r="Z40" s="22" t="n"/>
       <c r="AA40" s="22" t="n"/>
       <c r="AB40" s="22" t="n"/>
       <c r="AC40" s="22" t="n"/>
-      <c r="AD40" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>Salas y materiales</t>
+      <c r="AD40" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>6.3 Reservas del cliente</t>
         </is>
       </c>
       <c r="B41" s="22" t="n"/>
@@ -2488,23 +2408,23 @@
       <c r="T41" s="22" t="n"/>
       <c r="U41" s="22" t="n"/>
       <c r="V41" s="22" t="n"/>
-      <c r="W41" s="22" t="n"/>
+      <c r="W41" s="21" t="n"/>
       <c r="X41" s="22" t="n"/>
       <c r="Y41" s="22" t="n"/>
       <c r="Z41" s="22" t="n"/>
       <c r="AA41" s="22" t="n"/>
       <c r="AB41" s="22" t="n"/>
       <c r="AC41" s="22" t="n"/>
-      <c r="AD41" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD41" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" outlineLevel="1" ht="14" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>6.4 Testeo</t>
         </is>
       </c>
       <c r="B42" s="22" t="n"/>
@@ -2529,22 +2449,22 @@
       <c r="U42" s="22" t="n"/>
       <c r="V42" s="22" t="n"/>
       <c r="W42" s="22" t="n"/>
-      <c r="X42" s="22" t="n"/>
+      <c r="X42" s="21" t="n"/>
       <c r="Y42" s="22" t="n"/>
       <c r="Z42" s="22" t="n"/>
       <c r="AA42" s="22" t="n"/>
       <c r="AB42" s="22" t="n"/>
       <c r="AC42" s="22" t="n"/>
-      <c r="AD42" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD42" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" outlineLevel="1" ht="14" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>6.5 Documentación</t>
         </is>
       </c>
       <c r="B43" s="22" t="n"/>
@@ -2569,22 +2489,22 @@
       <c r="U43" s="22" t="n"/>
       <c r="V43" s="22" t="n"/>
       <c r="W43" s="22" t="n"/>
-      <c r="X43" s="22" t="n"/>
+      <c r="X43" s="21" t="n"/>
       <c r="Y43" s="22" t="n"/>
       <c r="Z43" s="22" t="n"/>
       <c r="AA43" s="22" t="n"/>
       <c r="AB43" s="22" t="n"/>
       <c r="AC43" s="22" t="n"/>
-      <c r="AD43" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
+      <c r="AD43" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>Fisioterapia y citas</t>
+          <t>7. Suscripciones</t>
         </is>
       </c>
       <c r="B44" s="22" t="n"/>
@@ -2610,21 +2530,21 @@
       <c r="V44" s="22" t="n"/>
       <c r="W44" s="22" t="n"/>
       <c r="X44" s="22" t="n"/>
-      <c r="Y44" s="22" t="n"/>
-      <c r="Z44" s="22" t="n"/>
+      <c r="Y44" s="21" t="n"/>
+      <c r="Z44" s="21" t="n"/>
       <c r="AA44" s="22" t="n"/>
       <c r="AB44" s="22" t="n"/>
       <c r="AC44" s="22" t="n"/>
-      <c r="AD44" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD44" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" outlineLevel="1" ht="14" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>7.1 Planes de suscripción</t>
         </is>
       </c>
       <c r="B45" s="22" t="n"/>
@@ -2650,21 +2570,21 @@
       <c r="V45" s="22" t="n"/>
       <c r="W45" s="22" t="n"/>
       <c r="X45" s="22" t="n"/>
-      <c r="Y45" s="22" t="n"/>
+      <c r="Y45" s="21" t="n"/>
       <c r="Z45" s="22" t="n"/>
       <c r="AA45" s="22" t="n"/>
       <c r="AB45" s="22" t="n"/>
       <c r="AC45" s="22" t="n"/>
-      <c r="AD45" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD45" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1" ht="14" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>7.2 Alta del cliente</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -2690,21 +2610,21 @@
       <c r="V46" s="22" t="n"/>
       <c r="W46" s="22" t="n"/>
       <c r="X46" s="22" t="n"/>
-      <c r="Y46" s="22" t="n"/>
+      <c r="Y46" s="21" t="n"/>
       <c r="Z46" s="22" t="n"/>
       <c r="AA46" s="22" t="n"/>
       <c r="AB46" s="22" t="n"/>
       <c r="AC46" s="22" t="n"/>
-      <c r="AD46" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>Comentarios, feedback y seguridad</t>
+      <c r="AD46" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>7.3 Renovación y baja</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -2730,21 +2650,21 @@
       <c r="V47" s="22" t="n"/>
       <c r="W47" s="22" t="n"/>
       <c r="X47" s="22" t="n"/>
-      <c r="Y47" s="22" t="n"/>
+      <c r="Y47" s="21" t="n"/>
       <c r="Z47" s="22" t="n"/>
       <c r="AA47" s="22" t="n"/>
       <c r="AB47" s="22" t="n"/>
       <c r="AC47" s="22" t="n"/>
-      <c r="AD47" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD47" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1" ht="14" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>7.4 Testeo</t>
         </is>
       </c>
       <c r="B48" s="22" t="n"/>
@@ -2771,20 +2691,20 @@
       <c r="W48" s="22" t="n"/>
       <c r="X48" s="22" t="n"/>
       <c r="Y48" s="22" t="n"/>
-      <c r="Z48" s="22" t="n"/>
+      <c r="Z48" s="21" t="n"/>
       <c r="AA48" s="22" t="n"/>
       <c r="AB48" s="22" t="n"/>
       <c r="AC48" s="22" t="n"/>
-      <c r="AD48" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD48" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1" ht="14" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>7.5 Documentación</t>
         </is>
       </c>
       <c r="B49" s="22" t="n"/>
@@ -2811,20 +2731,20 @@
       <c r="W49" s="22" t="n"/>
       <c r="X49" s="22" t="n"/>
       <c r="Y49" s="22" t="n"/>
-      <c r="Z49" s="22" t="n"/>
+      <c r="Z49" s="21" t="n"/>
       <c r="AA49" s="22" t="n"/>
       <c r="AB49" s="22" t="n"/>
       <c r="AC49" s="22" t="n"/>
-      <c r="AD49" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
+      <c r="AD49" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>Interfaz Tailwind, correo y cierre</t>
+          <t>8. Pagos con Stripe</t>
         </is>
       </c>
       <c r="B50" s="22" t="n"/>
@@ -2852,19 +2772,19 @@
       <c r="X50" s="22" t="n"/>
       <c r="Y50" s="22" t="n"/>
       <c r="Z50" s="22" t="n"/>
-      <c r="AA50" s="22" t="n"/>
-      <c r="AB50" s="22" t="n"/>
-      <c r="AC50" s="22" t="n"/>
-      <c r="AD50" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AA50" s="21" t="n"/>
+      <c r="AB50" s="21" t="n"/>
+      <c r="AC50" s="21" t="n"/>
+      <c r="AD50" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1" ht="14" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>8.1 Pasarela de Stripe</t>
         </is>
       </c>
       <c r="B51" s="22" t="n"/>
@@ -2892,19 +2812,19 @@
       <c r="X51" s="22" t="n"/>
       <c r="Y51" s="22" t="n"/>
       <c r="Z51" s="22" t="n"/>
-      <c r="AA51" s="22" t="n"/>
+      <c r="AA51" s="21" t="n"/>
       <c r="AB51" s="22" t="n"/>
       <c r="AC51" s="22" t="n"/>
-      <c r="AD51" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD51" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" outlineLevel="1" ht="14" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>8.2 Confirmación del pago</t>
         </is>
       </c>
       <c r="B52" s="22" t="n"/>
@@ -2935,203 +2855,1939 @@
       <c r="AA52" s="22" t="n"/>
       <c r="AB52" s="22" t="n"/>
       <c r="AC52" s="22" t="n"/>
-      <c r="AD52" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="31" t="n"/>
-      <c r="B53" s="32" t="n"/>
-      <c r="C53" s="32" t="n"/>
-      <c r="D53" s="32" t="n"/>
-      <c r="E53" s="32" t="n"/>
-      <c r="F53" s="32" t="n"/>
-      <c r="G53" s="32" t="n"/>
-      <c r="H53" s="32" t="n"/>
-      <c r="I53" s="32" t="n"/>
-      <c r="J53" s="32" t="n"/>
-      <c r="K53" s="32" t="n"/>
-      <c r="L53" s="32" t="n"/>
-      <c r="M53" s="32" t="n"/>
-      <c r="N53" s="32" t="n"/>
-      <c r="O53" s="32" t="n"/>
-      <c r="P53" s="32" t="n"/>
-      <c r="Q53" s="32" t="n"/>
-      <c r="R53" s="32" t="n"/>
-      <c r="S53" s="32" t="n"/>
-      <c r="T53" s="32" t="n"/>
-      <c r="U53" s="32" t="n"/>
-      <c r="V53" s="32" t="n"/>
-      <c r="W53" s="32" t="n"/>
-      <c r="X53" s="32" t="n"/>
-      <c r="Y53" s="32" t="n"/>
-      <c r="Z53" s="32" t="n"/>
-      <c r="AA53" s="32" t="n"/>
-      <c r="AB53" s="32" t="n"/>
-      <c r="AC53" s="32" t="n"/>
-      <c r="AD53" s="32" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="31" t="n"/>
-      <c r="B54" s="32" t="n"/>
-      <c r="C54" s="32" t="n"/>
-      <c r="D54" s="32" t="n"/>
-      <c r="E54" s="32" t="n"/>
-      <c r="F54" s="32" t="n"/>
-      <c r="G54" s="32" t="n"/>
-      <c r="H54" s="32" t="n"/>
-      <c r="I54" s="32" t="n"/>
-      <c r="J54" s="32" t="n"/>
-      <c r="K54" s="32" t="n"/>
-      <c r="L54" s="32" t="n"/>
-      <c r="M54" s="32" t="n"/>
-      <c r="N54" s="32" t="n"/>
-      <c r="O54" s="32" t="n"/>
-      <c r="P54" s="32" t="n"/>
-      <c r="Q54" s="32" t="n"/>
-      <c r="R54" s="32" t="n"/>
-      <c r="S54" s="32" t="n"/>
-      <c r="T54" s="32" t="n"/>
-      <c r="U54" s="32" t="n"/>
-      <c r="V54" s="32" t="n"/>
-      <c r="W54" s="32" t="n"/>
-      <c r="X54" s="32" t="n"/>
-      <c r="Y54" s="32" t="n"/>
-      <c r="Z54" s="32" t="n"/>
-      <c r="AA54" s="32" t="n"/>
-      <c r="AB54" s="32" t="n"/>
-      <c r="AC54" s="32" t="n"/>
-      <c r="AD54" s="32" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="31" t="n"/>
-      <c r="B55" s="32" t="n"/>
-      <c r="C55" s="32" t="n"/>
-      <c r="D55" s="32" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
-      <c r="G55" s="32" t="n"/>
-      <c r="H55" s="32" t="n"/>
-      <c r="I55" s="32" t="n"/>
-      <c r="J55" s="32" t="n"/>
-      <c r="K55" s="32" t="n"/>
-      <c r="L55" s="32" t="n"/>
-      <c r="M55" s="32" t="n"/>
-      <c r="N55" s="32" t="n"/>
-      <c r="O55" s="32" t="n"/>
-      <c r="P55" s="32" t="n"/>
-      <c r="Q55" s="32" t="n"/>
-      <c r="R55" s="32" t="n"/>
-      <c r="S55" s="32" t="n"/>
-      <c r="T55" s="32" t="n"/>
-      <c r="U55" s="32" t="n"/>
-      <c r="V55" s="32" t="n"/>
-      <c r="W55" s="32" t="n"/>
-      <c r="X55" s="32" t="n"/>
-      <c r="Y55" s="32" t="n"/>
-      <c r="Z55" s="32" t="n"/>
-      <c r="AA55" s="32" t="n"/>
-      <c r="AB55" s="32" t="n"/>
-      <c r="AC55" s="32" t="n"/>
-      <c r="AD55" s="32" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="31" t="n"/>
-      <c r="B56" s="32" t="n"/>
-      <c r="C56" s="32" t="n"/>
-      <c r="D56" s="32" t="n"/>
-      <c r="E56" s="32" t="n"/>
-      <c r="F56" s="32" t="n"/>
-      <c r="G56" s="32" t="n"/>
-      <c r="H56" s="32" t="n"/>
-      <c r="I56" s="32" t="n"/>
-      <c r="J56" s="32" t="n"/>
-      <c r="K56" s="32" t="n"/>
-      <c r="L56" s="32" t="n"/>
-      <c r="M56" s="32" t="n"/>
-      <c r="N56" s="32" t="n"/>
-      <c r="O56" s="32" t="n"/>
-      <c r="P56" s="32" t="n"/>
-      <c r="Q56" s="32" t="n"/>
-      <c r="R56" s="32" t="n"/>
-      <c r="S56" s="32" t="n"/>
-      <c r="T56" s="32" t="n"/>
-      <c r="U56" s="32" t="n"/>
-      <c r="V56" s="32" t="n"/>
-      <c r="W56" s="32" t="n"/>
-      <c r="X56" s="32" t="n"/>
-      <c r="Y56" s="32" t="n"/>
-      <c r="Z56" s="32" t="n"/>
-      <c r="AA56" s="32" t="n"/>
-      <c r="AB56" s="32" t="n"/>
-      <c r="AC56" s="32" t="n"/>
-      <c r="AD56" s="32" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="31" t="n"/>
-      <c r="B57" s="32" t="n"/>
-      <c r="C57" s="32" t="n"/>
-      <c r="D57" s="32" t="n"/>
-      <c r="E57" s="32" t="n"/>
-      <c r="F57" s="32" t="n"/>
-      <c r="G57" s="32" t="n"/>
-      <c r="H57" s="32" t="n"/>
-      <c r="I57" s="32" t="n"/>
-      <c r="J57" s="32" t="n"/>
-      <c r="K57" s="32" t="n"/>
-      <c r="L57" s="32" t="n"/>
-      <c r="M57" s="32" t="n"/>
-      <c r="N57" s="32" t="n"/>
-      <c r="O57" s="32" t="n"/>
-      <c r="P57" s="32" t="n"/>
-      <c r="Q57" s="32" t="n"/>
-      <c r="R57" s="32" t="n"/>
-      <c r="S57" s="32" t="n"/>
-      <c r="T57" s="32" t="n"/>
-      <c r="U57" s="32" t="n"/>
-      <c r="V57" s="32" t="n"/>
-      <c r="W57" s="32" t="n"/>
-      <c r="X57" s="32" t="n"/>
-      <c r="Y57" s="32" t="n"/>
-      <c r="Z57" s="32" t="n"/>
-      <c r="AA57" s="32" t="n"/>
-      <c r="AB57" s="32" t="n"/>
-      <c r="AC57" s="32" t="n"/>
-      <c r="AD57" s="32" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="31" t="n"/>
-      <c r="B58" s="32" t="n"/>
-      <c r="C58" s="32" t="n"/>
-      <c r="D58" s="32" t="n"/>
-      <c r="E58" s="32" t="n"/>
-      <c r="F58" s="32" t="n"/>
-      <c r="G58" s="32" t="n"/>
-      <c r="H58" s="32" t="n"/>
-      <c r="I58" s="32" t="n"/>
-      <c r="J58" s="32" t="n"/>
-      <c r="K58" s="32" t="n"/>
-      <c r="L58" s="32" t="n"/>
-      <c r="M58" s="32" t="n"/>
-      <c r="N58" s="32" t="n"/>
-      <c r="O58" s="32" t="n"/>
-      <c r="P58" s="32" t="n"/>
-      <c r="Q58" s="32" t="n"/>
-      <c r="R58" s="32" t="n"/>
-      <c r="S58" s="32" t="n"/>
-      <c r="T58" s="32" t="n"/>
-      <c r="U58" s="32" t="n"/>
-      <c r="V58" s="32" t="n"/>
-      <c r="W58" s="32" t="n"/>
-      <c r="X58" s="32" t="n"/>
-      <c r="Y58" s="32" t="n"/>
-      <c r="Z58" s="32" t="n"/>
-      <c r="AA58" s="32" t="n"/>
-      <c r="AB58" s="32" t="n"/>
-      <c r="AC58" s="32" t="n"/>
-      <c r="AD58" s="32" t="n"/>
+      <c r="AD52" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>8.3 Pago cancelado</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="22" t="n"/>
+      <c r="F53" s="22" t="n"/>
+      <c r="G53" s="22" t="n"/>
+      <c r="H53" s="22" t="n"/>
+      <c r="I53" s="22" t="n"/>
+      <c r="J53" s="22" t="n"/>
+      <c r="K53" s="22" t="n"/>
+      <c r="L53" s="22" t="n"/>
+      <c r="M53" s="22" t="n"/>
+      <c r="N53" s="22" t="n"/>
+      <c r="O53" s="22" t="n"/>
+      <c r="P53" s="22" t="n"/>
+      <c r="Q53" s="22" t="n"/>
+      <c r="R53" s="22" t="n"/>
+      <c r="S53" s="22" t="n"/>
+      <c r="T53" s="22" t="n"/>
+      <c r="U53" s="22" t="n"/>
+      <c r="V53" s="22" t="n"/>
+      <c r="W53" s="22" t="n"/>
+      <c r="X53" s="22" t="n"/>
+      <c r="Y53" s="22" t="n"/>
+      <c r="Z53" s="22" t="n"/>
+      <c r="AA53" s="22" t="n"/>
+      <c r="AB53" s="22" t="n"/>
+      <c r="AC53" s="22" t="n"/>
+      <c r="AD53" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>8.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
+      <c r="G54" s="22" t="n"/>
+      <c r="H54" s="22" t="n"/>
+      <c r="I54" s="22" t="n"/>
+      <c r="J54" s="22" t="n"/>
+      <c r="K54" s="22" t="n"/>
+      <c r="L54" s="22" t="n"/>
+      <c r="M54" s="22" t="n"/>
+      <c r="N54" s="22" t="n"/>
+      <c r="O54" s="22" t="n"/>
+      <c r="P54" s="22" t="n"/>
+      <c r="Q54" s="22" t="n"/>
+      <c r="R54" s="22" t="n"/>
+      <c r="S54" s="22" t="n"/>
+      <c r="T54" s="22" t="n"/>
+      <c r="U54" s="22" t="n"/>
+      <c r="V54" s="22" t="n"/>
+      <c r="W54" s="22" t="n"/>
+      <c r="X54" s="22" t="n"/>
+      <c r="Y54" s="22" t="n"/>
+      <c r="Z54" s="22" t="n"/>
+      <c r="AA54" s="22" t="n"/>
+      <c r="AB54" s="22" t="n"/>
+      <c r="AC54" s="22" t="n"/>
+      <c r="AD54" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>8.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="n"/>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="22" t="n"/>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="22" t="n"/>
+      <c r="H55" s="22" t="n"/>
+      <c r="I55" s="22" t="n"/>
+      <c r="J55" s="22" t="n"/>
+      <c r="K55" s="22" t="n"/>
+      <c r="L55" s="22" t="n"/>
+      <c r="M55" s="22" t="n"/>
+      <c r="N55" s="22" t="n"/>
+      <c r="O55" s="22" t="n"/>
+      <c r="P55" s="22" t="n"/>
+      <c r="Q55" s="22" t="n"/>
+      <c r="R55" s="22" t="n"/>
+      <c r="S55" s="22" t="n"/>
+      <c r="T55" s="22" t="n"/>
+      <c r="U55" s="22" t="n"/>
+      <c r="V55" s="22" t="n"/>
+      <c r="W55" s="22" t="n"/>
+      <c r="X55" s="22" t="n"/>
+      <c r="Y55" s="22" t="n"/>
+      <c r="Z55" s="22" t="n"/>
+      <c r="AA55" s="22" t="n"/>
+      <c r="AB55" s="22" t="n"/>
+      <c r="AC55" s="22" t="n"/>
+      <c r="AD55" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>9. Panel de administración</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="n"/>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="22" t="n"/>
+      <c r="F56" s="22" t="n"/>
+      <c r="G56" s="22" t="n"/>
+      <c r="H56" s="22" t="n"/>
+      <c r="I56" s="22" t="n"/>
+      <c r="J56" s="22" t="n"/>
+      <c r="K56" s="22" t="n"/>
+      <c r="L56" s="22" t="n"/>
+      <c r="M56" s="22" t="n"/>
+      <c r="N56" s="22" t="n"/>
+      <c r="O56" s="22" t="n"/>
+      <c r="P56" s="22" t="n"/>
+      <c r="Q56" s="22" t="n"/>
+      <c r="R56" s="22" t="n"/>
+      <c r="S56" s="22" t="n"/>
+      <c r="T56" s="22" t="n"/>
+      <c r="U56" s="22" t="n"/>
+      <c r="V56" s="22" t="n"/>
+      <c r="W56" s="22" t="n"/>
+      <c r="X56" s="22" t="n"/>
+      <c r="Y56" s="22" t="n"/>
+      <c r="Z56" s="22" t="n"/>
+      <c r="AA56" s="22" t="n"/>
+      <c r="AB56" s="22" t="n"/>
+      <c r="AC56" s="22" t="n"/>
+      <c r="AD56" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>9.1 Inicio del panel</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="n"/>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="22" t="n"/>
+      <c r="E57" s="22" t="n"/>
+      <c r="F57" s="22" t="n"/>
+      <c r="G57" s="22" t="n"/>
+      <c r="H57" s="22" t="n"/>
+      <c r="I57" s="22" t="n"/>
+      <c r="J57" s="22" t="n"/>
+      <c r="K57" s="22" t="n"/>
+      <c r="L57" s="22" t="n"/>
+      <c r="M57" s="22" t="n"/>
+      <c r="N57" s="22" t="n"/>
+      <c r="O57" s="22" t="n"/>
+      <c r="P57" s="22" t="n"/>
+      <c r="Q57" s="22" t="n"/>
+      <c r="R57" s="22" t="n"/>
+      <c r="S57" s="22" t="n"/>
+      <c r="T57" s="22" t="n"/>
+      <c r="U57" s="22" t="n"/>
+      <c r="V57" s="22" t="n"/>
+      <c r="W57" s="22" t="n"/>
+      <c r="X57" s="22" t="n"/>
+      <c r="Y57" s="22" t="n"/>
+      <c r="Z57" s="22" t="n"/>
+      <c r="AA57" s="22" t="n"/>
+      <c r="AB57" s="22" t="n"/>
+      <c r="AC57" s="22" t="n"/>
+      <c r="AD57" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>9.2 Menú y permisos</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="n"/>
+      <c r="C58" s="22" t="n"/>
+      <c r="D58" s="22" t="n"/>
+      <c r="E58" s="22" t="n"/>
+      <c r="F58" s="22" t="n"/>
+      <c r="G58" s="22" t="n"/>
+      <c r="H58" s="22" t="n"/>
+      <c r="I58" s="22" t="n"/>
+      <c r="J58" s="22" t="n"/>
+      <c r="K58" s="22" t="n"/>
+      <c r="L58" s="22" t="n"/>
+      <c r="M58" s="22" t="n"/>
+      <c r="N58" s="22" t="n"/>
+      <c r="O58" s="22" t="n"/>
+      <c r="P58" s="22" t="n"/>
+      <c r="Q58" s="22" t="n"/>
+      <c r="R58" s="22" t="n"/>
+      <c r="S58" s="22" t="n"/>
+      <c r="T58" s="22" t="n"/>
+      <c r="U58" s="22" t="n"/>
+      <c r="V58" s="22" t="n"/>
+      <c r="W58" s="22" t="n"/>
+      <c r="X58" s="22" t="n"/>
+      <c r="Y58" s="22" t="n"/>
+      <c r="Z58" s="22" t="n"/>
+      <c r="AA58" s="22" t="n"/>
+      <c r="AB58" s="22" t="n"/>
+      <c r="AC58" s="22" t="n"/>
+      <c r="AD58" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>9.3 Listados del panel</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="n"/>
+      <c r="C59" s="22" t="n"/>
+      <c r="D59" s="22" t="n"/>
+      <c r="E59" s="22" t="n"/>
+      <c r="F59" s="22" t="n"/>
+      <c r="G59" s="22" t="n"/>
+      <c r="H59" s="22" t="n"/>
+      <c r="I59" s="22" t="n"/>
+      <c r="J59" s="22" t="n"/>
+      <c r="K59" s="22" t="n"/>
+      <c r="L59" s="22" t="n"/>
+      <c r="M59" s="22" t="n"/>
+      <c r="N59" s="22" t="n"/>
+      <c r="O59" s="22" t="n"/>
+      <c r="P59" s="22" t="n"/>
+      <c r="Q59" s="22" t="n"/>
+      <c r="R59" s="22" t="n"/>
+      <c r="S59" s="22" t="n"/>
+      <c r="T59" s="22" t="n"/>
+      <c r="U59" s="22" t="n"/>
+      <c r="V59" s="22" t="n"/>
+      <c r="W59" s="22" t="n"/>
+      <c r="X59" s="22" t="n"/>
+      <c r="Y59" s="22" t="n"/>
+      <c r="Z59" s="22" t="n"/>
+      <c r="AA59" s="22" t="n"/>
+      <c r="AB59" s="22" t="n"/>
+      <c r="AC59" s="22" t="n"/>
+      <c r="AD59" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>9.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="n"/>
+      <c r="C60" s="22" t="n"/>
+      <c r="D60" s="22" t="n"/>
+      <c r="E60" s="22" t="n"/>
+      <c r="F60" s="22" t="n"/>
+      <c r="G60" s="22" t="n"/>
+      <c r="H60" s="22" t="n"/>
+      <c r="I60" s="22" t="n"/>
+      <c r="J60" s="22" t="n"/>
+      <c r="K60" s="22" t="n"/>
+      <c r="L60" s="22" t="n"/>
+      <c r="M60" s="22" t="n"/>
+      <c r="N60" s="22" t="n"/>
+      <c r="O60" s="22" t="n"/>
+      <c r="P60" s="22" t="n"/>
+      <c r="Q60" s="22" t="n"/>
+      <c r="R60" s="22" t="n"/>
+      <c r="S60" s="22" t="n"/>
+      <c r="T60" s="22" t="n"/>
+      <c r="U60" s="22" t="n"/>
+      <c r="V60" s="22" t="n"/>
+      <c r="W60" s="22" t="n"/>
+      <c r="X60" s="22" t="n"/>
+      <c r="Y60" s="22" t="n"/>
+      <c r="Z60" s="22" t="n"/>
+      <c r="AA60" s="22" t="n"/>
+      <c r="AB60" s="22" t="n"/>
+      <c r="AC60" s="22" t="n"/>
+      <c r="AD60" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>9.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="n"/>
+      <c r="C61" s="22" t="n"/>
+      <c r="D61" s="22" t="n"/>
+      <c r="E61" s="22" t="n"/>
+      <c r="F61" s="22" t="n"/>
+      <c r="G61" s="22" t="n"/>
+      <c r="H61" s="22" t="n"/>
+      <c r="I61" s="22" t="n"/>
+      <c r="J61" s="22" t="n"/>
+      <c r="K61" s="22" t="n"/>
+      <c r="L61" s="22" t="n"/>
+      <c r="M61" s="22" t="n"/>
+      <c r="N61" s="22" t="n"/>
+      <c r="O61" s="22" t="n"/>
+      <c r="P61" s="22" t="n"/>
+      <c r="Q61" s="22" t="n"/>
+      <c r="R61" s="22" t="n"/>
+      <c r="S61" s="22" t="n"/>
+      <c r="T61" s="22" t="n"/>
+      <c r="U61" s="22" t="n"/>
+      <c r="V61" s="22" t="n"/>
+      <c r="W61" s="22" t="n"/>
+      <c r="X61" s="22" t="n"/>
+      <c r="Y61" s="22" t="n"/>
+      <c r="Z61" s="22" t="n"/>
+      <c r="AA61" s="22" t="n"/>
+      <c r="AB61" s="22" t="n"/>
+      <c r="AC61" s="22" t="n"/>
+      <c r="AD61" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>10. Gestión de clientes</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="n"/>
+      <c r="C62" s="22" t="n"/>
+      <c r="D62" s="22" t="n"/>
+      <c r="E62" s="22" t="n"/>
+      <c r="F62" s="22" t="n"/>
+      <c r="G62" s="22" t="n"/>
+      <c r="H62" s="22" t="n"/>
+      <c r="I62" s="22" t="n"/>
+      <c r="J62" s="22" t="n"/>
+      <c r="K62" s="22" t="n"/>
+      <c r="L62" s="22" t="n"/>
+      <c r="M62" s="22" t="n"/>
+      <c r="N62" s="22" t="n"/>
+      <c r="O62" s="22" t="n"/>
+      <c r="P62" s="22" t="n"/>
+      <c r="Q62" s="22" t="n"/>
+      <c r="R62" s="22" t="n"/>
+      <c r="S62" s="22" t="n"/>
+      <c r="T62" s="22" t="n"/>
+      <c r="U62" s="22" t="n"/>
+      <c r="V62" s="22" t="n"/>
+      <c r="W62" s="22" t="n"/>
+      <c r="X62" s="22" t="n"/>
+      <c r="Y62" s="22" t="n"/>
+      <c r="Z62" s="22" t="n"/>
+      <c r="AA62" s="22" t="n"/>
+      <c r="AB62" s="22" t="n"/>
+      <c r="AC62" s="22" t="n"/>
+      <c r="AD62" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>10.1 Listado de clientes</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="n"/>
+      <c r="C63" s="22" t="n"/>
+      <c r="D63" s="22" t="n"/>
+      <c r="E63" s="22" t="n"/>
+      <c r="F63" s="22" t="n"/>
+      <c r="G63" s="22" t="n"/>
+      <c r="H63" s="22" t="n"/>
+      <c r="I63" s="22" t="n"/>
+      <c r="J63" s="22" t="n"/>
+      <c r="K63" s="22" t="n"/>
+      <c r="L63" s="22" t="n"/>
+      <c r="M63" s="22" t="n"/>
+      <c r="N63" s="22" t="n"/>
+      <c r="O63" s="22" t="n"/>
+      <c r="P63" s="22" t="n"/>
+      <c r="Q63" s="22" t="n"/>
+      <c r="R63" s="22" t="n"/>
+      <c r="S63" s="22" t="n"/>
+      <c r="T63" s="22" t="n"/>
+      <c r="U63" s="22" t="n"/>
+      <c r="V63" s="22" t="n"/>
+      <c r="W63" s="22" t="n"/>
+      <c r="X63" s="22" t="n"/>
+      <c r="Y63" s="22" t="n"/>
+      <c r="Z63" s="22" t="n"/>
+      <c r="AA63" s="22" t="n"/>
+      <c r="AB63" s="22" t="n"/>
+      <c r="AC63" s="22" t="n"/>
+      <c r="AD63" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>10.2 Ficha del cliente</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="n"/>
+      <c r="C64" s="22" t="n"/>
+      <c r="D64" s="22" t="n"/>
+      <c r="E64" s="22" t="n"/>
+      <c r="F64" s="22" t="n"/>
+      <c r="G64" s="22" t="n"/>
+      <c r="H64" s="22" t="n"/>
+      <c r="I64" s="22" t="n"/>
+      <c r="J64" s="22" t="n"/>
+      <c r="K64" s="22" t="n"/>
+      <c r="L64" s="22" t="n"/>
+      <c r="M64" s="22" t="n"/>
+      <c r="N64" s="22" t="n"/>
+      <c r="O64" s="22" t="n"/>
+      <c r="P64" s="22" t="n"/>
+      <c r="Q64" s="22" t="n"/>
+      <c r="R64" s="22" t="n"/>
+      <c r="S64" s="22" t="n"/>
+      <c r="T64" s="22" t="n"/>
+      <c r="U64" s="22" t="n"/>
+      <c r="V64" s="22" t="n"/>
+      <c r="W64" s="22" t="n"/>
+      <c r="X64" s="22" t="n"/>
+      <c r="Y64" s="22" t="n"/>
+      <c r="Z64" s="22" t="n"/>
+      <c r="AA64" s="22" t="n"/>
+      <c r="AB64" s="22" t="n"/>
+      <c r="AC64" s="22" t="n"/>
+      <c r="AD64" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>10.3 Edición de datos</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="n"/>
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="22" t="n"/>
+      <c r="E65" s="22" t="n"/>
+      <c r="F65" s="22" t="n"/>
+      <c r="G65" s="22" t="n"/>
+      <c r="H65" s="22" t="n"/>
+      <c r="I65" s="22" t="n"/>
+      <c r="J65" s="22" t="n"/>
+      <c r="K65" s="22" t="n"/>
+      <c r="L65" s="22" t="n"/>
+      <c r="M65" s="22" t="n"/>
+      <c r="N65" s="22" t="n"/>
+      <c r="O65" s="22" t="n"/>
+      <c r="P65" s="22" t="n"/>
+      <c r="Q65" s="22" t="n"/>
+      <c r="R65" s="22" t="n"/>
+      <c r="S65" s="22" t="n"/>
+      <c r="T65" s="22" t="n"/>
+      <c r="U65" s="22" t="n"/>
+      <c r="V65" s="22" t="n"/>
+      <c r="W65" s="22" t="n"/>
+      <c r="X65" s="22" t="n"/>
+      <c r="Y65" s="22" t="n"/>
+      <c r="Z65" s="22" t="n"/>
+      <c r="AA65" s="22" t="n"/>
+      <c r="AB65" s="22" t="n"/>
+      <c r="AC65" s="22" t="n"/>
+      <c r="AD65" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>10.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="n"/>
+      <c r="C66" s="22" t="n"/>
+      <c r="D66" s="22" t="n"/>
+      <c r="E66" s="22" t="n"/>
+      <c r="F66" s="22" t="n"/>
+      <c r="G66" s="22" t="n"/>
+      <c r="H66" s="22" t="n"/>
+      <c r="I66" s="22" t="n"/>
+      <c r="J66" s="22" t="n"/>
+      <c r="K66" s="22" t="n"/>
+      <c r="L66" s="22" t="n"/>
+      <c r="M66" s="22" t="n"/>
+      <c r="N66" s="22" t="n"/>
+      <c r="O66" s="22" t="n"/>
+      <c r="P66" s="22" t="n"/>
+      <c r="Q66" s="22" t="n"/>
+      <c r="R66" s="22" t="n"/>
+      <c r="S66" s="22" t="n"/>
+      <c r="T66" s="22" t="n"/>
+      <c r="U66" s="22" t="n"/>
+      <c r="V66" s="22" t="n"/>
+      <c r="W66" s="22" t="n"/>
+      <c r="X66" s="22" t="n"/>
+      <c r="Y66" s="22" t="n"/>
+      <c r="Z66" s="22" t="n"/>
+      <c r="AA66" s="22" t="n"/>
+      <c r="AB66" s="22" t="n"/>
+      <c r="AC66" s="22" t="n"/>
+      <c r="AD66" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>10.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="n"/>
+      <c r="C67" s="22" t="n"/>
+      <c r="D67" s="22" t="n"/>
+      <c r="E67" s="22" t="n"/>
+      <c r="F67" s="22" t="n"/>
+      <c r="G67" s="22" t="n"/>
+      <c r="H67" s="22" t="n"/>
+      <c r="I67" s="22" t="n"/>
+      <c r="J67" s="22" t="n"/>
+      <c r="K67" s="22" t="n"/>
+      <c r="L67" s="22" t="n"/>
+      <c r="M67" s="22" t="n"/>
+      <c r="N67" s="22" t="n"/>
+      <c r="O67" s="22" t="n"/>
+      <c r="P67" s="22" t="n"/>
+      <c r="Q67" s="22" t="n"/>
+      <c r="R67" s="22" t="n"/>
+      <c r="S67" s="22" t="n"/>
+      <c r="T67" s="22" t="n"/>
+      <c r="U67" s="22" t="n"/>
+      <c r="V67" s="22" t="n"/>
+      <c r="W67" s="22" t="n"/>
+      <c r="X67" s="22" t="n"/>
+      <c r="Y67" s="22" t="n"/>
+      <c r="Z67" s="22" t="n"/>
+      <c r="AA67" s="22" t="n"/>
+      <c r="AB67" s="22" t="n"/>
+      <c r="AC67" s="22" t="n"/>
+      <c r="AD67" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>11. Monitores y solicitudes</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="n"/>
+      <c r="C68" s="22" t="n"/>
+      <c r="D68" s="22" t="n"/>
+      <c r="E68" s="22" t="n"/>
+      <c r="F68" s="22" t="n"/>
+      <c r="G68" s="22" t="n"/>
+      <c r="H68" s="22" t="n"/>
+      <c r="I68" s="22" t="n"/>
+      <c r="J68" s="22" t="n"/>
+      <c r="K68" s="22" t="n"/>
+      <c r="L68" s="22" t="n"/>
+      <c r="M68" s="22" t="n"/>
+      <c r="N68" s="22" t="n"/>
+      <c r="O68" s="22" t="n"/>
+      <c r="P68" s="22" t="n"/>
+      <c r="Q68" s="22" t="n"/>
+      <c r="R68" s="22" t="n"/>
+      <c r="S68" s="22" t="n"/>
+      <c r="T68" s="22" t="n"/>
+      <c r="U68" s="22" t="n"/>
+      <c r="V68" s="22" t="n"/>
+      <c r="W68" s="22" t="n"/>
+      <c r="X68" s="22" t="n"/>
+      <c r="Y68" s="22" t="n"/>
+      <c r="Z68" s="22" t="n"/>
+      <c r="AA68" s="22" t="n"/>
+      <c r="AB68" s="22" t="n"/>
+      <c r="AC68" s="22" t="n"/>
+      <c r="AD68" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>11.1 Alta de monitores</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="n"/>
+      <c r="C69" s="22" t="n"/>
+      <c r="D69" s="22" t="n"/>
+      <c r="E69" s="22" t="n"/>
+      <c r="F69" s="22" t="n"/>
+      <c r="G69" s="22" t="n"/>
+      <c r="H69" s="22" t="n"/>
+      <c r="I69" s="22" t="n"/>
+      <c r="J69" s="22" t="n"/>
+      <c r="K69" s="22" t="n"/>
+      <c r="L69" s="22" t="n"/>
+      <c r="M69" s="22" t="n"/>
+      <c r="N69" s="22" t="n"/>
+      <c r="O69" s="22" t="n"/>
+      <c r="P69" s="22" t="n"/>
+      <c r="Q69" s="22" t="n"/>
+      <c r="R69" s="22" t="n"/>
+      <c r="S69" s="22" t="n"/>
+      <c r="T69" s="22" t="n"/>
+      <c r="U69" s="22" t="n"/>
+      <c r="V69" s="22" t="n"/>
+      <c r="W69" s="22" t="n"/>
+      <c r="X69" s="22" t="n"/>
+      <c r="Y69" s="22" t="n"/>
+      <c r="Z69" s="22" t="n"/>
+      <c r="AA69" s="22" t="n"/>
+      <c r="AB69" s="22" t="n"/>
+      <c r="AC69" s="22" t="n"/>
+      <c r="AD69" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>11.2 Solicitudes de clase</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="n"/>
+      <c r="C70" s="22" t="n"/>
+      <c r="D70" s="22" t="n"/>
+      <c r="E70" s="22" t="n"/>
+      <c r="F70" s="22" t="n"/>
+      <c r="G70" s="22" t="n"/>
+      <c r="H70" s="22" t="n"/>
+      <c r="I70" s="22" t="n"/>
+      <c r="J70" s="22" t="n"/>
+      <c r="K70" s="22" t="n"/>
+      <c r="L70" s="22" t="n"/>
+      <c r="M70" s="22" t="n"/>
+      <c r="N70" s="22" t="n"/>
+      <c r="O70" s="22" t="n"/>
+      <c r="P70" s="22" t="n"/>
+      <c r="Q70" s="22" t="n"/>
+      <c r="R70" s="22" t="n"/>
+      <c r="S70" s="22" t="n"/>
+      <c r="T70" s="22" t="n"/>
+      <c r="U70" s="22" t="n"/>
+      <c r="V70" s="22" t="n"/>
+      <c r="W70" s="22" t="n"/>
+      <c r="X70" s="22" t="n"/>
+      <c r="Y70" s="22" t="n"/>
+      <c r="Z70" s="22" t="n"/>
+      <c r="AA70" s="22" t="n"/>
+      <c r="AB70" s="22" t="n"/>
+      <c r="AC70" s="22" t="n"/>
+      <c r="AD70" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>11.3 Aprobación y rechazo</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="n"/>
+      <c r="C71" s="22" t="n"/>
+      <c r="D71" s="22" t="n"/>
+      <c r="E71" s="22" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="G71" s="22" t="n"/>
+      <c r="H71" s="22" t="n"/>
+      <c r="I71" s="22" t="n"/>
+      <c r="J71" s="22" t="n"/>
+      <c r="K71" s="22" t="n"/>
+      <c r="L71" s="22" t="n"/>
+      <c r="M71" s="22" t="n"/>
+      <c r="N71" s="22" t="n"/>
+      <c r="O71" s="22" t="n"/>
+      <c r="P71" s="22" t="n"/>
+      <c r="Q71" s="22" t="n"/>
+      <c r="R71" s="22" t="n"/>
+      <c r="S71" s="22" t="n"/>
+      <c r="T71" s="22" t="n"/>
+      <c r="U71" s="22" t="n"/>
+      <c r="V71" s="22" t="n"/>
+      <c r="W71" s="22" t="n"/>
+      <c r="X71" s="22" t="n"/>
+      <c r="Y71" s="22" t="n"/>
+      <c r="Z71" s="22" t="n"/>
+      <c r="AA71" s="22" t="n"/>
+      <c r="AB71" s="22" t="n"/>
+      <c r="AC71" s="22" t="n"/>
+      <c r="AD71" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>11.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="n"/>
+      <c r="C72" s="22" t="n"/>
+      <c r="D72" s="22" t="n"/>
+      <c r="E72" s="22" t="n"/>
+      <c r="F72" s="22" t="n"/>
+      <c r="G72" s="22" t="n"/>
+      <c r="H72" s="22" t="n"/>
+      <c r="I72" s="22" t="n"/>
+      <c r="J72" s="22" t="n"/>
+      <c r="K72" s="22" t="n"/>
+      <c r="L72" s="22" t="n"/>
+      <c r="M72" s="22" t="n"/>
+      <c r="N72" s="22" t="n"/>
+      <c r="O72" s="22" t="n"/>
+      <c r="P72" s="22" t="n"/>
+      <c r="Q72" s="22" t="n"/>
+      <c r="R72" s="22" t="n"/>
+      <c r="S72" s="22" t="n"/>
+      <c r="T72" s="22" t="n"/>
+      <c r="U72" s="22" t="n"/>
+      <c r="V72" s="22" t="n"/>
+      <c r="W72" s="22" t="n"/>
+      <c r="X72" s="22" t="n"/>
+      <c r="Y72" s="22" t="n"/>
+      <c r="Z72" s="22" t="n"/>
+      <c r="AA72" s="22" t="n"/>
+      <c r="AB72" s="22" t="n"/>
+      <c r="AC72" s="22" t="n"/>
+      <c r="AD72" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>11.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="n"/>
+      <c r="C73" s="22" t="n"/>
+      <c r="D73" s="22" t="n"/>
+      <c r="E73" s="22" t="n"/>
+      <c r="F73" s="22" t="n"/>
+      <c r="G73" s="22" t="n"/>
+      <c r="H73" s="22" t="n"/>
+      <c r="I73" s="22" t="n"/>
+      <c r="J73" s="22" t="n"/>
+      <c r="K73" s="22" t="n"/>
+      <c r="L73" s="22" t="n"/>
+      <c r="M73" s="22" t="n"/>
+      <c r="N73" s="22" t="n"/>
+      <c r="O73" s="22" t="n"/>
+      <c r="P73" s="22" t="n"/>
+      <c r="Q73" s="22" t="n"/>
+      <c r="R73" s="22" t="n"/>
+      <c r="S73" s="22" t="n"/>
+      <c r="T73" s="22" t="n"/>
+      <c r="U73" s="22" t="n"/>
+      <c r="V73" s="22" t="n"/>
+      <c r="W73" s="22" t="n"/>
+      <c r="X73" s="22" t="n"/>
+      <c r="Y73" s="22" t="n"/>
+      <c r="Z73" s="22" t="n"/>
+      <c r="AA73" s="22" t="n"/>
+      <c r="AB73" s="22" t="n"/>
+      <c r="AC73" s="22" t="n"/>
+      <c r="AD73" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>12. Salas y materiales</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="n"/>
+      <c r="C74" s="22" t="n"/>
+      <c r="D74" s="22" t="n"/>
+      <c r="E74" s="22" t="n"/>
+      <c r="F74" s="22" t="n"/>
+      <c r="G74" s="22" t="n"/>
+      <c r="H74" s="22" t="n"/>
+      <c r="I74" s="22" t="n"/>
+      <c r="J74" s="22" t="n"/>
+      <c r="K74" s="22" t="n"/>
+      <c r="L74" s="22" t="n"/>
+      <c r="M74" s="22" t="n"/>
+      <c r="N74" s="22" t="n"/>
+      <c r="O74" s="22" t="n"/>
+      <c r="P74" s="22" t="n"/>
+      <c r="Q74" s="22" t="n"/>
+      <c r="R74" s="22" t="n"/>
+      <c r="S74" s="22" t="n"/>
+      <c r="T74" s="22" t="n"/>
+      <c r="U74" s="22" t="n"/>
+      <c r="V74" s="22" t="n"/>
+      <c r="W74" s="22" t="n"/>
+      <c r="X74" s="22" t="n"/>
+      <c r="Y74" s="22" t="n"/>
+      <c r="Z74" s="22" t="n"/>
+      <c r="AA74" s="22" t="n"/>
+      <c r="AB74" s="22" t="n"/>
+      <c r="AC74" s="22" t="n"/>
+      <c r="AD74" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>12.1 Ficha de salas</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="n"/>
+      <c r="C75" s="22" t="n"/>
+      <c r="D75" s="22" t="n"/>
+      <c r="E75" s="22" t="n"/>
+      <c r="F75" s="22" t="n"/>
+      <c r="G75" s="22" t="n"/>
+      <c r="H75" s="22" t="n"/>
+      <c r="I75" s="22" t="n"/>
+      <c r="J75" s="22" t="n"/>
+      <c r="K75" s="22" t="n"/>
+      <c r="L75" s="22" t="n"/>
+      <c r="M75" s="22" t="n"/>
+      <c r="N75" s="22" t="n"/>
+      <c r="O75" s="22" t="n"/>
+      <c r="P75" s="22" t="n"/>
+      <c r="Q75" s="22" t="n"/>
+      <c r="R75" s="22" t="n"/>
+      <c r="S75" s="22" t="n"/>
+      <c r="T75" s="22" t="n"/>
+      <c r="U75" s="22" t="n"/>
+      <c r="V75" s="22" t="n"/>
+      <c r="W75" s="22" t="n"/>
+      <c r="X75" s="22" t="n"/>
+      <c r="Y75" s="22" t="n"/>
+      <c r="Z75" s="22" t="n"/>
+      <c r="AA75" s="22" t="n"/>
+      <c r="AB75" s="22" t="n"/>
+      <c r="AC75" s="22" t="n"/>
+      <c r="AD75" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>12.2 Inventario de materiales</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="n"/>
+      <c r="C76" s="22" t="n"/>
+      <c r="D76" s="22" t="n"/>
+      <c r="E76" s="22" t="n"/>
+      <c r="F76" s="22" t="n"/>
+      <c r="G76" s="22" t="n"/>
+      <c r="H76" s="22" t="n"/>
+      <c r="I76" s="22" t="n"/>
+      <c r="J76" s="22" t="n"/>
+      <c r="K76" s="22" t="n"/>
+      <c r="L76" s="22" t="n"/>
+      <c r="M76" s="22" t="n"/>
+      <c r="N76" s="22" t="n"/>
+      <c r="O76" s="22" t="n"/>
+      <c r="P76" s="22" t="n"/>
+      <c r="Q76" s="22" t="n"/>
+      <c r="R76" s="22" t="n"/>
+      <c r="S76" s="22" t="n"/>
+      <c r="T76" s="22" t="n"/>
+      <c r="U76" s="22" t="n"/>
+      <c r="V76" s="22" t="n"/>
+      <c r="W76" s="22" t="n"/>
+      <c r="X76" s="22" t="n"/>
+      <c r="Y76" s="22" t="n"/>
+      <c r="Z76" s="22" t="n"/>
+      <c r="AA76" s="22" t="n"/>
+      <c r="AB76" s="22" t="n"/>
+      <c r="AC76" s="22" t="n"/>
+      <c r="AD76" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>12.3 Alta y edición</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="n"/>
+      <c r="C77" s="22" t="n"/>
+      <c r="D77" s="22" t="n"/>
+      <c r="E77" s="22" t="n"/>
+      <c r="F77" s="22" t="n"/>
+      <c r="G77" s="22" t="n"/>
+      <c r="H77" s="22" t="n"/>
+      <c r="I77" s="22" t="n"/>
+      <c r="J77" s="22" t="n"/>
+      <c r="K77" s="22" t="n"/>
+      <c r="L77" s="22" t="n"/>
+      <c r="M77" s="22" t="n"/>
+      <c r="N77" s="22" t="n"/>
+      <c r="O77" s="22" t="n"/>
+      <c r="P77" s="22" t="n"/>
+      <c r="Q77" s="22" t="n"/>
+      <c r="R77" s="22" t="n"/>
+      <c r="S77" s="22" t="n"/>
+      <c r="T77" s="22" t="n"/>
+      <c r="U77" s="22" t="n"/>
+      <c r="V77" s="22" t="n"/>
+      <c r="W77" s="22" t="n"/>
+      <c r="X77" s="22" t="n"/>
+      <c r="Y77" s="22" t="n"/>
+      <c r="Z77" s="22" t="n"/>
+      <c r="AA77" s="22" t="n"/>
+      <c r="AB77" s="22" t="n"/>
+      <c r="AC77" s="22" t="n"/>
+      <c r="AD77" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>12.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="n"/>
+      <c r="C78" s="22" t="n"/>
+      <c r="D78" s="22" t="n"/>
+      <c r="E78" s="22" t="n"/>
+      <c r="F78" s="22" t="n"/>
+      <c r="G78" s="22" t="n"/>
+      <c r="H78" s="22" t="n"/>
+      <c r="I78" s="22" t="n"/>
+      <c r="J78" s="22" t="n"/>
+      <c r="K78" s="22" t="n"/>
+      <c r="L78" s="22" t="n"/>
+      <c r="M78" s="22" t="n"/>
+      <c r="N78" s="22" t="n"/>
+      <c r="O78" s="22" t="n"/>
+      <c r="P78" s="22" t="n"/>
+      <c r="Q78" s="22" t="n"/>
+      <c r="R78" s="22" t="n"/>
+      <c r="S78" s="22" t="n"/>
+      <c r="T78" s="22" t="n"/>
+      <c r="U78" s="22" t="n"/>
+      <c r="V78" s="22" t="n"/>
+      <c r="W78" s="22" t="n"/>
+      <c r="X78" s="22" t="n"/>
+      <c r="Y78" s="22" t="n"/>
+      <c r="Z78" s="22" t="n"/>
+      <c r="AA78" s="22" t="n"/>
+      <c r="AB78" s="22" t="n"/>
+      <c r="AC78" s="22" t="n"/>
+      <c r="AD78" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>12.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="n"/>
+      <c r="C79" s="22" t="n"/>
+      <c r="D79" s="22" t="n"/>
+      <c r="E79" s="22" t="n"/>
+      <c r="F79" s="22" t="n"/>
+      <c r="G79" s="22" t="n"/>
+      <c r="H79" s="22" t="n"/>
+      <c r="I79" s="22" t="n"/>
+      <c r="J79" s="22" t="n"/>
+      <c r="K79" s="22" t="n"/>
+      <c r="L79" s="22" t="n"/>
+      <c r="M79" s="22" t="n"/>
+      <c r="N79" s="22" t="n"/>
+      <c r="O79" s="22" t="n"/>
+      <c r="P79" s="22" t="n"/>
+      <c r="Q79" s="22" t="n"/>
+      <c r="R79" s="22" t="n"/>
+      <c r="S79" s="22" t="n"/>
+      <c r="T79" s="22" t="n"/>
+      <c r="U79" s="22" t="n"/>
+      <c r="V79" s="22" t="n"/>
+      <c r="W79" s="22" t="n"/>
+      <c r="X79" s="22" t="n"/>
+      <c r="Y79" s="22" t="n"/>
+      <c r="Z79" s="22" t="n"/>
+      <c r="AA79" s="22" t="n"/>
+      <c r="AB79" s="22" t="n"/>
+      <c r="AC79" s="22" t="n"/>
+      <c r="AD79" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>13. Fisioterapia y citas</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="n"/>
+      <c r="C80" s="22" t="n"/>
+      <c r="D80" s="22" t="n"/>
+      <c r="E80" s="22" t="n"/>
+      <c r="F80" s="22" t="n"/>
+      <c r="G80" s="22" t="n"/>
+      <c r="H80" s="22" t="n"/>
+      <c r="I80" s="22" t="n"/>
+      <c r="J80" s="22" t="n"/>
+      <c r="K80" s="22" t="n"/>
+      <c r="L80" s="22" t="n"/>
+      <c r="M80" s="22" t="n"/>
+      <c r="N80" s="22" t="n"/>
+      <c r="O80" s="22" t="n"/>
+      <c r="P80" s="22" t="n"/>
+      <c r="Q80" s="22" t="n"/>
+      <c r="R80" s="22" t="n"/>
+      <c r="S80" s="22" t="n"/>
+      <c r="T80" s="22" t="n"/>
+      <c r="U80" s="22" t="n"/>
+      <c r="V80" s="22" t="n"/>
+      <c r="W80" s="22" t="n"/>
+      <c r="X80" s="22" t="n"/>
+      <c r="Y80" s="22" t="n"/>
+      <c r="Z80" s="22" t="n"/>
+      <c r="AA80" s="22" t="n"/>
+      <c r="AB80" s="22" t="n"/>
+      <c r="AC80" s="22" t="n"/>
+      <c r="AD80" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>13.1 Solicitud de cita</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="n"/>
+      <c r="C81" s="22" t="n"/>
+      <c r="D81" s="22" t="n"/>
+      <c r="E81" s="22" t="n"/>
+      <c r="F81" s="22" t="n"/>
+      <c r="G81" s="22" t="n"/>
+      <c r="H81" s="22" t="n"/>
+      <c r="I81" s="22" t="n"/>
+      <c r="J81" s="22" t="n"/>
+      <c r="K81" s="22" t="n"/>
+      <c r="L81" s="22" t="n"/>
+      <c r="M81" s="22" t="n"/>
+      <c r="N81" s="22" t="n"/>
+      <c r="O81" s="22" t="n"/>
+      <c r="P81" s="22" t="n"/>
+      <c r="Q81" s="22" t="n"/>
+      <c r="R81" s="22" t="n"/>
+      <c r="S81" s="22" t="n"/>
+      <c r="T81" s="22" t="n"/>
+      <c r="U81" s="22" t="n"/>
+      <c r="V81" s="22" t="n"/>
+      <c r="W81" s="22" t="n"/>
+      <c r="X81" s="22" t="n"/>
+      <c r="Y81" s="22" t="n"/>
+      <c r="Z81" s="22" t="n"/>
+      <c r="AA81" s="22" t="n"/>
+      <c r="AB81" s="22" t="n"/>
+      <c r="AC81" s="22" t="n"/>
+      <c r="AD81" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>13.2 Agenda del fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="n"/>
+      <c r="C82" s="22" t="n"/>
+      <c r="D82" s="22" t="n"/>
+      <c r="E82" s="22" t="n"/>
+      <c r="F82" s="22" t="n"/>
+      <c r="G82" s="22" t="n"/>
+      <c r="H82" s="22" t="n"/>
+      <c r="I82" s="22" t="n"/>
+      <c r="J82" s="22" t="n"/>
+      <c r="K82" s="22" t="n"/>
+      <c r="L82" s="22" t="n"/>
+      <c r="M82" s="22" t="n"/>
+      <c r="N82" s="22" t="n"/>
+      <c r="O82" s="22" t="n"/>
+      <c r="P82" s="22" t="n"/>
+      <c r="Q82" s="22" t="n"/>
+      <c r="R82" s="22" t="n"/>
+      <c r="S82" s="22" t="n"/>
+      <c r="T82" s="22" t="n"/>
+      <c r="U82" s="22" t="n"/>
+      <c r="V82" s="22" t="n"/>
+      <c r="W82" s="22" t="n"/>
+      <c r="X82" s="22" t="n"/>
+      <c r="Y82" s="22" t="n"/>
+      <c r="Z82" s="22" t="n"/>
+      <c r="AA82" s="22" t="n"/>
+      <c r="AB82" s="22" t="n"/>
+      <c r="AC82" s="22" t="n"/>
+      <c r="AD82" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>13.3 Panel de citas</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="n"/>
+      <c r="C83" s="22" t="n"/>
+      <c r="D83" s="22" t="n"/>
+      <c r="E83" s="22" t="n"/>
+      <c r="F83" s="22" t="n"/>
+      <c r="G83" s="22" t="n"/>
+      <c r="H83" s="22" t="n"/>
+      <c r="I83" s="22" t="n"/>
+      <c r="J83" s="22" t="n"/>
+      <c r="K83" s="22" t="n"/>
+      <c r="L83" s="22" t="n"/>
+      <c r="M83" s="22" t="n"/>
+      <c r="N83" s="22" t="n"/>
+      <c r="O83" s="22" t="n"/>
+      <c r="P83" s="22" t="n"/>
+      <c r="Q83" s="22" t="n"/>
+      <c r="R83" s="22" t="n"/>
+      <c r="S83" s="22" t="n"/>
+      <c r="T83" s="22" t="n"/>
+      <c r="U83" s="22" t="n"/>
+      <c r="V83" s="22" t="n"/>
+      <c r="W83" s="22" t="n"/>
+      <c r="X83" s="22" t="n"/>
+      <c r="Y83" s="22" t="n"/>
+      <c r="Z83" s="22" t="n"/>
+      <c r="AA83" s="22" t="n"/>
+      <c r="AB83" s="22" t="n"/>
+      <c r="AC83" s="22" t="n"/>
+      <c r="AD83" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>13.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="n"/>
+      <c r="C84" s="22" t="n"/>
+      <c r="D84" s="22" t="n"/>
+      <c r="E84" s="22" t="n"/>
+      <c r="F84" s="22" t="n"/>
+      <c r="G84" s="22" t="n"/>
+      <c r="H84" s="22" t="n"/>
+      <c r="I84" s="22" t="n"/>
+      <c r="J84" s="22" t="n"/>
+      <c r="K84" s="22" t="n"/>
+      <c r="L84" s="22" t="n"/>
+      <c r="M84" s="22" t="n"/>
+      <c r="N84" s="22" t="n"/>
+      <c r="O84" s="22" t="n"/>
+      <c r="P84" s="22" t="n"/>
+      <c r="Q84" s="22" t="n"/>
+      <c r="R84" s="22" t="n"/>
+      <c r="S84" s="22" t="n"/>
+      <c r="T84" s="22" t="n"/>
+      <c r="U84" s="22" t="n"/>
+      <c r="V84" s="22" t="n"/>
+      <c r="W84" s="22" t="n"/>
+      <c r="X84" s="22" t="n"/>
+      <c r="Y84" s="22" t="n"/>
+      <c r="Z84" s="22" t="n"/>
+      <c r="AA84" s="22" t="n"/>
+      <c r="AB84" s="22" t="n"/>
+      <c r="AC84" s="22" t="n"/>
+      <c r="AD84" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>13.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="n"/>
+      <c r="C85" s="22" t="n"/>
+      <c r="D85" s="22" t="n"/>
+      <c r="E85" s="22" t="n"/>
+      <c r="F85" s="22" t="n"/>
+      <c r="G85" s="22" t="n"/>
+      <c r="H85" s="22" t="n"/>
+      <c r="I85" s="22" t="n"/>
+      <c r="J85" s="22" t="n"/>
+      <c r="K85" s="22" t="n"/>
+      <c r="L85" s="22" t="n"/>
+      <c r="M85" s="22" t="n"/>
+      <c r="N85" s="22" t="n"/>
+      <c r="O85" s="22" t="n"/>
+      <c r="P85" s="22" t="n"/>
+      <c r="Q85" s="22" t="n"/>
+      <c r="R85" s="22" t="n"/>
+      <c r="S85" s="22" t="n"/>
+      <c r="T85" s="22" t="n"/>
+      <c r="U85" s="22" t="n"/>
+      <c r="V85" s="22" t="n"/>
+      <c r="W85" s="22" t="n"/>
+      <c r="X85" s="22" t="n"/>
+      <c r="Y85" s="22" t="n"/>
+      <c r="Z85" s="22" t="n"/>
+      <c r="AA85" s="22" t="n"/>
+      <c r="AB85" s="22" t="n"/>
+      <c r="AC85" s="22" t="n"/>
+      <c r="AD85" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>14. Comentarios, feedback y seguridad</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="n"/>
+      <c r="C86" s="22" t="n"/>
+      <c r="D86" s="22" t="n"/>
+      <c r="E86" s="22" t="n"/>
+      <c r="F86" s="22" t="n"/>
+      <c r="G86" s="22" t="n"/>
+      <c r="H86" s="22" t="n"/>
+      <c r="I86" s="22" t="n"/>
+      <c r="J86" s="22" t="n"/>
+      <c r="K86" s="22" t="n"/>
+      <c r="L86" s="22" t="n"/>
+      <c r="M86" s="22" t="n"/>
+      <c r="N86" s="22" t="n"/>
+      <c r="O86" s="22" t="n"/>
+      <c r="P86" s="22" t="n"/>
+      <c r="Q86" s="22" t="n"/>
+      <c r="R86" s="22" t="n"/>
+      <c r="S86" s="22" t="n"/>
+      <c r="T86" s="22" t="n"/>
+      <c r="U86" s="22" t="n"/>
+      <c r="V86" s="22" t="n"/>
+      <c r="W86" s="22" t="n"/>
+      <c r="X86" s="22" t="n"/>
+      <c r="Y86" s="22" t="n"/>
+      <c r="Z86" s="22" t="n"/>
+      <c r="AA86" s="22" t="n"/>
+      <c r="AB86" s="22" t="n"/>
+      <c r="AC86" s="22" t="n"/>
+      <c r="AD86" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>14.1 Comentarios de actividad</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="n"/>
+      <c r="C87" s="22" t="n"/>
+      <c r="D87" s="22" t="n"/>
+      <c r="E87" s="22" t="n"/>
+      <c r="F87" s="22" t="n"/>
+      <c r="G87" s="22" t="n"/>
+      <c r="H87" s="22" t="n"/>
+      <c r="I87" s="22" t="n"/>
+      <c r="J87" s="22" t="n"/>
+      <c r="K87" s="22" t="n"/>
+      <c r="L87" s="22" t="n"/>
+      <c r="M87" s="22" t="n"/>
+      <c r="N87" s="22" t="n"/>
+      <c r="O87" s="22" t="n"/>
+      <c r="P87" s="22" t="n"/>
+      <c r="Q87" s="22" t="n"/>
+      <c r="R87" s="22" t="n"/>
+      <c r="S87" s="22" t="n"/>
+      <c r="T87" s="22" t="n"/>
+      <c r="U87" s="22" t="n"/>
+      <c r="V87" s="22" t="n"/>
+      <c r="W87" s="22" t="n"/>
+      <c r="X87" s="22" t="n"/>
+      <c r="Y87" s="22" t="n"/>
+      <c r="Z87" s="22" t="n"/>
+      <c r="AA87" s="22" t="n"/>
+      <c r="AB87" s="22" t="n"/>
+      <c r="AC87" s="22" t="n"/>
+      <c r="AD87" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>14.2 Buzón de feedback</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="n"/>
+      <c r="C88" s="22" t="n"/>
+      <c r="D88" s="22" t="n"/>
+      <c r="E88" s="22" t="n"/>
+      <c r="F88" s="22" t="n"/>
+      <c r="G88" s="22" t="n"/>
+      <c r="H88" s="22" t="n"/>
+      <c r="I88" s="22" t="n"/>
+      <c r="J88" s="22" t="n"/>
+      <c r="K88" s="22" t="n"/>
+      <c r="L88" s="22" t="n"/>
+      <c r="M88" s="22" t="n"/>
+      <c r="N88" s="22" t="n"/>
+      <c r="O88" s="22" t="n"/>
+      <c r="P88" s="22" t="n"/>
+      <c r="Q88" s="22" t="n"/>
+      <c r="R88" s="22" t="n"/>
+      <c r="S88" s="22" t="n"/>
+      <c r="T88" s="22" t="n"/>
+      <c r="U88" s="22" t="n"/>
+      <c r="V88" s="22" t="n"/>
+      <c r="W88" s="22" t="n"/>
+      <c r="X88" s="22" t="n"/>
+      <c r="Y88" s="22" t="n"/>
+      <c r="Z88" s="22" t="n"/>
+      <c r="AA88" s="22" t="n"/>
+      <c r="AB88" s="22" t="n"/>
+      <c r="AC88" s="22" t="n"/>
+      <c r="AD88" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>14.3 Configuración de seguridad</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="n"/>
+      <c r="C89" s="22" t="n"/>
+      <c r="D89" s="22" t="n"/>
+      <c r="E89" s="22" t="n"/>
+      <c r="F89" s="22" t="n"/>
+      <c r="G89" s="22" t="n"/>
+      <c r="H89" s="22" t="n"/>
+      <c r="I89" s="22" t="n"/>
+      <c r="J89" s="22" t="n"/>
+      <c r="K89" s="22" t="n"/>
+      <c r="L89" s="22" t="n"/>
+      <c r="M89" s="22" t="n"/>
+      <c r="N89" s="22" t="n"/>
+      <c r="O89" s="22" t="n"/>
+      <c r="P89" s="22" t="n"/>
+      <c r="Q89" s="22" t="n"/>
+      <c r="R89" s="22" t="n"/>
+      <c r="S89" s="22" t="n"/>
+      <c r="T89" s="22" t="n"/>
+      <c r="U89" s="22" t="n"/>
+      <c r="V89" s="22" t="n"/>
+      <c r="W89" s="22" t="n"/>
+      <c r="X89" s="22" t="n"/>
+      <c r="Y89" s="22" t="n"/>
+      <c r="Z89" s="22" t="n"/>
+      <c r="AA89" s="22" t="n"/>
+      <c r="AB89" s="22" t="n"/>
+      <c r="AC89" s="22" t="n"/>
+      <c r="AD89" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>14.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="n"/>
+      <c r="C90" s="22" t="n"/>
+      <c r="D90" s="22" t="n"/>
+      <c r="E90" s="22" t="n"/>
+      <c r="F90" s="22" t="n"/>
+      <c r="G90" s="22" t="n"/>
+      <c r="H90" s="22" t="n"/>
+      <c r="I90" s="22" t="n"/>
+      <c r="J90" s="22" t="n"/>
+      <c r="K90" s="22" t="n"/>
+      <c r="L90" s="22" t="n"/>
+      <c r="M90" s="22" t="n"/>
+      <c r="N90" s="22" t="n"/>
+      <c r="O90" s="22" t="n"/>
+      <c r="P90" s="22" t="n"/>
+      <c r="Q90" s="22" t="n"/>
+      <c r="R90" s="22" t="n"/>
+      <c r="S90" s="22" t="n"/>
+      <c r="T90" s="22" t="n"/>
+      <c r="U90" s="22" t="n"/>
+      <c r="V90" s="22" t="n"/>
+      <c r="W90" s="22" t="n"/>
+      <c r="X90" s="22" t="n"/>
+      <c r="Y90" s="22" t="n"/>
+      <c r="Z90" s="22" t="n"/>
+      <c r="AA90" s="22" t="n"/>
+      <c r="AB90" s="22" t="n"/>
+      <c r="AC90" s="22" t="n"/>
+      <c r="AD90" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t>14.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="n"/>
+      <c r="C91" s="22" t="n"/>
+      <c r="D91" s="22" t="n"/>
+      <c r="E91" s="22" t="n"/>
+      <c r="F91" s="22" t="n"/>
+      <c r="G91" s="22" t="n"/>
+      <c r="H91" s="22" t="n"/>
+      <c r="I91" s="22" t="n"/>
+      <c r="J91" s="22" t="n"/>
+      <c r="K91" s="22" t="n"/>
+      <c r="L91" s="22" t="n"/>
+      <c r="M91" s="22" t="n"/>
+      <c r="N91" s="22" t="n"/>
+      <c r="O91" s="22" t="n"/>
+      <c r="P91" s="22" t="n"/>
+      <c r="Q91" s="22" t="n"/>
+      <c r="R91" s="22" t="n"/>
+      <c r="S91" s="22" t="n"/>
+      <c r="T91" s="22" t="n"/>
+      <c r="U91" s="22" t="n"/>
+      <c r="V91" s="22" t="n"/>
+      <c r="W91" s="22" t="n"/>
+      <c r="X91" s="22" t="n"/>
+      <c r="Y91" s="22" t="n"/>
+      <c r="Z91" s="22" t="n"/>
+      <c r="AA91" s="22" t="n"/>
+      <c r="AB91" s="22" t="n"/>
+      <c r="AC91" s="22" t="n"/>
+      <c r="AD91" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>15. Interfaz Tailwind, correo y cierre</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="n"/>
+      <c r="C92" s="22" t="n"/>
+      <c r="D92" s="22" t="n"/>
+      <c r="E92" s="22" t="n"/>
+      <c r="F92" s="22" t="n"/>
+      <c r="G92" s="22" t="n"/>
+      <c r="H92" s="22" t="n"/>
+      <c r="I92" s="22" t="n"/>
+      <c r="J92" s="22" t="n"/>
+      <c r="K92" s="22" t="n"/>
+      <c r="L92" s="22" t="n"/>
+      <c r="M92" s="22" t="n"/>
+      <c r="N92" s="22" t="n"/>
+      <c r="O92" s="22" t="n"/>
+      <c r="P92" s="22" t="n"/>
+      <c r="Q92" s="22" t="n"/>
+      <c r="R92" s="22" t="n"/>
+      <c r="S92" s="22" t="n"/>
+      <c r="T92" s="22" t="n"/>
+      <c r="U92" s="22" t="n"/>
+      <c r="V92" s="22" t="n"/>
+      <c r="W92" s="22" t="n"/>
+      <c r="X92" s="22" t="n"/>
+      <c r="Y92" s="22" t="n"/>
+      <c r="Z92" s="22" t="n"/>
+      <c r="AA92" s="22" t="n"/>
+      <c r="AB92" s="22" t="n"/>
+      <c r="AC92" s="22" t="n"/>
+      <c r="AD92" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A93" s="24" t="inlineStr">
+        <is>
+          <t>15.1 Maquetación con Tailwind</t>
+        </is>
+      </c>
+      <c r="B93" s="22" t="n"/>
+      <c r="C93" s="22" t="n"/>
+      <c r="D93" s="22" t="n"/>
+      <c r="E93" s="22" t="n"/>
+      <c r="F93" s="22" t="n"/>
+      <c r="G93" s="22" t="n"/>
+      <c r="H93" s="22" t="n"/>
+      <c r="I93" s="22" t="n"/>
+      <c r="J93" s="22" t="n"/>
+      <c r="K93" s="22" t="n"/>
+      <c r="L93" s="22" t="n"/>
+      <c r="M93" s="22" t="n"/>
+      <c r="N93" s="22" t="n"/>
+      <c r="O93" s="22" t="n"/>
+      <c r="P93" s="22" t="n"/>
+      <c r="Q93" s="22" t="n"/>
+      <c r="R93" s="22" t="n"/>
+      <c r="S93" s="22" t="n"/>
+      <c r="T93" s="22" t="n"/>
+      <c r="U93" s="22" t="n"/>
+      <c r="V93" s="22" t="n"/>
+      <c r="W93" s="22" t="n"/>
+      <c r="X93" s="22" t="n"/>
+      <c r="Y93" s="22" t="n"/>
+      <c r="Z93" s="22" t="n"/>
+      <c r="AA93" s="22" t="n"/>
+      <c r="AB93" s="22" t="n"/>
+      <c r="AC93" s="22" t="n"/>
+      <c r="AD93" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A94" s="24" t="inlineStr">
+        <is>
+          <t>15.2 Correo del proyecto</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="n"/>
+      <c r="C94" s="22" t="n"/>
+      <c r="D94" s="22" t="n"/>
+      <c r="E94" s="22" t="n"/>
+      <c r="F94" s="22" t="n"/>
+      <c r="G94" s="22" t="n"/>
+      <c r="H94" s="22" t="n"/>
+      <c r="I94" s="22" t="n"/>
+      <c r="J94" s="22" t="n"/>
+      <c r="K94" s="22" t="n"/>
+      <c r="L94" s="22" t="n"/>
+      <c r="M94" s="22" t="n"/>
+      <c r="N94" s="22" t="n"/>
+      <c r="O94" s="22" t="n"/>
+      <c r="P94" s="22" t="n"/>
+      <c r="Q94" s="22" t="n"/>
+      <c r="R94" s="22" t="n"/>
+      <c r="S94" s="22" t="n"/>
+      <c r="T94" s="22" t="n"/>
+      <c r="U94" s="22" t="n"/>
+      <c r="V94" s="22" t="n"/>
+      <c r="W94" s="22" t="n"/>
+      <c r="X94" s="22" t="n"/>
+      <c r="Y94" s="22" t="n"/>
+      <c r="Z94" s="22" t="n"/>
+      <c r="AA94" s="22" t="n"/>
+      <c r="AB94" s="22" t="n"/>
+      <c r="AC94" s="22" t="n"/>
+      <c r="AD94" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A95" s="24" t="inlineStr">
+        <is>
+          <t>15.3 Cierre y revisión</t>
+        </is>
+      </c>
+      <c r="B95" s="22" t="n"/>
+      <c r="C95" s="22" t="n"/>
+      <c r="D95" s="22" t="n"/>
+      <c r="E95" s="22" t="n"/>
+      <c r="F95" s="22" t="n"/>
+      <c r="G95" s="22" t="n"/>
+      <c r="H95" s="22" t="n"/>
+      <c r="I95" s="22" t="n"/>
+      <c r="J95" s="22" t="n"/>
+      <c r="K95" s="22" t="n"/>
+      <c r="L95" s="22" t="n"/>
+      <c r="M95" s="22" t="n"/>
+      <c r="N95" s="22" t="n"/>
+      <c r="O95" s="22" t="n"/>
+      <c r="P95" s="22" t="n"/>
+      <c r="Q95" s="22" t="n"/>
+      <c r="R95" s="22" t="n"/>
+      <c r="S95" s="22" t="n"/>
+      <c r="T95" s="22" t="n"/>
+      <c r="U95" s="22" t="n"/>
+      <c r="V95" s="22" t="n"/>
+      <c r="W95" s="22" t="n"/>
+      <c r="X95" s="22" t="n"/>
+      <c r="Y95" s="22" t="n"/>
+      <c r="Z95" s="22" t="n"/>
+      <c r="AA95" s="22" t="n"/>
+      <c r="AB95" s="22" t="n"/>
+      <c r="AC95" s="22" t="n"/>
+      <c r="AD95" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>15.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B96" s="22" t="n"/>
+      <c r="C96" s="22" t="n"/>
+      <c r="D96" s="22" t="n"/>
+      <c r="E96" s="22" t="n"/>
+      <c r="F96" s="22" t="n"/>
+      <c r="G96" s="22" t="n"/>
+      <c r="H96" s="22" t="n"/>
+      <c r="I96" s="22" t="n"/>
+      <c r="J96" s="22" t="n"/>
+      <c r="K96" s="22" t="n"/>
+      <c r="L96" s="22" t="n"/>
+      <c r="M96" s="22" t="n"/>
+      <c r="N96" s="22" t="n"/>
+      <c r="O96" s="22" t="n"/>
+      <c r="P96" s="22" t="n"/>
+      <c r="Q96" s="22" t="n"/>
+      <c r="R96" s="22" t="n"/>
+      <c r="S96" s="22" t="n"/>
+      <c r="T96" s="22" t="n"/>
+      <c r="U96" s="22" t="n"/>
+      <c r="V96" s="22" t="n"/>
+      <c r="W96" s="22" t="n"/>
+      <c r="X96" s="22" t="n"/>
+      <c r="Y96" s="22" t="n"/>
+      <c r="Z96" s="22" t="n"/>
+      <c r="AA96" s="22" t="n"/>
+      <c r="AB96" s="22" t="n"/>
+      <c r="AC96" s="22" t="n"/>
+      <c r="AD96" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>15.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B97" s="22" t="n"/>
+      <c r="C97" s="22" t="n"/>
+      <c r="D97" s="22" t="n"/>
+      <c r="E97" s="22" t="n"/>
+      <c r="F97" s="22" t="n"/>
+      <c r="G97" s="22" t="n"/>
+      <c r="H97" s="22" t="n"/>
+      <c r="I97" s="22" t="n"/>
+      <c r="J97" s="22" t="n"/>
+      <c r="K97" s="22" t="n"/>
+      <c r="L97" s="22" t="n"/>
+      <c r="M97" s="22" t="n"/>
+      <c r="N97" s="22" t="n"/>
+      <c r="O97" s="22" t="n"/>
+      <c r="P97" s="22" t="n"/>
+      <c r="Q97" s="22" t="n"/>
+      <c r="R97" s="22" t="n"/>
+      <c r="S97" s="22" t="n"/>
+      <c r="T97" s="22" t="n"/>
+      <c r="U97" s="22" t="n"/>
+      <c r="V97" s="22" t="n"/>
+      <c r="W97" s="22" t="n"/>
+      <c r="X97" s="22" t="n"/>
+      <c r="Y97" s="22" t="n"/>
+      <c r="Z97" s="22" t="n"/>
+      <c r="AA97" s="22" t="n"/>
+      <c r="AB97" s="22" t="n"/>
+      <c r="AC97" s="22" t="n"/>
+      <c r="AD97" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="27" t="n"/>
+      <c r="B98" s="28" t="n"/>
+      <c r="C98" s="28" t="n"/>
+      <c r="D98" s="28" t="n"/>
+      <c r="E98" s="28" t="n"/>
+      <c r="F98" s="28" t="n"/>
+      <c r="G98" s="28" t="n"/>
+      <c r="H98" s="28" t="n"/>
+      <c r="I98" s="28" t="n"/>
+      <c r="J98" s="28" t="n"/>
+      <c r="K98" s="28" t="n"/>
+      <c r="L98" s="28" t="n"/>
+      <c r="M98" s="28" t="n"/>
+      <c r="N98" s="28" t="n"/>
+      <c r="O98" s="28" t="n"/>
+      <c r="P98" s="28" t="n"/>
+      <c r="Q98" s="28" t="n"/>
+      <c r="R98" s="28" t="n"/>
+      <c r="S98" s="28" t="n"/>
+      <c r="T98" s="28" t="n"/>
+      <c r="U98" s="28" t="n"/>
+      <c r="V98" s="28" t="n"/>
+      <c r="W98" s="28" t="n"/>
+      <c r="X98" s="28" t="n"/>
+      <c r="Y98" s="28" t="n"/>
+      <c r="Z98" s="28" t="n"/>
+      <c r="AA98" s="28" t="n"/>
+      <c r="AB98" s="28" t="n"/>
+      <c r="AC98" s="28" t="n"/>
+      <c r="AD98" s="28" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="27" t="n"/>
+      <c r="B99" s="28" t="n"/>
+      <c r="C99" s="28" t="n"/>
+      <c r="D99" s="28" t="n"/>
+      <c r="E99" s="28" t="n"/>
+      <c r="F99" s="28" t="n"/>
+      <c r="G99" s="28" t="n"/>
+      <c r="H99" s="28" t="n"/>
+      <c r="I99" s="28" t="n"/>
+      <c r="J99" s="28" t="n"/>
+      <c r="K99" s="28" t="n"/>
+      <c r="L99" s="28" t="n"/>
+      <c r="M99" s="28" t="n"/>
+      <c r="N99" s="28" t="n"/>
+      <c r="O99" s="28" t="n"/>
+      <c r="P99" s="28" t="n"/>
+      <c r="Q99" s="28" t="n"/>
+      <c r="R99" s="28" t="n"/>
+      <c r="S99" s="28" t="n"/>
+      <c r="T99" s="28" t="n"/>
+      <c r="U99" s="28" t="n"/>
+      <c r="V99" s="28" t="n"/>
+      <c r="W99" s="28" t="n"/>
+      <c r="X99" s="28" t="n"/>
+      <c r="Y99" s="28" t="n"/>
+      <c r="Z99" s="28" t="n"/>
+      <c r="AA99" s="28" t="n"/>
+      <c r="AB99" s="28" t="n"/>
+      <c r="AC99" s="28" t="n"/>
+      <c r="AD99" s="28" t="n"/>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="27" t="n"/>
+      <c r="B100" s="28" t="n"/>
+      <c r="C100" s="28" t="n"/>
+      <c r="D100" s="28" t="n"/>
+      <c r="E100" s="28" t="n"/>
+      <c r="F100" s="28" t="n"/>
+      <c r="G100" s="28" t="n"/>
+      <c r="H100" s="28" t="n"/>
+      <c r="I100" s="28" t="n"/>
+      <c r="J100" s="28" t="n"/>
+      <c r="K100" s="28" t="n"/>
+      <c r="L100" s="28" t="n"/>
+      <c r="M100" s="28" t="n"/>
+      <c r="N100" s="28" t="n"/>
+      <c r="O100" s="28" t="n"/>
+      <c r="P100" s="28" t="n"/>
+      <c r="Q100" s="28" t="n"/>
+      <c r="R100" s="28" t="n"/>
+      <c r="S100" s="28" t="n"/>
+      <c r="T100" s="28" t="n"/>
+      <c r="U100" s="28" t="n"/>
+      <c r="V100" s="28" t="n"/>
+      <c r="W100" s="28" t="n"/>
+      <c r="X100" s="28" t="n"/>
+      <c r="Y100" s="28" t="n"/>
+      <c r="Z100" s="28" t="n"/>
+      <c r="AA100" s="28" t="n"/>
+      <c r="AB100" s="28" t="n"/>
+      <c r="AC100" s="28" t="n"/>
+      <c r="AD100" s="28" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="27" t="n"/>
+      <c r="B101" s="28" t="n"/>
+      <c r="C101" s="28" t="n"/>
+      <c r="D101" s="28" t="n"/>
+      <c r="E101" s="28" t="n"/>
+      <c r="F101" s="28" t="n"/>
+      <c r="G101" s="28" t="n"/>
+      <c r="H101" s="28" t="n"/>
+      <c r="I101" s="28" t="n"/>
+      <c r="J101" s="28" t="n"/>
+      <c r="K101" s="28" t="n"/>
+      <c r="L101" s="28" t="n"/>
+      <c r="M101" s="28" t="n"/>
+      <c r="N101" s="28" t="n"/>
+      <c r="O101" s="28" t="n"/>
+      <c r="P101" s="28" t="n"/>
+      <c r="Q101" s="28" t="n"/>
+      <c r="R101" s="28" t="n"/>
+      <c r="S101" s="28" t="n"/>
+      <c r="T101" s="28" t="n"/>
+      <c r="U101" s="28" t="n"/>
+      <c r="V101" s="28" t="n"/>
+      <c r="W101" s="28" t="n"/>
+      <c r="X101" s="28" t="n"/>
+      <c r="Y101" s="28" t="n"/>
+      <c r="Z101" s="28" t="n"/>
+      <c r="AA101" s="28" t="n"/>
+      <c r="AB101" s="28" t="n"/>
+      <c r="AC101" s="28" t="n"/>
+      <c r="AD101" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3161,10 +4817,10 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD58"/>
+  <dimension ref="A1:AD101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
     <col width="3.7" customWidth="1" min="3" max="3"/>
     <col width="3.7" customWidth="1" min="4" max="4"/>
@@ -3576,10 +5232,10 @@
       </c>
       <c r="AD7" s="13" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Núcleo del proyecto</t>
+          <t>1. Núcleo del proyecto</t>
         </is>
       </c>
       <c r="B8" s="22" t="n"/>
@@ -3616,10 +5272,10 @@
         </is>
       </c>
     </row>
-    <row r="9" outlineLevel="1" ht="15" customHeight="1">
+    <row r="9" outlineLevel="1" ht="14" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>1.1 Estructura MVC y rutas</t>
         </is>
       </c>
       <c r="B9" s="22" t="n"/>
@@ -3656,10 +5312,10 @@
         </is>
       </c>
     </row>
-    <row r="10" outlineLevel="1" ht="15" customHeight="1">
+    <row r="10" outlineLevel="1" ht="14" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>1.2 Modelo de base de datos</t>
         </is>
       </c>
       <c r="B10" s="22" t="n"/>
@@ -3696,10 +5352,10 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Acceso, registro y sesión</t>
+    <row r="11" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>1.3 Conexión y configuración</t>
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
@@ -3736,10 +5392,10 @@
         </is>
       </c>
     </row>
-    <row r="12" outlineLevel="1" ht="15" customHeight="1">
+    <row r="12" outlineLevel="1" ht="14" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>1.4 Testeo</t>
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
@@ -3776,10 +5432,10 @@
         </is>
       </c>
     </row>
-    <row r="13" outlineLevel="1" ht="15" customHeight="1">
+    <row r="13" outlineLevel="1" ht="14" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>1.5 Documentación</t>
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
@@ -3816,10 +5472,10 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Recuperación de cuenta y tickets</t>
+          <t>2. Acceso, registro y sesión</t>
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
@@ -3856,10 +5512,10 @@
         </is>
       </c>
     </row>
-    <row r="15" outlineLevel="1" ht="15" customHeight="1">
+    <row r="15" outlineLevel="1" ht="14" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>2.1 Codificación de la sesión</t>
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
@@ -3896,10 +5552,10 @@
         </is>
       </c>
     </row>
-    <row r="16" outlineLevel="1" ht="15" customHeight="1">
+    <row r="16" outlineLevel="1" ht="14" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>2.2 Creación del formulario</t>
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
@@ -3936,10 +5592,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>Perfil, contraseña y baja</t>
+    <row r="17" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>2.3 Validación del formulario</t>
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
@@ -3976,10 +5632,10 @@
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="15" customHeight="1">
+    <row r="18" outlineLevel="1" ht="14" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>2.4 Testeo</t>
         </is>
       </c>
       <c r="B18" s="22" t="n"/>
@@ -4016,10 +5672,10 @@
         </is>
       </c>
     </row>
-    <row r="19" outlineLevel="1" ht="15" customHeight="1">
+    <row r="19" outlineLevel="1" ht="14" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>2.5 Documentación</t>
         </is>
       </c>
       <c r="B19" s="22" t="n"/>
@@ -4056,10 +5712,10 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Actividades y horario</t>
+          <t>3. Recuperación de cuenta y tickets</t>
         </is>
       </c>
       <c r="B20" s="22" t="n"/>
@@ -4090,16 +5746,16 @@
       <c r="AA20" s="22" t="n"/>
       <c r="AB20" s="22" t="n"/>
       <c r="AC20" s="22" t="n"/>
-      <c r="AD20" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD20" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" outlineLevel="1" ht="14" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>3.1 Formulario de recuperación</t>
         </is>
       </c>
       <c r="B21" s="22" t="n"/>
@@ -4130,16 +5786,16 @@
       <c r="AA21" s="22" t="n"/>
       <c r="AB21" s="22" t="n"/>
       <c r="AC21" s="22" t="n"/>
-      <c r="AD21" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD21" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1" ht="14" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>3.2 Tickets de la cuenta</t>
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
@@ -4170,16 +5826,16 @@
       <c r="AA22" s="22" t="n"/>
       <c r="AB22" s="22" t="n"/>
       <c r="AC22" s="22" t="n"/>
-      <c r="AD22" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Inscripciones y reservas</t>
+      <c r="AD22" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>3.3 Envío del enlace</t>
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
@@ -4210,16 +5866,16 @@
       <c r="AA23" s="22" t="n"/>
       <c r="AB23" s="22" t="n"/>
       <c r="AC23" s="22" t="n"/>
-      <c r="AD23" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD23" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" outlineLevel="1" ht="14" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>3.4 Testeo</t>
         </is>
       </c>
       <c r="B24" s="22" t="n"/>
@@ -4250,16 +5906,16 @@
       <c r="AA24" s="22" t="n"/>
       <c r="AB24" s="22" t="n"/>
       <c r="AC24" s="22" t="n"/>
-      <c r="AD24" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD24" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" outlineLevel="1" ht="14" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>3.5 Documentación</t>
         </is>
       </c>
       <c r="B25" s="22" t="n"/>
@@ -4290,16 +5946,16 @@
       <c r="AA25" s="22" t="n"/>
       <c r="AB25" s="22" t="n"/>
       <c r="AC25" s="22" t="n"/>
-      <c r="AD25" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+      <c r="AD25" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>Suscripciones</t>
+          <t>4. Perfil, contraseña y baja</t>
         </is>
       </c>
       <c r="B26" s="22" t="n"/>
@@ -4330,16 +5986,16 @@
       <c r="AA26" s="22" t="n"/>
       <c r="AB26" s="22" t="n"/>
       <c r="AC26" s="22" t="n"/>
-      <c r="AD26" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD26" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1" ht="14" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>4.1 Edición del perfil</t>
         </is>
       </c>
       <c r="B27" s="22" t="n"/>
@@ -4370,16 +6026,16 @@
       <c r="AA27" s="22" t="n"/>
       <c r="AB27" s="22" t="n"/>
       <c r="AC27" s="22" t="n"/>
-      <c r="AD27" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD27" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" outlineLevel="1" ht="14" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>4.2 Cambio de contraseña</t>
         </is>
       </c>
       <c r="B28" s="22" t="n"/>
@@ -4410,19 +6066,19 @@
       <c r="AA28" s="22" t="n"/>
       <c r="AB28" s="22" t="n"/>
       <c r="AC28" s="22" t="n"/>
-      <c r="AD28" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>Pagos con Stripe</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="n"/>
+      <c r="AD28" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>4.3 Baja y reactivación</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
       <c r="C29" s="22" t="n"/>
       <c r="D29" s="22" t="n"/>
       <c r="E29" s="22" t="n"/>
@@ -4450,20 +6106,20 @@
       <c r="AA29" s="22" t="n"/>
       <c r="AB29" s="22" t="n"/>
       <c r="AC29" s="22" t="n"/>
-      <c r="AD29" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD29" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1" ht="14" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>4.4 Testeo</t>
         </is>
       </c>
       <c r="B30" s="22" t="n"/>
-      <c r="C30" s="26" t="n"/>
+      <c r="C30" s="22" t="n"/>
       <c r="D30" s="22" t="n"/>
       <c r="E30" s="22" t="n"/>
       <c r="F30" s="22" t="n"/>
@@ -4490,20 +6146,20 @@
       <c r="AA30" s="22" t="n"/>
       <c r="AB30" s="22" t="n"/>
       <c r="AC30" s="22" t="n"/>
-      <c r="AD30" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD30" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1" ht="14" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>4.5 Documentación</t>
         </is>
       </c>
       <c r="B31" s="22" t="n"/>
-      <c r="C31" s="26" t="n"/>
+      <c r="C31" s="22" t="n"/>
       <c r="D31" s="22" t="n"/>
       <c r="E31" s="22" t="n"/>
       <c r="F31" s="22" t="n"/>
@@ -4530,21 +6186,21 @@
       <c r="AA31" s="22" t="n"/>
       <c r="AB31" s="22" t="n"/>
       <c r="AC31" s="22" t="n"/>
-      <c r="AD31" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+      <c r="AD31" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>Panel de administración</t>
+          <t>5. Actividades y horario</t>
         </is>
       </c>
       <c r="B32" s="22" t="n"/>
       <c r="C32" s="22" t="n"/>
-      <c r="D32" s="27" t="n"/>
+      <c r="D32" s="22" t="n"/>
       <c r="E32" s="22" t="n"/>
       <c r="F32" s="22" t="n"/>
       <c r="G32" s="22" t="n"/>
@@ -4570,22 +6226,22 @@
       <c r="AA32" s="22" t="n"/>
       <c r="AB32" s="22" t="n"/>
       <c r="AC32" s="22" t="n"/>
-      <c r="AD32" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD32" s="25" t="inlineStr">
+        <is>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1" ht="14" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>5.1 Listado de actividades</t>
         </is>
       </c>
       <c r="B33" s="22" t="n"/>
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="27" t="n"/>
+      <c r="E33" s="22" t="n"/>
       <c r="F33" s="22" t="n"/>
       <c r="G33" s="22" t="n"/>
       <c r="H33" s="22" t="n"/>
@@ -4610,22 +6266,22 @@
       <c r="AA33" s="22" t="n"/>
       <c r="AB33" s="22" t="n"/>
       <c r="AC33" s="22" t="n"/>
-      <c r="AD33" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD33" s="25" t="inlineStr">
+        <is>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1" ht="14" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>5.2 Horario del centro</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="22" t="n"/>
-      <c r="E34" s="27" t="n"/>
+      <c r="E34" s="22" t="n"/>
       <c r="F34" s="22" t="n"/>
       <c r="G34" s="22" t="n"/>
       <c r="H34" s="22" t="n"/>
@@ -4650,23 +6306,23 @@
       <c r="AA34" s="22" t="n"/>
       <c r="AB34" s="22" t="n"/>
       <c r="AC34" s="22" t="n"/>
-      <c r="AD34" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>Gestión de clientes</t>
+      <c r="AD34" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>5.3 Alta y edición</t>
         </is>
       </c>
       <c r="B35" s="22" t="n"/>
       <c r="C35" s="22" t="n"/>
       <c r="D35" s="22" t="n"/>
       <c r="E35" s="22" t="n"/>
-      <c r="F35" s="28" t="n"/>
+      <c r="F35" s="22" t="n"/>
       <c r="G35" s="22" t="n"/>
       <c r="H35" s="22" t="n"/>
       <c r="I35" s="22" t="n"/>
@@ -4690,16 +6346,16 @@
       <c r="AA35" s="22" t="n"/>
       <c r="AB35" s="22" t="n"/>
       <c r="AC35" s="22" t="n"/>
-      <c r="AD35" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD35" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" outlineLevel="1" ht="14" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>5.4 Testeo</t>
         </is>
       </c>
       <c r="B36" s="22" t="n"/>
@@ -4709,7 +6365,7 @@
       <c r="F36" s="22" t="n"/>
       <c r="G36" s="22" t="n"/>
       <c r="H36" s="22" t="n"/>
-      <c r="I36" s="28" t="n"/>
+      <c r="I36" s="22" t="n"/>
       <c r="J36" s="22" t="n"/>
       <c r="K36" s="22" t="n"/>
       <c r="L36" s="22" t="n"/>
@@ -4730,16 +6386,16 @@
       <c r="AA36" s="22" t="n"/>
       <c r="AB36" s="22" t="n"/>
       <c r="AC36" s="22" t="n"/>
-      <c r="AD36" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD36" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1" ht="14" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>5.5 Documentación</t>
         </is>
       </c>
       <c r="B37" s="22" t="n"/>
@@ -4749,7 +6405,7 @@
       <c r="F37" s="22" t="n"/>
       <c r="G37" s="22" t="n"/>
       <c r="H37" s="22" t="n"/>
-      <c r="I37" s="28" t="n"/>
+      <c r="I37" s="22" t="n"/>
       <c r="J37" s="22" t="n"/>
       <c r="K37" s="22" t="n"/>
       <c r="L37" s="22" t="n"/>
@@ -4770,16 +6426,16 @@
       <c r="AA37" s="22" t="n"/>
       <c r="AB37" s="22" t="n"/>
       <c r="AC37" s="22" t="n"/>
-      <c r="AD37" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
+      <c r="AD37" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>Monitores y solicitudes</t>
+          <t>6. Inscripciones y reservas</t>
         </is>
       </c>
       <c r="B38" s="22" t="n"/>
@@ -4790,8 +6446,8 @@
       <c r="G38" s="22" t="n"/>
       <c r="H38" s="22" t="n"/>
       <c r="I38" s="22" t="n"/>
-      <c r="J38" s="21" t="n"/>
-      <c r="K38" s="21" t="n"/>
+      <c r="J38" s="22" t="n"/>
+      <c r="K38" s="22" t="n"/>
       <c r="L38" s="22" t="n"/>
       <c r="M38" s="22" t="n"/>
       <c r="N38" s="22" t="n"/>
@@ -4810,16 +6466,16 @@
       <c r="AA38" s="22" t="n"/>
       <c r="AB38" s="22" t="n"/>
       <c r="AC38" s="22" t="n"/>
-      <c r="AD38" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD38" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" outlineLevel="1" ht="14" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>6.1 Formulario de inscripción</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -4832,7 +6488,7 @@
       <c r="I39" s="22" t="n"/>
       <c r="J39" s="22" t="n"/>
       <c r="K39" s="22" t="n"/>
-      <c r="L39" s="21" t="n"/>
+      <c r="L39" s="22" t="n"/>
       <c r="M39" s="22" t="n"/>
       <c r="N39" s="22" t="n"/>
       <c r="O39" s="22" t="n"/>
@@ -4850,16 +6506,16 @@
       <c r="AA39" s="22" t="n"/>
       <c r="AB39" s="22" t="n"/>
       <c r="AC39" s="22" t="n"/>
-      <c r="AD39" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD39" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" outlineLevel="1" ht="14" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>6.2 Control de plazas</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -4872,7 +6528,7 @@
       <c r="I40" s="22" t="n"/>
       <c r="J40" s="22" t="n"/>
       <c r="K40" s="22" t="n"/>
-      <c r="L40" s="21" t="n"/>
+      <c r="L40" s="22" t="n"/>
       <c r="M40" s="22" t="n"/>
       <c r="N40" s="22" t="n"/>
       <c r="O40" s="22" t="n"/>
@@ -4890,16 +6546,16 @@
       <c r="AA40" s="22" t="n"/>
       <c r="AB40" s="22" t="n"/>
       <c r="AC40" s="22" t="n"/>
-      <c r="AD40" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>Salas y materiales</t>
+      <c r="AD40" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>6.3 Reservas del cliente</t>
         </is>
       </c>
       <c r="B41" s="22" t="n"/>
@@ -4913,7 +6569,7 @@
       <c r="J41" s="22" t="n"/>
       <c r="K41" s="22" t="n"/>
       <c r="L41" s="22" t="n"/>
-      <c r="M41" s="25" t="n"/>
+      <c r="M41" s="22" t="n"/>
       <c r="N41" s="22" t="n"/>
       <c r="O41" s="22" t="n"/>
       <c r="P41" s="22" t="n"/>
@@ -4930,16 +6586,16 @@
       <c r="AA41" s="22" t="n"/>
       <c r="AB41" s="22" t="n"/>
       <c r="AC41" s="22" t="n"/>
-      <c r="AD41" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD41" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" outlineLevel="1" ht="14" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>6.4 Testeo</t>
         </is>
       </c>
       <c r="B42" s="22" t="n"/>
@@ -4956,7 +6612,7 @@
       <c r="M42" s="22" t="n"/>
       <c r="N42" s="22" t="n"/>
       <c r="O42" s="22" t="n"/>
-      <c r="P42" s="25" t="n"/>
+      <c r="P42" s="22" t="n"/>
       <c r="Q42" s="22" t="n"/>
       <c r="R42" s="22" t="n"/>
       <c r="S42" s="22" t="n"/>
@@ -4970,16 +6626,16 @@
       <c r="AA42" s="22" t="n"/>
       <c r="AB42" s="22" t="n"/>
       <c r="AC42" s="22" t="n"/>
-      <c r="AD42" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD42" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" outlineLevel="1" ht="14" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>6.5 Documentación</t>
         </is>
       </c>
       <c r="B43" s="22" t="n"/>
@@ -4996,7 +6652,7 @@
       <c r="M43" s="22" t="n"/>
       <c r="N43" s="22" t="n"/>
       <c r="O43" s="22" t="n"/>
-      <c r="P43" s="25" t="n"/>
+      <c r="P43" s="22" t="n"/>
       <c r="Q43" s="22" t="n"/>
       <c r="R43" s="22" t="n"/>
       <c r="S43" s="22" t="n"/>
@@ -5010,16 +6666,16 @@
       <c r="AA43" s="22" t="n"/>
       <c r="AB43" s="22" t="n"/>
       <c r="AC43" s="22" t="n"/>
-      <c r="AD43" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
+      <c r="AD43" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>Fisioterapia y citas</t>
+          <t>7. Suscripciones</t>
         </is>
       </c>
       <c r="B44" s="22" t="n"/>
@@ -5037,8 +6693,8 @@
       <c r="N44" s="22" t="n"/>
       <c r="O44" s="22" t="n"/>
       <c r="P44" s="22" t="n"/>
-      <c r="Q44" s="26" t="n"/>
-      <c r="R44" s="26" t="n"/>
+      <c r="Q44" s="22" t="n"/>
+      <c r="R44" s="22" t="n"/>
       <c r="S44" s="22" t="n"/>
       <c r="T44" s="22" t="n"/>
       <c r="U44" s="22" t="n"/>
@@ -5050,16 +6706,16 @@
       <c r="AA44" s="22" t="n"/>
       <c r="AB44" s="22" t="n"/>
       <c r="AC44" s="22" t="n"/>
-      <c r="AD44" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD44" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" outlineLevel="1" ht="14" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>7.1 Planes de suscripción</t>
         </is>
       </c>
       <c r="B45" s="22" t="n"/>
@@ -5079,7 +6735,7 @@
       <c r="P45" s="22" t="n"/>
       <c r="Q45" s="22" t="n"/>
       <c r="R45" s="22" t="n"/>
-      <c r="S45" s="26" t="n"/>
+      <c r="S45" s="22" t="n"/>
       <c r="T45" s="22" t="n"/>
       <c r="U45" s="22" t="n"/>
       <c r="V45" s="22" t="n"/>
@@ -5090,16 +6746,16 @@
       <c r="AA45" s="22" t="n"/>
       <c r="AB45" s="22" t="n"/>
       <c r="AC45" s="22" t="n"/>
-      <c r="AD45" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD45" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1" ht="14" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>7.2 Alta del cliente</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -5119,7 +6775,7 @@
       <c r="P46" s="22" t="n"/>
       <c r="Q46" s="22" t="n"/>
       <c r="R46" s="22" t="n"/>
-      <c r="S46" s="26" t="n"/>
+      <c r="S46" s="22" t="n"/>
       <c r="T46" s="22" t="n"/>
       <c r="U46" s="22" t="n"/>
       <c r="V46" s="22" t="n"/>
@@ -5130,16 +6786,16 @@
       <c r="AA46" s="22" t="n"/>
       <c r="AB46" s="22" t="n"/>
       <c r="AC46" s="22" t="n"/>
-      <c r="AD46" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>Comentarios, feedback y seguridad</t>
+      <c r="AD46" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>7.3 Renovación y baja</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -5160,26 +6816,26 @@
       <c r="Q47" s="22" t="n"/>
       <c r="R47" s="22" t="n"/>
       <c r="S47" s="22" t="n"/>
-      <c r="T47" s="27" t="n"/>
-      <c r="U47" s="27" t="n"/>
-      <c r="V47" s="27" t="n"/>
-      <c r="W47" s="27" t="n"/>
+      <c r="T47" s="22" t="n"/>
+      <c r="U47" s="22" t="n"/>
+      <c r="V47" s="22" t="n"/>
+      <c r="W47" s="22" t="n"/>
       <c r="X47" s="22" t="n"/>
       <c r="Y47" s="22" t="n"/>
       <c r="Z47" s="22" t="n"/>
       <c r="AA47" s="22" t="n"/>
       <c r="AB47" s="22" t="n"/>
       <c r="AC47" s="22" t="n"/>
-      <c r="AD47" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD47" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1" ht="14" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>7.4 Testeo</t>
         </is>
       </c>
       <c r="B48" s="22" t="n"/>
@@ -5204,22 +6860,22 @@
       <c r="U48" s="22" t="n"/>
       <c r="V48" s="22" t="n"/>
       <c r="W48" s="22" t="n"/>
-      <c r="X48" s="27" t="n"/>
+      <c r="X48" s="22" t="n"/>
       <c r="Y48" s="22" t="n"/>
       <c r="Z48" s="22" t="n"/>
       <c r="AA48" s="22" t="n"/>
       <c r="AB48" s="22" t="n"/>
       <c r="AC48" s="22" t="n"/>
-      <c r="AD48" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD48" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1" ht="14" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>7.5 Documentación</t>
         </is>
       </c>
       <c r="B49" s="22" t="n"/>
@@ -5244,26 +6900,26 @@
       <c r="U49" s="22" t="n"/>
       <c r="V49" s="22" t="n"/>
       <c r="W49" s="22" t="n"/>
-      <c r="X49" s="27" t="n"/>
+      <c r="X49" s="22" t="n"/>
       <c r="Y49" s="22" t="n"/>
       <c r="Z49" s="22" t="n"/>
       <c r="AA49" s="22" t="n"/>
       <c r="AB49" s="22" t="n"/>
       <c r="AC49" s="22" t="n"/>
-      <c r="AD49" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
+      <c r="AD49" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>Interfaz Tailwind, correo y cierre</t>
-        </is>
-      </c>
-      <c r="B50" s="22" t="n"/>
-      <c r="C50" s="22" t="n"/>
+          <t>8. Pagos con Stripe</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="21" t="n"/>
       <c r="D50" s="22" t="n"/>
       <c r="E50" s="22" t="n"/>
       <c r="F50" s="22" t="n"/>
@@ -5285,21 +6941,21 @@
       <c r="V50" s="22" t="n"/>
       <c r="W50" s="22" t="n"/>
       <c r="X50" s="22" t="n"/>
-      <c r="Y50" s="28" t="n"/>
-      <c r="Z50" s="28" t="n"/>
+      <c r="Y50" s="22" t="n"/>
+      <c r="Z50" s="22" t="n"/>
       <c r="AA50" s="22" t="n"/>
       <c r="AB50" s="22" t="n"/>
       <c r="AC50" s="22" t="n"/>
-      <c r="AD50" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AD50" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1" ht="14" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>8.1 Pasarela de Stripe</t>
         </is>
       </c>
       <c r="B51" s="22" t="n"/>
@@ -5327,22 +6983,22 @@
       <c r="X51" s="22" t="n"/>
       <c r="Y51" s="22" t="n"/>
       <c r="Z51" s="22" t="n"/>
-      <c r="AA51" s="28" t="n"/>
-      <c r="AB51" s="28" t="n"/>
-      <c r="AC51" s="28" t="n"/>
-      <c r="AD51" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" outlineLevel="1" ht="15" customHeight="1">
+      <c r="AA51" s="22" t="n"/>
+      <c r="AB51" s="22" t="n"/>
+      <c r="AC51" s="22" t="n"/>
+      <c r="AD51" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" outlineLevel="1" ht="14" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
-        </is>
-      </c>
-      <c r="B52" s="22" t="n"/>
+          <t>8.2 Confirmación del pago</t>
+        </is>
+      </c>
+      <c r="B52" s="21" t="n"/>
       <c r="C52" s="22" t="n"/>
       <c r="D52" s="22" t="n"/>
       <c r="E52" s="22" t="n"/>
@@ -5367,206 +7023,1942 @@
       <c r="X52" s="22" t="n"/>
       <c r="Y52" s="22" t="n"/>
       <c r="Z52" s="22" t="n"/>
-      <c r="AA52" s="28" t="n"/>
-      <c r="AB52" s="28" t="n"/>
-      <c r="AC52" s="28" t="n"/>
-      <c r="AD52" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="31" t="n"/>
-      <c r="B53" s="32" t="n"/>
-      <c r="C53" s="32" t="n"/>
-      <c r="D53" s="32" t="n"/>
-      <c r="E53" s="32" t="n"/>
-      <c r="F53" s="32" t="n"/>
-      <c r="G53" s="32" t="n"/>
-      <c r="H53" s="32" t="n"/>
-      <c r="I53" s="32" t="n"/>
-      <c r="J53" s="32" t="n"/>
-      <c r="K53" s="32" t="n"/>
-      <c r="L53" s="32" t="n"/>
-      <c r="M53" s="32" t="n"/>
-      <c r="N53" s="32" t="n"/>
-      <c r="O53" s="32" t="n"/>
-      <c r="P53" s="32" t="n"/>
-      <c r="Q53" s="32" t="n"/>
-      <c r="R53" s="32" t="n"/>
-      <c r="S53" s="32" t="n"/>
-      <c r="T53" s="32" t="n"/>
-      <c r="U53" s="32" t="n"/>
-      <c r="V53" s="32" t="n"/>
-      <c r="W53" s="32" t="n"/>
-      <c r="X53" s="32" t="n"/>
-      <c r="Y53" s="32" t="n"/>
-      <c r="Z53" s="32" t="n"/>
-      <c r="AA53" s="32" t="n"/>
-      <c r="AB53" s="32" t="n"/>
-      <c r="AC53" s="32" t="n"/>
-      <c r="AD53" s="32" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="31" t="n"/>
-      <c r="B54" s="32" t="n"/>
-      <c r="C54" s="32" t="n"/>
-      <c r="D54" s="32" t="n"/>
-      <c r="E54" s="32" t="n"/>
-      <c r="F54" s="32" t="n"/>
-      <c r="G54" s="32" t="n"/>
-      <c r="H54" s="32" t="n"/>
-      <c r="I54" s="32" t="n"/>
-      <c r="J54" s="32" t="n"/>
-      <c r="K54" s="32" t="n"/>
-      <c r="L54" s="32" t="n"/>
-      <c r="M54" s="32" t="n"/>
-      <c r="N54" s="32" t="n"/>
-      <c r="O54" s="32" t="n"/>
-      <c r="P54" s="32" t="n"/>
-      <c r="Q54" s="32" t="n"/>
-      <c r="R54" s="32" t="n"/>
-      <c r="S54" s="32" t="n"/>
-      <c r="T54" s="32" t="n"/>
-      <c r="U54" s="32" t="n"/>
-      <c r="V54" s="32" t="n"/>
-      <c r="W54" s="32" t="n"/>
-      <c r="X54" s="32" t="n"/>
-      <c r="Y54" s="32" t="n"/>
-      <c r="Z54" s="32" t="n"/>
-      <c r="AA54" s="32" t="n"/>
-      <c r="AB54" s="32" t="n"/>
-      <c r="AC54" s="32" t="n"/>
-      <c r="AD54" s="32" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="31" t="n"/>
-      <c r="B55" s="32" t="n"/>
-      <c r="C55" s="32" t="n"/>
-      <c r="D55" s="32" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
-      <c r="G55" s="32" t="n"/>
-      <c r="H55" s="32" t="n"/>
-      <c r="I55" s="32" t="n"/>
-      <c r="J55" s="32" t="n"/>
-      <c r="K55" s="32" t="n"/>
-      <c r="L55" s="32" t="n"/>
-      <c r="M55" s="32" t="n"/>
-      <c r="N55" s="32" t="n"/>
-      <c r="O55" s="32" t="n"/>
-      <c r="P55" s="32" t="n"/>
-      <c r="Q55" s="32" t="n"/>
-      <c r="R55" s="32" t="n"/>
-      <c r="S55" s="32" t="n"/>
-      <c r="T55" s="32" t="n"/>
-      <c r="U55" s="32" t="n"/>
-      <c r="V55" s="32" t="n"/>
-      <c r="W55" s="32" t="n"/>
-      <c r="X55" s="32" t="n"/>
-      <c r="Y55" s="32" t="n"/>
-      <c r="Z55" s="32" t="n"/>
-      <c r="AA55" s="32" t="n"/>
-      <c r="AB55" s="32" t="n"/>
-      <c r="AC55" s="32" t="n"/>
-      <c r="AD55" s="32" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="31" t="n"/>
-      <c r="B56" s="32" t="n"/>
-      <c r="C56" s="32" t="n"/>
-      <c r="D56" s="32" t="n"/>
-      <c r="E56" s="32" t="n"/>
-      <c r="F56" s="32" t="n"/>
-      <c r="G56" s="32" t="n"/>
-      <c r="H56" s="32" t="n"/>
-      <c r="I56" s="32" t="n"/>
-      <c r="J56" s="32" t="n"/>
-      <c r="K56" s="32" t="n"/>
-      <c r="L56" s="32" t="n"/>
-      <c r="M56" s="32" t="n"/>
-      <c r="N56" s="32" t="n"/>
-      <c r="O56" s="32" t="n"/>
-      <c r="P56" s="32" t="n"/>
-      <c r="Q56" s="32" t="n"/>
-      <c r="R56" s="32" t="n"/>
-      <c r="S56" s="32" t="n"/>
-      <c r="T56" s="32" t="n"/>
-      <c r="U56" s="32" t="n"/>
-      <c r="V56" s="32" t="n"/>
-      <c r="W56" s="32" t="n"/>
-      <c r="X56" s="32" t="n"/>
-      <c r="Y56" s="32" t="n"/>
-      <c r="Z56" s="32" t="n"/>
-      <c r="AA56" s="32" t="n"/>
-      <c r="AB56" s="32" t="n"/>
-      <c r="AC56" s="32" t="n"/>
-      <c r="AD56" s="32" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="31" t="n"/>
-      <c r="B57" s="32" t="n"/>
-      <c r="C57" s="32" t="n"/>
-      <c r="D57" s="32" t="n"/>
-      <c r="E57" s="32" t="n"/>
-      <c r="F57" s="32" t="n"/>
-      <c r="G57" s="32" t="n"/>
-      <c r="H57" s="32" t="n"/>
-      <c r="I57" s="32" t="n"/>
-      <c r="J57" s="32" t="n"/>
-      <c r="K57" s="32" t="n"/>
-      <c r="L57" s="32" t="n"/>
-      <c r="M57" s="32" t="n"/>
-      <c r="N57" s="32" t="n"/>
-      <c r="O57" s="32" t="n"/>
-      <c r="P57" s="32" t="n"/>
-      <c r="Q57" s="32" t="n"/>
-      <c r="R57" s="32" t="n"/>
-      <c r="S57" s="32" t="n"/>
-      <c r="T57" s="32" t="n"/>
-      <c r="U57" s="32" t="n"/>
-      <c r="V57" s="32" t="n"/>
-      <c r="W57" s="32" t="n"/>
-      <c r="X57" s="32" t="n"/>
-      <c r="Y57" s="32" t="n"/>
-      <c r="Z57" s="32" t="n"/>
-      <c r="AA57" s="32" t="n"/>
-      <c r="AB57" s="32" t="n"/>
-      <c r="AC57" s="32" t="n"/>
-      <c r="AD57" s="32" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="31" t="n"/>
-      <c r="B58" s="32" t="n"/>
-      <c r="C58" s="32" t="n"/>
-      <c r="D58" s="32" t="n"/>
-      <c r="E58" s="32" t="n"/>
-      <c r="F58" s="32" t="n"/>
-      <c r="G58" s="32" t="n"/>
-      <c r="H58" s="32" t="n"/>
-      <c r="I58" s="32" t="n"/>
-      <c r="J58" s="32" t="n"/>
-      <c r="K58" s="32" t="n"/>
-      <c r="L58" s="32" t="n"/>
-      <c r="M58" s="32" t="n"/>
-      <c r="N58" s="32" t="n"/>
-      <c r="O58" s="32" t="n"/>
-      <c r="P58" s="32" t="n"/>
-      <c r="Q58" s="32" t="n"/>
-      <c r="R58" s="32" t="n"/>
-      <c r="S58" s="32" t="n"/>
-      <c r="T58" s="32" t="n"/>
-      <c r="U58" s="32" t="n"/>
-      <c r="V58" s="32" t="n"/>
-      <c r="W58" s="32" t="n"/>
-      <c r="X58" s="32" t="n"/>
-      <c r="Y58" s="32" t="n"/>
-      <c r="Z58" s="32" t="n"/>
-      <c r="AA58" s="32" t="n"/>
-      <c r="AB58" s="32" t="n"/>
-      <c r="AC58" s="32" t="n"/>
-      <c r="AD58" s="32" t="n"/>
+      <c r="AA52" s="22" t="n"/>
+      <c r="AB52" s="22" t="n"/>
+      <c r="AC52" s="22" t="n"/>
+      <c r="AD52" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>8.3 Pago cancelado</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="22" t="n"/>
+      <c r="F53" s="22" t="n"/>
+      <c r="G53" s="22" t="n"/>
+      <c r="H53" s="22" t="n"/>
+      <c r="I53" s="22" t="n"/>
+      <c r="J53" s="22" t="n"/>
+      <c r="K53" s="22" t="n"/>
+      <c r="L53" s="22" t="n"/>
+      <c r="M53" s="22" t="n"/>
+      <c r="N53" s="22" t="n"/>
+      <c r="O53" s="22" t="n"/>
+      <c r="P53" s="22" t="n"/>
+      <c r="Q53" s="22" t="n"/>
+      <c r="R53" s="22" t="n"/>
+      <c r="S53" s="22" t="n"/>
+      <c r="T53" s="22" t="n"/>
+      <c r="U53" s="22" t="n"/>
+      <c r="V53" s="22" t="n"/>
+      <c r="W53" s="22" t="n"/>
+      <c r="X53" s="22" t="n"/>
+      <c r="Y53" s="22" t="n"/>
+      <c r="Z53" s="22" t="n"/>
+      <c r="AA53" s="22" t="n"/>
+      <c r="AB53" s="22" t="n"/>
+      <c r="AC53" s="22" t="n"/>
+      <c r="AD53" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>8.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
+      <c r="G54" s="22" t="n"/>
+      <c r="H54" s="22" t="n"/>
+      <c r="I54" s="22" t="n"/>
+      <c r="J54" s="22" t="n"/>
+      <c r="K54" s="22" t="n"/>
+      <c r="L54" s="22" t="n"/>
+      <c r="M54" s="22" t="n"/>
+      <c r="N54" s="22" t="n"/>
+      <c r="O54" s="22" t="n"/>
+      <c r="P54" s="22" t="n"/>
+      <c r="Q54" s="22" t="n"/>
+      <c r="R54" s="22" t="n"/>
+      <c r="S54" s="22" t="n"/>
+      <c r="T54" s="22" t="n"/>
+      <c r="U54" s="22" t="n"/>
+      <c r="V54" s="22" t="n"/>
+      <c r="W54" s="22" t="n"/>
+      <c r="X54" s="22" t="n"/>
+      <c r="Y54" s="22" t="n"/>
+      <c r="Z54" s="22" t="n"/>
+      <c r="AA54" s="22" t="n"/>
+      <c r="AB54" s="22" t="n"/>
+      <c r="AC54" s="22" t="n"/>
+      <c r="AD54" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>8.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="n"/>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="22" t="n"/>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="22" t="n"/>
+      <c r="H55" s="22" t="n"/>
+      <c r="I55" s="22" t="n"/>
+      <c r="J55" s="22" t="n"/>
+      <c r="K55" s="22" t="n"/>
+      <c r="L55" s="22" t="n"/>
+      <c r="M55" s="22" t="n"/>
+      <c r="N55" s="22" t="n"/>
+      <c r="O55" s="22" t="n"/>
+      <c r="P55" s="22" t="n"/>
+      <c r="Q55" s="22" t="n"/>
+      <c r="R55" s="22" t="n"/>
+      <c r="S55" s="22" t="n"/>
+      <c r="T55" s="22" t="n"/>
+      <c r="U55" s="22" t="n"/>
+      <c r="V55" s="22" t="n"/>
+      <c r="W55" s="22" t="n"/>
+      <c r="X55" s="22" t="n"/>
+      <c r="Y55" s="22" t="n"/>
+      <c r="Z55" s="22" t="n"/>
+      <c r="AA55" s="22" t="n"/>
+      <c r="AB55" s="22" t="n"/>
+      <c r="AC55" s="22" t="n"/>
+      <c r="AD55" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>9. Panel de administración</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="n"/>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="21" t="n"/>
+      <c r="F56" s="22" t="n"/>
+      <c r="G56" s="22" t="n"/>
+      <c r="H56" s="22" t="n"/>
+      <c r="I56" s="22" t="n"/>
+      <c r="J56" s="22" t="n"/>
+      <c r="K56" s="22" t="n"/>
+      <c r="L56" s="22" t="n"/>
+      <c r="M56" s="22" t="n"/>
+      <c r="N56" s="22" t="n"/>
+      <c r="O56" s="22" t="n"/>
+      <c r="P56" s="22" t="n"/>
+      <c r="Q56" s="22" t="n"/>
+      <c r="R56" s="22" t="n"/>
+      <c r="S56" s="22" t="n"/>
+      <c r="T56" s="22" t="n"/>
+      <c r="U56" s="22" t="n"/>
+      <c r="V56" s="22" t="n"/>
+      <c r="W56" s="22" t="n"/>
+      <c r="X56" s="22" t="n"/>
+      <c r="Y56" s="22" t="n"/>
+      <c r="Z56" s="22" t="n"/>
+      <c r="AA56" s="22" t="n"/>
+      <c r="AB56" s="22" t="n"/>
+      <c r="AC56" s="22" t="n"/>
+      <c r="AD56" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>9.1 Inicio del panel</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="n"/>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="22" t="n"/>
+      <c r="F57" s="22" t="n"/>
+      <c r="G57" s="22" t="n"/>
+      <c r="H57" s="22" t="n"/>
+      <c r="I57" s="22" t="n"/>
+      <c r="J57" s="22" t="n"/>
+      <c r="K57" s="22" t="n"/>
+      <c r="L57" s="22" t="n"/>
+      <c r="M57" s="22" t="n"/>
+      <c r="N57" s="22" t="n"/>
+      <c r="O57" s="22" t="n"/>
+      <c r="P57" s="22" t="n"/>
+      <c r="Q57" s="22" t="n"/>
+      <c r="R57" s="22" t="n"/>
+      <c r="S57" s="22" t="n"/>
+      <c r="T57" s="22" t="n"/>
+      <c r="U57" s="22" t="n"/>
+      <c r="V57" s="22" t="n"/>
+      <c r="W57" s="22" t="n"/>
+      <c r="X57" s="22" t="n"/>
+      <c r="Y57" s="22" t="n"/>
+      <c r="Z57" s="22" t="n"/>
+      <c r="AA57" s="22" t="n"/>
+      <c r="AB57" s="22" t="n"/>
+      <c r="AC57" s="22" t="n"/>
+      <c r="AD57" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>9.2 Menú y permisos</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="n"/>
+      <c r="C58" s="22" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="22" t="n"/>
+      <c r="F58" s="22" t="n"/>
+      <c r="G58" s="22" t="n"/>
+      <c r="H58" s="22" t="n"/>
+      <c r="I58" s="22" t="n"/>
+      <c r="J58" s="22" t="n"/>
+      <c r="K58" s="22" t="n"/>
+      <c r="L58" s="22" t="n"/>
+      <c r="M58" s="22" t="n"/>
+      <c r="N58" s="22" t="n"/>
+      <c r="O58" s="22" t="n"/>
+      <c r="P58" s="22" t="n"/>
+      <c r="Q58" s="22" t="n"/>
+      <c r="R58" s="22" t="n"/>
+      <c r="S58" s="22" t="n"/>
+      <c r="T58" s="22" t="n"/>
+      <c r="U58" s="22" t="n"/>
+      <c r="V58" s="22" t="n"/>
+      <c r="W58" s="22" t="n"/>
+      <c r="X58" s="22" t="n"/>
+      <c r="Y58" s="22" t="n"/>
+      <c r="Z58" s="22" t="n"/>
+      <c r="AA58" s="22" t="n"/>
+      <c r="AB58" s="22" t="n"/>
+      <c r="AC58" s="22" t="n"/>
+      <c r="AD58" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>9.3 Listados del panel</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="n"/>
+      <c r="C59" s="22" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="22" t="n"/>
+      <c r="F59" s="22" t="n"/>
+      <c r="G59" s="22" t="n"/>
+      <c r="H59" s="22" t="n"/>
+      <c r="I59" s="22" t="n"/>
+      <c r="J59" s="22" t="n"/>
+      <c r="K59" s="22" t="n"/>
+      <c r="L59" s="22" t="n"/>
+      <c r="M59" s="22" t="n"/>
+      <c r="N59" s="22" t="n"/>
+      <c r="O59" s="22" t="n"/>
+      <c r="P59" s="22" t="n"/>
+      <c r="Q59" s="22" t="n"/>
+      <c r="R59" s="22" t="n"/>
+      <c r="S59" s="22" t="n"/>
+      <c r="T59" s="22" t="n"/>
+      <c r="U59" s="22" t="n"/>
+      <c r="V59" s="22" t="n"/>
+      <c r="W59" s="22" t="n"/>
+      <c r="X59" s="22" t="n"/>
+      <c r="Y59" s="22" t="n"/>
+      <c r="Z59" s="22" t="n"/>
+      <c r="AA59" s="22" t="n"/>
+      <c r="AB59" s="22" t="n"/>
+      <c r="AC59" s="22" t="n"/>
+      <c r="AD59" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>9.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="n"/>
+      <c r="C60" s="22" t="n"/>
+      <c r="D60" s="22" t="n"/>
+      <c r="E60" s="21" t="n"/>
+      <c r="F60" s="22" t="n"/>
+      <c r="G60" s="22" t="n"/>
+      <c r="H60" s="22" t="n"/>
+      <c r="I60" s="22" t="n"/>
+      <c r="J60" s="22" t="n"/>
+      <c r="K60" s="22" t="n"/>
+      <c r="L60" s="22" t="n"/>
+      <c r="M60" s="22" t="n"/>
+      <c r="N60" s="22" t="n"/>
+      <c r="O60" s="22" t="n"/>
+      <c r="P60" s="22" t="n"/>
+      <c r="Q60" s="22" t="n"/>
+      <c r="R60" s="22" t="n"/>
+      <c r="S60" s="22" t="n"/>
+      <c r="T60" s="22" t="n"/>
+      <c r="U60" s="22" t="n"/>
+      <c r="V60" s="22" t="n"/>
+      <c r="W60" s="22" t="n"/>
+      <c r="X60" s="22" t="n"/>
+      <c r="Y60" s="22" t="n"/>
+      <c r="Z60" s="22" t="n"/>
+      <c r="AA60" s="22" t="n"/>
+      <c r="AB60" s="22" t="n"/>
+      <c r="AC60" s="22" t="n"/>
+      <c r="AD60" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>9.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="n"/>
+      <c r="C61" s="22" t="n"/>
+      <c r="D61" s="22" t="n"/>
+      <c r="E61" s="21" t="n"/>
+      <c r="F61" s="22" t="n"/>
+      <c r="G61" s="22" t="n"/>
+      <c r="H61" s="22" t="n"/>
+      <c r="I61" s="22" t="n"/>
+      <c r="J61" s="22" t="n"/>
+      <c r="K61" s="22" t="n"/>
+      <c r="L61" s="22" t="n"/>
+      <c r="M61" s="22" t="n"/>
+      <c r="N61" s="22" t="n"/>
+      <c r="O61" s="22" t="n"/>
+      <c r="P61" s="22" t="n"/>
+      <c r="Q61" s="22" t="n"/>
+      <c r="R61" s="22" t="n"/>
+      <c r="S61" s="22" t="n"/>
+      <c r="T61" s="22" t="n"/>
+      <c r="U61" s="22" t="n"/>
+      <c r="V61" s="22" t="n"/>
+      <c r="W61" s="22" t="n"/>
+      <c r="X61" s="22" t="n"/>
+      <c r="Y61" s="22" t="n"/>
+      <c r="Z61" s="22" t="n"/>
+      <c r="AA61" s="22" t="n"/>
+      <c r="AB61" s="22" t="n"/>
+      <c r="AC61" s="22" t="n"/>
+      <c r="AD61" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>10. Gestión de clientes</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="n"/>
+      <c r="C62" s="22" t="n"/>
+      <c r="D62" s="22" t="n"/>
+      <c r="E62" s="22" t="n"/>
+      <c r="F62" s="21" t="n"/>
+      <c r="G62" s="21" t="n"/>
+      <c r="H62" s="21" t="n"/>
+      <c r="I62" s="21" t="n"/>
+      <c r="J62" s="22" t="n"/>
+      <c r="K62" s="22" t="n"/>
+      <c r="L62" s="22" t="n"/>
+      <c r="M62" s="22" t="n"/>
+      <c r="N62" s="22" t="n"/>
+      <c r="O62" s="22" t="n"/>
+      <c r="P62" s="22" t="n"/>
+      <c r="Q62" s="22" t="n"/>
+      <c r="R62" s="22" t="n"/>
+      <c r="S62" s="22" t="n"/>
+      <c r="T62" s="22" t="n"/>
+      <c r="U62" s="22" t="n"/>
+      <c r="V62" s="22" t="n"/>
+      <c r="W62" s="22" t="n"/>
+      <c r="X62" s="22" t="n"/>
+      <c r="Y62" s="22" t="n"/>
+      <c r="Z62" s="22" t="n"/>
+      <c r="AA62" s="22" t="n"/>
+      <c r="AB62" s="22" t="n"/>
+      <c r="AC62" s="22" t="n"/>
+      <c r="AD62" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>10.1 Listado de clientes</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="n"/>
+      <c r="C63" s="22" t="n"/>
+      <c r="D63" s="22" t="n"/>
+      <c r="E63" s="22" t="n"/>
+      <c r="F63" s="21" t="n"/>
+      <c r="G63" s="22" t="n"/>
+      <c r="H63" s="22" t="n"/>
+      <c r="I63" s="22" t="n"/>
+      <c r="J63" s="22" t="n"/>
+      <c r="K63" s="22" t="n"/>
+      <c r="L63" s="22" t="n"/>
+      <c r="M63" s="22" t="n"/>
+      <c r="N63" s="22" t="n"/>
+      <c r="O63" s="22" t="n"/>
+      <c r="P63" s="22" t="n"/>
+      <c r="Q63" s="22" t="n"/>
+      <c r="R63" s="22" t="n"/>
+      <c r="S63" s="22" t="n"/>
+      <c r="T63" s="22" t="n"/>
+      <c r="U63" s="22" t="n"/>
+      <c r="V63" s="22" t="n"/>
+      <c r="W63" s="22" t="n"/>
+      <c r="X63" s="22" t="n"/>
+      <c r="Y63" s="22" t="n"/>
+      <c r="Z63" s="22" t="n"/>
+      <c r="AA63" s="22" t="n"/>
+      <c r="AB63" s="22" t="n"/>
+      <c r="AC63" s="22" t="n"/>
+      <c r="AD63" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>10.2 Ficha del cliente</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="n"/>
+      <c r="C64" s="22" t="n"/>
+      <c r="D64" s="22" t="n"/>
+      <c r="E64" s="22" t="n"/>
+      <c r="F64" s="21" t="n"/>
+      <c r="G64" s="22" t="n"/>
+      <c r="H64" s="22" t="n"/>
+      <c r="I64" s="22" t="n"/>
+      <c r="J64" s="22" t="n"/>
+      <c r="K64" s="22" t="n"/>
+      <c r="L64" s="22" t="n"/>
+      <c r="M64" s="22" t="n"/>
+      <c r="N64" s="22" t="n"/>
+      <c r="O64" s="22" t="n"/>
+      <c r="P64" s="22" t="n"/>
+      <c r="Q64" s="22" t="n"/>
+      <c r="R64" s="22" t="n"/>
+      <c r="S64" s="22" t="n"/>
+      <c r="T64" s="22" t="n"/>
+      <c r="U64" s="22" t="n"/>
+      <c r="V64" s="22" t="n"/>
+      <c r="W64" s="22" t="n"/>
+      <c r="X64" s="22" t="n"/>
+      <c r="Y64" s="22" t="n"/>
+      <c r="Z64" s="22" t="n"/>
+      <c r="AA64" s="22" t="n"/>
+      <c r="AB64" s="22" t="n"/>
+      <c r="AC64" s="22" t="n"/>
+      <c r="AD64" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>10.3 Edición de datos</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="n"/>
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="22" t="n"/>
+      <c r="E65" s="22" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="22" t="n"/>
+      <c r="H65" s="22" t="n"/>
+      <c r="I65" s="22" t="n"/>
+      <c r="J65" s="22" t="n"/>
+      <c r="K65" s="22" t="n"/>
+      <c r="L65" s="22" t="n"/>
+      <c r="M65" s="22" t="n"/>
+      <c r="N65" s="22" t="n"/>
+      <c r="O65" s="22" t="n"/>
+      <c r="P65" s="22" t="n"/>
+      <c r="Q65" s="22" t="n"/>
+      <c r="R65" s="22" t="n"/>
+      <c r="S65" s="22" t="n"/>
+      <c r="T65" s="22" t="n"/>
+      <c r="U65" s="22" t="n"/>
+      <c r="V65" s="22" t="n"/>
+      <c r="W65" s="22" t="n"/>
+      <c r="X65" s="22" t="n"/>
+      <c r="Y65" s="22" t="n"/>
+      <c r="Z65" s="22" t="n"/>
+      <c r="AA65" s="22" t="n"/>
+      <c r="AB65" s="22" t="n"/>
+      <c r="AC65" s="22" t="n"/>
+      <c r="AD65" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>10.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="n"/>
+      <c r="C66" s="22" t="n"/>
+      <c r="D66" s="22" t="n"/>
+      <c r="E66" s="22" t="n"/>
+      <c r="F66" s="22" t="n"/>
+      <c r="G66" s="22" t="n"/>
+      <c r="H66" s="22" t="n"/>
+      <c r="I66" s="21" t="n"/>
+      <c r="J66" s="22" t="n"/>
+      <c r="K66" s="22" t="n"/>
+      <c r="L66" s="22" t="n"/>
+      <c r="M66" s="22" t="n"/>
+      <c r="N66" s="22" t="n"/>
+      <c r="O66" s="22" t="n"/>
+      <c r="P66" s="22" t="n"/>
+      <c r="Q66" s="22" t="n"/>
+      <c r="R66" s="22" t="n"/>
+      <c r="S66" s="22" t="n"/>
+      <c r="T66" s="22" t="n"/>
+      <c r="U66" s="22" t="n"/>
+      <c r="V66" s="22" t="n"/>
+      <c r="W66" s="22" t="n"/>
+      <c r="X66" s="22" t="n"/>
+      <c r="Y66" s="22" t="n"/>
+      <c r="Z66" s="22" t="n"/>
+      <c r="AA66" s="22" t="n"/>
+      <c r="AB66" s="22" t="n"/>
+      <c r="AC66" s="22" t="n"/>
+      <c r="AD66" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>10.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="n"/>
+      <c r="C67" s="22" t="n"/>
+      <c r="D67" s="22" t="n"/>
+      <c r="E67" s="22" t="n"/>
+      <c r="F67" s="22" t="n"/>
+      <c r="G67" s="22" t="n"/>
+      <c r="H67" s="22" t="n"/>
+      <c r="I67" s="21" t="n"/>
+      <c r="J67" s="22" t="n"/>
+      <c r="K67" s="22" t="n"/>
+      <c r="L67" s="22" t="n"/>
+      <c r="M67" s="22" t="n"/>
+      <c r="N67" s="22" t="n"/>
+      <c r="O67" s="22" t="n"/>
+      <c r="P67" s="22" t="n"/>
+      <c r="Q67" s="22" t="n"/>
+      <c r="R67" s="22" t="n"/>
+      <c r="S67" s="22" t="n"/>
+      <c r="T67" s="22" t="n"/>
+      <c r="U67" s="22" t="n"/>
+      <c r="V67" s="22" t="n"/>
+      <c r="W67" s="22" t="n"/>
+      <c r="X67" s="22" t="n"/>
+      <c r="Y67" s="22" t="n"/>
+      <c r="Z67" s="22" t="n"/>
+      <c r="AA67" s="22" t="n"/>
+      <c r="AB67" s="22" t="n"/>
+      <c r="AC67" s="22" t="n"/>
+      <c r="AD67" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>11. Monitores y solicitudes</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="n"/>
+      <c r="C68" s="22" t="n"/>
+      <c r="D68" s="22" t="n"/>
+      <c r="E68" s="22" t="n"/>
+      <c r="F68" s="22" t="n"/>
+      <c r="G68" s="22" t="n"/>
+      <c r="H68" s="22" t="n"/>
+      <c r="I68" s="22" t="n"/>
+      <c r="J68" s="21" t="n"/>
+      <c r="K68" s="21" t="n"/>
+      <c r="L68" s="21" t="n"/>
+      <c r="M68" s="22" t="n"/>
+      <c r="N68" s="22" t="n"/>
+      <c r="O68" s="22" t="n"/>
+      <c r="P68" s="22" t="n"/>
+      <c r="Q68" s="22" t="n"/>
+      <c r="R68" s="22" t="n"/>
+      <c r="S68" s="22" t="n"/>
+      <c r="T68" s="22" t="n"/>
+      <c r="U68" s="22" t="n"/>
+      <c r="V68" s="22" t="n"/>
+      <c r="W68" s="22" t="n"/>
+      <c r="X68" s="22" t="n"/>
+      <c r="Y68" s="22" t="n"/>
+      <c r="Z68" s="22" t="n"/>
+      <c r="AA68" s="22" t="n"/>
+      <c r="AB68" s="22" t="n"/>
+      <c r="AC68" s="22" t="n"/>
+      <c r="AD68" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>11.1 Alta de monitores</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="n"/>
+      <c r="C69" s="22" t="n"/>
+      <c r="D69" s="22" t="n"/>
+      <c r="E69" s="22" t="n"/>
+      <c r="F69" s="22" t="n"/>
+      <c r="G69" s="22" t="n"/>
+      <c r="H69" s="22" t="n"/>
+      <c r="I69" s="22" t="n"/>
+      <c r="J69" s="21" t="n"/>
+      <c r="K69" s="22" t="n"/>
+      <c r="L69" s="22" t="n"/>
+      <c r="M69" s="22" t="n"/>
+      <c r="N69" s="22" t="n"/>
+      <c r="O69" s="22" t="n"/>
+      <c r="P69" s="22" t="n"/>
+      <c r="Q69" s="22" t="n"/>
+      <c r="R69" s="22" t="n"/>
+      <c r="S69" s="22" t="n"/>
+      <c r="T69" s="22" t="n"/>
+      <c r="U69" s="22" t="n"/>
+      <c r="V69" s="22" t="n"/>
+      <c r="W69" s="22" t="n"/>
+      <c r="X69" s="22" t="n"/>
+      <c r="Y69" s="22" t="n"/>
+      <c r="Z69" s="22" t="n"/>
+      <c r="AA69" s="22" t="n"/>
+      <c r="AB69" s="22" t="n"/>
+      <c r="AC69" s="22" t="n"/>
+      <c r="AD69" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>11.2 Solicitudes de clase</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="n"/>
+      <c r="C70" s="22" t="n"/>
+      <c r="D70" s="22" t="n"/>
+      <c r="E70" s="22" t="n"/>
+      <c r="F70" s="22" t="n"/>
+      <c r="G70" s="22" t="n"/>
+      <c r="H70" s="22" t="n"/>
+      <c r="I70" s="22" t="n"/>
+      <c r="J70" s="22" t="n"/>
+      <c r="K70" s="21" t="n"/>
+      <c r="L70" s="22" t="n"/>
+      <c r="M70" s="22" t="n"/>
+      <c r="N70" s="22" t="n"/>
+      <c r="O70" s="22" t="n"/>
+      <c r="P70" s="22" t="n"/>
+      <c r="Q70" s="22" t="n"/>
+      <c r="R70" s="22" t="n"/>
+      <c r="S70" s="22" t="n"/>
+      <c r="T70" s="22" t="n"/>
+      <c r="U70" s="22" t="n"/>
+      <c r="V70" s="22" t="n"/>
+      <c r="W70" s="22" t="n"/>
+      <c r="X70" s="22" t="n"/>
+      <c r="Y70" s="22" t="n"/>
+      <c r="Z70" s="22" t="n"/>
+      <c r="AA70" s="22" t="n"/>
+      <c r="AB70" s="22" t="n"/>
+      <c r="AC70" s="22" t="n"/>
+      <c r="AD70" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>11.3 Aprobación y rechazo</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="n"/>
+      <c r="C71" s="22" t="n"/>
+      <c r="D71" s="22" t="n"/>
+      <c r="E71" s="22" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="G71" s="22" t="n"/>
+      <c r="H71" s="22" t="n"/>
+      <c r="I71" s="22" t="n"/>
+      <c r="J71" s="22" t="n"/>
+      <c r="K71" s="21" t="n"/>
+      <c r="L71" s="22" t="n"/>
+      <c r="M71" s="22" t="n"/>
+      <c r="N71" s="22" t="n"/>
+      <c r="O71" s="22" t="n"/>
+      <c r="P71" s="22" t="n"/>
+      <c r="Q71" s="22" t="n"/>
+      <c r="R71" s="22" t="n"/>
+      <c r="S71" s="22" t="n"/>
+      <c r="T71" s="22" t="n"/>
+      <c r="U71" s="22" t="n"/>
+      <c r="V71" s="22" t="n"/>
+      <c r="W71" s="22" t="n"/>
+      <c r="X71" s="22" t="n"/>
+      <c r="Y71" s="22" t="n"/>
+      <c r="Z71" s="22" t="n"/>
+      <c r="AA71" s="22" t="n"/>
+      <c r="AB71" s="22" t="n"/>
+      <c r="AC71" s="22" t="n"/>
+      <c r="AD71" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>11.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="n"/>
+      <c r="C72" s="22" t="n"/>
+      <c r="D72" s="22" t="n"/>
+      <c r="E72" s="22" t="n"/>
+      <c r="F72" s="22" t="n"/>
+      <c r="G72" s="22" t="n"/>
+      <c r="H72" s="22" t="n"/>
+      <c r="I72" s="22" t="n"/>
+      <c r="J72" s="22" t="n"/>
+      <c r="K72" s="22" t="n"/>
+      <c r="L72" s="21" t="n"/>
+      <c r="M72" s="22" t="n"/>
+      <c r="N72" s="22" t="n"/>
+      <c r="O72" s="22" t="n"/>
+      <c r="P72" s="22" t="n"/>
+      <c r="Q72" s="22" t="n"/>
+      <c r="R72" s="22" t="n"/>
+      <c r="S72" s="22" t="n"/>
+      <c r="T72" s="22" t="n"/>
+      <c r="U72" s="22" t="n"/>
+      <c r="V72" s="22" t="n"/>
+      <c r="W72" s="22" t="n"/>
+      <c r="X72" s="22" t="n"/>
+      <c r="Y72" s="22" t="n"/>
+      <c r="Z72" s="22" t="n"/>
+      <c r="AA72" s="22" t="n"/>
+      <c r="AB72" s="22" t="n"/>
+      <c r="AC72" s="22" t="n"/>
+      <c r="AD72" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>11.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="n"/>
+      <c r="C73" s="22" t="n"/>
+      <c r="D73" s="22" t="n"/>
+      <c r="E73" s="22" t="n"/>
+      <c r="F73" s="22" t="n"/>
+      <c r="G73" s="22" t="n"/>
+      <c r="H73" s="22" t="n"/>
+      <c r="I73" s="22" t="n"/>
+      <c r="J73" s="22" t="n"/>
+      <c r="K73" s="22" t="n"/>
+      <c r="L73" s="21" t="n"/>
+      <c r="M73" s="22" t="n"/>
+      <c r="N73" s="22" t="n"/>
+      <c r="O73" s="22" t="n"/>
+      <c r="P73" s="22" t="n"/>
+      <c r="Q73" s="22" t="n"/>
+      <c r="R73" s="22" t="n"/>
+      <c r="S73" s="22" t="n"/>
+      <c r="T73" s="22" t="n"/>
+      <c r="U73" s="22" t="n"/>
+      <c r="V73" s="22" t="n"/>
+      <c r="W73" s="22" t="n"/>
+      <c r="X73" s="22" t="n"/>
+      <c r="Y73" s="22" t="n"/>
+      <c r="Z73" s="22" t="n"/>
+      <c r="AA73" s="22" t="n"/>
+      <c r="AB73" s="22" t="n"/>
+      <c r="AC73" s="22" t="n"/>
+      <c r="AD73" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>12. Salas y materiales</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="n"/>
+      <c r="C74" s="22" t="n"/>
+      <c r="D74" s="22" t="n"/>
+      <c r="E74" s="22" t="n"/>
+      <c r="F74" s="22" t="n"/>
+      <c r="G74" s="22" t="n"/>
+      <c r="H74" s="22" t="n"/>
+      <c r="I74" s="22" t="n"/>
+      <c r="J74" s="22" t="n"/>
+      <c r="K74" s="22" t="n"/>
+      <c r="L74" s="22" t="n"/>
+      <c r="M74" s="21" t="n"/>
+      <c r="N74" s="21" t="n"/>
+      <c r="O74" s="21" t="n"/>
+      <c r="P74" s="21" t="n"/>
+      <c r="Q74" s="22" t="n"/>
+      <c r="R74" s="22" t="n"/>
+      <c r="S74" s="22" t="n"/>
+      <c r="T74" s="22" t="n"/>
+      <c r="U74" s="22" t="n"/>
+      <c r="V74" s="22" t="n"/>
+      <c r="W74" s="22" t="n"/>
+      <c r="X74" s="22" t="n"/>
+      <c r="Y74" s="22" t="n"/>
+      <c r="Z74" s="22" t="n"/>
+      <c r="AA74" s="22" t="n"/>
+      <c r="AB74" s="22" t="n"/>
+      <c r="AC74" s="22" t="n"/>
+      <c r="AD74" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>12.1 Ficha de salas</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="n"/>
+      <c r="C75" s="22" t="n"/>
+      <c r="D75" s="22" t="n"/>
+      <c r="E75" s="22" t="n"/>
+      <c r="F75" s="22" t="n"/>
+      <c r="G75" s="22" t="n"/>
+      <c r="H75" s="22" t="n"/>
+      <c r="I75" s="22" t="n"/>
+      <c r="J75" s="22" t="n"/>
+      <c r="K75" s="22" t="n"/>
+      <c r="L75" s="22" t="n"/>
+      <c r="M75" s="21" t="n"/>
+      <c r="N75" s="22" t="n"/>
+      <c r="O75" s="22" t="n"/>
+      <c r="P75" s="22" t="n"/>
+      <c r="Q75" s="22" t="n"/>
+      <c r="R75" s="22" t="n"/>
+      <c r="S75" s="22" t="n"/>
+      <c r="T75" s="22" t="n"/>
+      <c r="U75" s="22" t="n"/>
+      <c r="V75" s="22" t="n"/>
+      <c r="W75" s="22" t="n"/>
+      <c r="X75" s="22" t="n"/>
+      <c r="Y75" s="22" t="n"/>
+      <c r="Z75" s="22" t="n"/>
+      <c r="AA75" s="22" t="n"/>
+      <c r="AB75" s="22" t="n"/>
+      <c r="AC75" s="22" t="n"/>
+      <c r="AD75" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>12.2 Inventario de materiales</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="n"/>
+      <c r="C76" s="22" t="n"/>
+      <c r="D76" s="22" t="n"/>
+      <c r="E76" s="22" t="n"/>
+      <c r="F76" s="22" t="n"/>
+      <c r="G76" s="22" t="n"/>
+      <c r="H76" s="22" t="n"/>
+      <c r="I76" s="22" t="n"/>
+      <c r="J76" s="22" t="n"/>
+      <c r="K76" s="22" t="n"/>
+      <c r="L76" s="22" t="n"/>
+      <c r="M76" s="21" t="n"/>
+      <c r="N76" s="22" t="n"/>
+      <c r="O76" s="22" t="n"/>
+      <c r="P76" s="22" t="n"/>
+      <c r="Q76" s="22" t="n"/>
+      <c r="R76" s="22" t="n"/>
+      <c r="S76" s="22" t="n"/>
+      <c r="T76" s="22" t="n"/>
+      <c r="U76" s="22" t="n"/>
+      <c r="V76" s="22" t="n"/>
+      <c r="W76" s="22" t="n"/>
+      <c r="X76" s="22" t="n"/>
+      <c r="Y76" s="22" t="n"/>
+      <c r="Z76" s="22" t="n"/>
+      <c r="AA76" s="22" t="n"/>
+      <c r="AB76" s="22" t="n"/>
+      <c r="AC76" s="22" t="n"/>
+      <c r="AD76" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>12.3 Alta y edición</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="n"/>
+      <c r="C77" s="22" t="n"/>
+      <c r="D77" s="22" t="n"/>
+      <c r="E77" s="22" t="n"/>
+      <c r="F77" s="22" t="n"/>
+      <c r="G77" s="22" t="n"/>
+      <c r="H77" s="22" t="n"/>
+      <c r="I77" s="22" t="n"/>
+      <c r="J77" s="22" t="n"/>
+      <c r="K77" s="22" t="n"/>
+      <c r="L77" s="22" t="n"/>
+      <c r="M77" s="21" t="n"/>
+      <c r="N77" s="22" t="n"/>
+      <c r="O77" s="22" t="n"/>
+      <c r="P77" s="22" t="n"/>
+      <c r="Q77" s="22" t="n"/>
+      <c r="R77" s="22" t="n"/>
+      <c r="S77" s="22" t="n"/>
+      <c r="T77" s="22" t="n"/>
+      <c r="U77" s="22" t="n"/>
+      <c r="V77" s="22" t="n"/>
+      <c r="W77" s="22" t="n"/>
+      <c r="X77" s="22" t="n"/>
+      <c r="Y77" s="22" t="n"/>
+      <c r="Z77" s="22" t="n"/>
+      <c r="AA77" s="22" t="n"/>
+      <c r="AB77" s="22" t="n"/>
+      <c r="AC77" s="22" t="n"/>
+      <c r="AD77" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>12.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="n"/>
+      <c r="C78" s="22" t="n"/>
+      <c r="D78" s="22" t="n"/>
+      <c r="E78" s="22" t="n"/>
+      <c r="F78" s="22" t="n"/>
+      <c r="G78" s="22" t="n"/>
+      <c r="H78" s="22" t="n"/>
+      <c r="I78" s="22" t="n"/>
+      <c r="J78" s="22" t="n"/>
+      <c r="K78" s="22" t="n"/>
+      <c r="L78" s="22" t="n"/>
+      <c r="M78" s="22" t="n"/>
+      <c r="N78" s="22" t="n"/>
+      <c r="O78" s="22" t="n"/>
+      <c r="P78" s="21" t="n"/>
+      <c r="Q78" s="22" t="n"/>
+      <c r="R78" s="22" t="n"/>
+      <c r="S78" s="22" t="n"/>
+      <c r="T78" s="22" t="n"/>
+      <c r="U78" s="22" t="n"/>
+      <c r="V78" s="22" t="n"/>
+      <c r="W78" s="22" t="n"/>
+      <c r="X78" s="22" t="n"/>
+      <c r="Y78" s="22" t="n"/>
+      <c r="Z78" s="22" t="n"/>
+      <c r="AA78" s="22" t="n"/>
+      <c r="AB78" s="22" t="n"/>
+      <c r="AC78" s="22" t="n"/>
+      <c r="AD78" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>12.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="n"/>
+      <c r="C79" s="22" t="n"/>
+      <c r="D79" s="22" t="n"/>
+      <c r="E79" s="22" t="n"/>
+      <c r="F79" s="22" t="n"/>
+      <c r="G79" s="22" t="n"/>
+      <c r="H79" s="22" t="n"/>
+      <c r="I79" s="22" t="n"/>
+      <c r="J79" s="22" t="n"/>
+      <c r="K79" s="22" t="n"/>
+      <c r="L79" s="22" t="n"/>
+      <c r="M79" s="22" t="n"/>
+      <c r="N79" s="22" t="n"/>
+      <c r="O79" s="22" t="n"/>
+      <c r="P79" s="21" t="n"/>
+      <c r="Q79" s="22" t="n"/>
+      <c r="R79" s="22" t="n"/>
+      <c r="S79" s="22" t="n"/>
+      <c r="T79" s="22" t="n"/>
+      <c r="U79" s="22" t="n"/>
+      <c r="V79" s="22" t="n"/>
+      <c r="W79" s="22" t="n"/>
+      <c r="X79" s="22" t="n"/>
+      <c r="Y79" s="22" t="n"/>
+      <c r="Z79" s="22" t="n"/>
+      <c r="AA79" s="22" t="n"/>
+      <c r="AB79" s="22" t="n"/>
+      <c r="AC79" s="22" t="n"/>
+      <c r="AD79" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>13. Fisioterapia y citas</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="n"/>
+      <c r="C80" s="22" t="n"/>
+      <c r="D80" s="22" t="n"/>
+      <c r="E80" s="22" t="n"/>
+      <c r="F80" s="22" t="n"/>
+      <c r="G80" s="22" t="n"/>
+      <c r="H80" s="22" t="n"/>
+      <c r="I80" s="22" t="n"/>
+      <c r="J80" s="22" t="n"/>
+      <c r="K80" s="22" t="n"/>
+      <c r="L80" s="22" t="n"/>
+      <c r="M80" s="22" t="n"/>
+      <c r="N80" s="22" t="n"/>
+      <c r="O80" s="22" t="n"/>
+      <c r="P80" s="22" t="n"/>
+      <c r="Q80" s="21" t="n"/>
+      <c r="R80" s="21" t="n"/>
+      <c r="S80" s="21" t="n"/>
+      <c r="T80" s="22" t="n"/>
+      <c r="U80" s="22" t="n"/>
+      <c r="V80" s="22" t="n"/>
+      <c r="W80" s="22" t="n"/>
+      <c r="X80" s="22" t="n"/>
+      <c r="Y80" s="22" t="n"/>
+      <c r="Z80" s="22" t="n"/>
+      <c r="AA80" s="22" t="n"/>
+      <c r="AB80" s="22" t="n"/>
+      <c r="AC80" s="22" t="n"/>
+      <c r="AD80" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>13.1 Solicitud de cita</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="n"/>
+      <c r="C81" s="22" t="n"/>
+      <c r="D81" s="22" t="n"/>
+      <c r="E81" s="22" t="n"/>
+      <c r="F81" s="22" t="n"/>
+      <c r="G81" s="22" t="n"/>
+      <c r="H81" s="22" t="n"/>
+      <c r="I81" s="22" t="n"/>
+      <c r="J81" s="22" t="n"/>
+      <c r="K81" s="22" t="n"/>
+      <c r="L81" s="22" t="n"/>
+      <c r="M81" s="22" t="n"/>
+      <c r="N81" s="22" t="n"/>
+      <c r="O81" s="22" t="n"/>
+      <c r="P81" s="22" t="n"/>
+      <c r="Q81" s="21" t="n"/>
+      <c r="R81" s="22" t="n"/>
+      <c r="S81" s="22" t="n"/>
+      <c r="T81" s="22" t="n"/>
+      <c r="U81" s="22" t="n"/>
+      <c r="V81" s="22" t="n"/>
+      <c r="W81" s="22" t="n"/>
+      <c r="X81" s="22" t="n"/>
+      <c r="Y81" s="22" t="n"/>
+      <c r="Z81" s="22" t="n"/>
+      <c r="AA81" s="22" t="n"/>
+      <c r="AB81" s="22" t="n"/>
+      <c r="AC81" s="22" t="n"/>
+      <c r="AD81" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>13.2 Agenda del fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="n"/>
+      <c r="C82" s="22" t="n"/>
+      <c r="D82" s="22" t="n"/>
+      <c r="E82" s="22" t="n"/>
+      <c r="F82" s="22" t="n"/>
+      <c r="G82" s="22" t="n"/>
+      <c r="H82" s="22" t="n"/>
+      <c r="I82" s="22" t="n"/>
+      <c r="J82" s="22" t="n"/>
+      <c r="K82" s="22" t="n"/>
+      <c r="L82" s="22" t="n"/>
+      <c r="M82" s="22" t="n"/>
+      <c r="N82" s="22" t="n"/>
+      <c r="O82" s="22" t="n"/>
+      <c r="P82" s="22" t="n"/>
+      <c r="Q82" s="22" t="n"/>
+      <c r="R82" s="21" t="n"/>
+      <c r="S82" s="22" t="n"/>
+      <c r="T82" s="22" t="n"/>
+      <c r="U82" s="22" t="n"/>
+      <c r="V82" s="22" t="n"/>
+      <c r="W82" s="22" t="n"/>
+      <c r="X82" s="22" t="n"/>
+      <c r="Y82" s="22" t="n"/>
+      <c r="Z82" s="22" t="n"/>
+      <c r="AA82" s="22" t="n"/>
+      <c r="AB82" s="22" t="n"/>
+      <c r="AC82" s="22" t="n"/>
+      <c r="AD82" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>13.3 Panel de citas</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="n"/>
+      <c r="C83" s="22" t="n"/>
+      <c r="D83" s="22" t="n"/>
+      <c r="E83" s="22" t="n"/>
+      <c r="F83" s="22" t="n"/>
+      <c r="G83" s="22" t="n"/>
+      <c r="H83" s="22" t="n"/>
+      <c r="I83" s="22" t="n"/>
+      <c r="J83" s="22" t="n"/>
+      <c r="K83" s="22" t="n"/>
+      <c r="L83" s="22" t="n"/>
+      <c r="M83" s="22" t="n"/>
+      <c r="N83" s="22" t="n"/>
+      <c r="O83" s="22" t="n"/>
+      <c r="P83" s="22" t="n"/>
+      <c r="Q83" s="22" t="n"/>
+      <c r="R83" s="21" t="n"/>
+      <c r="S83" s="22" t="n"/>
+      <c r="T83" s="22" t="n"/>
+      <c r="U83" s="22" t="n"/>
+      <c r="V83" s="22" t="n"/>
+      <c r="W83" s="22" t="n"/>
+      <c r="X83" s="22" t="n"/>
+      <c r="Y83" s="22" t="n"/>
+      <c r="Z83" s="22" t="n"/>
+      <c r="AA83" s="22" t="n"/>
+      <c r="AB83" s="22" t="n"/>
+      <c r="AC83" s="22" t="n"/>
+      <c r="AD83" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>13.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="n"/>
+      <c r="C84" s="22" t="n"/>
+      <c r="D84" s="22" t="n"/>
+      <c r="E84" s="22" t="n"/>
+      <c r="F84" s="22" t="n"/>
+      <c r="G84" s="22" t="n"/>
+      <c r="H84" s="22" t="n"/>
+      <c r="I84" s="22" t="n"/>
+      <c r="J84" s="22" t="n"/>
+      <c r="K84" s="22" t="n"/>
+      <c r="L84" s="22" t="n"/>
+      <c r="M84" s="22" t="n"/>
+      <c r="N84" s="22" t="n"/>
+      <c r="O84" s="22" t="n"/>
+      <c r="P84" s="22" t="n"/>
+      <c r="Q84" s="22" t="n"/>
+      <c r="R84" s="22" t="n"/>
+      <c r="S84" s="21" t="n"/>
+      <c r="T84" s="22" t="n"/>
+      <c r="U84" s="22" t="n"/>
+      <c r="V84" s="22" t="n"/>
+      <c r="W84" s="22" t="n"/>
+      <c r="X84" s="22" t="n"/>
+      <c r="Y84" s="22" t="n"/>
+      <c r="Z84" s="22" t="n"/>
+      <c r="AA84" s="22" t="n"/>
+      <c r="AB84" s="22" t="n"/>
+      <c r="AC84" s="22" t="n"/>
+      <c r="AD84" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>13.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="n"/>
+      <c r="C85" s="22" t="n"/>
+      <c r="D85" s="22" t="n"/>
+      <c r="E85" s="22" t="n"/>
+      <c r="F85" s="22" t="n"/>
+      <c r="G85" s="22" t="n"/>
+      <c r="H85" s="22" t="n"/>
+      <c r="I85" s="22" t="n"/>
+      <c r="J85" s="22" t="n"/>
+      <c r="K85" s="22" t="n"/>
+      <c r="L85" s="22" t="n"/>
+      <c r="M85" s="22" t="n"/>
+      <c r="N85" s="22" t="n"/>
+      <c r="O85" s="22" t="n"/>
+      <c r="P85" s="22" t="n"/>
+      <c r="Q85" s="22" t="n"/>
+      <c r="R85" s="22" t="n"/>
+      <c r="S85" s="21" t="n"/>
+      <c r="T85" s="22" t="n"/>
+      <c r="U85" s="22" t="n"/>
+      <c r="V85" s="22" t="n"/>
+      <c r="W85" s="22" t="n"/>
+      <c r="X85" s="22" t="n"/>
+      <c r="Y85" s="22" t="n"/>
+      <c r="Z85" s="22" t="n"/>
+      <c r="AA85" s="22" t="n"/>
+      <c r="AB85" s="22" t="n"/>
+      <c r="AC85" s="22" t="n"/>
+      <c r="AD85" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>14. Comentarios, feedback y seguridad</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="n"/>
+      <c r="C86" s="22" t="n"/>
+      <c r="D86" s="22" t="n"/>
+      <c r="E86" s="22" t="n"/>
+      <c r="F86" s="22" t="n"/>
+      <c r="G86" s="22" t="n"/>
+      <c r="H86" s="22" t="n"/>
+      <c r="I86" s="22" t="n"/>
+      <c r="J86" s="22" t="n"/>
+      <c r="K86" s="22" t="n"/>
+      <c r="L86" s="22" t="n"/>
+      <c r="M86" s="22" t="n"/>
+      <c r="N86" s="22" t="n"/>
+      <c r="O86" s="22" t="n"/>
+      <c r="P86" s="22" t="n"/>
+      <c r="Q86" s="22" t="n"/>
+      <c r="R86" s="22" t="n"/>
+      <c r="S86" s="22" t="n"/>
+      <c r="T86" s="21" t="n"/>
+      <c r="U86" s="21" t="n"/>
+      <c r="V86" s="21" t="n"/>
+      <c r="W86" s="21" t="n"/>
+      <c r="X86" s="21" t="n"/>
+      <c r="Y86" s="22" t="n"/>
+      <c r="Z86" s="22" t="n"/>
+      <c r="AA86" s="22" t="n"/>
+      <c r="AB86" s="22" t="n"/>
+      <c r="AC86" s="22" t="n"/>
+      <c r="AD86" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>14.1 Comentarios de actividad</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="n"/>
+      <c r="C87" s="22" t="n"/>
+      <c r="D87" s="22" t="n"/>
+      <c r="E87" s="22" t="n"/>
+      <c r="F87" s="22" t="n"/>
+      <c r="G87" s="22" t="n"/>
+      <c r="H87" s="22" t="n"/>
+      <c r="I87" s="22" t="n"/>
+      <c r="J87" s="22" t="n"/>
+      <c r="K87" s="22" t="n"/>
+      <c r="L87" s="22" t="n"/>
+      <c r="M87" s="22" t="n"/>
+      <c r="N87" s="22" t="n"/>
+      <c r="O87" s="22" t="n"/>
+      <c r="P87" s="22" t="n"/>
+      <c r="Q87" s="22" t="n"/>
+      <c r="R87" s="22" t="n"/>
+      <c r="S87" s="22" t="n"/>
+      <c r="T87" s="21" t="n"/>
+      <c r="U87" s="22" t="n"/>
+      <c r="V87" s="22" t="n"/>
+      <c r="W87" s="22" t="n"/>
+      <c r="X87" s="22" t="n"/>
+      <c r="Y87" s="22" t="n"/>
+      <c r="Z87" s="22" t="n"/>
+      <c r="AA87" s="22" t="n"/>
+      <c r="AB87" s="22" t="n"/>
+      <c r="AC87" s="22" t="n"/>
+      <c r="AD87" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>14.2 Buzón de feedback</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="n"/>
+      <c r="C88" s="22" t="n"/>
+      <c r="D88" s="22" t="n"/>
+      <c r="E88" s="22" t="n"/>
+      <c r="F88" s="22" t="n"/>
+      <c r="G88" s="22" t="n"/>
+      <c r="H88" s="22" t="n"/>
+      <c r="I88" s="22" t="n"/>
+      <c r="J88" s="22" t="n"/>
+      <c r="K88" s="22" t="n"/>
+      <c r="L88" s="22" t="n"/>
+      <c r="M88" s="22" t="n"/>
+      <c r="N88" s="22" t="n"/>
+      <c r="O88" s="22" t="n"/>
+      <c r="P88" s="22" t="n"/>
+      <c r="Q88" s="22" t="n"/>
+      <c r="R88" s="22" t="n"/>
+      <c r="S88" s="22" t="n"/>
+      <c r="T88" s="22" t="n"/>
+      <c r="U88" s="22" t="n"/>
+      <c r="V88" s="22" t="n"/>
+      <c r="W88" s="21" t="n"/>
+      <c r="X88" s="22" t="n"/>
+      <c r="Y88" s="22" t="n"/>
+      <c r="Z88" s="22" t="n"/>
+      <c r="AA88" s="22" t="n"/>
+      <c r="AB88" s="22" t="n"/>
+      <c r="AC88" s="22" t="n"/>
+      <c r="AD88" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>14.3 Configuración de seguridad</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="n"/>
+      <c r="C89" s="22" t="n"/>
+      <c r="D89" s="22" t="n"/>
+      <c r="E89" s="22" t="n"/>
+      <c r="F89" s="22" t="n"/>
+      <c r="G89" s="22" t="n"/>
+      <c r="H89" s="22" t="n"/>
+      <c r="I89" s="22" t="n"/>
+      <c r="J89" s="22" t="n"/>
+      <c r="K89" s="22" t="n"/>
+      <c r="L89" s="22" t="n"/>
+      <c r="M89" s="22" t="n"/>
+      <c r="N89" s="22" t="n"/>
+      <c r="O89" s="22" t="n"/>
+      <c r="P89" s="22" t="n"/>
+      <c r="Q89" s="22" t="n"/>
+      <c r="R89" s="22" t="n"/>
+      <c r="S89" s="22" t="n"/>
+      <c r="T89" s="22" t="n"/>
+      <c r="U89" s="22" t="n"/>
+      <c r="V89" s="22" t="n"/>
+      <c r="W89" s="21" t="n"/>
+      <c r="X89" s="22" t="n"/>
+      <c r="Y89" s="22" t="n"/>
+      <c r="Z89" s="22" t="n"/>
+      <c r="AA89" s="22" t="n"/>
+      <c r="AB89" s="22" t="n"/>
+      <c r="AC89" s="22" t="n"/>
+      <c r="AD89" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>14.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="n"/>
+      <c r="C90" s="22" t="n"/>
+      <c r="D90" s="22" t="n"/>
+      <c r="E90" s="22" t="n"/>
+      <c r="F90" s="22" t="n"/>
+      <c r="G90" s="22" t="n"/>
+      <c r="H90" s="22" t="n"/>
+      <c r="I90" s="22" t="n"/>
+      <c r="J90" s="22" t="n"/>
+      <c r="K90" s="22" t="n"/>
+      <c r="L90" s="22" t="n"/>
+      <c r="M90" s="22" t="n"/>
+      <c r="N90" s="22" t="n"/>
+      <c r="O90" s="22" t="n"/>
+      <c r="P90" s="22" t="n"/>
+      <c r="Q90" s="22" t="n"/>
+      <c r="R90" s="22" t="n"/>
+      <c r="S90" s="22" t="n"/>
+      <c r="T90" s="22" t="n"/>
+      <c r="U90" s="22" t="n"/>
+      <c r="V90" s="22" t="n"/>
+      <c r="W90" s="22" t="n"/>
+      <c r="X90" s="21" t="n"/>
+      <c r="Y90" s="22" t="n"/>
+      <c r="Z90" s="22" t="n"/>
+      <c r="AA90" s="22" t="n"/>
+      <c r="AB90" s="22" t="n"/>
+      <c r="AC90" s="22" t="n"/>
+      <c r="AD90" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t>14.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="n"/>
+      <c r="C91" s="22" t="n"/>
+      <c r="D91" s="22" t="n"/>
+      <c r="E91" s="22" t="n"/>
+      <c r="F91" s="22" t="n"/>
+      <c r="G91" s="22" t="n"/>
+      <c r="H91" s="22" t="n"/>
+      <c r="I91" s="22" t="n"/>
+      <c r="J91" s="22" t="n"/>
+      <c r="K91" s="22" t="n"/>
+      <c r="L91" s="22" t="n"/>
+      <c r="M91" s="22" t="n"/>
+      <c r="N91" s="22" t="n"/>
+      <c r="O91" s="22" t="n"/>
+      <c r="P91" s="22" t="n"/>
+      <c r="Q91" s="22" t="n"/>
+      <c r="R91" s="22" t="n"/>
+      <c r="S91" s="22" t="n"/>
+      <c r="T91" s="22" t="n"/>
+      <c r="U91" s="22" t="n"/>
+      <c r="V91" s="22" t="n"/>
+      <c r="W91" s="22" t="n"/>
+      <c r="X91" s="21" t="n"/>
+      <c r="Y91" s="22" t="n"/>
+      <c r="Z91" s="22" t="n"/>
+      <c r="AA91" s="22" t="n"/>
+      <c r="AB91" s="22" t="n"/>
+      <c r="AC91" s="22" t="n"/>
+      <c r="AD91" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>15. Interfaz Tailwind, correo y cierre</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="n"/>
+      <c r="C92" s="22" t="n"/>
+      <c r="D92" s="22" t="n"/>
+      <c r="E92" s="22" t="n"/>
+      <c r="F92" s="22" t="n"/>
+      <c r="G92" s="22" t="n"/>
+      <c r="H92" s="22" t="n"/>
+      <c r="I92" s="22" t="n"/>
+      <c r="J92" s="22" t="n"/>
+      <c r="K92" s="22" t="n"/>
+      <c r="L92" s="22" t="n"/>
+      <c r="M92" s="22" t="n"/>
+      <c r="N92" s="22" t="n"/>
+      <c r="O92" s="22" t="n"/>
+      <c r="P92" s="22" t="n"/>
+      <c r="Q92" s="22" t="n"/>
+      <c r="R92" s="22" t="n"/>
+      <c r="S92" s="22" t="n"/>
+      <c r="T92" s="22" t="n"/>
+      <c r="U92" s="22" t="n"/>
+      <c r="V92" s="22" t="n"/>
+      <c r="W92" s="22" t="n"/>
+      <c r="X92" s="22" t="n"/>
+      <c r="Y92" s="21" t="n"/>
+      <c r="Z92" s="21" t="n"/>
+      <c r="AA92" s="21" t="n"/>
+      <c r="AB92" s="21" t="n"/>
+      <c r="AC92" s="21" t="n"/>
+      <c r="AD92" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A93" s="24" t="inlineStr">
+        <is>
+          <t>15.1 Maquetación con Tailwind</t>
+        </is>
+      </c>
+      <c r="B93" s="22" t="n"/>
+      <c r="C93" s="22" t="n"/>
+      <c r="D93" s="22" t="n"/>
+      <c r="E93" s="22" t="n"/>
+      <c r="F93" s="22" t="n"/>
+      <c r="G93" s="22" t="n"/>
+      <c r="H93" s="22" t="n"/>
+      <c r="I93" s="22" t="n"/>
+      <c r="J93" s="22" t="n"/>
+      <c r="K93" s="22" t="n"/>
+      <c r="L93" s="22" t="n"/>
+      <c r="M93" s="22" t="n"/>
+      <c r="N93" s="22" t="n"/>
+      <c r="O93" s="22" t="n"/>
+      <c r="P93" s="22" t="n"/>
+      <c r="Q93" s="22" t="n"/>
+      <c r="R93" s="22" t="n"/>
+      <c r="S93" s="22" t="n"/>
+      <c r="T93" s="22" t="n"/>
+      <c r="U93" s="22" t="n"/>
+      <c r="V93" s="22" t="n"/>
+      <c r="W93" s="22" t="n"/>
+      <c r="X93" s="22" t="n"/>
+      <c r="Y93" s="21" t="n"/>
+      <c r="Z93" s="22" t="n"/>
+      <c r="AA93" s="22" t="n"/>
+      <c r="AB93" s="22" t="n"/>
+      <c r="AC93" s="22" t="n"/>
+      <c r="AD93" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A94" s="24" t="inlineStr">
+        <is>
+          <t>15.2 Correo del proyecto</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="n"/>
+      <c r="C94" s="22" t="n"/>
+      <c r="D94" s="22" t="n"/>
+      <c r="E94" s="22" t="n"/>
+      <c r="F94" s="22" t="n"/>
+      <c r="G94" s="22" t="n"/>
+      <c r="H94" s="22" t="n"/>
+      <c r="I94" s="22" t="n"/>
+      <c r="J94" s="22" t="n"/>
+      <c r="K94" s="22" t="n"/>
+      <c r="L94" s="22" t="n"/>
+      <c r="M94" s="22" t="n"/>
+      <c r="N94" s="22" t="n"/>
+      <c r="O94" s="22" t="n"/>
+      <c r="P94" s="22" t="n"/>
+      <c r="Q94" s="22" t="n"/>
+      <c r="R94" s="22" t="n"/>
+      <c r="S94" s="22" t="n"/>
+      <c r="T94" s="22" t="n"/>
+      <c r="U94" s="22" t="n"/>
+      <c r="V94" s="22" t="n"/>
+      <c r="W94" s="22" t="n"/>
+      <c r="X94" s="22" t="n"/>
+      <c r="Y94" s="22" t="n"/>
+      <c r="Z94" s="21" t="n"/>
+      <c r="AA94" s="22" t="n"/>
+      <c r="AB94" s="22" t="n"/>
+      <c r="AC94" s="22" t="n"/>
+      <c r="AD94" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A95" s="24" t="inlineStr">
+        <is>
+          <t>15.3 Cierre y revisión</t>
+        </is>
+      </c>
+      <c r="B95" s="22" t="n"/>
+      <c r="C95" s="22" t="n"/>
+      <c r="D95" s="22" t="n"/>
+      <c r="E95" s="22" t="n"/>
+      <c r="F95" s="22" t="n"/>
+      <c r="G95" s="22" t="n"/>
+      <c r="H95" s="22" t="n"/>
+      <c r="I95" s="22" t="n"/>
+      <c r="J95" s="22" t="n"/>
+      <c r="K95" s="22" t="n"/>
+      <c r="L95" s="22" t="n"/>
+      <c r="M95" s="22" t="n"/>
+      <c r="N95" s="22" t="n"/>
+      <c r="O95" s="22" t="n"/>
+      <c r="P95" s="22" t="n"/>
+      <c r="Q95" s="22" t="n"/>
+      <c r="R95" s="22" t="n"/>
+      <c r="S95" s="22" t="n"/>
+      <c r="T95" s="22" t="n"/>
+      <c r="U95" s="22" t="n"/>
+      <c r="V95" s="22" t="n"/>
+      <c r="W95" s="22" t="n"/>
+      <c r="X95" s="22" t="n"/>
+      <c r="Y95" s="22" t="n"/>
+      <c r="Z95" s="21" t="n"/>
+      <c r="AA95" s="22" t="n"/>
+      <c r="AB95" s="22" t="n"/>
+      <c r="AC95" s="22" t="n"/>
+      <c r="AD95" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>15.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B96" s="22" t="n"/>
+      <c r="C96" s="22" t="n"/>
+      <c r="D96" s="22" t="n"/>
+      <c r="E96" s="22" t="n"/>
+      <c r="F96" s="22" t="n"/>
+      <c r="G96" s="22" t="n"/>
+      <c r="H96" s="22" t="n"/>
+      <c r="I96" s="22" t="n"/>
+      <c r="J96" s="22" t="n"/>
+      <c r="K96" s="22" t="n"/>
+      <c r="L96" s="22" t="n"/>
+      <c r="M96" s="22" t="n"/>
+      <c r="N96" s="22" t="n"/>
+      <c r="O96" s="22" t="n"/>
+      <c r="P96" s="22" t="n"/>
+      <c r="Q96" s="22" t="n"/>
+      <c r="R96" s="22" t="n"/>
+      <c r="S96" s="22" t="n"/>
+      <c r="T96" s="22" t="n"/>
+      <c r="U96" s="22" t="n"/>
+      <c r="V96" s="22" t="n"/>
+      <c r="W96" s="22" t="n"/>
+      <c r="X96" s="22" t="n"/>
+      <c r="Y96" s="22" t="n"/>
+      <c r="Z96" s="22" t="n"/>
+      <c r="AA96" s="21" t="n"/>
+      <c r="AB96" s="21" t="n"/>
+      <c r="AC96" s="21" t="n"/>
+      <c r="AD96" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>15.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B97" s="22" t="n"/>
+      <c r="C97" s="22" t="n"/>
+      <c r="D97" s="22" t="n"/>
+      <c r="E97" s="22" t="n"/>
+      <c r="F97" s="22" t="n"/>
+      <c r="G97" s="22" t="n"/>
+      <c r="H97" s="22" t="n"/>
+      <c r="I97" s="22" t="n"/>
+      <c r="J97" s="22" t="n"/>
+      <c r="K97" s="22" t="n"/>
+      <c r="L97" s="22" t="n"/>
+      <c r="M97" s="22" t="n"/>
+      <c r="N97" s="22" t="n"/>
+      <c r="O97" s="22" t="n"/>
+      <c r="P97" s="22" t="n"/>
+      <c r="Q97" s="22" t="n"/>
+      <c r="R97" s="22" t="n"/>
+      <c r="S97" s="22" t="n"/>
+      <c r="T97" s="22" t="n"/>
+      <c r="U97" s="22" t="n"/>
+      <c r="V97" s="22" t="n"/>
+      <c r="W97" s="22" t="n"/>
+      <c r="X97" s="22" t="n"/>
+      <c r="Y97" s="22" t="n"/>
+      <c r="Z97" s="22" t="n"/>
+      <c r="AA97" s="21" t="n"/>
+      <c r="AB97" s="21" t="n"/>
+      <c r="AC97" s="21" t="n"/>
+      <c r="AD97" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="27" t="n"/>
+      <c r="B98" s="28" t="n"/>
+      <c r="C98" s="28" t="n"/>
+      <c r="D98" s="28" t="n"/>
+      <c r="E98" s="28" t="n"/>
+      <c r="F98" s="28" t="n"/>
+      <c r="G98" s="28" t="n"/>
+      <c r="H98" s="28" t="n"/>
+      <c r="I98" s="28" t="n"/>
+      <c r="J98" s="28" t="n"/>
+      <c r="K98" s="28" t="n"/>
+      <c r="L98" s="28" t="n"/>
+      <c r="M98" s="28" t="n"/>
+      <c r="N98" s="28" t="n"/>
+      <c r="O98" s="28" t="n"/>
+      <c r="P98" s="28" t="n"/>
+      <c r="Q98" s="28" t="n"/>
+      <c r="R98" s="28" t="n"/>
+      <c r="S98" s="28" t="n"/>
+      <c r="T98" s="28" t="n"/>
+      <c r="U98" s="28" t="n"/>
+      <c r="V98" s="28" t="n"/>
+      <c r="W98" s="28" t="n"/>
+      <c r="X98" s="28" t="n"/>
+      <c r="Y98" s="28" t="n"/>
+      <c r="Z98" s="28" t="n"/>
+      <c r="AA98" s="28" t="n"/>
+      <c r="AB98" s="28" t="n"/>
+      <c r="AC98" s="28" t="n"/>
+      <c r="AD98" s="28" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="27" t="n"/>
+      <c r="B99" s="28" t="n"/>
+      <c r="C99" s="28" t="n"/>
+      <c r="D99" s="28" t="n"/>
+      <c r="E99" s="28" t="n"/>
+      <c r="F99" s="28" t="n"/>
+      <c r="G99" s="28" t="n"/>
+      <c r="H99" s="28" t="n"/>
+      <c r="I99" s="28" t="n"/>
+      <c r="J99" s="28" t="n"/>
+      <c r="K99" s="28" t="n"/>
+      <c r="L99" s="28" t="n"/>
+      <c r="M99" s="28" t="n"/>
+      <c r="N99" s="28" t="n"/>
+      <c r="O99" s="28" t="n"/>
+      <c r="P99" s="28" t="n"/>
+      <c r="Q99" s="28" t="n"/>
+      <c r="R99" s="28" t="n"/>
+      <c r="S99" s="28" t="n"/>
+      <c r="T99" s="28" t="n"/>
+      <c r="U99" s="28" t="n"/>
+      <c r="V99" s="28" t="n"/>
+      <c r="W99" s="28" t="n"/>
+      <c r="X99" s="28" t="n"/>
+      <c r="Y99" s="28" t="n"/>
+      <c r="Z99" s="28" t="n"/>
+      <c r="AA99" s="28" t="n"/>
+      <c r="AB99" s="28" t="n"/>
+      <c r="AC99" s="28" t="n"/>
+      <c r="AD99" s="28" t="n"/>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="27" t="n"/>
+      <c r="B100" s="28" t="n"/>
+      <c r="C100" s="28" t="n"/>
+      <c r="D100" s="28" t="n"/>
+      <c r="E100" s="28" t="n"/>
+      <c r="F100" s="28" t="n"/>
+      <c r="G100" s="28" t="n"/>
+      <c r="H100" s="28" t="n"/>
+      <c r="I100" s="28" t="n"/>
+      <c r="J100" s="28" t="n"/>
+      <c r="K100" s="28" t="n"/>
+      <c r="L100" s="28" t="n"/>
+      <c r="M100" s="28" t="n"/>
+      <c r="N100" s="28" t="n"/>
+      <c r="O100" s="28" t="n"/>
+      <c r="P100" s="28" t="n"/>
+      <c r="Q100" s="28" t="n"/>
+      <c r="R100" s="28" t="n"/>
+      <c r="S100" s="28" t="n"/>
+      <c r="T100" s="28" t="n"/>
+      <c r="U100" s="28" t="n"/>
+      <c r="V100" s="28" t="n"/>
+      <c r="W100" s="28" t="n"/>
+      <c r="X100" s="28" t="n"/>
+      <c r="Y100" s="28" t="n"/>
+      <c r="Z100" s="28" t="n"/>
+      <c r="AA100" s="28" t="n"/>
+      <c r="AB100" s="28" t="n"/>
+      <c r="AC100" s="28" t="n"/>
+      <c r="AD100" s="28" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="27" t="n"/>
+      <c r="B101" s="28" t="n"/>
+      <c r="C101" s="28" t="n"/>
+      <c r="D101" s="28" t="n"/>
+      <c r="E101" s="28" t="n"/>
+      <c r="F101" s="28" t="n"/>
+      <c r="G101" s="28" t="n"/>
+      <c r="H101" s="28" t="n"/>
+      <c r="I101" s="28" t="n"/>
+      <c r="J101" s="28" t="n"/>
+      <c r="K101" s="28" t="n"/>
+      <c r="L101" s="28" t="n"/>
+      <c r="M101" s="28" t="n"/>
+      <c r="N101" s="28" t="n"/>
+      <c r="O101" s="28" t="n"/>
+      <c r="P101" s="28" t="n"/>
+      <c r="Q101" s="28" t="n"/>
+      <c r="R101" s="28" t="n"/>
+      <c r="S101" s="28" t="n"/>
+      <c r="T101" s="28" t="n"/>
+      <c r="U101" s="28" t="n"/>
+      <c r="V101" s="28" t="n"/>
+      <c r="W101" s="28" t="n"/>
+      <c r="X101" s="28" t="n"/>
+      <c r="Y101" s="28" t="n"/>
+      <c r="Z101" s="28" t="n"/>
+      <c r="AA101" s="28" t="n"/>
+      <c r="AB101" s="28" t="n"/>
+      <c r="AC101" s="28" t="n"/>
+      <c r="AD101" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -5596,10 +8988,10 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W58"/>
+  <dimension ref="A1:W101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
     <col width="3.7" customWidth="1" min="3" max="3"/>
     <col width="3.7" customWidth="1" min="4" max="4"/>
@@ -5919,10 +9311,10 @@
       </c>
       <c r="W7" s="13" t="n"/>
     </row>
-    <row r="8" ht="15" customHeight="1">
+    <row r="8" ht="14" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Núcleo del proyecto</t>
+          <t>1. Núcleo del proyecto</t>
         </is>
       </c>
       <c r="B8" s="22" t="n"/>
@@ -5952,10 +9344,10 @@
         </is>
       </c>
     </row>
-    <row r="9" outlineLevel="1" ht="15" customHeight="1">
+    <row r="9" outlineLevel="1" ht="14" customHeight="1">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>1.1 Estructura MVC y rutas</t>
         </is>
       </c>
       <c r="B9" s="22" t="n"/>
@@ -5985,10 +9377,10 @@
         </is>
       </c>
     </row>
-    <row r="10" outlineLevel="1" ht="15" customHeight="1">
+    <row r="10" outlineLevel="1" ht="14" customHeight="1">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>1.2 Modelo de base de datos</t>
         </is>
       </c>
       <c r="B10" s="22" t="n"/>
@@ -6018,10 +9410,10 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Acceso, registro y sesión</t>
+    <row r="11" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>1.3 Conexión y configuración</t>
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
@@ -6051,10 +9443,10 @@
         </is>
       </c>
     </row>
-    <row r="12" outlineLevel="1" ht="15" customHeight="1">
+    <row r="12" outlineLevel="1" ht="14" customHeight="1">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>1.4 Testeo</t>
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
@@ -6084,10 +9476,10 @@
         </is>
       </c>
     </row>
-    <row r="13" outlineLevel="1" ht="15" customHeight="1">
+    <row r="13" outlineLevel="1" ht="14" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>1.5 Documentación</t>
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
@@ -6117,10 +9509,10 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="14" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Recuperación de cuenta y tickets</t>
+          <t>2. Acceso, registro y sesión</t>
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
@@ -6150,10 +9542,10 @@
         </is>
       </c>
     </row>
-    <row r="15" outlineLevel="1" ht="15" customHeight="1">
+    <row r="15" outlineLevel="1" ht="14" customHeight="1">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>2.1 Codificación de la sesión</t>
         </is>
       </c>
       <c r="B15" s="22" t="n"/>
@@ -6183,10 +9575,10 @@
         </is>
       </c>
     </row>
-    <row r="16" outlineLevel="1" ht="15" customHeight="1">
+    <row r="16" outlineLevel="1" ht="14" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>2.2 Creación del formulario</t>
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
@@ -6216,10 +9608,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>Perfil, contraseña y baja</t>
+    <row r="17" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>2.3 Validación del formulario</t>
         </is>
       </c>
       <c r="B17" s="22" t="n"/>
@@ -6249,10 +9641,10 @@
         </is>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="15" customHeight="1">
+    <row r="18" outlineLevel="1" ht="14" customHeight="1">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>2.4 Testeo</t>
         </is>
       </c>
       <c r="B18" s="22" t="n"/>
@@ -6282,10 +9674,10 @@
         </is>
       </c>
     </row>
-    <row r="19" outlineLevel="1" ht="15" customHeight="1">
+    <row r="19" outlineLevel="1" ht="14" customHeight="1">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>2.5 Documentación</t>
         </is>
       </c>
       <c r="B19" s="22" t="n"/>
@@ -6315,10 +9707,10 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="14" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Actividades y horario</t>
+          <t>3. Recuperación de cuenta y tickets</t>
         </is>
       </c>
       <c r="B20" s="22" t="n"/>
@@ -6342,16 +9734,16 @@
       <c r="T20" s="22" t="n"/>
       <c r="U20" s="22" t="n"/>
       <c r="V20" s="22" t="n"/>
-      <c r="W20" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W20" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" outlineLevel="1" ht="14" customHeight="1">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>3.1 Formulario de recuperación</t>
         </is>
       </c>
       <c r="B21" s="22" t="n"/>
@@ -6375,16 +9767,16 @@
       <c r="T21" s="22" t="n"/>
       <c r="U21" s="22" t="n"/>
       <c r="V21" s="22" t="n"/>
-      <c r="W21" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W21" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1" ht="14" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>3.2 Tickets de la cuenta</t>
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
@@ -6408,16 +9800,16 @@
       <c r="T22" s="22" t="n"/>
       <c r="U22" s="22" t="n"/>
       <c r="V22" s="22" t="n"/>
-      <c r="W22" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>Inscripciones y reservas</t>
+      <c r="W22" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>3.3 Envío del enlace</t>
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
@@ -6441,16 +9833,16 @@
       <c r="T23" s="22" t="n"/>
       <c r="U23" s="22" t="n"/>
       <c r="V23" s="22" t="n"/>
-      <c r="W23" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W23" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" outlineLevel="1" ht="14" customHeight="1">
       <c r="A24" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>3.4 Testeo</t>
         </is>
       </c>
       <c r="B24" s="22" t="n"/>
@@ -6474,16 +9866,16 @@
       <c r="T24" s="22" t="n"/>
       <c r="U24" s="22" t="n"/>
       <c r="V24" s="22" t="n"/>
-      <c r="W24" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W24" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" outlineLevel="1" ht="14" customHeight="1">
       <c r="A25" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>3.5 Documentación</t>
         </is>
       </c>
       <c r="B25" s="22" t="n"/>
@@ -6507,16 +9899,16 @@
       <c r="T25" s="22" t="n"/>
       <c r="U25" s="22" t="n"/>
       <c r="V25" s="22" t="n"/>
-      <c r="W25" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
+      <c r="W25" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="14" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>Suscripciones</t>
+          <t>4. Perfil, contraseña y baja</t>
         </is>
       </c>
       <c r="B26" s="22" t="n"/>
@@ -6540,16 +9932,16 @@
       <c r="T26" s="22" t="n"/>
       <c r="U26" s="22" t="n"/>
       <c r="V26" s="22" t="n"/>
-      <c r="W26" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W26" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1" ht="14" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>4.1 Edición del perfil</t>
         </is>
       </c>
       <c r="B27" s="22" t="n"/>
@@ -6573,16 +9965,16 @@
       <c r="T27" s="22" t="n"/>
       <c r="U27" s="22" t="n"/>
       <c r="V27" s="22" t="n"/>
-      <c r="W27" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W27" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" outlineLevel="1" ht="14" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>4.2 Cambio de contraseña</t>
         </is>
       </c>
       <c r="B28" s="22" t="n"/>
@@ -6606,16 +9998,16 @@
       <c r="T28" s="22" t="n"/>
       <c r="U28" s="22" t="n"/>
       <c r="V28" s="22" t="n"/>
-      <c r="W28" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>Pagos con Stripe</t>
+      <c r="W28" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>4.3 Baja y reactivación</t>
         </is>
       </c>
       <c r="B29" s="22" t="n"/>
@@ -6639,16 +10031,16 @@
       <c r="T29" s="22" t="n"/>
       <c r="U29" s="22" t="n"/>
       <c r="V29" s="22" t="n"/>
-      <c r="W29" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W29" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1" ht="14" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>4.4 Testeo</t>
         </is>
       </c>
       <c r="B30" s="22" t="n"/>
@@ -6672,16 +10064,16 @@
       <c r="T30" s="22" t="n"/>
       <c r="U30" s="22" t="n"/>
       <c r="V30" s="22" t="n"/>
-      <c r="W30" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W30" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1" ht="14" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>4.5 Documentación</t>
         </is>
       </c>
       <c r="B31" s="22" t="n"/>
@@ -6705,16 +10097,16 @@
       <c r="T31" s="22" t="n"/>
       <c r="U31" s="22" t="n"/>
       <c r="V31" s="22" t="n"/>
-      <c r="W31" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+      <c r="W31" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="14" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>Panel de administración</t>
+          <t>5. Actividades y horario</t>
         </is>
       </c>
       <c r="B32" s="22" t="n"/>
@@ -6738,16 +10130,16 @@
       <c r="T32" s="22" t="n"/>
       <c r="U32" s="22" t="n"/>
       <c r="V32" s="22" t="n"/>
-      <c r="W32" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W32" s="25" t="inlineStr">
+        <is>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1" ht="14" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>5.1 Listado de actividades</t>
         </is>
       </c>
       <c r="B33" s="22" t="n"/>
@@ -6771,16 +10163,16 @@
       <c r="T33" s="22" t="n"/>
       <c r="U33" s="22" t="n"/>
       <c r="V33" s="22" t="n"/>
-      <c r="W33" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W33" s="25" t="inlineStr">
+        <is>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1" ht="14" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>5.2 Horario del centro</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
@@ -6804,16 +10196,16 @@
       <c r="T34" s="22" t="n"/>
       <c r="U34" s="22" t="n"/>
       <c r="V34" s="22" t="n"/>
-      <c r="W34" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>Gestión de clientes</t>
+      <c r="W34" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>5.3 Alta y edición</t>
         </is>
       </c>
       <c r="B35" s="22" t="n"/>
@@ -6837,16 +10229,16 @@
       <c r="T35" s="22" t="n"/>
       <c r="U35" s="22" t="n"/>
       <c r="V35" s="22" t="n"/>
-      <c r="W35" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W35" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" outlineLevel="1" ht="14" customHeight="1">
       <c r="A36" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>5.4 Testeo</t>
         </is>
       </c>
       <c r="B36" s="22" t="n"/>
@@ -6870,16 +10262,16 @@
       <c r="T36" s="22" t="n"/>
       <c r="U36" s="22" t="n"/>
       <c r="V36" s="22" t="n"/>
-      <c r="W36" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W36" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1" ht="14" customHeight="1">
       <c r="A37" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>5.5 Documentación</t>
         </is>
       </c>
       <c r="B37" s="22" t="n"/>
@@ -6903,16 +10295,16 @@
       <c r="T37" s="22" t="n"/>
       <c r="U37" s="22" t="n"/>
       <c r="V37" s="22" t="n"/>
-      <c r="W37" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
+      <c r="W37" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="14" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>Monitores y solicitudes</t>
+          <t>6. Inscripciones y reservas</t>
         </is>
       </c>
       <c r="B38" s="22" t="n"/>
@@ -6936,16 +10328,16 @@
       <c r="T38" s="22" t="n"/>
       <c r="U38" s="22" t="n"/>
       <c r="V38" s="22" t="n"/>
-      <c r="W38" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W38" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" outlineLevel="1" ht="14" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>6.1 Formulario de inscripción</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -6969,16 +10361,16 @@
       <c r="T39" s="22" t="n"/>
       <c r="U39" s="22" t="n"/>
       <c r="V39" s="22" t="n"/>
-      <c r="W39" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W39" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" outlineLevel="1" ht="14" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>6.2 Control de plazas</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7002,16 +10394,16 @@
       <c r="T40" s="22" t="n"/>
       <c r="U40" s="22" t="n"/>
       <c r="V40" s="22" t="n"/>
-      <c r="W40" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>Salas y materiales</t>
+      <c r="W40" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>6.3 Reservas del cliente</t>
         </is>
       </c>
       <c r="B41" s="22" t="n"/>
@@ -7035,16 +10427,16 @@
       <c r="T41" s="22" t="n"/>
       <c r="U41" s="22" t="n"/>
       <c r="V41" s="22" t="n"/>
-      <c r="W41" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W41" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" outlineLevel="1" ht="14" customHeight="1">
       <c r="A42" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>6.4 Testeo</t>
         </is>
       </c>
       <c r="B42" s="22" t="n"/>
@@ -7068,16 +10460,16 @@
       <c r="T42" s="22" t="n"/>
       <c r="U42" s="22" t="n"/>
       <c r="V42" s="22" t="n"/>
-      <c r="W42" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W42" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" outlineLevel="1" ht="14" customHeight="1">
       <c r="A43" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>6.5 Documentación</t>
         </is>
       </c>
       <c r="B43" s="22" t="n"/>
@@ -7101,16 +10493,16 @@
       <c r="T43" s="22" t="n"/>
       <c r="U43" s="22" t="n"/>
       <c r="V43" s="22" t="n"/>
-      <c r="W43" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
+      <c r="W43" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="14" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>Fisioterapia y citas</t>
+          <t>7. Suscripciones</t>
         </is>
       </c>
       <c r="B44" s="22" t="n"/>
@@ -7134,16 +10526,16 @@
       <c r="T44" s="22" t="n"/>
       <c r="U44" s="22" t="n"/>
       <c r="V44" s="22" t="n"/>
-      <c r="W44" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W44" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" outlineLevel="1" ht="14" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>7.1 Planes de suscripción</t>
         </is>
       </c>
       <c r="B45" s="22" t="n"/>
@@ -7167,16 +10559,16 @@
       <c r="T45" s="22" t="n"/>
       <c r="U45" s="22" t="n"/>
       <c r="V45" s="22" t="n"/>
-      <c r="W45" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W45" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1" ht="14" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>7.2 Alta del cliente</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -7200,16 +10592,16 @@
       <c r="T46" s="22" t="n"/>
       <c r="U46" s="22" t="n"/>
       <c r="V46" s="22" t="n"/>
-      <c r="W46" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>Comentarios, feedback y seguridad</t>
+      <c r="W46" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>7.3 Renovación y baja</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7233,16 +10625,16 @@
       <c r="T47" s="22" t="n"/>
       <c r="U47" s="22" t="n"/>
       <c r="V47" s="22" t="n"/>
-      <c r="W47" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W47" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1" ht="14" customHeight="1">
       <c r="A48" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
+          <t>7.4 Testeo</t>
         </is>
       </c>
       <c r="B48" s="22" t="n"/>
@@ -7266,16 +10658,16 @@
       <c r="T48" s="22" t="n"/>
       <c r="U48" s="22" t="n"/>
       <c r="V48" s="22" t="n"/>
-      <c r="W48" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W48" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" outlineLevel="1" ht="14" customHeight="1">
       <c r="A49" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
+          <t>7.5 Documentación</t>
         </is>
       </c>
       <c r="B49" s="22" t="n"/>
@@ -7299,16 +10691,16 @@
       <c r="T49" s="22" t="n"/>
       <c r="U49" s="22" t="n"/>
       <c r="V49" s="22" t="n"/>
-      <c r="W49" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
+      <c r="W49" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="14" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>Interfaz Tailwind, correo y cierre</t>
+          <t>8. Pagos con Stripe</t>
         </is>
       </c>
       <c r="B50" s="22" t="n"/>
@@ -7332,19 +10724,19 @@
       <c r="T50" s="22" t="n"/>
       <c r="U50" s="22" t="n"/>
       <c r="V50" s="22" t="n"/>
-      <c r="W50" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W50" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="1" ht="14" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>Documentación</t>
-        </is>
-      </c>
-      <c r="B51" s="28" t="n"/>
+          <t>8.1 Pasarela de Stripe</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="n"/>
       <c r="C51" s="22" t="n"/>
       <c r="D51" s="22" t="n"/>
       <c r="E51" s="22" t="n"/>
@@ -7365,23 +10757,23 @@
       <c r="T51" s="22" t="n"/>
       <c r="U51" s="22" t="n"/>
       <c r="V51" s="22" t="n"/>
-      <c r="W51" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" outlineLevel="1" ht="15" customHeight="1">
+      <c r="W51" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" outlineLevel="1" ht="14" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>Testeo</t>
-        </is>
-      </c>
-      <c r="B52" s="28" t="n"/>
-      <c r="C52" s="28" t="n"/>
-      <c r="D52" s="28" t="n"/>
-      <c r="E52" s="28" t="n"/>
-      <c r="F52" s="28" t="n"/>
+          <t>8.2 Confirmación del pago</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="n"/>
+      <c r="C52" s="22" t="n"/>
+      <c r="D52" s="22" t="n"/>
+      <c r="E52" s="22" t="n"/>
+      <c r="F52" s="22" t="n"/>
       <c r="G52" s="22" t="n"/>
       <c r="H52" s="22" t="n"/>
       <c r="I52" s="22" t="n"/>
@@ -7398,161 +10790,1596 @@
       <c r="T52" s="22" t="n"/>
       <c r="U52" s="22" t="n"/>
       <c r="V52" s="22" t="n"/>
-      <c r="W52" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="31" t="n"/>
-      <c r="B53" s="32" t="n"/>
-      <c r="C53" s="32" t="n"/>
-      <c r="D53" s="32" t="n"/>
-      <c r="E53" s="32" t="n"/>
-      <c r="F53" s="32" t="n"/>
-      <c r="G53" s="32" t="n"/>
-      <c r="H53" s="32" t="n"/>
-      <c r="I53" s="32" t="n"/>
-      <c r="J53" s="32" t="n"/>
-      <c r="K53" s="32" t="n"/>
-      <c r="L53" s="32" t="n"/>
-      <c r="M53" s="32" t="n"/>
-      <c r="N53" s="32" t="n"/>
-      <c r="O53" s="32" t="n"/>
-      <c r="P53" s="32" t="n"/>
-      <c r="Q53" s="32" t="n"/>
-      <c r="R53" s="32" t="n"/>
-      <c r="S53" s="32" t="n"/>
-      <c r="T53" s="32" t="n"/>
-      <c r="U53" s="32" t="n"/>
-      <c r="V53" s="32" t="n"/>
-      <c r="W53" s="32" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="31" t="n"/>
-      <c r="B54" s="32" t="n"/>
-      <c r="C54" s="32" t="n"/>
-      <c r="D54" s="32" t="n"/>
-      <c r="E54" s="32" t="n"/>
-      <c r="F54" s="32" t="n"/>
-      <c r="G54" s="32" t="n"/>
-      <c r="H54" s="32" t="n"/>
-      <c r="I54" s="32" t="n"/>
-      <c r="J54" s="32" t="n"/>
-      <c r="K54" s="32" t="n"/>
-      <c r="L54" s="32" t="n"/>
-      <c r="M54" s="32" t="n"/>
-      <c r="N54" s="32" t="n"/>
-      <c r="O54" s="32" t="n"/>
-      <c r="P54" s="32" t="n"/>
-      <c r="Q54" s="32" t="n"/>
-      <c r="R54" s="32" t="n"/>
-      <c r="S54" s="32" t="n"/>
-      <c r="T54" s="32" t="n"/>
-      <c r="U54" s="32" t="n"/>
-      <c r="V54" s="32" t="n"/>
-      <c r="W54" s="32" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="31" t="n"/>
-      <c r="B55" s="32" t="n"/>
-      <c r="C55" s="32" t="n"/>
-      <c r="D55" s="32" t="n"/>
-      <c r="E55" s="32" t="n"/>
-      <c r="F55" s="32" t="n"/>
-      <c r="G55" s="32" t="n"/>
-      <c r="H55" s="32" t="n"/>
-      <c r="I55" s="32" t="n"/>
-      <c r="J55" s="32" t="n"/>
-      <c r="K55" s="32" t="n"/>
-      <c r="L55" s="32" t="n"/>
-      <c r="M55" s="32" t="n"/>
-      <c r="N55" s="32" t="n"/>
-      <c r="O55" s="32" t="n"/>
-      <c r="P55" s="32" t="n"/>
-      <c r="Q55" s="32" t="n"/>
-      <c r="R55" s="32" t="n"/>
-      <c r="S55" s="32" t="n"/>
-      <c r="T55" s="32" t="n"/>
-      <c r="U55" s="32" t="n"/>
-      <c r="V55" s="32" t="n"/>
-      <c r="W55" s="32" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="31" t="n"/>
-      <c r="B56" s="32" t="n"/>
-      <c r="C56" s="32" t="n"/>
-      <c r="D56" s="32" t="n"/>
-      <c r="E56" s="32" t="n"/>
-      <c r="F56" s="32" t="n"/>
-      <c r="G56" s="32" t="n"/>
-      <c r="H56" s="32" t="n"/>
-      <c r="I56" s="32" t="n"/>
-      <c r="J56" s="32" t="n"/>
-      <c r="K56" s="32" t="n"/>
-      <c r="L56" s="32" t="n"/>
-      <c r="M56" s="32" t="n"/>
-      <c r="N56" s="32" t="n"/>
-      <c r="O56" s="32" t="n"/>
-      <c r="P56" s="32" t="n"/>
-      <c r="Q56" s="32" t="n"/>
-      <c r="R56" s="32" t="n"/>
-      <c r="S56" s="32" t="n"/>
-      <c r="T56" s="32" t="n"/>
-      <c r="U56" s="32" t="n"/>
-      <c r="V56" s="32" t="n"/>
-      <c r="W56" s="32" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="31" t="n"/>
-      <c r="B57" s="32" t="n"/>
-      <c r="C57" s="32" t="n"/>
-      <c r="D57" s="32" t="n"/>
-      <c r="E57" s="32" t="n"/>
-      <c r="F57" s="32" t="n"/>
-      <c r="G57" s="32" t="n"/>
-      <c r="H57" s="32" t="n"/>
-      <c r="I57" s="32" t="n"/>
-      <c r="J57" s="32" t="n"/>
-      <c r="K57" s="32" t="n"/>
-      <c r="L57" s="32" t="n"/>
-      <c r="M57" s="32" t="n"/>
-      <c r="N57" s="32" t="n"/>
-      <c r="O57" s="32" t="n"/>
-      <c r="P57" s="32" t="n"/>
-      <c r="Q57" s="32" t="n"/>
-      <c r="R57" s="32" t="n"/>
-      <c r="S57" s="32" t="n"/>
-      <c r="T57" s="32" t="n"/>
-      <c r="U57" s="32" t="n"/>
-      <c r="V57" s="32" t="n"/>
-      <c r="W57" s="32" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="31" t="n"/>
-      <c r="B58" s="32" t="n"/>
-      <c r="C58" s="32" t="n"/>
-      <c r="D58" s="32" t="n"/>
-      <c r="E58" s="32" t="n"/>
-      <c r="F58" s="32" t="n"/>
-      <c r="G58" s="32" t="n"/>
-      <c r="H58" s="32" t="n"/>
-      <c r="I58" s="32" t="n"/>
-      <c r="J58" s="32" t="n"/>
-      <c r="K58" s="32" t="n"/>
-      <c r="L58" s="32" t="n"/>
-      <c r="M58" s="32" t="n"/>
-      <c r="N58" s="32" t="n"/>
-      <c r="O58" s="32" t="n"/>
-      <c r="P58" s="32" t="n"/>
-      <c r="Q58" s="32" t="n"/>
-      <c r="R58" s="32" t="n"/>
-      <c r="S58" s="32" t="n"/>
-      <c r="T58" s="32" t="n"/>
-      <c r="U58" s="32" t="n"/>
-      <c r="V58" s="32" t="n"/>
-      <c r="W58" s="32" t="n"/>
+      <c r="W52" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>8.3 Pago cancelado</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="n"/>
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="22" t="n"/>
+      <c r="F53" s="22" t="n"/>
+      <c r="G53" s="22" t="n"/>
+      <c r="H53" s="22" t="n"/>
+      <c r="I53" s="22" t="n"/>
+      <c r="J53" s="22" t="n"/>
+      <c r="K53" s="22" t="n"/>
+      <c r="L53" s="22" t="n"/>
+      <c r="M53" s="22" t="n"/>
+      <c r="N53" s="22" t="n"/>
+      <c r="O53" s="22" t="n"/>
+      <c r="P53" s="22" t="n"/>
+      <c r="Q53" s="22" t="n"/>
+      <c r="R53" s="22" t="n"/>
+      <c r="S53" s="22" t="n"/>
+      <c r="T53" s="22" t="n"/>
+      <c r="U53" s="22" t="n"/>
+      <c r="V53" s="22" t="n"/>
+      <c r="W53" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>8.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="22" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="22" t="n"/>
+      <c r="G54" s="22" t="n"/>
+      <c r="H54" s="22" t="n"/>
+      <c r="I54" s="22" t="n"/>
+      <c r="J54" s="22" t="n"/>
+      <c r="K54" s="22" t="n"/>
+      <c r="L54" s="22" t="n"/>
+      <c r="M54" s="22" t="n"/>
+      <c r="N54" s="22" t="n"/>
+      <c r="O54" s="22" t="n"/>
+      <c r="P54" s="22" t="n"/>
+      <c r="Q54" s="22" t="n"/>
+      <c r="R54" s="22" t="n"/>
+      <c r="S54" s="22" t="n"/>
+      <c r="T54" s="22" t="n"/>
+      <c r="U54" s="22" t="n"/>
+      <c r="V54" s="22" t="n"/>
+      <c r="W54" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>8.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="n"/>
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="22" t="n"/>
+      <c r="E55" s="22" t="n"/>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="22" t="n"/>
+      <c r="H55" s="22" t="n"/>
+      <c r="I55" s="22" t="n"/>
+      <c r="J55" s="22" t="n"/>
+      <c r="K55" s="22" t="n"/>
+      <c r="L55" s="22" t="n"/>
+      <c r="M55" s="22" t="n"/>
+      <c r="N55" s="22" t="n"/>
+      <c r="O55" s="22" t="n"/>
+      <c r="P55" s="22" t="n"/>
+      <c r="Q55" s="22" t="n"/>
+      <c r="R55" s="22" t="n"/>
+      <c r="S55" s="22" t="n"/>
+      <c r="T55" s="22" t="n"/>
+      <c r="U55" s="22" t="n"/>
+      <c r="V55" s="22" t="n"/>
+      <c r="W55" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>9. Panel de administración</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="n"/>
+      <c r="C56" s="22" t="n"/>
+      <c r="D56" s="22" t="n"/>
+      <c r="E56" s="22" t="n"/>
+      <c r="F56" s="22" t="n"/>
+      <c r="G56" s="22" t="n"/>
+      <c r="H56" s="22" t="n"/>
+      <c r="I56" s="22" t="n"/>
+      <c r="J56" s="22" t="n"/>
+      <c r="K56" s="22" t="n"/>
+      <c r="L56" s="22" t="n"/>
+      <c r="M56" s="22" t="n"/>
+      <c r="N56" s="22" t="n"/>
+      <c r="O56" s="22" t="n"/>
+      <c r="P56" s="22" t="n"/>
+      <c r="Q56" s="22" t="n"/>
+      <c r="R56" s="22" t="n"/>
+      <c r="S56" s="22" t="n"/>
+      <c r="T56" s="22" t="n"/>
+      <c r="U56" s="22" t="n"/>
+      <c r="V56" s="22" t="n"/>
+      <c r="W56" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>9.1 Inicio del panel</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="n"/>
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="22" t="n"/>
+      <c r="E57" s="22" t="n"/>
+      <c r="F57" s="22" t="n"/>
+      <c r="G57" s="22" t="n"/>
+      <c r="H57" s="22" t="n"/>
+      <c r="I57" s="22" t="n"/>
+      <c r="J57" s="22" t="n"/>
+      <c r="K57" s="22" t="n"/>
+      <c r="L57" s="22" t="n"/>
+      <c r="M57" s="22" t="n"/>
+      <c r="N57" s="22" t="n"/>
+      <c r="O57" s="22" t="n"/>
+      <c r="P57" s="22" t="n"/>
+      <c r="Q57" s="22" t="n"/>
+      <c r="R57" s="22" t="n"/>
+      <c r="S57" s="22" t="n"/>
+      <c r="T57" s="22" t="n"/>
+      <c r="U57" s="22" t="n"/>
+      <c r="V57" s="22" t="n"/>
+      <c r="W57" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>9.2 Menú y permisos</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="n"/>
+      <c r="C58" s="22" t="n"/>
+      <c r="D58" s="22" t="n"/>
+      <c r="E58" s="22" t="n"/>
+      <c r="F58" s="22" t="n"/>
+      <c r="G58" s="22" t="n"/>
+      <c r="H58" s="22" t="n"/>
+      <c r="I58" s="22" t="n"/>
+      <c r="J58" s="22" t="n"/>
+      <c r="K58" s="22" t="n"/>
+      <c r="L58" s="22" t="n"/>
+      <c r="M58" s="22" t="n"/>
+      <c r="N58" s="22" t="n"/>
+      <c r="O58" s="22" t="n"/>
+      <c r="P58" s="22" t="n"/>
+      <c r="Q58" s="22" t="n"/>
+      <c r="R58" s="22" t="n"/>
+      <c r="S58" s="22" t="n"/>
+      <c r="T58" s="22" t="n"/>
+      <c r="U58" s="22" t="n"/>
+      <c r="V58" s="22" t="n"/>
+      <c r="W58" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>9.3 Listados del panel</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="n"/>
+      <c r="C59" s="22" t="n"/>
+      <c r="D59" s="22" t="n"/>
+      <c r="E59" s="22" t="n"/>
+      <c r="F59" s="22" t="n"/>
+      <c r="G59" s="22" t="n"/>
+      <c r="H59" s="22" t="n"/>
+      <c r="I59" s="22" t="n"/>
+      <c r="J59" s="22" t="n"/>
+      <c r="K59" s="22" t="n"/>
+      <c r="L59" s="22" t="n"/>
+      <c r="M59" s="22" t="n"/>
+      <c r="N59" s="22" t="n"/>
+      <c r="O59" s="22" t="n"/>
+      <c r="P59" s="22" t="n"/>
+      <c r="Q59" s="22" t="n"/>
+      <c r="R59" s="22" t="n"/>
+      <c r="S59" s="22" t="n"/>
+      <c r="T59" s="22" t="n"/>
+      <c r="U59" s="22" t="n"/>
+      <c r="V59" s="22" t="n"/>
+      <c r="W59" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>9.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="n"/>
+      <c r="C60" s="22" t="n"/>
+      <c r="D60" s="22" t="n"/>
+      <c r="E60" s="22" t="n"/>
+      <c r="F60" s="22" t="n"/>
+      <c r="G60" s="22" t="n"/>
+      <c r="H60" s="22" t="n"/>
+      <c r="I60" s="22" t="n"/>
+      <c r="J60" s="22" t="n"/>
+      <c r="K60" s="22" t="n"/>
+      <c r="L60" s="22" t="n"/>
+      <c r="M60" s="22" t="n"/>
+      <c r="N60" s="22" t="n"/>
+      <c r="O60" s="22" t="n"/>
+      <c r="P60" s="22" t="n"/>
+      <c r="Q60" s="22" t="n"/>
+      <c r="R60" s="22" t="n"/>
+      <c r="S60" s="22" t="n"/>
+      <c r="T60" s="22" t="n"/>
+      <c r="U60" s="22" t="n"/>
+      <c r="V60" s="22" t="n"/>
+      <c r="W60" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>9.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="n"/>
+      <c r="C61" s="22" t="n"/>
+      <c r="D61" s="22" t="n"/>
+      <c r="E61" s="22" t="n"/>
+      <c r="F61" s="22" t="n"/>
+      <c r="G61" s="22" t="n"/>
+      <c r="H61" s="22" t="n"/>
+      <c r="I61" s="22" t="n"/>
+      <c r="J61" s="22" t="n"/>
+      <c r="K61" s="22" t="n"/>
+      <c r="L61" s="22" t="n"/>
+      <c r="M61" s="22" t="n"/>
+      <c r="N61" s="22" t="n"/>
+      <c r="O61" s="22" t="n"/>
+      <c r="P61" s="22" t="n"/>
+      <c r="Q61" s="22" t="n"/>
+      <c r="R61" s="22" t="n"/>
+      <c r="S61" s="22" t="n"/>
+      <c r="T61" s="22" t="n"/>
+      <c r="U61" s="22" t="n"/>
+      <c r="V61" s="22" t="n"/>
+      <c r="W61" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>10. Gestión de clientes</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="n"/>
+      <c r="C62" s="22" t="n"/>
+      <c r="D62" s="22" t="n"/>
+      <c r="E62" s="22" t="n"/>
+      <c r="F62" s="22" t="n"/>
+      <c r="G62" s="22" t="n"/>
+      <c r="H62" s="22" t="n"/>
+      <c r="I62" s="22" t="n"/>
+      <c r="J62" s="22" t="n"/>
+      <c r="K62" s="22" t="n"/>
+      <c r="L62" s="22" t="n"/>
+      <c r="M62" s="22" t="n"/>
+      <c r="N62" s="22" t="n"/>
+      <c r="O62" s="22" t="n"/>
+      <c r="P62" s="22" t="n"/>
+      <c r="Q62" s="22" t="n"/>
+      <c r="R62" s="22" t="n"/>
+      <c r="S62" s="22" t="n"/>
+      <c r="T62" s="22" t="n"/>
+      <c r="U62" s="22" t="n"/>
+      <c r="V62" s="22" t="n"/>
+      <c r="W62" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>10.1 Listado de clientes</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="n"/>
+      <c r="C63" s="22" t="n"/>
+      <c r="D63" s="22" t="n"/>
+      <c r="E63" s="22" t="n"/>
+      <c r="F63" s="22" t="n"/>
+      <c r="G63" s="22" t="n"/>
+      <c r="H63" s="22" t="n"/>
+      <c r="I63" s="22" t="n"/>
+      <c r="J63" s="22" t="n"/>
+      <c r="K63" s="22" t="n"/>
+      <c r="L63" s="22" t="n"/>
+      <c r="M63" s="22" t="n"/>
+      <c r="N63" s="22" t="n"/>
+      <c r="O63" s="22" t="n"/>
+      <c r="P63" s="22" t="n"/>
+      <c r="Q63" s="22" t="n"/>
+      <c r="R63" s="22" t="n"/>
+      <c r="S63" s="22" t="n"/>
+      <c r="T63" s="22" t="n"/>
+      <c r="U63" s="22" t="n"/>
+      <c r="V63" s="22" t="n"/>
+      <c r="W63" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>10.2 Ficha del cliente</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="n"/>
+      <c r="C64" s="22" t="n"/>
+      <c r="D64" s="22" t="n"/>
+      <c r="E64" s="22" t="n"/>
+      <c r="F64" s="22" t="n"/>
+      <c r="G64" s="22" t="n"/>
+      <c r="H64" s="22" t="n"/>
+      <c r="I64" s="22" t="n"/>
+      <c r="J64" s="22" t="n"/>
+      <c r="K64" s="22" t="n"/>
+      <c r="L64" s="22" t="n"/>
+      <c r="M64" s="22" t="n"/>
+      <c r="N64" s="22" t="n"/>
+      <c r="O64" s="22" t="n"/>
+      <c r="P64" s="22" t="n"/>
+      <c r="Q64" s="22" t="n"/>
+      <c r="R64" s="22" t="n"/>
+      <c r="S64" s="22" t="n"/>
+      <c r="T64" s="22" t="n"/>
+      <c r="U64" s="22" t="n"/>
+      <c r="V64" s="22" t="n"/>
+      <c r="W64" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>10.3 Edición de datos</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="n"/>
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="22" t="n"/>
+      <c r="E65" s="22" t="n"/>
+      <c r="F65" s="22" t="n"/>
+      <c r="G65" s="22" t="n"/>
+      <c r="H65" s="22" t="n"/>
+      <c r="I65" s="22" t="n"/>
+      <c r="J65" s="22" t="n"/>
+      <c r="K65" s="22" t="n"/>
+      <c r="L65" s="22" t="n"/>
+      <c r="M65" s="22" t="n"/>
+      <c r="N65" s="22" t="n"/>
+      <c r="O65" s="22" t="n"/>
+      <c r="P65" s="22" t="n"/>
+      <c r="Q65" s="22" t="n"/>
+      <c r="R65" s="22" t="n"/>
+      <c r="S65" s="22" t="n"/>
+      <c r="T65" s="22" t="n"/>
+      <c r="U65" s="22" t="n"/>
+      <c r="V65" s="22" t="n"/>
+      <c r="W65" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>10.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="n"/>
+      <c r="C66" s="22" t="n"/>
+      <c r="D66" s="22" t="n"/>
+      <c r="E66" s="22" t="n"/>
+      <c r="F66" s="22" t="n"/>
+      <c r="G66" s="22" t="n"/>
+      <c r="H66" s="22" t="n"/>
+      <c r="I66" s="22" t="n"/>
+      <c r="J66" s="22" t="n"/>
+      <c r="K66" s="22" t="n"/>
+      <c r="L66" s="22" t="n"/>
+      <c r="M66" s="22" t="n"/>
+      <c r="N66" s="22" t="n"/>
+      <c r="O66" s="22" t="n"/>
+      <c r="P66" s="22" t="n"/>
+      <c r="Q66" s="22" t="n"/>
+      <c r="R66" s="22" t="n"/>
+      <c r="S66" s="22" t="n"/>
+      <c r="T66" s="22" t="n"/>
+      <c r="U66" s="22" t="n"/>
+      <c r="V66" s="22" t="n"/>
+      <c r="W66" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>10.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="n"/>
+      <c r="C67" s="22" t="n"/>
+      <c r="D67" s="22" t="n"/>
+      <c r="E67" s="22" t="n"/>
+      <c r="F67" s="22" t="n"/>
+      <c r="G67" s="22" t="n"/>
+      <c r="H67" s="22" t="n"/>
+      <c r="I67" s="22" t="n"/>
+      <c r="J67" s="22" t="n"/>
+      <c r="K67" s="22" t="n"/>
+      <c r="L67" s="22" t="n"/>
+      <c r="M67" s="22" t="n"/>
+      <c r="N67" s="22" t="n"/>
+      <c r="O67" s="22" t="n"/>
+      <c r="P67" s="22" t="n"/>
+      <c r="Q67" s="22" t="n"/>
+      <c r="R67" s="22" t="n"/>
+      <c r="S67" s="22" t="n"/>
+      <c r="T67" s="22" t="n"/>
+      <c r="U67" s="22" t="n"/>
+      <c r="V67" s="22" t="n"/>
+      <c r="W67" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>11. Monitores y solicitudes</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="n"/>
+      <c r="C68" s="22" t="n"/>
+      <c r="D68" s="22" t="n"/>
+      <c r="E68" s="22" t="n"/>
+      <c r="F68" s="22" t="n"/>
+      <c r="G68" s="22" t="n"/>
+      <c r="H68" s="22" t="n"/>
+      <c r="I68" s="22" t="n"/>
+      <c r="J68" s="22" t="n"/>
+      <c r="K68" s="22" t="n"/>
+      <c r="L68" s="22" t="n"/>
+      <c r="M68" s="22" t="n"/>
+      <c r="N68" s="22" t="n"/>
+      <c r="O68" s="22" t="n"/>
+      <c r="P68" s="22" t="n"/>
+      <c r="Q68" s="22" t="n"/>
+      <c r="R68" s="22" t="n"/>
+      <c r="S68" s="22" t="n"/>
+      <c r="T68" s="22" t="n"/>
+      <c r="U68" s="22" t="n"/>
+      <c r="V68" s="22" t="n"/>
+      <c r="W68" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>11.1 Alta de monitores</t>
+        </is>
+      </c>
+      <c r="B69" s="22" t="n"/>
+      <c r="C69" s="22" t="n"/>
+      <c r="D69" s="22" t="n"/>
+      <c r="E69" s="22" t="n"/>
+      <c r="F69" s="22" t="n"/>
+      <c r="G69" s="22" t="n"/>
+      <c r="H69" s="22" t="n"/>
+      <c r="I69" s="22" t="n"/>
+      <c r="J69" s="22" t="n"/>
+      <c r="K69" s="22" t="n"/>
+      <c r="L69" s="22" t="n"/>
+      <c r="M69" s="22" t="n"/>
+      <c r="N69" s="22" t="n"/>
+      <c r="O69" s="22" t="n"/>
+      <c r="P69" s="22" t="n"/>
+      <c r="Q69" s="22" t="n"/>
+      <c r="R69" s="22" t="n"/>
+      <c r="S69" s="22" t="n"/>
+      <c r="T69" s="22" t="n"/>
+      <c r="U69" s="22" t="n"/>
+      <c r="V69" s="22" t="n"/>
+      <c r="W69" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>11.2 Solicitudes de clase</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="n"/>
+      <c r="C70" s="22" t="n"/>
+      <c r="D70" s="22" t="n"/>
+      <c r="E70" s="22" t="n"/>
+      <c r="F70" s="22" t="n"/>
+      <c r="G70" s="22" t="n"/>
+      <c r="H70" s="22" t="n"/>
+      <c r="I70" s="22" t="n"/>
+      <c r="J70" s="22" t="n"/>
+      <c r="K70" s="22" t="n"/>
+      <c r="L70" s="22" t="n"/>
+      <c r="M70" s="22" t="n"/>
+      <c r="N70" s="22" t="n"/>
+      <c r="O70" s="22" t="n"/>
+      <c r="P70" s="22" t="n"/>
+      <c r="Q70" s="22" t="n"/>
+      <c r="R70" s="22" t="n"/>
+      <c r="S70" s="22" t="n"/>
+      <c r="T70" s="22" t="n"/>
+      <c r="U70" s="22" t="n"/>
+      <c r="V70" s="22" t="n"/>
+      <c r="W70" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>11.3 Aprobación y rechazo</t>
+        </is>
+      </c>
+      <c r="B71" s="22" t="n"/>
+      <c r="C71" s="22" t="n"/>
+      <c r="D71" s="22" t="n"/>
+      <c r="E71" s="22" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="G71" s="22" t="n"/>
+      <c r="H71" s="22" t="n"/>
+      <c r="I71" s="22" t="n"/>
+      <c r="J71" s="22" t="n"/>
+      <c r="K71" s="22" t="n"/>
+      <c r="L71" s="22" t="n"/>
+      <c r="M71" s="22" t="n"/>
+      <c r="N71" s="22" t="n"/>
+      <c r="O71" s="22" t="n"/>
+      <c r="P71" s="22" t="n"/>
+      <c r="Q71" s="22" t="n"/>
+      <c r="R71" s="22" t="n"/>
+      <c r="S71" s="22" t="n"/>
+      <c r="T71" s="22" t="n"/>
+      <c r="U71" s="22" t="n"/>
+      <c r="V71" s="22" t="n"/>
+      <c r="W71" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>11.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="n"/>
+      <c r="C72" s="22" t="n"/>
+      <c r="D72" s="22" t="n"/>
+      <c r="E72" s="22" t="n"/>
+      <c r="F72" s="22" t="n"/>
+      <c r="G72" s="22" t="n"/>
+      <c r="H72" s="22" t="n"/>
+      <c r="I72" s="22" t="n"/>
+      <c r="J72" s="22" t="n"/>
+      <c r="K72" s="22" t="n"/>
+      <c r="L72" s="22" t="n"/>
+      <c r="M72" s="22" t="n"/>
+      <c r="N72" s="22" t="n"/>
+      <c r="O72" s="22" t="n"/>
+      <c r="P72" s="22" t="n"/>
+      <c r="Q72" s="22" t="n"/>
+      <c r="R72" s="22" t="n"/>
+      <c r="S72" s="22" t="n"/>
+      <c r="T72" s="22" t="n"/>
+      <c r="U72" s="22" t="n"/>
+      <c r="V72" s="22" t="n"/>
+      <c r="W72" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>11.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B73" s="22" t="n"/>
+      <c r="C73" s="22" t="n"/>
+      <c r="D73" s="22" t="n"/>
+      <c r="E73" s="22" t="n"/>
+      <c r="F73" s="22" t="n"/>
+      <c r="G73" s="22" t="n"/>
+      <c r="H73" s="22" t="n"/>
+      <c r="I73" s="22" t="n"/>
+      <c r="J73" s="22" t="n"/>
+      <c r="K73" s="22" t="n"/>
+      <c r="L73" s="22" t="n"/>
+      <c r="M73" s="22" t="n"/>
+      <c r="N73" s="22" t="n"/>
+      <c r="O73" s="22" t="n"/>
+      <c r="P73" s="22" t="n"/>
+      <c r="Q73" s="22" t="n"/>
+      <c r="R73" s="22" t="n"/>
+      <c r="S73" s="22" t="n"/>
+      <c r="T73" s="22" t="n"/>
+      <c r="U73" s="22" t="n"/>
+      <c r="V73" s="22" t="n"/>
+      <c r="W73" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>12. Salas y materiales</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="n"/>
+      <c r="C74" s="22" t="n"/>
+      <c r="D74" s="22" t="n"/>
+      <c r="E74" s="22" t="n"/>
+      <c r="F74" s="22" t="n"/>
+      <c r="G74" s="22" t="n"/>
+      <c r="H74" s="22" t="n"/>
+      <c r="I74" s="22" t="n"/>
+      <c r="J74" s="22" t="n"/>
+      <c r="K74" s="22" t="n"/>
+      <c r="L74" s="22" t="n"/>
+      <c r="M74" s="22" t="n"/>
+      <c r="N74" s="22" t="n"/>
+      <c r="O74" s="22" t="n"/>
+      <c r="P74" s="22" t="n"/>
+      <c r="Q74" s="22" t="n"/>
+      <c r="R74" s="22" t="n"/>
+      <c r="S74" s="22" t="n"/>
+      <c r="T74" s="22" t="n"/>
+      <c r="U74" s="22" t="n"/>
+      <c r="V74" s="22" t="n"/>
+      <c r="W74" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>12.1 Ficha de salas</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="n"/>
+      <c r="C75" s="22" t="n"/>
+      <c r="D75" s="22" t="n"/>
+      <c r="E75" s="22" t="n"/>
+      <c r="F75" s="22" t="n"/>
+      <c r="G75" s="22" t="n"/>
+      <c r="H75" s="22" t="n"/>
+      <c r="I75" s="22" t="n"/>
+      <c r="J75" s="22" t="n"/>
+      <c r="K75" s="22" t="n"/>
+      <c r="L75" s="22" t="n"/>
+      <c r="M75" s="22" t="n"/>
+      <c r="N75" s="22" t="n"/>
+      <c r="O75" s="22" t="n"/>
+      <c r="P75" s="22" t="n"/>
+      <c r="Q75" s="22" t="n"/>
+      <c r="R75" s="22" t="n"/>
+      <c r="S75" s="22" t="n"/>
+      <c r="T75" s="22" t="n"/>
+      <c r="U75" s="22" t="n"/>
+      <c r="V75" s="22" t="n"/>
+      <c r="W75" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>12.2 Inventario de materiales</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="n"/>
+      <c r="C76" s="22" t="n"/>
+      <c r="D76" s="22" t="n"/>
+      <c r="E76" s="22" t="n"/>
+      <c r="F76" s="22" t="n"/>
+      <c r="G76" s="22" t="n"/>
+      <c r="H76" s="22" t="n"/>
+      <c r="I76" s="22" t="n"/>
+      <c r="J76" s="22" t="n"/>
+      <c r="K76" s="22" t="n"/>
+      <c r="L76" s="22" t="n"/>
+      <c r="M76" s="22" t="n"/>
+      <c r="N76" s="22" t="n"/>
+      <c r="O76" s="22" t="n"/>
+      <c r="P76" s="22" t="n"/>
+      <c r="Q76" s="22" t="n"/>
+      <c r="R76" s="22" t="n"/>
+      <c r="S76" s="22" t="n"/>
+      <c r="T76" s="22" t="n"/>
+      <c r="U76" s="22" t="n"/>
+      <c r="V76" s="22" t="n"/>
+      <c r="W76" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>12.3 Alta y edición</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="n"/>
+      <c r="C77" s="22" t="n"/>
+      <c r="D77" s="22" t="n"/>
+      <c r="E77" s="22" t="n"/>
+      <c r="F77" s="22" t="n"/>
+      <c r="G77" s="22" t="n"/>
+      <c r="H77" s="22" t="n"/>
+      <c r="I77" s="22" t="n"/>
+      <c r="J77" s="22" t="n"/>
+      <c r="K77" s="22" t="n"/>
+      <c r="L77" s="22" t="n"/>
+      <c r="M77" s="22" t="n"/>
+      <c r="N77" s="22" t="n"/>
+      <c r="O77" s="22" t="n"/>
+      <c r="P77" s="22" t="n"/>
+      <c r="Q77" s="22" t="n"/>
+      <c r="R77" s="22" t="n"/>
+      <c r="S77" s="22" t="n"/>
+      <c r="T77" s="22" t="n"/>
+      <c r="U77" s="22" t="n"/>
+      <c r="V77" s="22" t="n"/>
+      <c r="W77" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>12.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="n"/>
+      <c r="C78" s="22" t="n"/>
+      <c r="D78" s="22" t="n"/>
+      <c r="E78" s="22" t="n"/>
+      <c r="F78" s="22" t="n"/>
+      <c r="G78" s="22" t="n"/>
+      <c r="H78" s="22" t="n"/>
+      <c r="I78" s="22" t="n"/>
+      <c r="J78" s="22" t="n"/>
+      <c r="K78" s="22" t="n"/>
+      <c r="L78" s="22" t="n"/>
+      <c r="M78" s="22" t="n"/>
+      <c r="N78" s="22" t="n"/>
+      <c r="O78" s="22" t="n"/>
+      <c r="P78" s="22" t="n"/>
+      <c r="Q78" s="22" t="n"/>
+      <c r="R78" s="22" t="n"/>
+      <c r="S78" s="22" t="n"/>
+      <c r="T78" s="22" t="n"/>
+      <c r="U78" s="22" t="n"/>
+      <c r="V78" s="22" t="n"/>
+      <c r="W78" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>12.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="n"/>
+      <c r="C79" s="22" t="n"/>
+      <c r="D79" s="22" t="n"/>
+      <c r="E79" s="22" t="n"/>
+      <c r="F79" s="22" t="n"/>
+      <c r="G79" s="22" t="n"/>
+      <c r="H79" s="22" t="n"/>
+      <c r="I79" s="22" t="n"/>
+      <c r="J79" s="22" t="n"/>
+      <c r="K79" s="22" t="n"/>
+      <c r="L79" s="22" t="n"/>
+      <c r="M79" s="22" t="n"/>
+      <c r="N79" s="22" t="n"/>
+      <c r="O79" s="22" t="n"/>
+      <c r="P79" s="22" t="n"/>
+      <c r="Q79" s="22" t="n"/>
+      <c r="R79" s="22" t="n"/>
+      <c r="S79" s="22" t="n"/>
+      <c r="T79" s="22" t="n"/>
+      <c r="U79" s="22" t="n"/>
+      <c r="V79" s="22" t="n"/>
+      <c r="W79" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>13. Fisioterapia y citas</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="n"/>
+      <c r="C80" s="22" t="n"/>
+      <c r="D80" s="22" t="n"/>
+      <c r="E80" s="22" t="n"/>
+      <c r="F80" s="22" t="n"/>
+      <c r="G80" s="22" t="n"/>
+      <c r="H80" s="22" t="n"/>
+      <c r="I80" s="22" t="n"/>
+      <c r="J80" s="22" t="n"/>
+      <c r="K80" s="22" t="n"/>
+      <c r="L80" s="22" t="n"/>
+      <c r="M80" s="22" t="n"/>
+      <c r="N80" s="22" t="n"/>
+      <c r="O80" s="22" t="n"/>
+      <c r="P80" s="22" t="n"/>
+      <c r="Q80" s="22" t="n"/>
+      <c r="R80" s="22" t="n"/>
+      <c r="S80" s="22" t="n"/>
+      <c r="T80" s="22" t="n"/>
+      <c r="U80" s="22" t="n"/>
+      <c r="V80" s="22" t="n"/>
+      <c r="W80" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>13.1 Solicitud de cita</t>
+        </is>
+      </c>
+      <c r="B81" s="22" t="n"/>
+      <c r="C81" s="22" t="n"/>
+      <c r="D81" s="22" t="n"/>
+      <c r="E81" s="22" t="n"/>
+      <c r="F81" s="22" t="n"/>
+      <c r="G81" s="22" t="n"/>
+      <c r="H81" s="22" t="n"/>
+      <c r="I81" s="22" t="n"/>
+      <c r="J81" s="22" t="n"/>
+      <c r="K81" s="22" t="n"/>
+      <c r="L81" s="22" t="n"/>
+      <c r="M81" s="22" t="n"/>
+      <c r="N81" s="22" t="n"/>
+      <c r="O81" s="22" t="n"/>
+      <c r="P81" s="22" t="n"/>
+      <c r="Q81" s="22" t="n"/>
+      <c r="R81" s="22" t="n"/>
+      <c r="S81" s="22" t="n"/>
+      <c r="T81" s="22" t="n"/>
+      <c r="U81" s="22" t="n"/>
+      <c r="V81" s="22" t="n"/>
+      <c r="W81" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>13.2 Agenda del fisioterapeuta</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="n"/>
+      <c r="C82" s="22" t="n"/>
+      <c r="D82" s="22" t="n"/>
+      <c r="E82" s="22" t="n"/>
+      <c r="F82" s="22" t="n"/>
+      <c r="G82" s="22" t="n"/>
+      <c r="H82" s="22" t="n"/>
+      <c r="I82" s="22" t="n"/>
+      <c r="J82" s="22" t="n"/>
+      <c r="K82" s="22" t="n"/>
+      <c r="L82" s="22" t="n"/>
+      <c r="M82" s="22" t="n"/>
+      <c r="N82" s="22" t="n"/>
+      <c r="O82" s="22" t="n"/>
+      <c r="P82" s="22" t="n"/>
+      <c r="Q82" s="22" t="n"/>
+      <c r="R82" s="22" t="n"/>
+      <c r="S82" s="22" t="n"/>
+      <c r="T82" s="22" t="n"/>
+      <c r="U82" s="22" t="n"/>
+      <c r="V82" s="22" t="n"/>
+      <c r="W82" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>13.3 Panel de citas</t>
+        </is>
+      </c>
+      <c r="B83" s="22" t="n"/>
+      <c r="C83" s="22" t="n"/>
+      <c r="D83" s="22" t="n"/>
+      <c r="E83" s="22" t="n"/>
+      <c r="F83" s="22" t="n"/>
+      <c r="G83" s="22" t="n"/>
+      <c r="H83" s="22" t="n"/>
+      <c r="I83" s="22" t="n"/>
+      <c r="J83" s="22" t="n"/>
+      <c r="K83" s="22" t="n"/>
+      <c r="L83" s="22" t="n"/>
+      <c r="M83" s="22" t="n"/>
+      <c r="N83" s="22" t="n"/>
+      <c r="O83" s="22" t="n"/>
+      <c r="P83" s="22" t="n"/>
+      <c r="Q83" s="22" t="n"/>
+      <c r="R83" s="22" t="n"/>
+      <c r="S83" s="22" t="n"/>
+      <c r="T83" s="22" t="n"/>
+      <c r="U83" s="22" t="n"/>
+      <c r="V83" s="22" t="n"/>
+      <c r="W83" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>13.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="n"/>
+      <c r="C84" s="22" t="n"/>
+      <c r="D84" s="22" t="n"/>
+      <c r="E84" s="22" t="n"/>
+      <c r="F84" s="22" t="n"/>
+      <c r="G84" s="22" t="n"/>
+      <c r="H84" s="22" t="n"/>
+      <c r="I84" s="22" t="n"/>
+      <c r="J84" s="22" t="n"/>
+      <c r="K84" s="22" t="n"/>
+      <c r="L84" s="22" t="n"/>
+      <c r="M84" s="22" t="n"/>
+      <c r="N84" s="22" t="n"/>
+      <c r="O84" s="22" t="n"/>
+      <c r="P84" s="22" t="n"/>
+      <c r="Q84" s="22" t="n"/>
+      <c r="R84" s="22" t="n"/>
+      <c r="S84" s="22" t="n"/>
+      <c r="T84" s="22" t="n"/>
+      <c r="U84" s="22" t="n"/>
+      <c r="V84" s="22" t="n"/>
+      <c r="W84" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>13.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B85" s="22" t="n"/>
+      <c r="C85" s="22" t="n"/>
+      <c r="D85" s="22" t="n"/>
+      <c r="E85" s="22" t="n"/>
+      <c r="F85" s="22" t="n"/>
+      <c r="G85" s="22" t="n"/>
+      <c r="H85" s="22" t="n"/>
+      <c r="I85" s="22" t="n"/>
+      <c r="J85" s="22" t="n"/>
+      <c r="K85" s="22" t="n"/>
+      <c r="L85" s="22" t="n"/>
+      <c r="M85" s="22" t="n"/>
+      <c r="N85" s="22" t="n"/>
+      <c r="O85" s="22" t="n"/>
+      <c r="P85" s="22" t="n"/>
+      <c r="Q85" s="22" t="n"/>
+      <c r="R85" s="22" t="n"/>
+      <c r="S85" s="22" t="n"/>
+      <c r="T85" s="22" t="n"/>
+      <c r="U85" s="22" t="n"/>
+      <c r="V85" s="22" t="n"/>
+      <c r="W85" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>14. Comentarios, feedback y seguridad</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="n"/>
+      <c r="C86" s="22" t="n"/>
+      <c r="D86" s="22" t="n"/>
+      <c r="E86" s="22" t="n"/>
+      <c r="F86" s="22" t="n"/>
+      <c r="G86" s="22" t="n"/>
+      <c r="H86" s="22" t="n"/>
+      <c r="I86" s="22" t="n"/>
+      <c r="J86" s="22" t="n"/>
+      <c r="K86" s="22" t="n"/>
+      <c r="L86" s="22" t="n"/>
+      <c r="M86" s="22" t="n"/>
+      <c r="N86" s="22" t="n"/>
+      <c r="O86" s="22" t="n"/>
+      <c r="P86" s="22" t="n"/>
+      <c r="Q86" s="22" t="n"/>
+      <c r="R86" s="22" t="n"/>
+      <c r="S86" s="22" t="n"/>
+      <c r="T86" s="22" t="n"/>
+      <c r="U86" s="22" t="n"/>
+      <c r="V86" s="22" t="n"/>
+      <c r="W86" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>14.1 Comentarios de actividad</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="n"/>
+      <c r="C87" s="22" t="n"/>
+      <c r="D87" s="22" t="n"/>
+      <c r="E87" s="22" t="n"/>
+      <c r="F87" s="22" t="n"/>
+      <c r="G87" s="22" t="n"/>
+      <c r="H87" s="22" t="n"/>
+      <c r="I87" s="22" t="n"/>
+      <c r="J87" s="22" t="n"/>
+      <c r="K87" s="22" t="n"/>
+      <c r="L87" s="22" t="n"/>
+      <c r="M87" s="22" t="n"/>
+      <c r="N87" s="22" t="n"/>
+      <c r="O87" s="22" t="n"/>
+      <c r="P87" s="22" t="n"/>
+      <c r="Q87" s="22" t="n"/>
+      <c r="R87" s="22" t="n"/>
+      <c r="S87" s="22" t="n"/>
+      <c r="T87" s="22" t="n"/>
+      <c r="U87" s="22" t="n"/>
+      <c r="V87" s="22" t="n"/>
+      <c r="W87" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>14.2 Buzón de feedback</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="n"/>
+      <c r="C88" s="22" t="n"/>
+      <c r="D88" s="22" t="n"/>
+      <c r="E88" s="22" t="n"/>
+      <c r="F88" s="22" t="n"/>
+      <c r="G88" s="22" t="n"/>
+      <c r="H88" s="22" t="n"/>
+      <c r="I88" s="22" t="n"/>
+      <c r="J88" s="22" t="n"/>
+      <c r="K88" s="22" t="n"/>
+      <c r="L88" s="22" t="n"/>
+      <c r="M88" s="22" t="n"/>
+      <c r="N88" s="22" t="n"/>
+      <c r="O88" s="22" t="n"/>
+      <c r="P88" s="22" t="n"/>
+      <c r="Q88" s="22" t="n"/>
+      <c r="R88" s="22" t="n"/>
+      <c r="S88" s="22" t="n"/>
+      <c r="T88" s="22" t="n"/>
+      <c r="U88" s="22" t="n"/>
+      <c r="V88" s="22" t="n"/>
+      <c r="W88" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>14.3 Configuración de seguridad</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="n"/>
+      <c r="C89" s="22" t="n"/>
+      <c r="D89" s="22" t="n"/>
+      <c r="E89" s="22" t="n"/>
+      <c r="F89" s="22" t="n"/>
+      <c r="G89" s="22" t="n"/>
+      <c r="H89" s="22" t="n"/>
+      <c r="I89" s="22" t="n"/>
+      <c r="J89" s="22" t="n"/>
+      <c r="K89" s="22" t="n"/>
+      <c r="L89" s="22" t="n"/>
+      <c r="M89" s="22" t="n"/>
+      <c r="N89" s="22" t="n"/>
+      <c r="O89" s="22" t="n"/>
+      <c r="P89" s="22" t="n"/>
+      <c r="Q89" s="22" t="n"/>
+      <c r="R89" s="22" t="n"/>
+      <c r="S89" s="22" t="n"/>
+      <c r="T89" s="22" t="n"/>
+      <c r="U89" s="22" t="n"/>
+      <c r="V89" s="22" t="n"/>
+      <c r="W89" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>14.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="n"/>
+      <c r="C90" s="22" t="n"/>
+      <c r="D90" s="22" t="n"/>
+      <c r="E90" s="22" t="n"/>
+      <c r="F90" s="22" t="n"/>
+      <c r="G90" s="22" t="n"/>
+      <c r="H90" s="22" t="n"/>
+      <c r="I90" s="22" t="n"/>
+      <c r="J90" s="22" t="n"/>
+      <c r="K90" s="22" t="n"/>
+      <c r="L90" s="22" t="n"/>
+      <c r="M90" s="22" t="n"/>
+      <c r="N90" s="22" t="n"/>
+      <c r="O90" s="22" t="n"/>
+      <c r="P90" s="22" t="n"/>
+      <c r="Q90" s="22" t="n"/>
+      <c r="R90" s="22" t="n"/>
+      <c r="S90" s="22" t="n"/>
+      <c r="T90" s="22" t="n"/>
+      <c r="U90" s="22" t="n"/>
+      <c r="V90" s="22" t="n"/>
+      <c r="W90" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t>14.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="n"/>
+      <c r="C91" s="22" t="n"/>
+      <c r="D91" s="22" t="n"/>
+      <c r="E91" s="22" t="n"/>
+      <c r="F91" s="22" t="n"/>
+      <c r="G91" s="22" t="n"/>
+      <c r="H91" s="22" t="n"/>
+      <c r="I91" s="22" t="n"/>
+      <c r="J91" s="22" t="n"/>
+      <c r="K91" s="22" t="n"/>
+      <c r="L91" s="22" t="n"/>
+      <c r="M91" s="22" t="n"/>
+      <c r="N91" s="22" t="n"/>
+      <c r="O91" s="22" t="n"/>
+      <c r="P91" s="22" t="n"/>
+      <c r="Q91" s="22" t="n"/>
+      <c r="R91" s="22" t="n"/>
+      <c r="S91" s="22" t="n"/>
+      <c r="T91" s="22" t="n"/>
+      <c r="U91" s="22" t="n"/>
+      <c r="V91" s="22" t="n"/>
+      <c r="W91" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>15. Interfaz Tailwind, correo y cierre</t>
+        </is>
+      </c>
+      <c r="B92" s="21" t="n"/>
+      <c r="C92" s="21" t="n"/>
+      <c r="D92" s="21" t="n"/>
+      <c r="E92" s="21" t="n"/>
+      <c r="F92" s="21" t="n"/>
+      <c r="G92" s="22" t="n"/>
+      <c r="H92" s="22" t="n"/>
+      <c r="I92" s="22" t="n"/>
+      <c r="J92" s="22" t="n"/>
+      <c r="K92" s="22" t="n"/>
+      <c r="L92" s="22" t="n"/>
+      <c r="M92" s="22" t="n"/>
+      <c r="N92" s="22" t="n"/>
+      <c r="O92" s="22" t="n"/>
+      <c r="P92" s="22" t="n"/>
+      <c r="Q92" s="22" t="n"/>
+      <c r="R92" s="22" t="n"/>
+      <c r="S92" s="22" t="n"/>
+      <c r="T92" s="22" t="n"/>
+      <c r="U92" s="22" t="n"/>
+      <c r="V92" s="22" t="n"/>
+      <c r="W92" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A93" s="24" t="inlineStr">
+        <is>
+          <t>15.1 Maquetación con Tailwind</t>
+        </is>
+      </c>
+      <c r="B93" s="22" t="n"/>
+      <c r="C93" s="22" t="n"/>
+      <c r="D93" s="22" t="n"/>
+      <c r="E93" s="22" t="n"/>
+      <c r="F93" s="22" t="n"/>
+      <c r="G93" s="22" t="n"/>
+      <c r="H93" s="22" t="n"/>
+      <c r="I93" s="22" t="n"/>
+      <c r="J93" s="22" t="n"/>
+      <c r="K93" s="22" t="n"/>
+      <c r="L93" s="22" t="n"/>
+      <c r="M93" s="22" t="n"/>
+      <c r="N93" s="22" t="n"/>
+      <c r="O93" s="22" t="n"/>
+      <c r="P93" s="22" t="n"/>
+      <c r="Q93" s="22" t="n"/>
+      <c r="R93" s="22" t="n"/>
+      <c r="S93" s="22" t="n"/>
+      <c r="T93" s="22" t="n"/>
+      <c r="U93" s="22" t="n"/>
+      <c r="V93" s="22" t="n"/>
+      <c r="W93" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A94" s="24" t="inlineStr">
+        <is>
+          <t>15.2 Correo del proyecto</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="n"/>
+      <c r="C94" s="22" t="n"/>
+      <c r="D94" s="22" t="n"/>
+      <c r="E94" s="22" t="n"/>
+      <c r="F94" s="22" t="n"/>
+      <c r="G94" s="22" t="n"/>
+      <c r="H94" s="22" t="n"/>
+      <c r="I94" s="22" t="n"/>
+      <c r="J94" s="22" t="n"/>
+      <c r="K94" s="22" t="n"/>
+      <c r="L94" s="22" t="n"/>
+      <c r="M94" s="22" t="n"/>
+      <c r="N94" s="22" t="n"/>
+      <c r="O94" s="22" t="n"/>
+      <c r="P94" s="22" t="n"/>
+      <c r="Q94" s="22" t="n"/>
+      <c r="R94" s="22" t="n"/>
+      <c r="S94" s="22" t="n"/>
+      <c r="T94" s="22" t="n"/>
+      <c r="U94" s="22" t="n"/>
+      <c r="V94" s="22" t="n"/>
+      <c r="W94" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A95" s="24" t="inlineStr">
+        <is>
+          <t>15.3 Cierre y revisión</t>
+        </is>
+      </c>
+      <c r="B95" s="22" t="n"/>
+      <c r="C95" s="22" t="n"/>
+      <c r="D95" s="22" t="n"/>
+      <c r="E95" s="22" t="n"/>
+      <c r="F95" s="22" t="n"/>
+      <c r="G95" s="22" t="n"/>
+      <c r="H95" s="22" t="n"/>
+      <c r="I95" s="22" t="n"/>
+      <c r="J95" s="22" t="n"/>
+      <c r="K95" s="22" t="n"/>
+      <c r="L95" s="22" t="n"/>
+      <c r="M95" s="22" t="n"/>
+      <c r="N95" s="22" t="n"/>
+      <c r="O95" s="22" t="n"/>
+      <c r="P95" s="22" t="n"/>
+      <c r="Q95" s="22" t="n"/>
+      <c r="R95" s="22" t="n"/>
+      <c r="S95" s="22" t="n"/>
+      <c r="T95" s="22" t="n"/>
+      <c r="U95" s="22" t="n"/>
+      <c r="V95" s="22" t="n"/>
+      <c r="W95" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>15.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B96" s="21" t="n"/>
+      <c r="C96" s="21" t="n"/>
+      <c r="D96" s="21" t="n"/>
+      <c r="E96" s="21" t="n"/>
+      <c r="F96" s="21" t="n"/>
+      <c r="G96" s="22" t="n"/>
+      <c r="H96" s="22" t="n"/>
+      <c r="I96" s="22" t="n"/>
+      <c r="J96" s="22" t="n"/>
+      <c r="K96" s="22" t="n"/>
+      <c r="L96" s="22" t="n"/>
+      <c r="M96" s="22" t="n"/>
+      <c r="N96" s="22" t="n"/>
+      <c r="O96" s="22" t="n"/>
+      <c r="P96" s="22" t="n"/>
+      <c r="Q96" s="22" t="n"/>
+      <c r="R96" s="22" t="n"/>
+      <c r="S96" s="22" t="n"/>
+      <c r="T96" s="22" t="n"/>
+      <c r="U96" s="22" t="n"/>
+      <c r="V96" s="22" t="n"/>
+      <c r="W96" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>15.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B97" s="21" t="n"/>
+      <c r="C97" s="22" t="n"/>
+      <c r="D97" s="22" t="n"/>
+      <c r="E97" s="22" t="n"/>
+      <c r="F97" s="22" t="n"/>
+      <c r="G97" s="22" t="n"/>
+      <c r="H97" s="22" t="n"/>
+      <c r="I97" s="22" t="n"/>
+      <c r="J97" s="22" t="n"/>
+      <c r="K97" s="22" t="n"/>
+      <c r="L97" s="22" t="n"/>
+      <c r="M97" s="22" t="n"/>
+      <c r="N97" s="22" t="n"/>
+      <c r="O97" s="22" t="n"/>
+      <c r="P97" s="22" t="n"/>
+      <c r="Q97" s="22" t="n"/>
+      <c r="R97" s="22" t="n"/>
+      <c r="S97" s="22" t="n"/>
+      <c r="T97" s="22" t="n"/>
+      <c r="U97" s="22" t="n"/>
+      <c r="V97" s="22" t="n"/>
+      <c r="W97" s="26" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="27" t="n"/>
+      <c r="B98" s="28" t="n"/>
+      <c r="C98" s="28" t="n"/>
+      <c r="D98" s="28" t="n"/>
+      <c r="E98" s="28" t="n"/>
+      <c r="F98" s="28" t="n"/>
+      <c r="G98" s="28" t="n"/>
+      <c r="H98" s="28" t="n"/>
+      <c r="I98" s="28" t="n"/>
+      <c r="J98" s="28" t="n"/>
+      <c r="K98" s="28" t="n"/>
+      <c r="L98" s="28" t="n"/>
+      <c r="M98" s="28" t="n"/>
+      <c r="N98" s="28" t="n"/>
+      <c r="O98" s="28" t="n"/>
+      <c r="P98" s="28" t="n"/>
+      <c r="Q98" s="28" t="n"/>
+      <c r="R98" s="28" t="n"/>
+      <c r="S98" s="28" t="n"/>
+      <c r="T98" s="28" t="n"/>
+      <c r="U98" s="28" t="n"/>
+      <c r="V98" s="28" t="n"/>
+      <c r="W98" s="28" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="27" t="n"/>
+      <c r="B99" s="28" t="n"/>
+      <c r="C99" s="28" t="n"/>
+      <c r="D99" s="28" t="n"/>
+      <c r="E99" s="28" t="n"/>
+      <c r="F99" s="28" t="n"/>
+      <c r="G99" s="28" t="n"/>
+      <c r="H99" s="28" t="n"/>
+      <c r="I99" s="28" t="n"/>
+      <c r="J99" s="28" t="n"/>
+      <c r="K99" s="28" t="n"/>
+      <c r="L99" s="28" t="n"/>
+      <c r="M99" s="28" t="n"/>
+      <c r="N99" s="28" t="n"/>
+      <c r="O99" s="28" t="n"/>
+      <c r="P99" s="28" t="n"/>
+      <c r="Q99" s="28" t="n"/>
+      <c r="R99" s="28" t="n"/>
+      <c r="S99" s="28" t="n"/>
+      <c r="T99" s="28" t="n"/>
+      <c r="U99" s="28" t="n"/>
+      <c r="V99" s="28" t="n"/>
+      <c r="W99" s="28" t="n"/>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="27" t="n"/>
+      <c r="B100" s="28" t="n"/>
+      <c r="C100" s="28" t="n"/>
+      <c r="D100" s="28" t="n"/>
+      <c r="E100" s="28" t="n"/>
+      <c r="F100" s="28" t="n"/>
+      <c r="G100" s="28" t="n"/>
+      <c r="H100" s="28" t="n"/>
+      <c r="I100" s="28" t="n"/>
+      <c r="J100" s="28" t="n"/>
+      <c r="K100" s="28" t="n"/>
+      <c r="L100" s="28" t="n"/>
+      <c r="M100" s="28" t="n"/>
+      <c r="N100" s="28" t="n"/>
+      <c r="O100" s="28" t="n"/>
+      <c r="P100" s="28" t="n"/>
+      <c r="Q100" s="28" t="n"/>
+      <c r="R100" s="28" t="n"/>
+      <c r="S100" s="28" t="n"/>
+      <c r="T100" s="28" t="n"/>
+      <c r="U100" s="28" t="n"/>
+      <c r="V100" s="28" t="n"/>
+      <c r="W100" s="28" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="27" t="n"/>
+      <c r="B101" s="28" t="n"/>
+      <c r="C101" s="28" t="n"/>
+      <c r="D101" s="28" t="n"/>
+      <c r="E101" s="28" t="n"/>
+      <c r="F101" s="28" t="n"/>
+      <c r="G101" s="28" t="n"/>
+      <c r="H101" s="28" t="n"/>
+      <c r="I101" s="28" t="n"/>
+      <c r="J101" s="28" t="n"/>
+      <c r="K101" s="28" t="n"/>
+      <c r="L101" s="28" t="n"/>
+      <c r="M101" s="28" t="n"/>
+      <c r="N101" s="28" t="n"/>
+      <c r="O101" s="28" t="n"/>
+      <c r="P101" s="28" t="n"/>
+      <c r="Q101" s="28" t="n"/>
+      <c r="R101" s="28" t="n"/>
+      <c r="S101" s="28" t="n"/>
+      <c r="T101" s="28" t="n"/>
+      <c r="U101" s="28" t="n"/>
+      <c r="V101" s="28" t="n"/>
+      <c r="W101" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/docs/Spartum_Gantt.xlsx
+++ b/docs/Spartum_Gantt.xlsx
@@ -81,7 +81,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.7999816888943144"/>
+        <fgColor theme="9" tint="0.7999816888943144"/>
       </patternFill>
     </fill>
     <fill>
@@ -463,7 +463,7 @@
         <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
         <a:srgbClr val="4BACC6"/>
@@ -1354,8 +1354,8 @@
           <t>1.4 Testeo</t>
         </is>
       </c>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
       <c r="D12" s="29" t="n"/>
       <c r="E12" s="23" t="n"/>
       <c r="F12" s="23" t="n"/>
@@ -1394,8 +1394,8 @@
           <t>1.5 Documentación</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
+      <c r="B13" s="22" t="n"/>
+      <c r="C13" s="22" t="n"/>
       <c r="D13" s="22" t="n"/>
       <c r="E13" s="23" t="n"/>
       <c r="F13" s="23" t="n"/>
@@ -1597,10 +1597,10 @@
       <c r="B18" s="23" t="n"/>
       <c r="C18" s="23" t="n"/>
       <c r="D18" s="23" t="n"/>
-      <c r="E18" s="23" t="n"/>
-      <c r="F18" s="23" t="n"/>
-      <c r="G18" s="23" t="n"/>
-      <c r="H18" s="23" t="n"/>
+      <c r="E18" s="22" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
       <c r="I18" s="22" t="n"/>
       <c r="J18" s="23" t="n"/>
       <c r="K18" s="23" t="n"/>
@@ -1637,10 +1637,10 @@
       <c r="B19" s="23" t="n"/>
       <c r="C19" s="23" t="n"/>
       <c r="D19" s="23" t="n"/>
-      <c r="E19" s="23" t="n"/>
-      <c r="F19" s="23" t="n"/>
-      <c r="G19" s="23" t="n"/>
-      <c r="H19" s="23" t="n"/>
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="26" t="n"/>
+      <c r="G19" s="26" t="n"/>
+      <c r="H19" s="26" t="n"/>
       <c r="I19" s="26" t="n"/>
       <c r="J19" s="23" t="n"/>
       <c r="K19" s="23" t="n"/>
@@ -1842,8 +1842,8 @@
       <c r="G24" s="23" t="n"/>
       <c r="H24" s="23" t="n"/>
       <c r="I24" s="23" t="n"/>
-      <c r="J24" s="23" t="n"/>
-      <c r="K24" s="23" t="n"/>
+      <c r="J24" s="26" t="n"/>
+      <c r="K24" s="26" t="n"/>
       <c r="L24" s="26" t="n"/>
       <c r="M24" s="23" t="n"/>
       <c r="N24" s="23" t="n"/>
@@ -1882,8 +1882,8 @@
       <c r="G25" s="23" t="n"/>
       <c r="H25" s="23" t="n"/>
       <c r="I25" s="23" t="n"/>
-      <c r="J25" s="23" t="n"/>
-      <c r="K25" s="23" t="n"/>
+      <c r="J25" s="27" t="n"/>
+      <c r="K25" s="27" t="n"/>
       <c r="L25" s="27" t="n"/>
       <c r="M25" s="23" t="n"/>
       <c r="N25" s="23" t="n"/>
@@ -2085,9 +2085,9 @@
       <c r="J30" s="23" t="n"/>
       <c r="K30" s="23" t="n"/>
       <c r="L30" s="23" t="n"/>
-      <c r="M30" s="23" t="n"/>
-      <c r="N30" s="23" t="n"/>
-      <c r="O30" s="23" t="n"/>
+      <c r="M30" s="27" t="n"/>
+      <c r="N30" s="27" t="n"/>
+      <c r="O30" s="27" t="n"/>
       <c r="P30" s="27" t="n"/>
       <c r="Q30" s="23" t="n"/>
       <c r="R30" s="23" t="n"/>
@@ -2125,9 +2125,9 @@
       <c r="J31" s="23" t="n"/>
       <c r="K31" s="23" t="n"/>
       <c r="L31" s="23" t="n"/>
-      <c r="M31" s="23" t="n"/>
-      <c r="N31" s="23" t="n"/>
-      <c r="O31" s="23" t="n"/>
+      <c r="M31" s="28" t="n"/>
+      <c r="N31" s="28" t="n"/>
+      <c r="O31" s="28" t="n"/>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="23" t="n"/>
       <c r="R31" s="23" t="n"/>
@@ -2329,8 +2329,8 @@
       <c r="N36" s="23" t="n"/>
       <c r="O36" s="23" t="n"/>
       <c r="P36" s="23" t="n"/>
-      <c r="Q36" s="23" t="n"/>
-      <c r="R36" s="23" t="n"/>
+      <c r="Q36" s="28" t="n"/>
+      <c r="R36" s="28" t="n"/>
       <c r="S36" s="28" t="n"/>
       <c r="T36" s="23" t="n"/>
       <c r="U36" s="23" t="n"/>
@@ -2342,9 +2342,9 @@
       <c r="AA36" s="23" t="n"/>
       <c r="AB36" s="23" t="n"/>
       <c r="AC36" s="23" t="n"/>
-      <c r="AD36" s="31" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD36" s="30" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -2369,8 +2369,8 @@
       <c r="N37" s="23" t="n"/>
       <c r="O37" s="23" t="n"/>
       <c r="P37" s="23" t="n"/>
-      <c r="Q37" s="23" t="n"/>
-      <c r="R37" s="23" t="n"/>
+      <c r="Q37" s="29" t="n"/>
+      <c r="R37" s="29" t="n"/>
       <c r="S37" s="29" t="n"/>
       <c r="T37" s="23" t="n"/>
       <c r="U37" s="23" t="n"/>
@@ -2382,9 +2382,9 @@
       <c r="AA37" s="23" t="n"/>
       <c r="AB37" s="23" t="n"/>
       <c r="AC37" s="23" t="n"/>
-      <c r="AD37" s="31" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD37" s="30" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -2572,10 +2572,10 @@
       <c r="Q42" s="23" t="n"/>
       <c r="R42" s="23" t="n"/>
       <c r="S42" s="23" t="n"/>
-      <c r="T42" s="23" t="n"/>
-      <c r="U42" s="23" t="n"/>
-      <c r="V42" s="23" t="n"/>
-      <c r="W42" s="23" t="n"/>
+      <c r="T42" s="29" t="n"/>
+      <c r="U42" s="29" t="n"/>
+      <c r="V42" s="29" t="n"/>
+      <c r="W42" s="29" t="n"/>
       <c r="X42" s="29" t="n"/>
       <c r="Y42" s="23" t="n"/>
       <c r="Z42" s="23" t="n"/>
@@ -2612,10 +2612,10 @@
       <c r="Q43" s="23" t="n"/>
       <c r="R43" s="23" t="n"/>
       <c r="S43" s="23" t="n"/>
-      <c r="T43" s="23" t="n"/>
-      <c r="U43" s="23" t="n"/>
-      <c r="V43" s="23" t="n"/>
-      <c r="W43" s="23" t="n"/>
+      <c r="T43" s="22" t="n"/>
+      <c r="U43" s="22" t="n"/>
+      <c r="V43" s="22" t="n"/>
+      <c r="W43" s="22" t="n"/>
       <c r="X43" s="22" t="n"/>
       <c r="Y43" s="23" t="n"/>
       <c r="Z43" s="23" t="n"/>
@@ -2817,7 +2817,7 @@
       <c r="V48" s="23" t="n"/>
       <c r="W48" s="23" t="n"/>
       <c r="X48" s="23" t="n"/>
-      <c r="Y48" s="23" t="n"/>
+      <c r="Y48" s="22" t="n"/>
       <c r="Z48" s="22" t="n"/>
       <c r="AA48" s="23" t="n"/>
       <c r="AB48" s="23" t="n"/>
@@ -2857,7 +2857,7 @@
       <c r="V49" s="23" t="n"/>
       <c r="W49" s="23" t="n"/>
       <c r="X49" s="23" t="n"/>
-      <c r="Y49" s="23" t="n"/>
+      <c r="Y49" s="26" t="n"/>
       <c r="Z49" s="26" t="n"/>
       <c r="AA49" s="23" t="n"/>
       <c r="AB49" s="23" t="n"/>
@@ -3059,9 +3059,9 @@
       <c r="X54" s="23" t="n"/>
       <c r="Y54" s="23" t="n"/>
       <c r="Z54" s="23" t="n"/>
-      <c r="AA54" s="23" t="n"/>
-      <c r="AB54" s="23" t="n"/>
-      <c r="AC54" s="23" t="n"/>
+      <c r="AA54" s="26" t="n"/>
+      <c r="AB54" s="26" t="n"/>
+      <c r="AC54" s="26" t="n"/>
       <c r="AD54" s="31" t="inlineStr">
         <is>
           <t>sin iniciar</t>
@@ -3099,9 +3099,9 @@
       <c r="X55" s="23" t="n"/>
       <c r="Y55" s="23" t="n"/>
       <c r="Z55" s="23" t="n"/>
-      <c r="AA55" s="23" t="n"/>
-      <c r="AB55" s="23" t="n"/>
-      <c r="AC55" s="23" t="n"/>
+      <c r="AA55" s="27" t="n"/>
+      <c r="AB55" s="27" t="n"/>
+      <c r="AC55" s="27" t="n"/>
       <c r="AD55" s="31" t="inlineStr">
         <is>
           <t>sin iniciar</t>
@@ -6559,9 +6559,9 @@
       <c r="AA36" s="23" t="n"/>
       <c r="AB36" s="23" t="n"/>
       <c r="AC36" s="23" t="n"/>
-      <c r="AD36" s="31" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD36" s="30" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -6599,9 +6599,9 @@
       <c r="AA37" s="23" t="n"/>
       <c r="AB37" s="23" t="n"/>
       <c r="AC37" s="23" t="n"/>
-      <c r="AD37" s="31" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD37" s="30" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
           <t>8.4 Testeo</t>
         </is>
       </c>
-      <c r="B54" s="23" t="n"/>
+      <c r="B54" s="26" t="n"/>
       <c r="C54" s="26" t="n"/>
       <c r="D54" s="23" t="n"/>
       <c r="E54" s="23" t="n"/>
@@ -7291,7 +7291,7 @@
           <t>8.5 Documentación</t>
         </is>
       </c>
-      <c r="B55" s="23" t="n"/>
+      <c r="B55" s="27" t="n"/>
       <c r="C55" s="27" t="n"/>
       <c r="D55" s="23" t="n"/>
       <c r="E55" s="23" t="n"/>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="B60" s="23" t="n"/>
       <c r="C60" s="23" t="n"/>
-      <c r="D60" s="23" t="n"/>
+      <c r="D60" s="27" t="n"/>
       <c r="E60" s="27" t="n"/>
       <c r="F60" s="23" t="n"/>
       <c r="G60" s="23" t="n"/>
@@ -7533,7 +7533,7 @@
       </c>
       <c r="B61" s="23" t="n"/>
       <c r="C61" s="23" t="n"/>
-      <c r="D61" s="23" t="n"/>
+      <c r="D61" s="28" t="n"/>
       <c r="E61" s="28" t="n"/>
       <c r="F61" s="23" t="n"/>
       <c r="G61" s="23" t="n"/>
@@ -7735,9 +7735,9 @@
       <c r="C66" s="23" t="n"/>
       <c r="D66" s="23" t="n"/>
       <c r="E66" s="23" t="n"/>
-      <c r="F66" s="23" t="n"/>
-      <c r="G66" s="23" t="n"/>
-      <c r="H66" s="23" t="n"/>
+      <c r="F66" s="28" t="n"/>
+      <c r="G66" s="28" t="n"/>
+      <c r="H66" s="28" t="n"/>
       <c r="I66" s="28" t="n"/>
       <c r="J66" s="23" t="n"/>
       <c r="K66" s="23" t="n"/>
@@ -7775,9 +7775,9 @@
       <c r="C67" s="23" t="n"/>
       <c r="D67" s="23" t="n"/>
       <c r="E67" s="23" t="n"/>
-      <c r="F67" s="23" t="n"/>
-      <c r="G67" s="23" t="n"/>
-      <c r="H67" s="23" t="n"/>
+      <c r="F67" s="29" t="n"/>
+      <c r="G67" s="29" t="n"/>
+      <c r="H67" s="29" t="n"/>
       <c r="I67" s="29" t="n"/>
       <c r="J67" s="23" t="n"/>
       <c r="K67" s="23" t="n"/>
@@ -7979,8 +7979,8 @@
       <c r="G72" s="23" t="n"/>
       <c r="H72" s="23" t="n"/>
       <c r="I72" s="23" t="n"/>
-      <c r="J72" s="23" t="n"/>
-      <c r="K72" s="23" t="n"/>
+      <c r="J72" s="29" t="n"/>
+      <c r="K72" s="29" t="n"/>
       <c r="L72" s="29" t="n"/>
       <c r="M72" s="23" t="n"/>
       <c r="N72" s="23" t="n"/>
@@ -8019,8 +8019,8 @@
       <c r="G73" s="23" t="n"/>
       <c r="H73" s="23" t="n"/>
       <c r="I73" s="23" t="n"/>
-      <c r="J73" s="23" t="n"/>
-      <c r="K73" s="23" t="n"/>
+      <c r="J73" s="22" t="n"/>
+      <c r="K73" s="22" t="n"/>
       <c r="L73" s="22" t="n"/>
       <c r="M73" s="23" t="n"/>
       <c r="N73" s="23" t="n"/>
@@ -8222,9 +8222,9 @@
       <c r="J78" s="23" t="n"/>
       <c r="K78" s="23" t="n"/>
       <c r="L78" s="23" t="n"/>
-      <c r="M78" s="23" t="n"/>
-      <c r="N78" s="23" t="n"/>
-      <c r="O78" s="23" t="n"/>
+      <c r="M78" s="22" t="n"/>
+      <c r="N78" s="22" t="n"/>
+      <c r="O78" s="22" t="n"/>
       <c r="P78" s="22" t="n"/>
       <c r="Q78" s="23" t="n"/>
       <c r="R78" s="23" t="n"/>
@@ -8262,9 +8262,9 @@
       <c r="J79" s="23" t="n"/>
       <c r="K79" s="23" t="n"/>
       <c r="L79" s="23" t="n"/>
-      <c r="M79" s="23" t="n"/>
-      <c r="N79" s="23" t="n"/>
-      <c r="O79" s="23" t="n"/>
+      <c r="M79" s="26" t="n"/>
+      <c r="N79" s="26" t="n"/>
+      <c r="O79" s="26" t="n"/>
       <c r="P79" s="26" t="n"/>
       <c r="Q79" s="23" t="n"/>
       <c r="R79" s="23" t="n"/>
@@ -8466,8 +8466,8 @@
       <c r="N84" s="23" t="n"/>
       <c r="O84" s="23" t="n"/>
       <c r="P84" s="23" t="n"/>
-      <c r="Q84" s="23" t="n"/>
-      <c r="R84" s="23" t="n"/>
+      <c r="Q84" s="26" t="n"/>
+      <c r="R84" s="26" t="n"/>
       <c r="S84" s="26" t="n"/>
       <c r="T84" s="23" t="n"/>
       <c r="U84" s="23" t="n"/>
@@ -8506,8 +8506,8 @@
       <c r="N85" s="23" t="n"/>
       <c r="O85" s="23" t="n"/>
       <c r="P85" s="23" t="n"/>
-      <c r="Q85" s="23" t="n"/>
-      <c r="R85" s="23" t="n"/>
+      <c r="Q85" s="27" t="n"/>
+      <c r="R85" s="27" t="n"/>
       <c r="S85" s="27" t="n"/>
       <c r="T85" s="23" t="n"/>
       <c r="U85" s="23" t="n"/>
@@ -8709,10 +8709,10 @@
       <c r="Q90" s="23" t="n"/>
       <c r="R90" s="23" t="n"/>
       <c r="S90" s="23" t="n"/>
-      <c r="T90" s="23" t="n"/>
-      <c r="U90" s="23" t="n"/>
-      <c r="V90" s="23" t="n"/>
-      <c r="W90" s="23" t="n"/>
+      <c r="T90" s="27" t="n"/>
+      <c r="U90" s="27" t="n"/>
+      <c r="V90" s="27" t="n"/>
+      <c r="W90" s="27" t="n"/>
       <c r="X90" s="27" t="n"/>
       <c r="Y90" s="23" t="n"/>
       <c r="Z90" s="23" t="n"/>
@@ -8749,10 +8749,10 @@
       <c r="Q91" s="23" t="n"/>
       <c r="R91" s="23" t="n"/>
       <c r="S91" s="23" t="n"/>
-      <c r="T91" s="23" t="n"/>
-      <c r="U91" s="23" t="n"/>
-      <c r="V91" s="23" t="n"/>
-      <c r="W91" s="23" t="n"/>
+      <c r="T91" s="28" t="n"/>
+      <c r="U91" s="28" t="n"/>
+      <c r="V91" s="28" t="n"/>
+      <c r="W91" s="28" t="n"/>
       <c r="X91" s="28" t="n"/>
       <c r="Y91" s="23" t="n"/>
       <c r="Z91" s="23" t="n"/>
@@ -8954,8 +8954,8 @@
       <c r="V96" s="23" t="n"/>
       <c r="W96" s="23" t="n"/>
       <c r="X96" s="23" t="n"/>
-      <c r="Y96" s="23" t="n"/>
-      <c r="Z96" s="23" t="n"/>
+      <c r="Y96" s="28" t="n"/>
+      <c r="Z96" s="28" t="n"/>
       <c r="AA96" s="28" t="n"/>
       <c r="AB96" s="28" t="n"/>
       <c r="AC96" s="28" t="n"/>
@@ -8994,8 +8994,8 @@
       <c r="V97" s="23" t="n"/>
       <c r="W97" s="23" t="n"/>
       <c r="X97" s="23" t="n"/>
-      <c r="Y97" s="23" t="n"/>
-      <c r="Z97" s="23" t="n"/>
+      <c r="Y97" s="29" t="n"/>
+      <c r="Z97" s="29" t="n"/>
       <c r="AA97" s="29" t="n"/>
       <c r="AB97" s="29" t="n"/>
       <c r="AC97" s="29" t="n"/>
@@ -10481,9 +10481,9 @@
       <c r="T36" s="23" t="n"/>
       <c r="U36" s="23" t="n"/>
       <c r="V36" s="23" t="n"/>
-      <c r="W36" s="31" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W36" s="30" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -10514,9 +10514,9 @@
       <c r="T37" s="23" t="n"/>
       <c r="U37" s="23" t="n"/>
       <c r="V37" s="23" t="n"/>
-      <c r="W37" s="31" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W37" s="30" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -12474,10 +12474,10 @@
         </is>
       </c>
       <c r="B97" s="29" t="n"/>
-      <c r="C97" s="23" t="n"/>
-      <c r="D97" s="23" t="n"/>
-      <c r="E97" s="23" t="n"/>
-      <c r="F97" s="23" t="n"/>
+      <c r="C97" s="29" t="n"/>
+      <c r="D97" s="29" t="n"/>
+      <c r="E97" s="29" t="n"/>
+      <c r="F97" s="29" t="n"/>
       <c r="G97" s="23" t="n"/>
       <c r="H97" s="23" t="n"/>
       <c r="I97" s="23" t="n"/>

--- a/docs/Spartum_Gantt.xlsx
+++ b/docs/Spartum_Gantt.xlsx
@@ -12,9 +12,9 @@
     <sheet name="Planificación Mes 3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Planificación Mes 1'!$A$1:$AD$129</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planificación Mes 2'!$A$1:$AD$129</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Planificación Mes 3'!$A$1:$W$129</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Planificación Mes 1'!$A$1:$AD$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planificación Mes 2'!$A$1:$AD$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Planificación Mes 3'!$A$1:$W$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -801,10 +801,10 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD129"/>
+  <dimension ref="A1:AD101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
     <col width="3.7" customWidth="1" min="3" max="3"/>
     <col width="3.7" customWidth="1" min="4" max="4"/>
@@ -1541,7 +1541,7 @@
     <row r="16" outlineLevel="1" ht="14" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>2.2 Creación del formulario</t>
+          <t>2.2 Formulario de alta → correo de registro</t>
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
@@ -1781,7 +1781,7 @@
     <row r="22" outlineLevel="1" ht="14" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>3.2 Tickets de la cuenta</t>
+          <t>3.2 Ticket de contraseña → usuario</t>
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
@@ -1821,7 +1821,7 @@
     <row r="23" outlineLevel="1" ht="14" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>3.3 Envío del enlace</t>
+          <t>3.3 Restablecer contraseña → usuario</t>
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
@@ -2202,19 +2202,19 @@
       <c r="Q32" s="28" t="n"/>
       <c r="R32" s="28" t="n"/>
       <c r="S32" s="28" t="n"/>
-      <c r="T32" s="22" t="n"/>
-      <c r="U32" s="22" t="n"/>
-      <c r="V32" s="22" t="n"/>
-      <c r="W32" s="22" t="n"/>
-      <c r="X32" s="22" t="n"/>
-      <c r="Y32" s="22" t="n"/>
-      <c r="Z32" s="22" t="n"/>
+      <c r="T32" s="28" t="n"/>
+      <c r="U32" s="28" t="n"/>
+      <c r="V32" s="28" t="n"/>
+      <c r="W32" s="28" t="n"/>
+      <c r="X32" s="28" t="n"/>
+      <c r="Y32" s="28" t="n"/>
+      <c r="Z32" s="28" t="n"/>
       <c r="AA32" s="22" t="n"/>
       <c r="AB32" s="22" t="n"/>
       <c r="AC32" s="22" t="n"/>
-      <c r="AD32" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD32" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
     <row r="34" outlineLevel="1" ht="14" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>5.2 Horario del centro</t>
+          <t>5.2 Horario y avisos → inscritos</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
@@ -2301,7 +2301,7 @@
     <row r="35" outlineLevel="1" ht="14" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>5.3 Alta y edición</t>
+          <t>5.3 Mínimo de personas para empezar</t>
         </is>
       </c>
       <c r="B35" s="22" t="n"/>
@@ -2320,7 +2320,7 @@
       <c r="O35" s="22" t="n"/>
       <c r="P35" s="22" t="n"/>
       <c r="Q35" s="22" t="n"/>
-      <c r="R35" s="26" t="n"/>
+      <c r="R35" s="22" t="n"/>
       <c r="S35" s="22" t="n"/>
       <c r="T35" s="22" t="n"/>
       <c r="U35" s="22" t="n"/>
@@ -2328,13 +2328,13 @@
       <c r="W35" s="22" t="n"/>
       <c r="X35" s="22" t="n"/>
       <c r="Y35" s="22" t="n"/>
-      <c r="Z35" s="22" t="n"/>
+      <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="22" t="n"/>
       <c r="AB35" s="22" t="n"/>
       <c r="AC35" s="22" t="n"/>
-      <c r="AD35" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD35" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
@@ -2362,19 +2362,19 @@
       <c r="Q36" s="27" t="n"/>
       <c r="R36" s="27" t="n"/>
       <c r="S36" s="27" t="n"/>
-      <c r="T36" s="22" t="n"/>
-      <c r="U36" s="22" t="n"/>
-      <c r="V36" s="22" t="n"/>
-      <c r="W36" s="22" t="n"/>
-      <c r="X36" s="22" t="n"/>
-      <c r="Y36" s="22" t="n"/>
-      <c r="Z36" s="22" t="n"/>
+      <c r="T36" s="27" t="n"/>
+      <c r="U36" s="27" t="n"/>
+      <c r="V36" s="27" t="n"/>
+      <c r="W36" s="27" t="n"/>
+      <c r="X36" s="27" t="n"/>
+      <c r="Y36" s="27" t="n"/>
+      <c r="Z36" s="27" t="n"/>
       <c r="AA36" s="22" t="n"/>
       <c r="AB36" s="22" t="n"/>
       <c r="AC36" s="22" t="n"/>
-      <c r="AD36" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD36" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -2402,26 +2402,26 @@
       <c r="Q37" s="28" t="n"/>
       <c r="R37" s="28" t="n"/>
       <c r="S37" s="28" t="n"/>
-      <c r="T37" s="22" t="n"/>
-      <c r="U37" s="22" t="n"/>
-      <c r="V37" s="22" t="n"/>
-      <c r="W37" s="22" t="n"/>
-      <c r="X37" s="22" t="n"/>
-      <c r="Y37" s="22" t="n"/>
-      <c r="Z37" s="22" t="n"/>
+      <c r="T37" s="28" t="n"/>
+      <c r="U37" s="28" t="n"/>
+      <c r="V37" s="28" t="n"/>
+      <c r="W37" s="28" t="n"/>
+      <c r="X37" s="28" t="n"/>
+      <c r="Y37" s="28" t="n"/>
+      <c r="Z37" s="28" t="n"/>
       <c r="AA37" s="22" t="n"/>
       <c r="AB37" s="22" t="n"/>
       <c r="AC37" s="22" t="n"/>
-      <c r="AD37" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD37" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>6. Transiciones</t>
+          <t>6. Inscripciones y reservas</t>
         </is>
       </c>
       <c r="B38" s="22" t="n"/>
@@ -2442,26 +2442,26 @@
       <c r="Q38" s="22" t="n"/>
       <c r="R38" s="22" t="n"/>
       <c r="S38" s="22" t="n"/>
-      <c r="T38" s="21" t="n"/>
-      <c r="U38" s="21" t="n"/>
-      <c r="V38" s="21" t="n"/>
-      <c r="W38" s="21" t="n"/>
+      <c r="T38" s="22" t="n"/>
+      <c r="U38" s="22" t="n"/>
+      <c r="V38" s="22" t="n"/>
+      <c r="W38" s="22" t="n"/>
       <c r="X38" s="22" t="n"/>
       <c r="Y38" s="22" t="n"/>
       <c r="Z38" s="22" t="n"/>
       <c r="AA38" s="22" t="n"/>
       <c r="AB38" s="22" t="n"/>
       <c r="AC38" s="22" t="n"/>
-      <c r="AD38" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD38" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="39" outlineLevel="1" ht="14" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>6.1 Transición entre páginas</t>
+          <t>6.1 Formulario de inscripción</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -2482,7 +2482,7 @@
       <c r="Q39" s="22" t="n"/>
       <c r="R39" s="22" t="n"/>
       <c r="S39" s="22" t="n"/>
-      <c r="T39" s="25" t="n"/>
+      <c r="T39" s="22" t="n"/>
       <c r="U39" s="22" t="n"/>
       <c r="V39" s="22" t="n"/>
       <c r="W39" s="22" t="n"/>
@@ -2492,16 +2492,16 @@
       <c r="AA39" s="22" t="n"/>
       <c r="AB39" s="22" t="n"/>
       <c r="AC39" s="22" t="n"/>
-      <c r="AD39" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD39" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="40" outlineLevel="1" ht="14" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>6.2 Transición de los paneles</t>
+          <t>6.2 Control de plazas</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -2525,23 +2525,23 @@
       <c r="T40" s="22" t="n"/>
       <c r="U40" s="22" t="n"/>
       <c r="V40" s="22" t="n"/>
-      <c r="W40" s="26" t="n"/>
+      <c r="W40" s="22" t="n"/>
       <c r="X40" s="22" t="n"/>
       <c r="Y40" s="22" t="n"/>
       <c r="Z40" s="22" t="n"/>
       <c r="AA40" s="22" t="n"/>
       <c r="AB40" s="22" t="n"/>
       <c r="AC40" s="22" t="n"/>
-      <c r="AD40" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD40" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="41" outlineLevel="1" ht="14" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>6.3 Cierre y revisión visual</t>
+          <t>6.3 Reserva → correo del cliente</t>
         </is>
       </c>
       <c r="B41" s="22" t="n"/>
@@ -2565,16 +2565,16 @@
       <c r="T41" s="22" t="n"/>
       <c r="U41" s="22" t="n"/>
       <c r="V41" s="22" t="n"/>
-      <c r="W41" s="27" t="n"/>
+      <c r="W41" s="22" t="n"/>
       <c r="X41" s="22" t="n"/>
       <c r="Y41" s="22" t="n"/>
       <c r="Z41" s="22" t="n"/>
       <c r="AA41" s="22" t="n"/>
       <c r="AB41" s="22" t="n"/>
       <c r="AC41" s="22" t="n"/>
-      <c r="AD41" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD41" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
@@ -2602,19 +2602,19 @@
       <c r="Q42" s="22" t="n"/>
       <c r="R42" s="22" t="n"/>
       <c r="S42" s="22" t="n"/>
-      <c r="T42" s="28" t="n"/>
-      <c r="U42" s="28" t="n"/>
-      <c r="V42" s="28" t="n"/>
-      <c r="W42" s="28" t="n"/>
+      <c r="T42" s="22" t="n"/>
+      <c r="U42" s="22" t="n"/>
+      <c r="V42" s="22" t="n"/>
+      <c r="W42" s="22" t="n"/>
       <c r="X42" s="22" t="n"/>
       <c r="Y42" s="22" t="n"/>
       <c r="Z42" s="22" t="n"/>
       <c r="AA42" s="22" t="n"/>
       <c r="AB42" s="22" t="n"/>
       <c r="AC42" s="22" t="n"/>
-      <c r="AD42" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD42" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
@@ -2642,26 +2642,26 @@
       <c r="Q43" s="22" t="n"/>
       <c r="R43" s="22" t="n"/>
       <c r="S43" s="22" t="n"/>
-      <c r="T43" s="21" t="n"/>
-      <c r="U43" s="21" t="n"/>
-      <c r="V43" s="21" t="n"/>
-      <c r="W43" s="21" t="n"/>
+      <c r="T43" s="22" t="n"/>
+      <c r="U43" s="22" t="n"/>
+      <c r="V43" s="22" t="n"/>
+      <c r="W43" s="22" t="n"/>
       <c r="X43" s="22" t="n"/>
       <c r="Y43" s="22" t="n"/>
       <c r="Z43" s="22" t="n"/>
       <c r="AA43" s="22" t="n"/>
       <c r="AB43" s="22" t="n"/>
       <c r="AC43" s="22" t="n"/>
-      <c r="AD43" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD43" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>7. Planes con mejor información</t>
+          <t>7. Suscripciones</t>
         </is>
       </c>
       <c r="B44" s="22" t="n"/>
@@ -2701,7 +2701,7 @@
     <row r="45" outlineLevel="1" ht="14" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>7.1 Datos que ve el cliente</t>
+          <t>7.1 Planes con mejor información</t>
         </is>
       </c>
       <c r="B45" s="22" t="n"/>
@@ -2741,7 +2741,7 @@
     <row r="46" outlineLevel="1" ht="14" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>7.2 Detalle de cada plan</t>
+          <t>7.2 Alta del cliente</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -2781,7 +2781,7 @@
     <row r="47" outlineLevel="1" ht="14" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>7.3 Textos del alta</t>
+          <t>7.3 Renovación y baja</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -2901,7 +2901,7 @@
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>8. Clases con mínimo de personas</t>
+          <t>8. Pagos con Stripe</t>
         </is>
       </c>
       <c r="B50" s="22" t="n"/>
@@ -2928,7 +2928,7 @@
       <c r="W50" s="22" t="n"/>
       <c r="X50" s="22" t="n"/>
       <c r="Y50" s="22" t="n"/>
-      <c r="Z50" s="26" t="n"/>
+      <c r="Z50" s="22" t="n"/>
       <c r="AA50" s="22" t="n"/>
       <c r="AB50" s="22" t="n"/>
       <c r="AC50" s="22" t="n"/>
@@ -2941,7 +2941,7 @@
     <row r="51" outlineLevel="1" ht="14" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>8.1 Mínimo para abrir la clase</t>
+          <t>8.1 Pasarela de Stripe</t>
         </is>
       </c>
       <c r="B51" s="22" t="n"/>
@@ -2968,7 +2968,7 @@
       <c r="W51" s="22" t="n"/>
       <c r="X51" s="22" t="n"/>
       <c r="Y51" s="22" t="n"/>
-      <c r="Z51" s="27" t="n"/>
+      <c r="Z51" s="22" t="n"/>
       <c r="AA51" s="22" t="n"/>
       <c r="AB51" s="22" t="n"/>
       <c r="AC51" s="22" t="n"/>
@@ -2981,7 +2981,7 @@
     <row r="52" outlineLevel="1" ht="14" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>8.2 Aviso si no se llega</t>
+          <t>8.2 Confirmación del pago</t>
         </is>
       </c>
       <c r="B52" s="22" t="n"/>
@@ -3008,7 +3008,7 @@
       <c r="W52" s="22" t="n"/>
       <c r="X52" s="22" t="n"/>
       <c r="Y52" s="22" t="n"/>
-      <c r="Z52" s="28" t="n"/>
+      <c r="Z52" s="22" t="n"/>
       <c r="AA52" s="22" t="n"/>
       <c r="AB52" s="22" t="n"/>
       <c r="AC52" s="22" t="n"/>
@@ -3021,7 +3021,7 @@
     <row r="53" outlineLevel="1" ht="14" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>8.3 Regla al reservar</t>
+          <t>8.3 Pago cancelado</t>
         </is>
       </c>
       <c r="B53" s="22" t="n"/>
@@ -3048,7 +3048,7 @@
       <c r="W53" s="22" t="n"/>
       <c r="X53" s="22" t="n"/>
       <c r="Y53" s="22" t="n"/>
-      <c r="Z53" s="21" t="n"/>
+      <c r="Z53" s="22" t="n"/>
       <c r="AA53" s="22" t="n"/>
       <c r="AB53" s="22" t="n"/>
       <c r="AC53" s="22" t="n"/>
@@ -3088,7 +3088,7 @@
       <c r="W54" s="22" t="n"/>
       <c r="X54" s="22" t="n"/>
       <c r="Y54" s="22" t="n"/>
-      <c r="Z54" s="25" t="n"/>
+      <c r="Z54" s="22" t="n"/>
       <c r="AA54" s="22" t="n"/>
       <c r="AB54" s="22" t="n"/>
       <c r="AC54" s="22" t="n"/>
@@ -3128,7 +3128,7 @@
       <c r="W55" s="22" t="n"/>
       <c r="X55" s="22" t="n"/>
       <c r="Y55" s="22" t="n"/>
-      <c r="Z55" s="26" t="n"/>
+      <c r="Z55" s="22" t="n"/>
       <c r="AA55" s="22" t="n"/>
       <c r="AB55" s="22" t="n"/>
       <c r="AC55" s="22" t="n"/>
@@ -3141,7 +3141,7 @@
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>9. Correos ya en funcionamiento</t>
+          <t>9. Panel de administración</t>
         </is>
       </c>
       <c r="B56" s="22" t="n"/>
@@ -3169,7 +3169,7 @@
       <c r="X56" s="22" t="n"/>
       <c r="Y56" s="22" t="n"/>
       <c r="Z56" s="22" t="n"/>
-      <c r="AA56" s="27" t="n"/>
+      <c r="AA56" s="22" t="n"/>
       <c r="AB56" s="22" t="n"/>
       <c r="AC56" s="22" t="n"/>
       <c r="AD56" s="30" t="inlineStr">
@@ -3181,7 +3181,7 @@
     <row r="57" outlineLevel="1" ht="14" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>9.1 Confirma tu cuenta → registro</t>
+          <t>9.1 Inicio del panel</t>
         </is>
       </c>
       <c r="B57" s="22" t="n"/>
@@ -3209,7 +3209,7 @@
       <c r="X57" s="22" t="n"/>
       <c r="Y57" s="22" t="n"/>
       <c r="Z57" s="22" t="n"/>
-      <c r="AA57" s="28" t="n"/>
+      <c r="AA57" s="22" t="n"/>
       <c r="AB57" s="22" t="n"/>
       <c r="AC57" s="22" t="n"/>
       <c r="AD57" s="30" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="58" outlineLevel="1" ht="14" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>9.2 Restablecer contraseña → usuario</t>
+          <t>9.2 Menú y permisos</t>
         </is>
       </c>
       <c r="B58" s="22" t="n"/>
@@ -3249,7 +3249,7 @@
       <c r="X58" s="22" t="n"/>
       <c r="Y58" s="22" t="n"/>
       <c r="Z58" s="22" t="n"/>
-      <c r="AA58" s="21" t="n"/>
+      <c r="AA58" s="22" t="n"/>
       <c r="AB58" s="22" t="n"/>
       <c r="AC58" s="22" t="n"/>
       <c r="AD58" s="30" t="inlineStr">
@@ -3261,7 +3261,7 @@
     <row r="59" outlineLevel="1" ht="14" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>9.3 Ticket de contraseña → usuario</t>
+          <t>9.3 Listados del panel</t>
         </is>
       </c>
       <c r="B59" s="22" t="n"/>
@@ -3289,7 +3289,7 @@
       <c r="X59" s="22" t="n"/>
       <c r="Y59" s="22" t="n"/>
       <c r="Z59" s="22" t="n"/>
-      <c r="AA59" s="25" t="n"/>
+      <c r="AA59" s="22" t="n"/>
       <c r="AB59" s="22" t="n"/>
       <c r="AC59" s="22" t="n"/>
       <c r="AD59" s="30" t="inlineStr">
@@ -3301,7 +3301,7 @@
     <row r="60" outlineLevel="1" ht="14" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>9.4 Confirmación de reserva → cliente</t>
+          <t>9.4 Testeo</t>
         </is>
       </c>
       <c r="B60" s="22" t="n"/>
@@ -3329,7 +3329,7 @@
       <c r="X60" s="22" t="n"/>
       <c r="Y60" s="22" t="n"/>
       <c r="Z60" s="22" t="n"/>
-      <c r="AA60" s="26" t="n"/>
+      <c r="AA60" s="22" t="n"/>
       <c r="AB60" s="22" t="n"/>
       <c r="AC60" s="22" t="n"/>
       <c r="AD60" s="30" t="inlineStr">
@@ -3341,7 +3341,7 @@
     <row r="61" outlineLevel="1" ht="14" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>9.5 Cambio en tu clase → inscritos</t>
+          <t>9.5 Documentación</t>
         </is>
       </c>
       <c r="B61" s="22" t="n"/>
@@ -3369,7 +3369,7 @@
       <c r="X61" s="22" t="n"/>
       <c r="Y61" s="22" t="n"/>
       <c r="Z61" s="22" t="n"/>
-      <c r="AA61" s="27" t="n"/>
+      <c r="AA61" s="22" t="n"/>
       <c r="AB61" s="22" t="n"/>
       <c r="AC61" s="22" t="n"/>
       <c r="AD61" s="30" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
     </row>
-    <row r="62" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
-        <is>
-          <t>9.6 Actividad cancelada → inscritos</t>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>10. Gestión de clientes</t>
         </is>
       </c>
       <c r="B62" s="22" t="n"/>
@@ -3409,7 +3409,7 @@
       <c r="X62" s="22" t="n"/>
       <c r="Y62" s="22" t="n"/>
       <c r="Z62" s="22" t="n"/>
-      <c r="AA62" s="28" t="n"/>
+      <c r="AA62" s="22" t="n"/>
       <c r="AB62" s="22" t="n"/>
       <c r="AC62" s="22" t="n"/>
       <c r="AD62" s="30" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="63" outlineLevel="1" ht="14" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>9.7 Respuesta de contacto → remitente</t>
+          <t>10.1 Listado de clientes</t>
         </is>
       </c>
       <c r="B63" s="22" t="n"/>
@@ -3449,7 +3449,7 @@
       <c r="X63" s="22" t="n"/>
       <c r="Y63" s="22" t="n"/>
       <c r="Z63" s="22" t="n"/>
-      <c r="AA63" s="21" t="n"/>
+      <c r="AA63" s="22" t="n"/>
       <c r="AB63" s="22" t="n"/>
       <c r="AC63" s="22" t="n"/>
       <c r="AD63" s="30" t="inlineStr">
@@ -3461,7 +3461,7 @@
     <row r="64" outlineLevel="1" ht="14" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>9.8 Testeo</t>
+          <t>10.2 Ficha del cliente</t>
         </is>
       </c>
       <c r="B64" s="22" t="n"/>
@@ -3489,7 +3489,7 @@
       <c r="X64" s="22" t="n"/>
       <c r="Y64" s="22" t="n"/>
       <c r="Z64" s="22" t="n"/>
-      <c r="AA64" s="25" t="n"/>
+      <c r="AA64" s="22" t="n"/>
       <c r="AB64" s="22" t="n"/>
       <c r="AC64" s="22" t="n"/>
       <c r="AD64" s="30" t="inlineStr">
@@ -3501,7 +3501,7 @@
     <row r="65" outlineLevel="1" ht="14" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>9.9 Documentación</t>
+          <t>10.3 Edición de datos</t>
         </is>
       </c>
       <c r="B65" s="22" t="n"/>
@@ -3529,7 +3529,7 @@
       <c r="X65" s="22" t="n"/>
       <c r="Y65" s="22" t="n"/>
       <c r="Z65" s="22" t="n"/>
-      <c r="AA65" s="26" t="n"/>
+      <c r="AA65" s="22" t="n"/>
       <c r="AB65" s="22" t="n"/>
       <c r="AC65" s="22" t="n"/>
       <c r="AD65" s="30" t="inlineStr">
@@ -3538,10 +3538,10 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="20" t="inlineStr">
-        <is>
-          <t>10. Inscripciones y reservas</t>
+    <row r="66" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>10.4 Testeo</t>
         </is>
       </c>
       <c r="B66" s="22" t="n"/>
@@ -3581,7 +3581,7 @@
     <row r="67" outlineLevel="1" ht="14" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>10.1 Formulario de inscripción</t>
+          <t>10.5 Documentación</t>
         </is>
       </c>
       <c r="B67" s="22" t="n"/>
@@ -3618,10 +3618,10 @@
         </is>
       </c>
     </row>
-    <row r="68" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A68" s="24" t="inlineStr">
-        <is>
-          <t>10.2 Control de plazas</t>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>11. Monitores y solicitudes</t>
         </is>
       </c>
       <c r="B68" s="22" t="n"/>
@@ -3661,7 +3661,7 @@
     <row r="69" outlineLevel="1" ht="14" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>10.3 Reservas del cliente</t>
+          <t>11.1 Alta de monitores</t>
         </is>
       </c>
       <c r="B69" s="22" t="n"/>
@@ -3701,7 +3701,7 @@
     <row r="70" outlineLevel="1" ht="14" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>10.4 Testeo</t>
+          <t>11.2 Solicitudes de clase</t>
         </is>
       </c>
       <c r="B70" s="22" t="n"/>
@@ -3741,7 +3741,7 @@
     <row r="71" outlineLevel="1" ht="14" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>10.5 Documentación</t>
+          <t>11.3 Aprobación y rechazo</t>
         </is>
       </c>
       <c r="B71" s="22" t="n"/>
@@ -3778,10 +3778,10 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
-        <is>
-          <t>11. Suscripciones</t>
+    <row r="72" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>11.4 Testeo</t>
         </is>
       </c>
       <c r="B72" s="22" t="n"/>
@@ -3821,7 +3821,7 @@
     <row r="73" outlineLevel="1" ht="14" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>11.1 Planes de suscripción</t>
+          <t>11.5 Documentación</t>
         </is>
       </c>
       <c r="B73" s="22" t="n"/>
@@ -3858,10 +3858,10 @@
         </is>
       </c>
     </row>
-    <row r="74" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A74" s="24" t="inlineStr">
-        <is>
-          <t>11.2 Alta del cliente</t>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>12. Salas y materiales</t>
         </is>
       </c>
       <c r="B74" s="22" t="n"/>
@@ -3901,7 +3901,7 @@
     <row r="75" outlineLevel="1" ht="14" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>11.3 Renovación y baja</t>
+          <t>12.1 Ficha de salas</t>
         </is>
       </c>
       <c r="B75" s="22" t="n"/>
@@ -3941,7 +3941,7 @@
     <row r="76" outlineLevel="1" ht="14" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>11.4 Testeo</t>
+          <t>12.2 Inventario de materiales</t>
         </is>
       </c>
       <c r="B76" s="22" t="n"/>
@@ -3981,7 +3981,7 @@
     <row r="77" outlineLevel="1" ht="14" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>11.5 Documentación</t>
+          <t>12.3 Alta y edición</t>
         </is>
       </c>
       <c r="B77" s="22" t="n"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>12. Pagos con Stripe</t>
+    <row r="78" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>12.4 Testeo</t>
         </is>
       </c>
       <c r="B78" s="22" t="n"/>
@@ -4061,7 +4061,7 @@
     <row r="79" outlineLevel="1" ht="14" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>12.1 Pasarela de Stripe</t>
+          <t>12.5 Documentación</t>
         </is>
       </c>
       <c r="B79" s="22" t="n"/>
@@ -4098,10 +4098,10 @@
         </is>
       </c>
     </row>
-    <row r="80" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A80" s="24" t="inlineStr">
-        <is>
-          <t>12.2 Confirmación del pago</t>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>13. Fisioterapia y citas</t>
         </is>
       </c>
       <c r="B80" s="22" t="n"/>
@@ -4141,7 +4141,7 @@
     <row r="81" outlineLevel="1" ht="14" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>12.3 Pago cancelado</t>
+          <t>13.1 Solicitud de cita</t>
         </is>
       </c>
       <c r="B81" s="22" t="n"/>
@@ -4181,7 +4181,7 @@
     <row r="82" outlineLevel="1" ht="14" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>12.4 Testeo</t>
+          <t>13.2 Agenda del fisioterapeuta</t>
         </is>
       </c>
       <c r="B82" s="22" t="n"/>
@@ -4221,7 +4221,7 @@
     <row r="83" outlineLevel="1" ht="14" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>12.5 Documentación</t>
+          <t>13.3 Panel de citas</t>
         </is>
       </c>
       <c r="B83" s="22" t="n"/>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>13. Panel de administración</t>
+    <row r="84" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>13.4 Testeo</t>
         </is>
       </c>
       <c r="B84" s="22" t="n"/>
@@ -4301,7 +4301,7 @@
     <row r="85" outlineLevel="1" ht="14" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>13.1 Inicio del panel</t>
+          <t>13.5 Documentación</t>
         </is>
       </c>
       <c r="B85" s="22" t="n"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
     </row>
-    <row r="86" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A86" s="24" t="inlineStr">
-        <is>
-          <t>13.2 Menú y permisos</t>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>14. Comentarios, feedback y seguridad</t>
         </is>
       </c>
       <c r="B86" s="22" t="n"/>
@@ -4381,7 +4381,7 @@
     <row r="87" outlineLevel="1" ht="14" customHeight="1">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>13.3 Listados del panel</t>
+          <t>14.1 Comentarios de actividad</t>
         </is>
       </c>
       <c r="B87" s="22" t="n"/>
@@ -4421,7 +4421,7 @@
     <row r="88" outlineLevel="1" ht="14" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
         <is>
-          <t>13.4 Testeo</t>
+          <t>14.2 Respuesta de contacto → remitente</t>
         </is>
       </c>
       <c r="B88" s="22" t="n"/>
@@ -4461,7 +4461,7 @@
     <row r="89" outlineLevel="1" ht="14" customHeight="1">
       <c r="A89" s="24" t="inlineStr">
         <is>
-          <t>13.5 Documentación</t>
+          <t>14.3 Configuración de seguridad</t>
         </is>
       </c>
       <c r="B89" s="22" t="n"/>
@@ -4498,10 +4498,10 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="14" customHeight="1">
-      <c r="A90" s="20" t="inlineStr">
-        <is>
-          <t>14. Gestión de clientes</t>
+    <row r="90" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>14.4 Testeo</t>
         </is>
       </c>
       <c r="B90" s="22" t="n"/>
@@ -4541,7 +4541,7 @@
     <row r="91" outlineLevel="1" ht="14" customHeight="1">
       <c r="A91" s="24" t="inlineStr">
         <is>
-          <t>14.1 Listado de clientes</t>
+          <t>14.5 Documentación</t>
         </is>
       </c>
       <c r="B91" s="22" t="n"/>
@@ -4578,10 +4578,10 @@
         </is>
       </c>
     </row>
-    <row r="92" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A92" s="24" t="inlineStr">
-        <is>
-          <t>14.2 Ficha del cliente</t>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>15. Interfaz Tailwind, correo y cierre</t>
         </is>
       </c>
       <c r="B92" s="22" t="n"/>
@@ -4602,26 +4602,26 @@
       <c r="Q92" s="22" t="n"/>
       <c r="R92" s="22" t="n"/>
       <c r="S92" s="22" t="n"/>
-      <c r="T92" s="22" t="n"/>
-      <c r="U92" s="22" t="n"/>
-      <c r="V92" s="22" t="n"/>
-      <c r="W92" s="22" t="n"/>
-      <c r="X92" s="22" t="n"/>
-      <c r="Y92" s="22" t="n"/>
-      <c r="Z92" s="22" t="n"/>
-      <c r="AA92" s="22" t="n"/>
-      <c r="AB92" s="22" t="n"/>
-      <c r="AC92" s="22" t="n"/>
-      <c r="AD92" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="T92" s="28" t="n"/>
+      <c r="U92" s="28" t="n"/>
+      <c r="V92" s="28" t="n"/>
+      <c r="W92" s="28" t="n"/>
+      <c r="X92" s="28" t="n"/>
+      <c r="Y92" s="28" t="n"/>
+      <c r="Z92" s="28" t="n"/>
+      <c r="AA92" s="28" t="n"/>
+      <c r="AB92" s="28" t="n"/>
+      <c r="AC92" s="28" t="n"/>
+      <c r="AD92" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="93" outlineLevel="1" ht="14" customHeight="1">
       <c r="A93" s="24" t="inlineStr">
         <is>
-          <t>14.3 Edición de datos</t>
+          <t>15.1 Transiciones del front</t>
         </is>
       </c>
       <c r="B93" s="22" t="n"/>
@@ -4642,26 +4642,26 @@
       <c r="Q93" s="22" t="n"/>
       <c r="R93" s="22" t="n"/>
       <c r="S93" s="22" t="n"/>
-      <c r="T93" s="22" t="n"/>
-      <c r="U93" s="22" t="n"/>
-      <c r="V93" s="22" t="n"/>
-      <c r="W93" s="22" t="n"/>
+      <c r="T93" s="21" t="n"/>
+      <c r="U93" s="21" t="n"/>
+      <c r="V93" s="21" t="n"/>
+      <c r="W93" s="21" t="n"/>
       <c r="X93" s="22" t="n"/>
       <c r="Y93" s="22" t="n"/>
       <c r="Z93" s="22" t="n"/>
       <c r="AA93" s="22" t="n"/>
       <c r="AB93" s="22" t="n"/>
       <c r="AC93" s="22" t="n"/>
-      <c r="AD93" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD93" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="94" outlineLevel="1" ht="14" customHeight="1">
       <c r="A94" s="24" t="inlineStr">
         <is>
-          <t>14.4 Testeo</t>
+          <t>15.2 Correos ya en funcionamiento</t>
         </is>
       </c>
       <c r="B94" s="22" t="n"/>
@@ -4689,7 +4689,7 @@
       <c r="X94" s="22" t="n"/>
       <c r="Y94" s="22" t="n"/>
       <c r="Z94" s="22" t="n"/>
-      <c r="AA94" s="22" t="n"/>
+      <c r="AA94" s="25" t="n"/>
       <c r="AB94" s="22" t="n"/>
       <c r="AC94" s="22" t="n"/>
       <c r="AD94" s="30" t="inlineStr">
@@ -4701,7 +4701,7 @@
     <row r="95" outlineLevel="1" ht="14" customHeight="1">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>14.5 Documentación</t>
+          <t>15.3 Cierre y revisión</t>
         </is>
       </c>
       <c r="B95" s="22" t="n"/>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="14" customHeight="1">
-      <c r="A96" s="20" t="inlineStr">
-        <is>
-          <t>15. Monitores y solicitudes</t>
+    <row r="96" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>15.4 Testeo</t>
         </is>
       </c>
       <c r="B96" s="22" t="n"/>
@@ -4762,26 +4762,26 @@
       <c r="Q96" s="22" t="n"/>
       <c r="R96" s="22" t="n"/>
       <c r="S96" s="22" t="n"/>
-      <c r="T96" s="22" t="n"/>
-      <c r="U96" s="22" t="n"/>
-      <c r="V96" s="22" t="n"/>
-      <c r="W96" s="22" t="n"/>
-      <c r="X96" s="22" t="n"/>
-      <c r="Y96" s="22" t="n"/>
-      <c r="Z96" s="22" t="n"/>
-      <c r="AA96" s="22" t="n"/>
-      <c r="AB96" s="22" t="n"/>
-      <c r="AC96" s="22" t="n"/>
-      <c r="AD96" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="T96" s="27" t="n"/>
+      <c r="U96" s="27" t="n"/>
+      <c r="V96" s="27" t="n"/>
+      <c r="W96" s="27" t="n"/>
+      <c r="X96" s="27" t="n"/>
+      <c r="Y96" s="27" t="n"/>
+      <c r="Z96" s="27" t="n"/>
+      <c r="AA96" s="27" t="n"/>
+      <c r="AB96" s="27" t="n"/>
+      <c r="AC96" s="27" t="n"/>
+      <c r="AD96" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="97" outlineLevel="1" ht="14" customHeight="1">
       <c r="A97" s="24" t="inlineStr">
         <is>
-          <t>15.1 Alta de monitores</t>
+          <t>15.5 Documentación</t>
         </is>
       </c>
       <c r="B97" s="22" t="n"/>
@@ -4802,28 +4802,24 @@
       <c r="Q97" s="22" t="n"/>
       <c r="R97" s="22" t="n"/>
       <c r="S97" s="22" t="n"/>
-      <c r="T97" s="22" t="n"/>
-      <c r="U97" s="22" t="n"/>
-      <c r="V97" s="22" t="n"/>
-      <c r="W97" s="22" t="n"/>
-      <c r="X97" s="22" t="n"/>
-      <c r="Y97" s="22" t="n"/>
-      <c r="Z97" s="22" t="n"/>
-      <c r="AA97" s="22" t="n"/>
-      <c r="AB97" s="22" t="n"/>
-      <c r="AC97" s="22" t="n"/>
-      <c r="AD97" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A98" s="24" t="inlineStr">
-        <is>
-          <t>15.2 Solicitudes de clase</t>
-        </is>
-      </c>
+      <c r="T97" s="28" t="n"/>
+      <c r="U97" s="28" t="n"/>
+      <c r="V97" s="28" t="n"/>
+      <c r="W97" s="28" t="n"/>
+      <c r="X97" s="28" t="n"/>
+      <c r="Y97" s="28" t="n"/>
+      <c r="Z97" s="28" t="n"/>
+      <c r="AA97" s="28" t="n"/>
+      <c r="AB97" s="28" t="n"/>
+      <c r="AC97" s="28" t="n"/>
+      <c r="AD97" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="22" t="n"/>
       <c r="B98" s="22" t="n"/>
       <c r="C98" s="22" t="n"/>
       <c r="D98" s="22" t="n"/>
@@ -4852,18 +4848,10 @@
       <c r="AA98" s="22" t="n"/>
       <c r="AB98" s="22" t="n"/>
       <c r="AC98" s="22" t="n"/>
-      <c r="AD98" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A99" s="24" t="inlineStr">
-        <is>
-          <t>15.3 Aprobación y rechazo</t>
-        </is>
-      </c>
+      <c r="AD98" s="22" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="22" t="n"/>
       <c r="B99" s="22" t="n"/>
       <c r="C99" s="22" t="n"/>
       <c r="D99" s="22" t="n"/>
@@ -4892,18 +4880,10 @@
       <c r="AA99" s="22" t="n"/>
       <c r="AB99" s="22" t="n"/>
       <c r="AC99" s="22" t="n"/>
-      <c r="AD99" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A100" s="24" t="inlineStr">
-        <is>
-          <t>15.4 Testeo</t>
-        </is>
-      </c>
+      <c r="AD99" s="22" t="n"/>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="22" t="n"/>
       <c r="B100" s="22" t="n"/>
       <c r="C100" s="22" t="n"/>
       <c r="D100" s="22" t="n"/>
@@ -4932,18 +4912,10 @@
       <c r="AA100" s="22" t="n"/>
       <c r="AB100" s="22" t="n"/>
       <c r="AC100" s="22" t="n"/>
-      <c r="AD100" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A101" s="24" t="inlineStr">
-        <is>
-          <t>15.5 Documentación</t>
-        </is>
-      </c>
+      <c r="AD100" s="22" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="22" t="n"/>
       <c r="B101" s="22" t="n"/>
       <c r="C101" s="22" t="n"/>
       <c r="D101" s="22" t="n"/>
@@ -4972,1099 +4944,7 @@
       <c r="AA101" s="22" t="n"/>
       <c r="AB101" s="22" t="n"/>
       <c r="AC101" s="22" t="n"/>
-      <c r="AD101" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="14" customHeight="1">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>16. Salas y materiales</t>
-        </is>
-      </c>
-      <c r="B102" s="22" t="n"/>
-      <c r="C102" s="22" t="n"/>
-      <c r="D102" s="22" t="n"/>
-      <c r="E102" s="22" t="n"/>
-      <c r="F102" s="22" t="n"/>
-      <c r="G102" s="22" t="n"/>
-      <c r="H102" s="22" t="n"/>
-      <c r="I102" s="22" t="n"/>
-      <c r="J102" s="22" t="n"/>
-      <c r="K102" s="22" t="n"/>
-      <c r="L102" s="22" t="n"/>
-      <c r="M102" s="22" t="n"/>
-      <c r="N102" s="22" t="n"/>
-      <c r="O102" s="22" t="n"/>
-      <c r="P102" s="22" t="n"/>
-      <c r="Q102" s="22" t="n"/>
-      <c r="R102" s="22" t="n"/>
-      <c r="S102" s="22" t="n"/>
-      <c r="T102" s="22" t="n"/>
-      <c r="U102" s="22" t="n"/>
-      <c r="V102" s="22" t="n"/>
-      <c r="W102" s="22" t="n"/>
-      <c r="X102" s="22" t="n"/>
-      <c r="Y102" s="22" t="n"/>
-      <c r="Z102" s="22" t="n"/>
-      <c r="AA102" s="22" t="n"/>
-      <c r="AB102" s="22" t="n"/>
-      <c r="AC102" s="22" t="n"/>
-      <c r="AD102" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A103" s="24" t="inlineStr">
-        <is>
-          <t>16.1 Ficha de salas</t>
-        </is>
-      </c>
-      <c r="B103" s="22" t="n"/>
-      <c r="C103" s="22" t="n"/>
-      <c r="D103" s="22" t="n"/>
-      <c r="E103" s="22" t="n"/>
-      <c r="F103" s="22" t="n"/>
-      <c r="G103" s="22" t="n"/>
-      <c r="H103" s="22" t="n"/>
-      <c r="I103" s="22" t="n"/>
-      <c r="J103" s="22" t="n"/>
-      <c r="K103" s="22" t="n"/>
-      <c r="L103" s="22" t="n"/>
-      <c r="M103" s="22" t="n"/>
-      <c r="N103" s="22" t="n"/>
-      <c r="O103" s="22" t="n"/>
-      <c r="P103" s="22" t="n"/>
-      <c r="Q103" s="22" t="n"/>
-      <c r="R103" s="22" t="n"/>
-      <c r="S103" s="22" t="n"/>
-      <c r="T103" s="22" t="n"/>
-      <c r="U103" s="22" t="n"/>
-      <c r="V103" s="22" t="n"/>
-      <c r="W103" s="22" t="n"/>
-      <c r="X103" s="22" t="n"/>
-      <c r="Y103" s="22" t="n"/>
-      <c r="Z103" s="22" t="n"/>
-      <c r="AA103" s="22" t="n"/>
-      <c r="AB103" s="22" t="n"/>
-      <c r="AC103" s="22" t="n"/>
-      <c r="AD103" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A104" s="24" t="inlineStr">
-        <is>
-          <t>16.2 Inventario de materiales</t>
-        </is>
-      </c>
-      <c r="B104" s="22" t="n"/>
-      <c r="C104" s="22" t="n"/>
-      <c r="D104" s="22" t="n"/>
-      <c r="E104" s="22" t="n"/>
-      <c r="F104" s="22" t="n"/>
-      <c r="G104" s="22" t="n"/>
-      <c r="H104" s="22" t="n"/>
-      <c r="I104" s="22" t="n"/>
-      <c r="J104" s="22" t="n"/>
-      <c r="K104" s="22" t="n"/>
-      <c r="L104" s="22" t="n"/>
-      <c r="M104" s="22" t="n"/>
-      <c r="N104" s="22" t="n"/>
-      <c r="O104" s="22" t="n"/>
-      <c r="P104" s="22" t="n"/>
-      <c r="Q104" s="22" t="n"/>
-      <c r="R104" s="22" t="n"/>
-      <c r="S104" s="22" t="n"/>
-      <c r="T104" s="22" t="n"/>
-      <c r="U104" s="22" t="n"/>
-      <c r="V104" s="22" t="n"/>
-      <c r="W104" s="22" t="n"/>
-      <c r="X104" s="22" t="n"/>
-      <c r="Y104" s="22" t="n"/>
-      <c r="Z104" s="22" t="n"/>
-      <c r="AA104" s="22" t="n"/>
-      <c r="AB104" s="22" t="n"/>
-      <c r="AC104" s="22" t="n"/>
-      <c r="AD104" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A105" s="24" t="inlineStr">
-        <is>
-          <t>16.3 Alta y edición</t>
-        </is>
-      </c>
-      <c r="B105" s="22" t="n"/>
-      <c r="C105" s="22" t="n"/>
-      <c r="D105" s="22" t="n"/>
-      <c r="E105" s="22" t="n"/>
-      <c r="F105" s="22" t="n"/>
-      <c r="G105" s="22" t="n"/>
-      <c r="H105" s="22" t="n"/>
-      <c r="I105" s="22" t="n"/>
-      <c r="J105" s="22" t="n"/>
-      <c r="K105" s="22" t="n"/>
-      <c r="L105" s="22" t="n"/>
-      <c r="M105" s="22" t="n"/>
-      <c r="N105" s="22" t="n"/>
-      <c r="O105" s="22" t="n"/>
-      <c r="P105" s="22" t="n"/>
-      <c r="Q105" s="22" t="n"/>
-      <c r="R105" s="22" t="n"/>
-      <c r="S105" s="22" t="n"/>
-      <c r="T105" s="22" t="n"/>
-      <c r="U105" s="22" t="n"/>
-      <c r="V105" s="22" t="n"/>
-      <c r="W105" s="22" t="n"/>
-      <c r="X105" s="22" t="n"/>
-      <c r="Y105" s="22" t="n"/>
-      <c r="Z105" s="22" t="n"/>
-      <c r="AA105" s="22" t="n"/>
-      <c r="AB105" s="22" t="n"/>
-      <c r="AC105" s="22" t="n"/>
-      <c r="AD105" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A106" s="24" t="inlineStr">
-        <is>
-          <t>16.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B106" s="22" t="n"/>
-      <c r="C106" s="22" t="n"/>
-      <c r="D106" s="22" t="n"/>
-      <c r="E106" s="22" t="n"/>
-      <c r="F106" s="22" t="n"/>
-      <c r="G106" s="22" t="n"/>
-      <c r="H106" s="22" t="n"/>
-      <c r="I106" s="22" t="n"/>
-      <c r="J106" s="22" t="n"/>
-      <c r="K106" s="22" t="n"/>
-      <c r="L106" s="22" t="n"/>
-      <c r="M106" s="22" t="n"/>
-      <c r="N106" s="22" t="n"/>
-      <c r="O106" s="22" t="n"/>
-      <c r="P106" s="22" t="n"/>
-      <c r="Q106" s="22" t="n"/>
-      <c r="R106" s="22" t="n"/>
-      <c r="S106" s="22" t="n"/>
-      <c r="T106" s="22" t="n"/>
-      <c r="U106" s="22" t="n"/>
-      <c r="V106" s="22" t="n"/>
-      <c r="W106" s="22" t="n"/>
-      <c r="X106" s="22" t="n"/>
-      <c r="Y106" s="22" t="n"/>
-      <c r="Z106" s="22" t="n"/>
-      <c r="AA106" s="22" t="n"/>
-      <c r="AB106" s="22" t="n"/>
-      <c r="AC106" s="22" t="n"/>
-      <c r="AD106" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A107" s="24" t="inlineStr">
-        <is>
-          <t>16.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B107" s="22" t="n"/>
-      <c r="C107" s="22" t="n"/>
-      <c r="D107" s="22" t="n"/>
-      <c r="E107" s="22" t="n"/>
-      <c r="F107" s="22" t="n"/>
-      <c r="G107" s="22" t="n"/>
-      <c r="H107" s="22" t="n"/>
-      <c r="I107" s="22" t="n"/>
-      <c r="J107" s="22" t="n"/>
-      <c r="K107" s="22" t="n"/>
-      <c r="L107" s="22" t="n"/>
-      <c r="M107" s="22" t="n"/>
-      <c r="N107" s="22" t="n"/>
-      <c r="O107" s="22" t="n"/>
-      <c r="P107" s="22" t="n"/>
-      <c r="Q107" s="22" t="n"/>
-      <c r="R107" s="22" t="n"/>
-      <c r="S107" s="22" t="n"/>
-      <c r="T107" s="22" t="n"/>
-      <c r="U107" s="22" t="n"/>
-      <c r="V107" s="22" t="n"/>
-      <c r="W107" s="22" t="n"/>
-      <c r="X107" s="22" t="n"/>
-      <c r="Y107" s="22" t="n"/>
-      <c r="Z107" s="22" t="n"/>
-      <c r="AA107" s="22" t="n"/>
-      <c r="AB107" s="22" t="n"/>
-      <c r="AC107" s="22" t="n"/>
-      <c r="AD107" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="14" customHeight="1">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>17. Fisioterapia y citas</t>
-        </is>
-      </c>
-      <c r="B108" s="22" t="n"/>
-      <c r="C108" s="22" t="n"/>
-      <c r="D108" s="22" t="n"/>
-      <c r="E108" s="22" t="n"/>
-      <c r="F108" s="22" t="n"/>
-      <c r="G108" s="22" t="n"/>
-      <c r="H108" s="22" t="n"/>
-      <c r="I108" s="22" t="n"/>
-      <c r="J108" s="22" t="n"/>
-      <c r="K108" s="22" t="n"/>
-      <c r="L108" s="22" t="n"/>
-      <c r="M108" s="22" t="n"/>
-      <c r="N108" s="22" t="n"/>
-      <c r="O108" s="22" t="n"/>
-      <c r="P108" s="22" t="n"/>
-      <c r="Q108" s="22" t="n"/>
-      <c r="R108" s="22" t="n"/>
-      <c r="S108" s="22" t="n"/>
-      <c r="T108" s="22" t="n"/>
-      <c r="U108" s="22" t="n"/>
-      <c r="V108" s="22" t="n"/>
-      <c r="W108" s="22" t="n"/>
-      <c r="X108" s="22" t="n"/>
-      <c r="Y108" s="22" t="n"/>
-      <c r="Z108" s="22" t="n"/>
-      <c r="AA108" s="22" t="n"/>
-      <c r="AB108" s="22" t="n"/>
-      <c r="AC108" s="22" t="n"/>
-      <c r="AD108" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A109" s="24" t="inlineStr">
-        <is>
-          <t>17.1 Solicitud de cita</t>
-        </is>
-      </c>
-      <c r="B109" s="22" t="n"/>
-      <c r="C109" s="22" t="n"/>
-      <c r="D109" s="22" t="n"/>
-      <c r="E109" s="22" t="n"/>
-      <c r="F109" s="22" t="n"/>
-      <c r="G109" s="22" t="n"/>
-      <c r="H109" s="22" t="n"/>
-      <c r="I109" s="22" t="n"/>
-      <c r="J109" s="22" t="n"/>
-      <c r="K109" s="22" t="n"/>
-      <c r="L109" s="22" t="n"/>
-      <c r="M109" s="22" t="n"/>
-      <c r="N109" s="22" t="n"/>
-      <c r="O109" s="22" t="n"/>
-      <c r="P109" s="22" t="n"/>
-      <c r="Q109" s="22" t="n"/>
-      <c r="R109" s="22" t="n"/>
-      <c r="S109" s="22" t="n"/>
-      <c r="T109" s="22" t="n"/>
-      <c r="U109" s="22" t="n"/>
-      <c r="V109" s="22" t="n"/>
-      <c r="W109" s="22" t="n"/>
-      <c r="X109" s="22" t="n"/>
-      <c r="Y109" s="22" t="n"/>
-      <c r="Z109" s="22" t="n"/>
-      <c r="AA109" s="22" t="n"/>
-      <c r="AB109" s="22" t="n"/>
-      <c r="AC109" s="22" t="n"/>
-      <c r="AD109" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A110" s="24" t="inlineStr">
-        <is>
-          <t>17.2 Agenda del fisioterapeuta</t>
-        </is>
-      </c>
-      <c r="B110" s="22" t="n"/>
-      <c r="C110" s="22" t="n"/>
-      <c r="D110" s="22" t="n"/>
-      <c r="E110" s="22" t="n"/>
-      <c r="F110" s="22" t="n"/>
-      <c r="G110" s="22" t="n"/>
-      <c r="H110" s="22" t="n"/>
-      <c r="I110" s="22" t="n"/>
-      <c r="J110" s="22" t="n"/>
-      <c r="K110" s="22" t="n"/>
-      <c r="L110" s="22" t="n"/>
-      <c r="M110" s="22" t="n"/>
-      <c r="N110" s="22" t="n"/>
-      <c r="O110" s="22" t="n"/>
-      <c r="P110" s="22" t="n"/>
-      <c r="Q110" s="22" t="n"/>
-      <c r="R110" s="22" t="n"/>
-      <c r="S110" s="22" t="n"/>
-      <c r="T110" s="22" t="n"/>
-      <c r="U110" s="22" t="n"/>
-      <c r="V110" s="22" t="n"/>
-      <c r="W110" s="22" t="n"/>
-      <c r="X110" s="22" t="n"/>
-      <c r="Y110" s="22" t="n"/>
-      <c r="Z110" s="22" t="n"/>
-      <c r="AA110" s="22" t="n"/>
-      <c r="AB110" s="22" t="n"/>
-      <c r="AC110" s="22" t="n"/>
-      <c r="AD110" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A111" s="24" t="inlineStr">
-        <is>
-          <t>17.3 Panel de citas</t>
-        </is>
-      </c>
-      <c r="B111" s="22" t="n"/>
-      <c r="C111" s="22" t="n"/>
-      <c r="D111" s="22" t="n"/>
-      <c r="E111" s="22" t="n"/>
-      <c r="F111" s="22" t="n"/>
-      <c r="G111" s="22" t="n"/>
-      <c r="H111" s="22" t="n"/>
-      <c r="I111" s="22" t="n"/>
-      <c r="J111" s="22" t="n"/>
-      <c r="K111" s="22" t="n"/>
-      <c r="L111" s="22" t="n"/>
-      <c r="M111" s="22" t="n"/>
-      <c r="N111" s="22" t="n"/>
-      <c r="O111" s="22" t="n"/>
-      <c r="P111" s="22" t="n"/>
-      <c r="Q111" s="22" t="n"/>
-      <c r="R111" s="22" t="n"/>
-      <c r="S111" s="22" t="n"/>
-      <c r="T111" s="22" t="n"/>
-      <c r="U111" s="22" t="n"/>
-      <c r="V111" s="22" t="n"/>
-      <c r="W111" s="22" t="n"/>
-      <c r="X111" s="22" t="n"/>
-      <c r="Y111" s="22" t="n"/>
-      <c r="Z111" s="22" t="n"/>
-      <c r="AA111" s="22" t="n"/>
-      <c r="AB111" s="22" t="n"/>
-      <c r="AC111" s="22" t="n"/>
-      <c r="AD111" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A112" s="24" t="inlineStr">
-        <is>
-          <t>17.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B112" s="22" t="n"/>
-      <c r="C112" s="22" t="n"/>
-      <c r="D112" s="22" t="n"/>
-      <c r="E112" s="22" t="n"/>
-      <c r="F112" s="22" t="n"/>
-      <c r="G112" s="22" t="n"/>
-      <c r="H112" s="22" t="n"/>
-      <c r="I112" s="22" t="n"/>
-      <c r="J112" s="22" t="n"/>
-      <c r="K112" s="22" t="n"/>
-      <c r="L112" s="22" t="n"/>
-      <c r="M112" s="22" t="n"/>
-      <c r="N112" s="22" t="n"/>
-      <c r="O112" s="22" t="n"/>
-      <c r="P112" s="22" t="n"/>
-      <c r="Q112" s="22" t="n"/>
-      <c r="R112" s="22" t="n"/>
-      <c r="S112" s="22" t="n"/>
-      <c r="T112" s="22" t="n"/>
-      <c r="U112" s="22" t="n"/>
-      <c r="V112" s="22" t="n"/>
-      <c r="W112" s="22" t="n"/>
-      <c r="X112" s="22" t="n"/>
-      <c r="Y112" s="22" t="n"/>
-      <c r="Z112" s="22" t="n"/>
-      <c r="AA112" s="22" t="n"/>
-      <c r="AB112" s="22" t="n"/>
-      <c r="AC112" s="22" t="n"/>
-      <c r="AD112" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A113" s="24" t="inlineStr">
-        <is>
-          <t>17.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B113" s="22" t="n"/>
-      <c r="C113" s="22" t="n"/>
-      <c r="D113" s="22" t="n"/>
-      <c r="E113" s="22" t="n"/>
-      <c r="F113" s="22" t="n"/>
-      <c r="G113" s="22" t="n"/>
-      <c r="H113" s="22" t="n"/>
-      <c r="I113" s="22" t="n"/>
-      <c r="J113" s="22" t="n"/>
-      <c r="K113" s="22" t="n"/>
-      <c r="L113" s="22" t="n"/>
-      <c r="M113" s="22" t="n"/>
-      <c r="N113" s="22" t="n"/>
-      <c r="O113" s="22" t="n"/>
-      <c r="P113" s="22" t="n"/>
-      <c r="Q113" s="22" t="n"/>
-      <c r="R113" s="22" t="n"/>
-      <c r="S113" s="22" t="n"/>
-      <c r="T113" s="22" t="n"/>
-      <c r="U113" s="22" t="n"/>
-      <c r="V113" s="22" t="n"/>
-      <c r="W113" s="22" t="n"/>
-      <c r="X113" s="22" t="n"/>
-      <c r="Y113" s="22" t="n"/>
-      <c r="Z113" s="22" t="n"/>
-      <c r="AA113" s="22" t="n"/>
-      <c r="AB113" s="22" t="n"/>
-      <c r="AC113" s="22" t="n"/>
-      <c r="AD113" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="14" customHeight="1">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>18. Comentarios, feedback y seguridad</t>
-        </is>
-      </c>
-      <c r="B114" s="22" t="n"/>
-      <c r="C114" s="22" t="n"/>
-      <c r="D114" s="22" t="n"/>
-      <c r="E114" s="22" t="n"/>
-      <c r="F114" s="22" t="n"/>
-      <c r="G114" s="22" t="n"/>
-      <c r="H114" s="22" t="n"/>
-      <c r="I114" s="22" t="n"/>
-      <c r="J114" s="22" t="n"/>
-      <c r="K114" s="22" t="n"/>
-      <c r="L114" s="22" t="n"/>
-      <c r="M114" s="22" t="n"/>
-      <c r="N114" s="22" t="n"/>
-      <c r="O114" s="22" t="n"/>
-      <c r="P114" s="22" t="n"/>
-      <c r="Q114" s="22" t="n"/>
-      <c r="R114" s="22" t="n"/>
-      <c r="S114" s="22" t="n"/>
-      <c r="T114" s="22" t="n"/>
-      <c r="U114" s="22" t="n"/>
-      <c r="V114" s="22" t="n"/>
-      <c r="W114" s="22" t="n"/>
-      <c r="X114" s="22" t="n"/>
-      <c r="Y114" s="22" t="n"/>
-      <c r="Z114" s="22" t="n"/>
-      <c r="AA114" s="22" t="n"/>
-      <c r="AB114" s="22" t="n"/>
-      <c r="AC114" s="22" t="n"/>
-      <c r="AD114" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A115" s="24" t="inlineStr">
-        <is>
-          <t>18.1 Comentarios de actividad</t>
-        </is>
-      </c>
-      <c r="B115" s="22" t="n"/>
-      <c r="C115" s="22" t="n"/>
-      <c r="D115" s="22" t="n"/>
-      <c r="E115" s="22" t="n"/>
-      <c r="F115" s="22" t="n"/>
-      <c r="G115" s="22" t="n"/>
-      <c r="H115" s="22" t="n"/>
-      <c r="I115" s="22" t="n"/>
-      <c r="J115" s="22" t="n"/>
-      <c r="K115" s="22" t="n"/>
-      <c r="L115" s="22" t="n"/>
-      <c r="M115" s="22" t="n"/>
-      <c r="N115" s="22" t="n"/>
-      <c r="O115" s="22" t="n"/>
-      <c r="P115" s="22" t="n"/>
-      <c r="Q115" s="22" t="n"/>
-      <c r="R115" s="22" t="n"/>
-      <c r="S115" s="22" t="n"/>
-      <c r="T115" s="22" t="n"/>
-      <c r="U115" s="22" t="n"/>
-      <c r="V115" s="22" t="n"/>
-      <c r="W115" s="22" t="n"/>
-      <c r="X115" s="22" t="n"/>
-      <c r="Y115" s="22" t="n"/>
-      <c r="Z115" s="22" t="n"/>
-      <c r="AA115" s="22" t="n"/>
-      <c r="AB115" s="22" t="n"/>
-      <c r="AC115" s="22" t="n"/>
-      <c r="AD115" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A116" s="24" t="inlineStr">
-        <is>
-          <t>18.2 Buzón de feedback</t>
-        </is>
-      </c>
-      <c r="B116" s="22" t="n"/>
-      <c r="C116" s="22" t="n"/>
-      <c r="D116" s="22" t="n"/>
-      <c r="E116" s="22" t="n"/>
-      <c r="F116" s="22" t="n"/>
-      <c r="G116" s="22" t="n"/>
-      <c r="H116" s="22" t="n"/>
-      <c r="I116" s="22" t="n"/>
-      <c r="J116" s="22" t="n"/>
-      <c r="K116" s="22" t="n"/>
-      <c r="L116" s="22" t="n"/>
-      <c r="M116" s="22" t="n"/>
-      <c r="N116" s="22" t="n"/>
-      <c r="O116" s="22" t="n"/>
-      <c r="P116" s="22" t="n"/>
-      <c r="Q116" s="22" t="n"/>
-      <c r="R116" s="22" t="n"/>
-      <c r="S116" s="22" t="n"/>
-      <c r="T116" s="22" t="n"/>
-      <c r="U116" s="22" t="n"/>
-      <c r="V116" s="22" t="n"/>
-      <c r="W116" s="22" t="n"/>
-      <c r="X116" s="22" t="n"/>
-      <c r="Y116" s="22" t="n"/>
-      <c r="Z116" s="22" t="n"/>
-      <c r="AA116" s="22" t="n"/>
-      <c r="AB116" s="22" t="n"/>
-      <c r="AC116" s="22" t="n"/>
-      <c r="AD116" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A117" s="24" t="inlineStr">
-        <is>
-          <t>18.3 Configuración de seguridad</t>
-        </is>
-      </c>
-      <c r="B117" s="22" t="n"/>
-      <c r="C117" s="22" t="n"/>
-      <c r="D117" s="22" t="n"/>
-      <c r="E117" s="22" t="n"/>
-      <c r="F117" s="22" t="n"/>
-      <c r="G117" s="22" t="n"/>
-      <c r="H117" s="22" t="n"/>
-      <c r="I117" s="22" t="n"/>
-      <c r="J117" s="22" t="n"/>
-      <c r="K117" s="22" t="n"/>
-      <c r="L117" s="22" t="n"/>
-      <c r="M117" s="22" t="n"/>
-      <c r="N117" s="22" t="n"/>
-      <c r="O117" s="22" t="n"/>
-      <c r="P117" s="22" t="n"/>
-      <c r="Q117" s="22" t="n"/>
-      <c r="R117" s="22" t="n"/>
-      <c r="S117" s="22" t="n"/>
-      <c r="T117" s="22" t="n"/>
-      <c r="U117" s="22" t="n"/>
-      <c r="V117" s="22" t="n"/>
-      <c r="W117" s="22" t="n"/>
-      <c r="X117" s="22" t="n"/>
-      <c r="Y117" s="22" t="n"/>
-      <c r="Z117" s="22" t="n"/>
-      <c r="AA117" s="22" t="n"/>
-      <c r="AB117" s="22" t="n"/>
-      <c r="AC117" s="22" t="n"/>
-      <c r="AD117" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A118" s="24" t="inlineStr">
-        <is>
-          <t>18.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B118" s="22" t="n"/>
-      <c r="C118" s="22" t="n"/>
-      <c r="D118" s="22" t="n"/>
-      <c r="E118" s="22" t="n"/>
-      <c r="F118" s="22" t="n"/>
-      <c r="G118" s="22" t="n"/>
-      <c r="H118" s="22" t="n"/>
-      <c r="I118" s="22" t="n"/>
-      <c r="J118" s="22" t="n"/>
-      <c r="K118" s="22" t="n"/>
-      <c r="L118" s="22" t="n"/>
-      <c r="M118" s="22" t="n"/>
-      <c r="N118" s="22" t="n"/>
-      <c r="O118" s="22" t="n"/>
-      <c r="P118" s="22" t="n"/>
-      <c r="Q118" s="22" t="n"/>
-      <c r="R118" s="22" t="n"/>
-      <c r="S118" s="22" t="n"/>
-      <c r="T118" s="22" t="n"/>
-      <c r="U118" s="22" t="n"/>
-      <c r="V118" s="22" t="n"/>
-      <c r="W118" s="22" t="n"/>
-      <c r="X118" s="22" t="n"/>
-      <c r="Y118" s="22" t="n"/>
-      <c r="Z118" s="22" t="n"/>
-      <c r="AA118" s="22" t="n"/>
-      <c r="AB118" s="22" t="n"/>
-      <c r="AC118" s="22" t="n"/>
-      <c r="AD118" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A119" s="24" t="inlineStr">
-        <is>
-          <t>18.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B119" s="22" t="n"/>
-      <c r="C119" s="22" t="n"/>
-      <c r="D119" s="22" t="n"/>
-      <c r="E119" s="22" t="n"/>
-      <c r="F119" s="22" t="n"/>
-      <c r="G119" s="22" t="n"/>
-      <c r="H119" s="22" t="n"/>
-      <c r="I119" s="22" t="n"/>
-      <c r="J119" s="22" t="n"/>
-      <c r="K119" s="22" t="n"/>
-      <c r="L119" s="22" t="n"/>
-      <c r="M119" s="22" t="n"/>
-      <c r="N119" s="22" t="n"/>
-      <c r="O119" s="22" t="n"/>
-      <c r="P119" s="22" t="n"/>
-      <c r="Q119" s="22" t="n"/>
-      <c r="R119" s="22" t="n"/>
-      <c r="S119" s="22" t="n"/>
-      <c r="T119" s="22" t="n"/>
-      <c r="U119" s="22" t="n"/>
-      <c r="V119" s="22" t="n"/>
-      <c r="W119" s="22" t="n"/>
-      <c r="X119" s="22" t="n"/>
-      <c r="Y119" s="22" t="n"/>
-      <c r="Z119" s="22" t="n"/>
-      <c r="AA119" s="22" t="n"/>
-      <c r="AB119" s="22" t="n"/>
-      <c r="AC119" s="22" t="n"/>
-      <c r="AD119" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="14" customHeight="1">
-      <c r="A120" s="20" t="inlineStr">
-        <is>
-          <t>19. Interfaz Tailwind y cierre</t>
-        </is>
-      </c>
-      <c r="B120" s="22" t="n"/>
-      <c r="C120" s="22" t="n"/>
-      <c r="D120" s="22" t="n"/>
-      <c r="E120" s="22" t="n"/>
-      <c r="F120" s="22" t="n"/>
-      <c r="G120" s="22" t="n"/>
-      <c r="H120" s="22" t="n"/>
-      <c r="I120" s="22" t="n"/>
-      <c r="J120" s="22" t="n"/>
-      <c r="K120" s="22" t="n"/>
-      <c r="L120" s="22" t="n"/>
-      <c r="M120" s="22" t="n"/>
-      <c r="N120" s="22" t="n"/>
-      <c r="O120" s="22" t="n"/>
-      <c r="P120" s="22" t="n"/>
-      <c r="Q120" s="22" t="n"/>
-      <c r="R120" s="22" t="n"/>
-      <c r="S120" s="22" t="n"/>
-      <c r="T120" s="22" t="n"/>
-      <c r="U120" s="22" t="n"/>
-      <c r="V120" s="22" t="n"/>
-      <c r="W120" s="22" t="n"/>
-      <c r="X120" s="22" t="n"/>
-      <c r="Y120" s="22" t="n"/>
-      <c r="Z120" s="22" t="n"/>
-      <c r="AA120" s="22" t="n"/>
-      <c r="AB120" s="22" t="n"/>
-      <c r="AC120" s="22" t="n"/>
-      <c r="AD120" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A121" s="24" t="inlineStr">
-        <is>
-          <t>19.1 Maquetación con Tailwind</t>
-        </is>
-      </c>
-      <c r="B121" s="22" t="n"/>
-      <c r="C121" s="22" t="n"/>
-      <c r="D121" s="22" t="n"/>
-      <c r="E121" s="22" t="n"/>
-      <c r="F121" s="22" t="n"/>
-      <c r="G121" s="22" t="n"/>
-      <c r="H121" s="22" t="n"/>
-      <c r="I121" s="22" t="n"/>
-      <c r="J121" s="22" t="n"/>
-      <c r="K121" s="22" t="n"/>
-      <c r="L121" s="22" t="n"/>
-      <c r="M121" s="22" t="n"/>
-      <c r="N121" s="22" t="n"/>
-      <c r="O121" s="22" t="n"/>
-      <c r="P121" s="22" t="n"/>
-      <c r="Q121" s="22" t="n"/>
-      <c r="R121" s="22" t="n"/>
-      <c r="S121" s="22" t="n"/>
-      <c r="T121" s="22" t="n"/>
-      <c r="U121" s="22" t="n"/>
-      <c r="V121" s="22" t="n"/>
-      <c r="W121" s="22" t="n"/>
-      <c r="X121" s="22" t="n"/>
-      <c r="Y121" s="22" t="n"/>
-      <c r="Z121" s="22" t="n"/>
-      <c r="AA121" s="22" t="n"/>
-      <c r="AB121" s="22" t="n"/>
-      <c r="AC121" s="22" t="n"/>
-      <c r="AD121" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A122" s="24" t="inlineStr">
-        <is>
-          <t>19.2 Revisión visual</t>
-        </is>
-      </c>
-      <c r="B122" s="22" t="n"/>
-      <c r="C122" s="22" t="n"/>
-      <c r="D122" s="22" t="n"/>
-      <c r="E122" s="22" t="n"/>
-      <c r="F122" s="22" t="n"/>
-      <c r="G122" s="22" t="n"/>
-      <c r="H122" s="22" t="n"/>
-      <c r="I122" s="22" t="n"/>
-      <c r="J122" s="22" t="n"/>
-      <c r="K122" s="22" t="n"/>
-      <c r="L122" s="22" t="n"/>
-      <c r="M122" s="22" t="n"/>
-      <c r="N122" s="22" t="n"/>
-      <c r="O122" s="22" t="n"/>
-      <c r="P122" s="22" t="n"/>
-      <c r="Q122" s="22" t="n"/>
-      <c r="R122" s="22" t="n"/>
-      <c r="S122" s="22" t="n"/>
-      <c r="T122" s="22" t="n"/>
-      <c r="U122" s="22" t="n"/>
-      <c r="V122" s="22" t="n"/>
-      <c r="W122" s="22" t="n"/>
-      <c r="X122" s="22" t="n"/>
-      <c r="Y122" s="22" t="n"/>
-      <c r="Z122" s="22" t="n"/>
-      <c r="AA122" s="22" t="n"/>
-      <c r="AB122" s="22" t="n"/>
-      <c r="AC122" s="22" t="n"/>
-      <c r="AD122" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A123" s="24" t="inlineStr">
-        <is>
-          <t>19.3 Cierre y revisión</t>
-        </is>
-      </c>
-      <c r="B123" s="22" t="n"/>
-      <c r="C123" s="22" t="n"/>
-      <c r="D123" s="22" t="n"/>
-      <c r="E123" s="22" t="n"/>
-      <c r="F123" s="22" t="n"/>
-      <c r="G123" s="22" t="n"/>
-      <c r="H123" s="22" t="n"/>
-      <c r="I123" s="22" t="n"/>
-      <c r="J123" s="22" t="n"/>
-      <c r="K123" s="22" t="n"/>
-      <c r="L123" s="22" t="n"/>
-      <c r="M123" s="22" t="n"/>
-      <c r="N123" s="22" t="n"/>
-      <c r="O123" s="22" t="n"/>
-      <c r="P123" s="22" t="n"/>
-      <c r="Q123" s="22" t="n"/>
-      <c r="R123" s="22" t="n"/>
-      <c r="S123" s="22" t="n"/>
-      <c r="T123" s="22" t="n"/>
-      <c r="U123" s="22" t="n"/>
-      <c r="V123" s="22" t="n"/>
-      <c r="W123" s="22" t="n"/>
-      <c r="X123" s="22" t="n"/>
-      <c r="Y123" s="22" t="n"/>
-      <c r="Z123" s="22" t="n"/>
-      <c r="AA123" s="22" t="n"/>
-      <c r="AB123" s="22" t="n"/>
-      <c r="AC123" s="22" t="n"/>
-      <c r="AD123" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A124" s="24" t="inlineStr">
-        <is>
-          <t>19.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B124" s="22" t="n"/>
-      <c r="C124" s="22" t="n"/>
-      <c r="D124" s="22" t="n"/>
-      <c r="E124" s="22" t="n"/>
-      <c r="F124" s="22" t="n"/>
-      <c r="G124" s="22" t="n"/>
-      <c r="H124" s="22" t="n"/>
-      <c r="I124" s="22" t="n"/>
-      <c r="J124" s="22" t="n"/>
-      <c r="K124" s="22" t="n"/>
-      <c r="L124" s="22" t="n"/>
-      <c r="M124" s="22" t="n"/>
-      <c r="N124" s="22" t="n"/>
-      <c r="O124" s="22" t="n"/>
-      <c r="P124" s="22" t="n"/>
-      <c r="Q124" s="22" t="n"/>
-      <c r="R124" s="22" t="n"/>
-      <c r="S124" s="22" t="n"/>
-      <c r="T124" s="22" t="n"/>
-      <c r="U124" s="22" t="n"/>
-      <c r="V124" s="22" t="n"/>
-      <c r="W124" s="22" t="n"/>
-      <c r="X124" s="22" t="n"/>
-      <c r="Y124" s="22" t="n"/>
-      <c r="Z124" s="22" t="n"/>
-      <c r="AA124" s="22" t="n"/>
-      <c r="AB124" s="22" t="n"/>
-      <c r="AC124" s="22" t="n"/>
-      <c r="AD124" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A125" s="24" t="inlineStr">
-        <is>
-          <t>19.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B125" s="22" t="n"/>
-      <c r="C125" s="22" t="n"/>
-      <c r="D125" s="22" t="n"/>
-      <c r="E125" s="22" t="n"/>
-      <c r="F125" s="22" t="n"/>
-      <c r="G125" s="22" t="n"/>
-      <c r="H125" s="22" t="n"/>
-      <c r="I125" s="22" t="n"/>
-      <c r="J125" s="22" t="n"/>
-      <c r="K125" s="22" t="n"/>
-      <c r="L125" s="22" t="n"/>
-      <c r="M125" s="22" t="n"/>
-      <c r="N125" s="22" t="n"/>
-      <c r="O125" s="22" t="n"/>
-      <c r="P125" s="22" t="n"/>
-      <c r="Q125" s="22" t="n"/>
-      <c r="R125" s="22" t="n"/>
-      <c r="S125" s="22" t="n"/>
-      <c r="T125" s="22" t="n"/>
-      <c r="U125" s="22" t="n"/>
-      <c r="V125" s="22" t="n"/>
-      <c r="W125" s="22" t="n"/>
-      <c r="X125" s="22" t="n"/>
-      <c r="Y125" s="22" t="n"/>
-      <c r="Z125" s="22" t="n"/>
-      <c r="AA125" s="22" t="n"/>
-      <c r="AB125" s="22" t="n"/>
-      <c r="AC125" s="22" t="n"/>
-      <c r="AD125" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="22" t="n"/>
-      <c r="B126" s="22" t="n"/>
-      <c r="C126" s="22" t="n"/>
-      <c r="D126" s="22" t="n"/>
-      <c r="E126" s="22" t="n"/>
-      <c r="F126" s="22" t="n"/>
-      <c r="G126" s="22" t="n"/>
-      <c r="H126" s="22" t="n"/>
-      <c r="I126" s="22" t="n"/>
-      <c r="J126" s="22" t="n"/>
-      <c r="K126" s="22" t="n"/>
-      <c r="L126" s="22" t="n"/>
-      <c r="M126" s="22" t="n"/>
-      <c r="N126" s="22" t="n"/>
-      <c r="O126" s="22" t="n"/>
-      <c r="P126" s="22" t="n"/>
-      <c r="Q126" s="22" t="n"/>
-      <c r="R126" s="22" t="n"/>
-      <c r="S126" s="22" t="n"/>
-      <c r="T126" s="22" t="n"/>
-      <c r="U126" s="22" t="n"/>
-      <c r="V126" s="22" t="n"/>
-      <c r="W126" s="22" t="n"/>
-      <c r="X126" s="22" t="n"/>
-      <c r="Y126" s="22" t="n"/>
-      <c r="Z126" s="22" t="n"/>
-      <c r="AA126" s="22" t="n"/>
-      <c r="AB126" s="22" t="n"/>
-      <c r="AC126" s="22" t="n"/>
-      <c r="AD126" s="22" t="n"/>
-    </row>
-    <row r="127" ht="14" customHeight="1">
-      <c r="A127" s="22" t="n"/>
-      <c r="B127" s="22" t="n"/>
-      <c r="C127" s="22" t="n"/>
-      <c r="D127" s="22" t="n"/>
-      <c r="E127" s="22" t="n"/>
-      <c r="F127" s="22" t="n"/>
-      <c r="G127" s="22" t="n"/>
-      <c r="H127" s="22" t="n"/>
-      <c r="I127" s="22" t="n"/>
-      <c r="J127" s="22" t="n"/>
-      <c r="K127" s="22" t="n"/>
-      <c r="L127" s="22" t="n"/>
-      <c r="M127" s="22" t="n"/>
-      <c r="N127" s="22" t="n"/>
-      <c r="O127" s="22" t="n"/>
-      <c r="P127" s="22" t="n"/>
-      <c r="Q127" s="22" t="n"/>
-      <c r="R127" s="22" t="n"/>
-      <c r="S127" s="22" t="n"/>
-      <c r="T127" s="22" t="n"/>
-      <c r="U127" s="22" t="n"/>
-      <c r="V127" s="22" t="n"/>
-      <c r="W127" s="22" t="n"/>
-      <c r="X127" s="22" t="n"/>
-      <c r="Y127" s="22" t="n"/>
-      <c r="Z127" s="22" t="n"/>
-      <c r="AA127" s="22" t="n"/>
-      <c r="AB127" s="22" t="n"/>
-      <c r="AC127" s="22" t="n"/>
-      <c r="AD127" s="22" t="n"/>
-    </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="22" t="n"/>
-      <c r="B128" s="22" t="n"/>
-      <c r="C128" s="22" t="n"/>
-      <c r="D128" s="22" t="n"/>
-      <c r="E128" s="22" t="n"/>
-      <c r="F128" s="22" t="n"/>
-      <c r="G128" s="22" t="n"/>
-      <c r="H128" s="22" t="n"/>
-      <c r="I128" s="22" t="n"/>
-      <c r="J128" s="22" t="n"/>
-      <c r="K128" s="22" t="n"/>
-      <c r="L128" s="22" t="n"/>
-      <c r="M128" s="22" t="n"/>
-      <c r="N128" s="22" t="n"/>
-      <c r="O128" s="22" t="n"/>
-      <c r="P128" s="22" t="n"/>
-      <c r="Q128" s="22" t="n"/>
-      <c r="R128" s="22" t="n"/>
-      <c r="S128" s="22" t="n"/>
-      <c r="T128" s="22" t="n"/>
-      <c r="U128" s="22" t="n"/>
-      <c r="V128" s="22" t="n"/>
-      <c r="W128" s="22" t="n"/>
-      <c r="X128" s="22" t="n"/>
-      <c r="Y128" s="22" t="n"/>
-      <c r="Z128" s="22" t="n"/>
-      <c r="AA128" s="22" t="n"/>
-      <c r="AB128" s="22" t="n"/>
-      <c r="AC128" s="22" t="n"/>
-      <c r="AD128" s="22" t="n"/>
-    </row>
-    <row r="129" ht="14" customHeight="1">
-      <c r="A129" s="22" t="n"/>
-      <c r="B129" s="22" t="n"/>
-      <c r="C129" s="22" t="n"/>
-      <c r="D129" s="22" t="n"/>
-      <c r="E129" s="22" t="n"/>
-      <c r="F129" s="22" t="n"/>
-      <c r="G129" s="22" t="n"/>
-      <c r="H129" s="22" t="n"/>
-      <c r="I129" s="22" t="n"/>
-      <c r="J129" s="22" t="n"/>
-      <c r="K129" s="22" t="n"/>
-      <c r="L129" s="22" t="n"/>
-      <c r="M129" s="22" t="n"/>
-      <c r="N129" s="22" t="n"/>
-      <c r="O129" s="22" t="n"/>
-      <c r="P129" s="22" t="n"/>
-      <c r="Q129" s="22" t="n"/>
-      <c r="R129" s="22" t="n"/>
-      <c r="S129" s="22" t="n"/>
-      <c r="T129" s="22" t="n"/>
-      <c r="U129" s="22" t="n"/>
-      <c r="V129" s="22" t="n"/>
-      <c r="W129" s="22" t="n"/>
-      <c r="X129" s="22" t="n"/>
-      <c r="Y129" s="22" t="n"/>
-      <c r="Z129" s="22" t="n"/>
-      <c r="AA129" s="22" t="n"/>
-      <c r="AB129" s="22" t="n"/>
-      <c r="AC129" s="22" t="n"/>
-      <c r="AD129" s="22" t="n"/>
+      <c r="AD101" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -6094,10 +4974,10 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AD129"/>
+  <dimension ref="A1:AD101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
     <col width="3.7" customWidth="1" min="3" max="3"/>
     <col width="3.7" customWidth="1" min="4" max="4"/>
@@ -6834,7 +5714,7 @@
     <row r="16" outlineLevel="1" ht="14" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>2.2 Creación del formulario</t>
+          <t>2.2 Formulario de alta → correo de registro</t>
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
@@ -7074,7 +5954,7 @@
     <row r="22" outlineLevel="1" ht="14" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>3.2 Tickets de la cuenta</t>
+          <t>3.2 Ticket de contraseña → usuario</t>
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
@@ -7114,7 +5994,7 @@
     <row r="23" outlineLevel="1" ht="14" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>3.3 Envío del enlace</t>
+          <t>3.3 Restablecer contraseña → usuario</t>
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
@@ -7505,9 +6385,9 @@
       <c r="AA32" s="22" t="n"/>
       <c r="AB32" s="22" t="n"/>
       <c r="AC32" s="22" t="n"/>
-      <c r="AD32" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD32" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -7554,7 +6434,7 @@
     <row r="34" outlineLevel="1" ht="14" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>5.2 Horario del centro</t>
+          <t>5.2 Horario y avisos → inscritos</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
@@ -7594,7 +6474,7 @@
     <row r="35" outlineLevel="1" ht="14" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>5.3 Alta y edición</t>
+          <t>5.3 Mínimo de personas para empezar</t>
         </is>
       </c>
       <c r="B35" s="22" t="n"/>
@@ -7625,9 +6505,9 @@
       <c r="AA35" s="22" t="n"/>
       <c r="AB35" s="22" t="n"/>
       <c r="AC35" s="22" t="n"/>
-      <c r="AD35" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD35" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
@@ -7665,9 +6545,9 @@
       <c r="AA36" s="22" t="n"/>
       <c r="AB36" s="22" t="n"/>
       <c r="AC36" s="22" t="n"/>
-      <c r="AD36" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD36" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -7705,23 +6585,23 @@
       <c r="AA37" s="22" t="n"/>
       <c r="AB37" s="22" t="n"/>
       <c r="AC37" s="22" t="n"/>
-      <c r="AD37" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD37" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>6. Transiciones</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="22" t="n"/>
-      <c r="F38" s="22" t="n"/>
+          <t>6. Inscripciones y reservas</t>
+        </is>
+      </c>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="21" t="n"/>
+      <c r="F38" s="21" t="n"/>
       <c r="G38" s="22" t="n"/>
       <c r="H38" s="22" t="n"/>
       <c r="I38" s="22" t="n"/>
@@ -7745,19 +6625,19 @@
       <c r="AA38" s="22" t="n"/>
       <c r="AB38" s="22" t="n"/>
       <c r="AC38" s="22" t="n"/>
-      <c r="AD38" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD38" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="39" outlineLevel="1" ht="14" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>6.1 Transición entre páginas</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="n"/>
+          <t>6.1 Formulario de inscripción</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n"/>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="22" t="n"/>
       <c r="E39" s="22" t="n"/>
@@ -7785,22 +6665,22 @@
       <c r="AA39" s="22" t="n"/>
       <c r="AB39" s="22" t="n"/>
       <c r="AC39" s="22" t="n"/>
-      <c r="AD39" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD39" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="40" outlineLevel="1" ht="14" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>6.2 Transición de los paneles</t>
+          <t>6.2 Control de plazas</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="22" t="n"/>
-      <c r="E40" s="22" t="n"/>
+      <c r="E40" s="26" t="n"/>
       <c r="F40" s="22" t="n"/>
       <c r="G40" s="22" t="n"/>
       <c r="H40" s="22" t="n"/>
@@ -7825,22 +6705,22 @@
       <c r="AA40" s="22" t="n"/>
       <c r="AB40" s="22" t="n"/>
       <c r="AC40" s="22" t="n"/>
-      <c r="AD40" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD40" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="41" outlineLevel="1" ht="14" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>6.3 Cierre y revisión visual</t>
+          <t>6.3 Reserva → correo del cliente</t>
         </is>
       </c>
       <c r="B41" s="22" t="n"/>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="22" t="n"/>
-      <c r="E41" s="22" t="n"/>
+      <c r="E41" s="27" t="n"/>
       <c r="F41" s="22" t="n"/>
       <c r="G41" s="22" t="n"/>
       <c r="H41" s="22" t="n"/>
@@ -7865,9 +6745,9 @@
       <c r="AA41" s="22" t="n"/>
       <c r="AB41" s="22" t="n"/>
       <c r="AC41" s="22" t="n"/>
-      <c r="AD41" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD41" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
@@ -7877,11 +6757,11 @@
           <t>6.4 Testeo</t>
         </is>
       </c>
-      <c r="B42" s="22" t="n"/>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="22" t="n"/>
-      <c r="F42" s="22" t="n"/>
+      <c r="B42" s="28" t="n"/>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="28" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="28" t="n"/>
       <c r="G42" s="22" t="n"/>
       <c r="H42" s="22" t="n"/>
       <c r="I42" s="22" t="n"/>
@@ -7905,9 +6785,9 @@
       <c r="AA42" s="22" t="n"/>
       <c r="AB42" s="22" t="n"/>
       <c r="AC42" s="22" t="n"/>
-      <c r="AD42" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD42" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
@@ -7917,11 +6797,11 @@
           <t>6.5 Documentación</t>
         </is>
       </c>
-      <c r="B43" s="22" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="22" t="n"/>
-      <c r="F43" s="22" t="n"/>
+      <c r="B43" s="21" t="n"/>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
       <c r="G43" s="22" t="n"/>
       <c r="H43" s="22" t="n"/>
       <c r="I43" s="22" t="n"/>
@@ -7945,16 +6825,16 @@
       <c r="AA43" s="22" t="n"/>
       <c r="AB43" s="22" t="n"/>
       <c r="AC43" s="22" t="n"/>
-      <c r="AD43" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD43" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>7. Planes con mejor información</t>
+          <t>7. Suscripciones</t>
         </is>
       </c>
       <c r="B44" s="22" t="n"/>
@@ -7994,7 +6874,7 @@
     <row r="45" outlineLevel="1" ht="14" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>7.1 Datos que ve el cliente</t>
+          <t>7.1 Planes con mejor información</t>
         </is>
       </c>
       <c r="B45" s="22" t="n"/>
@@ -8034,7 +6914,7 @@
     <row r="46" outlineLevel="1" ht="14" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>7.2 Detalle de cada plan</t>
+          <t>7.2 Alta del cliente</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -8074,7 +6954,7 @@
     <row r="47" outlineLevel="1" ht="14" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>7.3 Textos del alta</t>
+          <t>7.3 Renovación y baja</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -8194,7 +7074,7 @@
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>8. Clases con mínimo de personas</t>
+          <t>8. Pagos con Stripe</t>
         </is>
       </c>
       <c r="B50" s="22" t="n"/>
@@ -8204,11 +7084,11 @@
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="22" t="n"/>
       <c r="H50" s="22" t="n"/>
-      <c r="I50" s="22" t="n"/>
-      <c r="J50" s="22" t="n"/>
-      <c r="K50" s="22" t="n"/>
-      <c r="L50" s="22" t="n"/>
-      <c r="M50" s="22" t="n"/>
+      <c r="I50" s="26" t="n"/>
+      <c r="J50" s="26" t="n"/>
+      <c r="K50" s="26" t="n"/>
+      <c r="L50" s="26" t="n"/>
+      <c r="M50" s="26" t="n"/>
       <c r="N50" s="22" t="n"/>
       <c r="O50" s="22" t="n"/>
       <c r="P50" s="22" t="n"/>
@@ -8234,7 +7114,7 @@
     <row r="51" outlineLevel="1" ht="14" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>8.1 Mínimo para abrir la clase</t>
+          <t>8.1 Pasarela de Stripe</t>
         </is>
       </c>
       <c r="B51" s="22" t="n"/>
@@ -8244,7 +7124,7 @@
       <c r="F51" s="22" t="n"/>
       <c r="G51" s="22" t="n"/>
       <c r="H51" s="22" t="n"/>
-      <c r="I51" s="22" t="n"/>
+      <c r="I51" s="27" t="n"/>
       <c r="J51" s="22" t="n"/>
       <c r="K51" s="22" t="n"/>
       <c r="L51" s="22" t="n"/>
@@ -8274,7 +7154,7 @@
     <row r="52" outlineLevel="1" ht="14" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>8.2 Aviso si no se llega</t>
+          <t>8.2 Confirmación del pago</t>
         </is>
       </c>
       <c r="B52" s="22" t="n"/>
@@ -8287,7 +7167,7 @@
       <c r="I52" s="22" t="n"/>
       <c r="J52" s="22" t="n"/>
       <c r="K52" s="22" t="n"/>
-      <c r="L52" s="22" t="n"/>
+      <c r="L52" s="28" t="n"/>
       <c r="M52" s="22" t="n"/>
       <c r="N52" s="22" t="n"/>
       <c r="O52" s="22" t="n"/>
@@ -8314,7 +7194,7 @@
     <row r="53" outlineLevel="1" ht="14" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>8.3 Regla al reservar</t>
+          <t>8.3 Pago cancelado</t>
         </is>
       </c>
       <c r="B53" s="22" t="n"/>
@@ -8327,7 +7207,7 @@
       <c r="I53" s="22" t="n"/>
       <c r="J53" s="22" t="n"/>
       <c r="K53" s="22" t="n"/>
-      <c r="L53" s="22" t="n"/>
+      <c r="L53" s="21" t="n"/>
       <c r="M53" s="22" t="n"/>
       <c r="N53" s="22" t="n"/>
       <c r="O53" s="22" t="n"/>
@@ -8364,11 +7244,11 @@
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="22" t="n"/>
       <c r="H54" s="22" t="n"/>
-      <c r="I54" s="22" t="n"/>
-      <c r="J54" s="22" t="n"/>
-      <c r="K54" s="22" t="n"/>
-      <c r="L54" s="22" t="n"/>
-      <c r="M54" s="22" t="n"/>
+      <c r="I54" s="25" t="n"/>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="25" t="n"/>
+      <c r="L54" s="25" t="n"/>
+      <c r="M54" s="25" t="n"/>
       <c r="N54" s="22" t="n"/>
       <c r="O54" s="22" t="n"/>
       <c r="P54" s="22" t="n"/>
@@ -8404,11 +7284,11 @@
       <c r="F55" s="22" t="n"/>
       <c r="G55" s="22" t="n"/>
       <c r="H55" s="22" t="n"/>
-      <c r="I55" s="22" t="n"/>
-      <c r="J55" s="22" t="n"/>
-      <c r="K55" s="22" t="n"/>
-      <c r="L55" s="22" t="n"/>
-      <c r="M55" s="22" t="n"/>
+      <c r="I55" s="26" t="n"/>
+      <c r="J55" s="26" t="n"/>
+      <c r="K55" s="26" t="n"/>
+      <c r="L55" s="26" t="n"/>
+      <c r="M55" s="26" t="n"/>
       <c r="N55" s="22" t="n"/>
       <c r="O55" s="22" t="n"/>
       <c r="P55" s="22" t="n"/>
@@ -8434,7 +7314,7 @@
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>9. Correos ya en funcionamiento</t>
+          <t>9. Panel de administración</t>
         </is>
       </c>
       <c r="B56" s="22" t="n"/>
@@ -8449,8 +7329,8 @@
       <c r="K56" s="22" t="n"/>
       <c r="L56" s="22" t="n"/>
       <c r="M56" s="22" t="n"/>
-      <c r="N56" s="22" t="n"/>
-      <c r="O56" s="22" t="n"/>
+      <c r="N56" s="27" t="n"/>
+      <c r="O56" s="27" t="n"/>
       <c r="P56" s="22" t="n"/>
       <c r="Q56" s="22" t="n"/>
       <c r="R56" s="22" t="n"/>
@@ -8474,7 +7354,7 @@
     <row r="57" outlineLevel="1" ht="14" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>9.1 Confirma tu cuenta → registro</t>
+          <t>9.1 Inicio del panel</t>
         </is>
       </c>
       <c r="B57" s="22" t="n"/>
@@ -8489,7 +7369,7 @@
       <c r="K57" s="22" t="n"/>
       <c r="L57" s="22" t="n"/>
       <c r="M57" s="22" t="n"/>
-      <c r="N57" s="22" t="n"/>
+      <c r="N57" s="28" t="n"/>
       <c r="O57" s="22" t="n"/>
       <c r="P57" s="22" t="n"/>
       <c r="Q57" s="22" t="n"/>
@@ -8514,7 +7394,7 @@
     <row r="58" outlineLevel="1" ht="14" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>9.2 Restablecer contraseña → usuario</t>
+          <t>9.2 Menú y permisos</t>
         </is>
       </c>
       <c r="B58" s="22" t="n"/>
@@ -8529,7 +7409,7 @@
       <c r="K58" s="22" t="n"/>
       <c r="L58" s="22" t="n"/>
       <c r="M58" s="22" t="n"/>
-      <c r="N58" s="22" t="n"/>
+      <c r="N58" s="21" t="n"/>
       <c r="O58" s="22" t="n"/>
       <c r="P58" s="22" t="n"/>
       <c r="Q58" s="22" t="n"/>
@@ -8554,7 +7434,7 @@
     <row r="59" outlineLevel="1" ht="14" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>9.3 Ticket de contraseña → usuario</t>
+          <t>9.3 Listados del panel</t>
         </is>
       </c>
       <c r="B59" s="22" t="n"/>
@@ -8569,7 +7449,7 @@
       <c r="K59" s="22" t="n"/>
       <c r="L59" s="22" t="n"/>
       <c r="M59" s="22" t="n"/>
-      <c r="N59" s="22" t="n"/>
+      <c r="N59" s="25" t="n"/>
       <c r="O59" s="22" t="n"/>
       <c r="P59" s="22" t="n"/>
       <c r="Q59" s="22" t="n"/>
@@ -8594,7 +7474,7 @@
     <row r="60" outlineLevel="1" ht="14" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>9.4 Confirmación de reserva → cliente</t>
+          <t>9.4 Testeo</t>
         </is>
       </c>
       <c r="B60" s="22" t="n"/>
@@ -8609,8 +7489,8 @@
       <c r="K60" s="22" t="n"/>
       <c r="L60" s="22" t="n"/>
       <c r="M60" s="22" t="n"/>
-      <c r="N60" s="22" t="n"/>
-      <c r="O60" s="22" t="n"/>
+      <c r="N60" s="26" t="n"/>
+      <c r="O60" s="26" t="n"/>
       <c r="P60" s="22" t="n"/>
       <c r="Q60" s="22" t="n"/>
       <c r="R60" s="22" t="n"/>
@@ -8634,7 +7514,7 @@
     <row r="61" outlineLevel="1" ht="14" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>9.5 Cambio en tu clase → inscritos</t>
+          <t>9.5 Documentación</t>
         </is>
       </c>
       <c r="B61" s="22" t="n"/>
@@ -8649,8 +7529,8 @@
       <c r="K61" s="22" t="n"/>
       <c r="L61" s="22" t="n"/>
       <c r="M61" s="22" t="n"/>
-      <c r="N61" s="22" t="n"/>
-      <c r="O61" s="22" t="n"/>
+      <c r="N61" s="27" t="n"/>
+      <c r="O61" s="27" t="n"/>
       <c r="P61" s="22" t="n"/>
       <c r="Q61" s="22" t="n"/>
       <c r="R61" s="22" t="n"/>
@@ -8671,10 +7551,10 @@
         </is>
       </c>
     </row>
-    <row r="62" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
-        <is>
-          <t>9.6 Actividad cancelada → inscritos</t>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>10. Gestión de clientes</t>
         </is>
       </c>
       <c r="B62" s="22" t="n"/>
@@ -8691,10 +7571,10 @@
       <c r="M62" s="22" t="n"/>
       <c r="N62" s="22" t="n"/>
       <c r="O62" s="22" t="n"/>
-      <c r="P62" s="22" t="n"/>
-      <c r="Q62" s="22" t="n"/>
-      <c r="R62" s="22" t="n"/>
-      <c r="S62" s="22" t="n"/>
+      <c r="P62" s="28" t="n"/>
+      <c r="Q62" s="28" t="n"/>
+      <c r="R62" s="28" t="n"/>
+      <c r="S62" s="28" t="n"/>
       <c r="T62" s="22" t="n"/>
       <c r="U62" s="22" t="n"/>
       <c r="V62" s="22" t="n"/>
@@ -8714,7 +7594,7 @@
     <row r="63" outlineLevel="1" ht="14" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>9.7 Respuesta de contacto → remitente</t>
+          <t>10.1 Listado de clientes</t>
         </is>
       </c>
       <c r="B63" s="22" t="n"/>
@@ -8731,7 +7611,7 @@
       <c r="M63" s="22" t="n"/>
       <c r="N63" s="22" t="n"/>
       <c r="O63" s="22" t="n"/>
-      <c r="P63" s="22" t="n"/>
+      <c r="P63" s="21" t="n"/>
       <c r="Q63" s="22" t="n"/>
       <c r="R63" s="22" t="n"/>
       <c r="S63" s="22" t="n"/>
@@ -8754,7 +7634,7 @@
     <row r="64" outlineLevel="1" ht="14" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>9.8 Testeo</t>
+          <t>10.2 Ficha del cliente</t>
         </is>
       </c>
       <c r="B64" s="22" t="n"/>
@@ -8771,7 +7651,7 @@
       <c r="M64" s="22" t="n"/>
       <c r="N64" s="22" t="n"/>
       <c r="O64" s="22" t="n"/>
-      <c r="P64" s="22" t="n"/>
+      <c r="P64" s="25" t="n"/>
       <c r="Q64" s="22" t="n"/>
       <c r="R64" s="22" t="n"/>
       <c r="S64" s="22" t="n"/>
@@ -8794,7 +7674,7 @@
     <row r="65" outlineLevel="1" ht="14" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>9.9 Documentación</t>
+          <t>10.3 Edición de datos</t>
         </is>
       </c>
       <c r="B65" s="22" t="n"/>
@@ -8811,7 +7691,7 @@
       <c r="M65" s="22" t="n"/>
       <c r="N65" s="22" t="n"/>
       <c r="O65" s="22" t="n"/>
-      <c r="P65" s="22" t="n"/>
+      <c r="P65" s="26" t="n"/>
       <c r="Q65" s="22" t="n"/>
       <c r="R65" s="22" t="n"/>
       <c r="S65" s="22" t="n"/>
@@ -8831,30 +7711,30 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="20" t="inlineStr">
-        <is>
-          <t>10. Inscripciones y reservas</t>
+    <row r="66" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>10.4 Testeo</t>
         </is>
       </c>
       <c r="B66" s="22" t="n"/>
       <c r="C66" s="22" t="n"/>
       <c r="D66" s="22" t="n"/>
       <c r="E66" s="22" t="n"/>
-      <c r="F66" s="27" t="n"/>
-      <c r="G66" s="27" t="n"/>
-      <c r="H66" s="27" t="n"/>
-      <c r="I66" s="27" t="n"/>
-      <c r="J66" s="27" t="n"/>
+      <c r="F66" s="22" t="n"/>
+      <c r="G66" s="22" t="n"/>
+      <c r="H66" s="22" t="n"/>
+      <c r="I66" s="22" t="n"/>
+      <c r="J66" s="22" t="n"/>
       <c r="K66" s="22" t="n"/>
       <c r="L66" s="22" t="n"/>
       <c r="M66" s="22" t="n"/>
       <c r="N66" s="22" t="n"/>
       <c r="O66" s="22" t="n"/>
-      <c r="P66" s="22" t="n"/>
-      <c r="Q66" s="22" t="n"/>
-      <c r="R66" s="22" t="n"/>
-      <c r="S66" s="22" t="n"/>
+      <c r="P66" s="27" t="n"/>
+      <c r="Q66" s="27" t="n"/>
+      <c r="R66" s="27" t="n"/>
+      <c r="S66" s="27" t="n"/>
       <c r="T66" s="22" t="n"/>
       <c r="U66" s="22" t="n"/>
       <c r="V66" s="22" t="n"/>
@@ -8874,14 +7754,14 @@
     <row r="67" outlineLevel="1" ht="14" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>10.1 Formulario de inscripción</t>
+          <t>10.5 Documentación</t>
         </is>
       </c>
       <c r="B67" s="22" t="n"/>
       <c r="C67" s="22" t="n"/>
       <c r="D67" s="22" t="n"/>
       <c r="E67" s="22" t="n"/>
-      <c r="F67" s="28" t="n"/>
+      <c r="F67" s="22" t="n"/>
       <c r="G67" s="22" t="n"/>
       <c r="H67" s="22" t="n"/>
       <c r="I67" s="22" t="n"/>
@@ -8891,10 +7771,10 @@
       <c r="M67" s="22" t="n"/>
       <c r="N67" s="22" t="n"/>
       <c r="O67" s="22" t="n"/>
-      <c r="P67" s="22" t="n"/>
-      <c r="Q67" s="22" t="n"/>
-      <c r="R67" s="22" t="n"/>
-      <c r="S67" s="22" t="n"/>
+      <c r="P67" s="28" t="n"/>
+      <c r="Q67" s="28" t="n"/>
+      <c r="R67" s="28" t="n"/>
+      <c r="S67" s="28" t="n"/>
       <c r="T67" s="22" t="n"/>
       <c r="U67" s="22" t="n"/>
       <c r="V67" s="22" t="n"/>
@@ -8911,10 +7791,10 @@
         </is>
       </c>
     </row>
-    <row r="68" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A68" s="24" t="inlineStr">
-        <is>
-          <t>10.2 Control de plazas</t>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>11. Monitores y solicitudes</t>
         </is>
       </c>
       <c r="B68" s="22" t="n"/>
@@ -8924,7 +7804,7 @@
       <c r="F68" s="22" t="n"/>
       <c r="G68" s="22" t="n"/>
       <c r="H68" s="22" t="n"/>
-      <c r="I68" s="21" t="n"/>
+      <c r="I68" s="22" t="n"/>
       <c r="J68" s="22" t="n"/>
       <c r="K68" s="22" t="n"/>
       <c r="L68" s="22" t="n"/>
@@ -8935,9 +7815,9 @@
       <c r="Q68" s="22" t="n"/>
       <c r="R68" s="22" t="n"/>
       <c r="S68" s="22" t="n"/>
-      <c r="T68" s="22" t="n"/>
-      <c r="U68" s="22" t="n"/>
-      <c r="V68" s="22" t="n"/>
+      <c r="T68" s="21" t="n"/>
+      <c r="U68" s="21" t="n"/>
+      <c r="V68" s="21" t="n"/>
       <c r="W68" s="22" t="n"/>
       <c r="X68" s="22" t="n"/>
       <c r="Y68" s="22" t="n"/>
@@ -8954,7 +7834,7 @@
     <row r="69" outlineLevel="1" ht="14" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>10.3 Reservas del cliente</t>
+          <t>11.1 Alta de monitores</t>
         </is>
       </c>
       <c r="B69" s="22" t="n"/>
@@ -8964,7 +7844,7 @@
       <c r="F69" s="22" t="n"/>
       <c r="G69" s="22" t="n"/>
       <c r="H69" s="22" t="n"/>
-      <c r="I69" s="25" t="n"/>
+      <c r="I69" s="22" t="n"/>
       <c r="J69" s="22" t="n"/>
       <c r="K69" s="22" t="n"/>
       <c r="L69" s="22" t="n"/>
@@ -8975,7 +7855,7 @@
       <c r="Q69" s="22" t="n"/>
       <c r="R69" s="22" t="n"/>
       <c r="S69" s="22" t="n"/>
-      <c r="T69" s="22" t="n"/>
+      <c r="T69" s="25" t="n"/>
       <c r="U69" s="22" t="n"/>
       <c r="V69" s="22" t="n"/>
       <c r="W69" s="22" t="n"/>
@@ -8994,18 +7874,18 @@
     <row r="70" outlineLevel="1" ht="14" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>10.4 Testeo</t>
+          <t>11.2 Solicitudes de clase</t>
         </is>
       </c>
       <c r="B70" s="22" t="n"/>
       <c r="C70" s="22" t="n"/>
       <c r="D70" s="22" t="n"/>
       <c r="E70" s="22" t="n"/>
-      <c r="F70" s="26" t="n"/>
-      <c r="G70" s="26" t="n"/>
-      <c r="H70" s="26" t="n"/>
-      <c r="I70" s="26" t="n"/>
-      <c r="J70" s="26" t="n"/>
+      <c r="F70" s="22" t="n"/>
+      <c r="G70" s="22" t="n"/>
+      <c r="H70" s="22" t="n"/>
+      <c r="I70" s="22" t="n"/>
+      <c r="J70" s="22" t="n"/>
       <c r="K70" s="22" t="n"/>
       <c r="L70" s="22" t="n"/>
       <c r="M70" s="22" t="n"/>
@@ -9016,7 +7896,7 @@
       <c r="R70" s="22" t="n"/>
       <c r="S70" s="22" t="n"/>
       <c r="T70" s="22" t="n"/>
-      <c r="U70" s="22" t="n"/>
+      <c r="U70" s="26" t="n"/>
       <c r="V70" s="22" t="n"/>
       <c r="W70" s="22" t="n"/>
       <c r="X70" s="22" t="n"/>
@@ -9034,18 +7914,18 @@
     <row r="71" outlineLevel="1" ht="14" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>10.5 Documentación</t>
+          <t>11.3 Aprobación y rechazo</t>
         </is>
       </c>
       <c r="B71" s="22" t="n"/>
       <c r="C71" s="22" t="n"/>
       <c r="D71" s="22" t="n"/>
       <c r="E71" s="22" t="n"/>
-      <c r="F71" s="27" t="n"/>
-      <c r="G71" s="27" t="n"/>
-      <c r="H71" s="27" t="n"/>
-      <c r="I71" s="27" t="n"/>
-      <c r="J71" s="27" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="G71" s="22" t="n"/>
+      <c r="H71" s="22" t="n"/>
+      <c r="I71" s="22" t="n"/>
+      <c r="J71" s="22" t="n"/>
       <c r="K71" s="22" t="n"/>
       <c r="L71" s="22" t="n"/>
       <c r="M71" s="22" t="n"/>
@@ -9056,7 +7936,7 @@
       <c r="R71" s="22" t="n"/>
       <c r="S71" s="22" t="n"/>
       <c r="T71" s="22" t="n"/>
-      <c r="U71" s="22" t="n"/>
+      <c r="U71" s="27" t="n"/>
       <c r="V71" s="22" t="n"/>
       <c r="W71" s="22" t="n"/>
       <c r="X71" s="22" t="n"/>
@@ -9071,10 +7951,10 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
-        <is>
-          <t>11. Suscripciones</t>
+    <row r="72" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>11.4 Testeo</t>
         </is>
       </c>
       <c r="B72" s="22" t="n"/>
@@ -9086,8 +7966,8 @@
       <c r="H72" s="22" t="n"/>
       <c r="I72" s="22" t="n"/>
       <c r="J72" s="22" t="n"/>
-      <c r="K72" s="28" t="n"/>
-      <c r="L72" s="28" t="n"/>
+      <c r="K72" s="22" t="n"/>
+      <c r="L72" s="22" t="n"/>
       <c r="M72" s="22" t="n"/>
       <c r="N72" s="22" t="n"/>
       <c r="O72" s="22" t="n"/>
@@ -9095,9 +7975,9 @@
       <c r="Q72" s="22" t="n"/>
       <c r="R72" s="22" t="n"/>
       <c r="S72" s="22" t="n"/>
-      <c r="T72" s="22" t="n"/>
-      <c r="U72" s="22" t="n"/>
-      <c r="V72" s="22" t="n"/>
+      <c r="T72" s="28" t="n"/>
+      <c r="U72" s="28" t="n"/>
+      <c r="V72" s="28" t="n"/>
       <c r="W72" s="22" t="n"/>
       <c r="X72" s="22" t="n"/>
       <c r="Y72" s="22" t="n"/>
@@ -9114,7 +7994,7 @@
     <row r="73" outlineLevel="1" ht="14" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>11.1 Planes de suscripción</t>
+          <t>11.5 Documentación</t>
         </is>
       </c>
       <c r="B73" s="22" t="n"/>
@@ -9126,7 +8006,7 @@
       <c r="H73" s="22" t="n"/>
       <c r="I73" s="22" t="n"/>
       <c r="J73" s="22" t="n"/>
-      <c r="K73" s="21" t="n"/>
+      <c r="K73" s="22" t="n"/>
       <c r="L73" s="22" t="n"/>
       <c r="M73" s="22" t="n"/>
       <c r="N73" s="22" t="n"/>
@@ -9135,9 +8015,9 @@
       <c r="Q73" s="22" t="n"/>
       <c r="R73" s="22" t="n"/>
       <c r="S73" s="22" t="n"/>
-      <c r="T73" s="22" t="n"/>
-      <c r="U73" s="22" t="n"/>
-      <c r="V73" s="22" t="n"/>
+      <c r="T73" s="21" t="n"/>
+      <c r="U73" s="21" t="n"/>
+      <c r="V73" s="21" t="n"/>
       <c r="W73" s="22" t="n"/>
       <c r="X73" s="22" t="n"/>
       <c r="Y73" s="22" t="n"/>
@@ -9151,10 +8031,10 @@
         </is>
       </c>
     </row>
-    <row r="74" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A74" s="24" t="inlineStr">
-        <is>
-          <t>11.2 Alta del cliente</t>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>12. Salas y materiales</t>
         </is>
       </c>
       <c r="B74" s="22" t="n"/>
@@ -9166,7 +8046,7 @@
       <c r="H74" s="22" t="n"/>
       <c r="I74" s="22" t="n"/>
       <c r="J74" s="22" t="n"/>
-      <c r="K74" s="25" t="n"/>
+      <c r="K74" s="22" t="n"/>
       <c r="L74" s="22" t="n"/>
       <c r="M74" s="22" t="n"/>
       <c r="N74" s="22" t="n"/>
@@ -9178,10 +8058,10 @@
       <c r="T74" s="22" t="n"/>
       <c r="U74" s="22" t="n"/>
       <c r="V74" s="22" t="n"/>
-      <c r="W74" s="22" t="n"/>
-      <c r="X74" s="22" t="n"/>
-      <c r="Y74" s="22" t="n"/>
-      <c r="Z74" s="22" t="n"/>
+      <c r="W74" s="25" t="n"/>
+      <c r="X74" s="25" t="n"/>
+      <c r="Y74" s="25" t="n"/>
+      <c r="Z74" s="25" t="n"/>
       <c r="AA74" s="22" t="n"/>
       <c r="AB74" s="22" t="n"/>
       <c r="AC74" s="22" t="n"/>
@@ -9194,7 +8074,7 @@
     <row r="75" outlineLevel="1" ht="14" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>11.3 Renovación y baja</t>
+          <t>12.1 Ficha de salas</t>
         </is>
       </c>
       <c r="B75" s="22" t="n"/>
@@ -9206,7 +8086,7 @@
       <c r="H75" s="22" t="n"/>
       <c r="I75" s="22" t="n"/>
       <c r="J75" s="22" t="n"/>
-      <c r="K75" s="26" t="n"/>
+      <c r="K75" s="22" t="n"/>
       <c r="L75" s="22" t="n"/>
       <c r="M75" s="22" t="n"/>
       <c r="N75" s="22" t="n"/>
@@ -9218,7 +8098,7 @@
       <c r="T75" s="22" t="n"/>
       <c r="U75" s="22" t="n"/>
       <c r="V75" s="22" t="n"/>
-      <c r="W75" s="22" t="n"/>
+      <c r="W75" s="26" t="n"/>
       <c r="X75" s="22" t="n"/>
       <c r="Y75" s="22" t="n"/>
       <c r="Z75" s="22" t="n"/>
@@ -9234,7 +8114,7 @@
     <row r="76" outlineLevel="1" ht="14" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>11.4 Testeo</t>
+          <t>12.2 Inventario de materiales</t>
         </is>
       </c>
       <c r="B76" s="22" t="n"/>
@@ -9246,8 +8126,8 @@
       <c r="H76" s="22" t="n"/>
       <c r="I76" s="22" t="n"/>
       <c r="J76" s="22" t="n"/>
-      <c r="K76" s="27" t="n"/>
-      <c r="L76" s="27" t="n"/>
+      <c r="K76" s="22" t="n"/>
+      <c r="L76" s="22" t="n"/>
       <c r="M76" s="22" t="n"/>
       <c r="N76" s="22" t="n"/>
       <c r="O76" s="22" t="n"/>
@@ -9258,7 +8138,7 @@
       <c r="T76" s="22" t="n"/>
       <c r="U76" s="22" t="n"/>
       <c r="V76" s="22" t="n"/>
-      <c r="W76" s="22" t="n"/>
+      <c r="W76" s="27" t="n"/>
       <c r="X76" s="22" t="n"/>
       <c r="Y76" s="22" t="n"/>
       <c r="Z76" s="22" t="n"/>
@@ -9274,7 +8154,7 @@
     <row r="77" outlineLevel="1" ht="14" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>11.5 Documentación</t>
+          <t>12.3 Alta y edición</t>
         </is>
       </c>
       <c r="B77" s="22" t="n"/>
@@ -9286,8 +8166,8 @@
       <c r="H77" s="22" t="n"/>
       <c r="I77" s="22" t="n"/>
       <c r="J77" s="22" t="n"/>
-      <c r="K77" s="28" t="n"/>
-      <c r="L77" s="28" t="n"/>
+      <c r="K77" s="22" t="n"/>
+      <c r="L77" s="22" t="n"/>
       <c r="M77" s="22" t="n"/>
       <c r="N77" s="22" t="n"/>
       <c r="O77" s="22" t="n"/>
@@ -9298,7 +8178,7 @@
       <c r="T77" s="22" t="n"/>
       <c r="U77" s="22" t="n"/>
       <c r="V77" s="22" t="n"/>
-      <c r="W77" s="22" t="n"/>
+      <c r="W77" s="28" t="n"/>
       <c r="X77" s="22" t="n"/>
       <c r="Y77" s="22" t="n"/>
       <c r="Z77" s="22" t="n"/>
@@ -9311,10 +8191,10 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>12. Pagos con Stripe</t>
+    <row r="78" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>12.4 Testeo</t>
         </is>
       </c>
       <c r="B78" s="22" t="n"/>
@@ -9328,20 +8208,20 @@
       <c r="J78" s="22" t="n"/>
       <c r="K78" s="22" t="n"/>
       <c r="L78" s="22" t="n"/>
-      <c r="M78" s="21" t="n"/>
-      <c r="N78" s="21" t="n"/>
-      <c r="O78" s="21" t="n"/>
-      <c r="P78" s="21" t="n"/>
-      <c r="Q78" s="21" t="n"/>
+      <c r="M78" s="22" t="n"/>
+      <c r="N78" s="22" t="n"/>
+      <c r="O78" s="22" t="n"/>
+      <c r="P78" s="22" t="n"/>
+      <c r="Q78" s="22" t="n"/>
       <c r="R78" s="22" t="n"/>
       <c r="S78" s="22" t="n"/>
       <c r="T78" s="22" t="n"/>
       <c r="U78" s="22" t="n"/>
       <c r="V78" s="22" t="n"/>
-      <c r="W78" s="22" t="n"/>
-      <c r="X78" s="22" t="n"/>
-      <c r="Y78" s="22" t="n"/>
-      <c r="Z78" s="22" t="n"/>
+      <c r="W78" s="21" t="n"/>
+      <c r="X78" s="21" t="n"/>
+      <c r="Y78" s="21" t="n"/>
+      <c r="Z78" s="21" t="n"/>
       <c r="AA78" s="22" t="n"/>
       <c r="AB78" s="22" t="n"/>
       <c r="AC78" s="22" t="n"/>
@@ -9354,7 +8234,7 @@
     <row r="79" outlineLevel="1" ht="14" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>12.1 Pasarela de Stripe</t>
+          <t>12.5 Documentación</t>
         </is>
       </c>
       <c r="B79" s="22" t="n"/>
@@ -9368,7 +8248,7 @@
       <c r="J79" s="22" t="n"/>
       <c r="K79" s="22" t="n"/>
       <c r="L79" s="22" t="n"/>
-      <c r="M79" s="25" t="n"/>
+      <c r="M79" s="22" t="n"/>
       <c r="N79" s="22" t="n"/>
       <c r="O79" s="22" t="n"/>
       <c r="P79" s="22" t="n"/>
@@ -9378,10 +8258,10 @@
       <c r="T79" s="22" t="n"/>
       <c r="U79" s="22" t="n"/>
       <c r="V79" s="22" t="n"/>
-      <c r="W79" s="22" t="n"/>
-      <c r="X79" s="22" t="n"/>
-      <c r="Y79" s="22" t="n"/>
-      <c r="Z79" s="22" t="n"/>
+      <c r="W79" s="25" t="n"/>
+      <c r="X79" s="25" t="n"/>
+      <c r="Y79" s="25" t="n"/>
+      <c r="Z79" s="25" t="n"/>
       <c r="AA79" s="22" t="n"/>
       <c r="AB79" s="22" t="n"/>
       <c r="AC79" s="22" t="n"/>
@@ -9391,10 +8271,10 @@
         </is>
       </c>
     </row>
-    <row r="80" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A80" s="24" t="inlineStr">
-        <is>
-          <t>12.2 Confirmación del pago</t>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>13. Fisioterapia y citas</t>
         </is>
       </c>
       <c r="B80" s="22" t="n"/>
@@ -9411,7 +8291,7 @@
       <c r="M80" s="22" t="n"/>
       <c r="N80" s="22" t="n"/>
       <c r="O80" s="22" t="n"/>
-      <c r="P80" s="26" t="n"/>
+      <c r="P80" s="22" t="n"/>
       <c r="Q80" s="22" t="n"/>
       <c r="R80" s="22" t="n"/>
       <c r="S80" s="22" t="n"/>
@@ -9422,9 +8302,9 @@
       <c r="X80" s="22" t="n"/>
       <c r="Y80" s="22" t="n"/>
       <c r="Z80" s="22" t="n"/>
-      <c r="AA80" s="22" t="n"/>
-      <c r="AB80" s="22" t="n"/>
-      <c r="AC80" s="22" t="n"/>
+      <c r="AA80" s="26" t="n"/>
+      <c r="AB80" s="26" t="n"/>
+      <c r="AC80" s="26" t="n"/>
       <c r="AD80" s="30" t="inlineStr">
         <is>
           <t>sin iniciar</t>
@@ -9434,7 +8314,7 @@
     <row r="81" outlineLevel="1" ht="14" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>12.3 Pago cancelado</t>
+          <t>13.1 Solicitud de cita</t>
         </is>
       </c>
       <c r="B81" s="22" t="n"/>
@@ -9451,7 +8331,7 @@
       <c r="M81" s="22" t="n"/>
       <c r="N81" s="22" t="n"/>
       <c r="O81" s="22" t="n"/>
-      <c r="P81" s="27" t="n"/>
+      <c r="P81" s="22" t="n"/>
       <c r="Q81" s="22" t="n"/>
       <c r="R81" s="22" t="n"/>
       <c r="S81" s="22" t="n"/>
@@ -9462,7 +8342,7 @@
       <c r="X81" s="22" t="n"/>
       <c r="Y81" s="22" t="n"/>
       <c r="Z81" s="22" t="n"/>
-      <c r="AA81" s="22" t="n"/>
+      <c r="AA81" s="27" t="n"/>
       <c r="AB81" s="22" t="n"/>
       <c r="AC81" s="22" t="n"/>
       <c r="AD81" s="30" t="inlineStr">
@@ -9474,7 +8354,7 @@
     <row r="82" outlineLevel="1" ht="14" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>12.4 Testeo</t>
+          <t>13.2 Agenda del fisioterapeuta</t>
         </is>
       </c>
       <c r="B82" s="22" t="n"/>
@@ -9488,11 +8368,11 @@
       <c r="J82" s="22" t="n"/>
       <c r="K82" s="22" t="n"/>
       <c r="L82" s="22" t="n"/>
-      <c r="M82" s="28" t="n"/>
-      <c r="N82" s="28" t="n"/>
-      <c r="O82" s="28" t="n"/>
-      <c r="P82" s="28" t="n"/>
-      <c r="Q82" s="28" t="n"/>
+      <c r="M82" s="22" t="n"/>
+      <c r="N82" s="22" t="n"/>
+      <c r="O82" s="22" t="n"/>
+      <c r="P82" s="22" t="n"/>
+      <c r="Q82" s="22" t="n"/>
       <c r="R82" s="22" t="n"/>
       <c r="S82" s="22" t="n"/>
       <c r="T82" s="22" t="n"/>
@@ -9503,7 +8383,7 @@
       <c r="Y82" s="22" t="n"/>
       <c r="Z82" s="22" t="n"/>
       <c r="AA82" s="22" t="n"/>
-      <c r="AB82" s="22" t="n"/>
+      <c r="AB82" s="28" t="n"/>
       <c r="AC82" s="22" t="n"/>
       <c r="AD82" s="30" t="inlineStr">
         <is>
@@ -9514,7 +8394,7 @@
     <row r="83" outlineLevel="1" ht="14" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>12.5 Documentación</t>
+          <t>13.3 Panel de citas</t>
         </is>
       </c>
       <c r="B83" s="22" t="n"/>
@@ -9528,11 +8408,11 @@
       <c r="J83" s="22" t="n"/>
       <c r="K83" s="22" t="n"/>
       <c r="L83" s="22" t="n"/>
-      <c r="M83" s="21" t="n"/>
-      <c r="N83" s="21" t="n"/>
-      <c r="O83" s="21" t="n"/>
-      <c r="P83" s="21" t="n"/>
-      <c r="Q83" s="21" t="n"/>
+      <c r="M83" s="22" t="n"/>
+      <c r="N83" s="22" t="n"/>
+      <c r="O83" s="22" t="n"/>
+      <c r="P83" s="22" t="n"/>
+      <c r="Q83" s="22" t="n"/>
       <c r="R83" s="22" t="n"/>
       <c r="S83" s="22" t="n"/>
       <c r="T83" s="22" t="n"/>
@@ -9543,7 +8423,7 @@
       <c r="Y83" s="22" t="n"/>
       <c r="Z83" s="22" t="n"/>
       <c r="AA83" s="22" t="n"/>
-      <c r="AB83" s="22" t="n"/>
+      <c r="AB83" s="21" t="n"/>
       <c r="AC83" s="22" t="n"/>
       <c r="AD83" s="30" t="inlineStr">
         <is>
@@ -9551,10 +8431,10 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>13. Panel de administración</t>
+    <row r="84" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>13.4 Testeo</t>
         </is>
       </c>
       <c r="B84" s="22" t="n"/>
@@ -9573,8 +8453,8 @@
       <c r="O84" s="22" t="n"/>
       <c r="P84" s="22" t="n"/>
       <c r="Q84" s="22" t="n"/>
-      <c r="R84" s="25" t="n"/>
-      <c r="S84" s="25" t="n"/>
+      <c r="R84" s="22" t="n"/>
+      <c r="S84" s="22" t="n"/>
       <c r="T84" s="22" t="n"/>
       <c r="U84" s="22" t="n"/>
       <c r="V84" s="22" t="n"/>
@@ -9582,9 +8462,9 @@
       <c r="X84" s="22" t="n"/>
       <c r="Y84" s="22" t="n"/>
       <c r="Z84" s="22" t="n"/>
-      <c r="AA84" s="22" t="n"/>
-      <c r="AB84" s="22" t="n"/>
-      <c r="AC84" s="22" t="n"/>
+      <c r="AA84" s="25" t="n"/>
+      <c r="AB84" s="25" t="n"/>
+      <c r="AC84" s="25" t="n"/>
       <c r="AD84" s="30" t="inlineStr">
         <is>
           <t>sin iniciar</t>
@@ -9594,7 +8474,7 @@
     <row r="85" outlineLevel="1" ht="14" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>13.1 Inicio del panel</t>
+          <t>13.5 Documentación</t>
         </is>
       </c>
       <c r="B85" s="22" t="n"/>
@@ -9613,7 +8493,7 @@
       <c r="O85" s="22" t="n"/>
       <c r="P85" s="22" t="n"/>
       <c r="Q85" s="22" t="n"/>
-      <c r="R85" s="26" t="n"/>
+      <c r="R85" s="22" t="n"/>
       <c r="S85" s="22" t="n"/>
       <c r="T85" s="22" t="n"/>
       <c r="U85" s="22" t="n"/>
@@ -9622,19 +8502,19 @@
       <c r="X85" s="22" t="n"/>
       <c r="Y85" s="22" t="n"/>
       <c r="Z85" s="22" t="n"/>
-      <c r="AA85" s="22" t="n"/>
-      <c r="AB85" s="22" t="n"/>
-      <c r="AC85" s="22" t="n"/>
+      <c r="AA85" s="26" t="n"/>
+      <c r="AB85" s="26" t="n"/>
+      <c r="AC85" s="26" t="n"/>
       <c r="AD85" s="30" t="inlineStr">
         <is>
           <t>sin iniciar</t>
         </is>
       </c>
     </row>
-    <row r="86" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A86" s="24" t="inlineStr">
-        <is>
-          <t>13.2 Menú y permisos</t>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>14. Comentarios, feedback y seguridad</t>
         </is>
       </c>
       <c r="B86" s="22" t="n"/>
@@ -9653,7 +8533,7 @@
       <c r="O86" s="22" t="n"/>
       <c r="P86" s="22" t="n"/>
       <c r="Q86" s="22" t="n"/>
-      <c r="R86" s="27" t="n"/>
+      <c r="R86" s="22" t="n"/>
       <c r="S86" s="22" t="n"/>
       <c r="T86" s="22" t="n"/>
       <c r="U86" s="22" t="n"/>
@@ -9674,7 +8554,7 @@
     <row r="87" outlineLevel="1" ht="14" customHeight="1">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>13.3 Listados del panel</t>
+          <t>14.1 Comentarios de actividad</t>
         </is>
       </c>
       <c r="B87" s="22" t="n"/>
@@ -9693,7 +8573,7 @@
       <c r="O87" s="22" t="n"/>
       <c r="P87" s="22" t="n"/>
       <c r="Q87" s="22" t="n"/>
-      <c r="R87" s="28" t="n"/>
+      <c r="R87" s="22" t="n"/>
       <c r="S87" s="22" t="n"/>
       <c r="T87" s="22" t="n"/>
       <c r="U87" s="22" t="n"/>
@@ -9714,7 +8594,7 @@
     <row r="88" outlineLevel="1" ht="14" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
         <is>
-          <t>13.4 Testeo</t>
+          <t>14.2 Respuesta de contacto → remitente</t>
         </is>
       </c>
       <c r="B88" s="22" t="n"/>
@@ -9733,8 +8613,8 @@
       <c r="O88" s="22" t="n"/>
       <c r="P88" s="22" t="n"/>
       <c r="Q88" s="22" t="n"/>
-      <c r="R88" s="21" t="n"/>
-      <c r="S88" s="21" t="n"/>
+      <c r="R88" s="22" t="n"/>
+      <c r="S88" s="22" t="n"/>
       <c r="T88" s="22" t="n"/>
       <c r="U88" s="22" t="n"/>
       <c r="V88" s="22" t="n"/>
@@ -9754,7 +8634,7 @@
     <row r="89" outlineLevel="1" ht="14" customHeight="1">
       <c r="A89" s="24" t="inlineStr">
         <is>
-          <t>13.5 Documentación</t>
+          <t>14.3 Configuración de seguridad</t>
         </is>
       </c>
       <c r="B89" s="22" t="n"/>
@@ -9773,8 +8653,8 @@
       <c r="O89" s="22" t="n"/>
       <c r="P89" s="22" t="n"/>
       <c r="Q89" s="22" t="n"/>
-      <c r="R89" s="25" t="n"/>
-      <c r="S89" s="25" t="n"/>
+      <c r="R89" s="22" t="n"/>
+      <c r="S89" s="22" t="n"/>
       <c r="T89" s="22" t="n"/>
       <c r="U89" s="22" t="n"/>
       <c r="V89" s="22" t="n"/>
@@ -9791,10 +8671,10 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="14" customHeight="1">
-      <c r="A90" s="20" t="inlineStr">
-        <is>
-          <t>14. Gestión de clientes</t>
+    <row r="90" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>14.4 Testeo</t>
         </is>
       </c>
       <c r="B90" s="22" t="n"/>
@@ -9815,10 +8695,10 @@
       <c r="Q90" s="22" t="n"/>
       <c r="R90" s="22" t="n"/>
       <c r="S90" s="22" t="n"/>
-      <c r="T90" s="26" t="n"/>
-      <c r="U90" s="26" t="n"/>
-      <c r="V90" s="26" t="n"/>
-      <c r="W90" s="26" t="n"/>
+      <c r="T90" s="22" t="n"/>
+      <c r="U90" s="22" t="n"/>
+      <c r="V90" s="22" t="n"/>
+      <c r="W90" s="22" t="n"/>
       <c r="X90" s="22" t="n"/>
       <c r="Y90" s="22" t="n"/>
       <c r="Z90" s="22" t="n"/>
@@ -9834,7 +8714,7 @@
     <row r="91" outlineLevel="1" ht="14" customHeight="1">
       <c r="A91" s="24" t="inlineStr">
         <is>
-          <t>14.1 Listado de clientes</t>
+          <t>14.5 Documentación</t>
         </is>
       </c>
       <c r="B91" s="22" t="n"/>
@@ -9855,7 +8735,7 @@
       <c r="Q91" s="22" t="n"/>
       <c r="R91" s="22" t="n"/>
       <c r="S91" s="22" t="n"/>
-      <c r="T91" s="27" t="n"/>
+      <c r="T91" s="22" t="n"/>
       <c r="U91" s="22" t="n"/>
       <c r="V91" s="22" t="n"/>
       <c r="W91" s="22" t="n"/>
@@ -9871,50 +8751,50 @@
         </is>
       </c>
     </row>
-    <row r="92" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A92" s="24" t="inlineStr">
-        <is>
-          <t>14.2 Ficha del cliente</t>
-        </is>
-      </c>
-      <c r="B92" s="22" t="n"/>
-      <c r="C92" s="22" t="n"/>
-      <c r="D92" s="22" t="n"/>
-      <c r="E92" s="22" t="n"/>
-      <c r="F92" s="22" t="n"/>
-      <c r="G92" s="22" t="n"/>
-      <c r="H92" s="22" t="n"/>
-      <c r="I92" s="22" t="n"/>
-      <c r="J92" s="22" t="n"/>
-      <c r="K92" s="22" t="n"/>
-      <c r="L92" s="22" t="n"/>
-      <c r="M92" s="22" t="n"/>
-      <c r="N92" s="22" t="n"/>
-      <c r="O92" s="22" t="n"/>
-      <c r="P92" s="22" t="n"/>
-      <c r="Q92" s="22" t="n"/>
-      <c r="R92" s="22" t="n"/>
-      <c r="S92" s="22" t="n"/>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>15. Interfaz Tailwind, correo y cierre</t>
+        </is>
+      </c>
+      <c r="B92" s="28" t="n"/>
+      <c r="C92" s="28" t="n"/>
+      <c r="D92" s="28" t="n"/>
+      <c r="E92" s="28" t="n"/>
+      <c r="F92" s="28" t="n"/>
+      <c r="G92" s="28" t="n"/>
+      <c r="H92" s="28" t="n"/>
+      <c r="I92" s="28" t="n"/>
+      <c r="J92" s="28" t="n"/>
+      <c r="K92" s="28" t="n"/>
+      <c r="L92" s="28" t="n"/>
+      <c r="M92" s="28" t="n"/>
+      <c r="N92" s="28" t="n"/>
+      <c r="O92" s="28" t="n"/>
+      <c r="P92" s="28" t="n"/>
+      <c r="Q92" s="28" t="n"/>
+      <c r="R92" s="28" t="n"/>
+      <c r="S92" s="28" t="n"/>
       <c r="T92" s="28" t="n"/>
-      <c r="U92" s="22" t="n"/>
-      <c r="V92" s="22" t="n"/>
-      <c r="W92" s="22" t="n"/>
-      <c r="X92" s="22" t="n"/>
-      <c r="Y92" s="22" t="n"/>
-      <c r="Z92" s="22" t="n"/>
-      <c r="AA92" s="22" t="n"/>
-      <c r="AB92" s="22" t="n"/>
-      <c r="AC92" s="22" t="n"/>
-      <c r="AD92" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="U92" s="28" t="n"/>
+      <c r="V92" s="28" t="n"/>
+      <c r="W92" s="28" t="n"/>
+      <c r="X92" s="28" t="n"/>
+      <c r="Y92" s="28" t="n"/>
+      <c r="Z92" s="28" t="n"/>
+      <c r="AA92" s="28" t="n"/>
+      <c r="AB92" s="28" t="n"/>
+      <c r="AC92" s="28" t="n"/>
+      <c r="AD92" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="93" outlineLevel="1" ht="14" customHeight="1">
       <c r="A93" s="24" t="inlineStr">
         <is>
-          <t>14.3 Edición de datos</t>
+          <t>15.1 Transiciones del front</t>
         </is>
       </c>
       <c r="B93" s="22" t="n"/>
@@ -9935,7 +8815,7 @@
       <c r="Q93" s="22" t="n"/>
       <c r="R93" s="22" t="n"/>
       <c r="S93" s="22" t="n"/>
-      <c r="T93" s="21" t="n"/>
+      <c r="T93" s="22" t="n"/>
       <c r="U93" s="22" t="n"/>
       <c r="V93" s="22" t="n"/>
       <c r="W93" s="22" t="n"/>
@@ -9945,16 +8825,16 @@
       <c r="AA93" s="22" t="n"/>
       <c r="AB93" s="22" t="n"/>
       <c r="AC93" s="22" t="n"/>
-      <c r="AD93" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD93" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="94" outlineLevel="1" ht="14" customHeight="1">
       <c r="A94" s="24" t="inlineStr">
         <is>
-          <t>14.4 Testeo</t>
+          <t>15.2 Correos ya en funcionamiento</t>
         </is>
       </c>
       <c r="B94" s="22" t="n"/>
@@ -9975,10 +8855,10 @@
       <c r="Q94" s="22" t="n"/>
       <c r="R94" s="22" t="n"/>
       <c r="S94" s="22" t="n"/>
-      <c r="T94" s="25" t="n"/>
-      <c r="U94" s="25" t="n"/>
-      <c r="V94" s="25" t="n"/>
-      <c r="W94" s="25" t="n"/>
+      <c r="T94" s="22" t="n"/>
+      <c r="U94" s="22" t="n"/>
+      <c r="V94" s="22" t="n"/>
+      <c r="W94" s="22" t="n"/>
       <c r="X94" s="22" t="n"/>
       <c r="Y94" s="22" t="n"/>
       <c r="Z94" s="22" t="n"/>
@@ -9994,7 +8874,7 @@
     <row r="95" outlineLevel="1" ht="14" customHeight="1">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>14.5 Documentación</t>
+          <t>15.3 Cierre y revisión</t>
         </is>
       </c>
       <c r="B95" s="22" t="n"/>
@@ -10015,10 +8895,10 @@
       <c r="Q95" s="22" t="n"/>
       <c r="R95" s="22" t="n"/>
       <c r="S95" s="22" t="n"/>
-      <c r="T95" s="26" t="n"/>
-      <c r="U95" s="26" t="n"/>
-      <c r="V95" s="26" t="n"/>
-      <c r="W95" s="26" t="n"/>
+      <c r="T95" s="22" t="n"/>
+      <c r="U95" s="22" t="n"/>
+      <c r="V95" s="22" t="n"/>
+      <c r="W95" s="22" t="n"/>
       <c r="X95" s="22" t="n"/>
       <c r="Y95" s="22" t="n"/>
       <c r="Z95" s="22" t="n"/>
@@ -10031,92 +8911,88 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="14" customHeight="1">
-      <c r="A96" s="20" t="inlineStr">
-        <is>
-          <t>15. Monitores y solicitudes</t>
-        </is>
-      </c>
-      <c r="B96" s="22" t="n"/>
-      <c r="C96" s="22" t="n"/>
-      <c r="D96" s="22" t="n"/>
-      <c r="E96" s="22" t="n"/>
-      <c r="F96" s="22" t="n"/>
-      <c r="G96" s="22" t="n"/>
-      <c r="H96" s="22" t="n"/>
-      <c r="I96" s="22" t="n"/>
-      <c r="J96" s="22" t="n"/>
-      <c r="K96" s="22" t="n"/>
-      <c r="L96" s="22" t="n"/>
-      <c r="M96" s="22" t="n"/>
-      <c r="N96" s="22" t="n"/>
-      <c r="O96" s="22" t="n"/>
-      <c r="P96" s="22" t="n"/>
-      <c r="Q96" s="22" t="n"/>
-      <c r="R96" s="22" t="n"/>
-      <c r="S96" s="22" t="n"/>
-      <c r="T96" s="22" t="n"/>
-      <c r="U96" s="22" t="n"/>
-      <c r="V96" s="22" t="n"/>
-      <c r="W96" s="22" t="n"/>
+    <row r="96" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>15.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B96" s="27" t="n"/>
+      <c r="C96" s="27" t="n"/>
+      <c r="D96" s="27" t="n"/>
+      <c r="E96" s="27" t="n"/>
+      <c r="F96" s="27" t="n"/>
+      <c r="G96" s="27" t="n"/>
+      <c r="H96" s="27" t="n"/>
+      <c r="I96" s="27" t="n"/>
+      <c r="J96" s="27" t="n"/>
+      <c r="K96" s="27" t="n"/>
+      <c r="L96" s="27" t="n"/>
+      <c r="M96" s="27" t="n"/>
+      <c r="N96" s="27" t="n"/>
+      <c r="O96" s="27" t="n"/>
+      <c r="P96" s="27" t="n"/>
+      <c r="Q96" s="27" t="n"/>
+      <c r="R96" s="27" t="n"/>
+      <c r="S96" s="27" t="n"/>
+      <c r="T96" s="27" t="n"/>
+      <c r="U96" s="27" t="n"/>
+      <c r="V96" s="27" t="n"/>
+      <c r="W96" s="27" t="n"/>
       <c r="X96" s="27" t="n"/>
       <c r="Y96" s="27" t="n"/>
       <c r="Z96" s="27" t="n"/>
-      <c r="AA96" s="22" t="n"/>
-      <c r="AB96" s="22" t="n"/>
-      <c r="AC96" s="22" t="n"/>
-      <c r="AD96" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AA96" s="27" t="n"/>
+      <c r="AB96" s="27" t="n"/>
+      <c r="AC96" s="27" t="n"/>
+      <c r="AD96" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="97" outlineLevel="1" ht="14" customHeight="1">
       <c r="A97" s="24" t="inlineStr">
         <is>
-          <t>15.1 Alta de monitores</t>
-        </is>
-      </c>
-      <c r="B97" s="22" t="n"/>
-      <c r="C97" s="22" t="n"/>
-      <c r="D97" s="22" t="n"/>
-      <c r="E97" s="22" t="n"/>
-      <c r="F97" s="22" t="n"/>
-      <c r="G97" s="22" t="n"/>
-      <c r="H97" s="22" t="n"/>
-      <c r="I97" s="22" t="n"/>
-      <c r="J97" s="22" t="n"/>
-      <c r="K97" s="22" t="n"/>
-      <c r="L97" s="22" t="n"/>
-      <c r="M97" s="22" t="n"/>
-      <c r="N97" s="22" t="n"/>
-      <c r="O97" s="22" t="n"/>
-      <c r="P97" s="22" t="n"/>
-      <c r="Q97" s="22" t="n"/>
-      <c r="R97" s="22" t="n"/>
-      <c r="S97" s="22" t="n"/>
-      <c r="T97" s="22" t="n"/>
-      <c r="U97" s="22" t="n"/>
-      <c r="V97" s="22" t="n"/>
-      <c r="W97" s="22" t="n"/>
+          <t>15.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B97" s="28" t="n"/>
+      <c r="C97" s="28" t="n"/>
+      <c r="D97" s="28" t="n"/>
+      <c r="E97" s="28" t="n"/>
+      <c r="F97" s="28" t="n"/>
+      <c r="G97" s="28" t="n"/>
+      <c r="H97" s="28" t="n"/>
+      <c r="I97" s="28" t="n"/>
+      <c r="J97" s="28" t="n"/>
+      <c r="K97" s="28" t="n"/>
+      <c r="L97" s="28" t="n"/>
+      <c r="M97" s="28" t="n"/>
+      <c r="N97" s="28" t="n"/>
+      <c r="O97" s="28" t="n"/>
+      <c r="P97" s="28" t="n"/>
+      <c r="Q97" s="28" t="n"/>
+      <c r="R97" s="28" t="n"/>
+      <c r="S97" s="28" t="n"/>
+      <c r="T97" s="28" t="n"/>
+      <c r="U97" s="28" t="n"/>
+      <c r="V97" s="28" t="n"/>
+      <c r="W97" s="28" t="n"/>
       <c r="X97" s="28" t="n"/>
-      <c r="Y97" s="22" t="n"/>
-      <c r="Z97" s="22" t="n"/>
-      <c r="AA97" s="22" t="n"/>
-      <c r="AB97" s="22" t="n"/>
-      <c r="AC97" s="22" t="n"/>
-      <c r="AD97" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A98" s="24" t="inlineStr">
-        <is>
-          <t>15.2 Solicitudes de clase</t>
-        </is>
-      </c>
+      <c r="Y97" s="28" t="n"/>
+      <c r="Z97" s="28" t="n"/>
+      <c r="AA97" s="28" t="n"/>
+      <c r="AB97" s="28" t="n"/>
+      <c r="AC97" s="28" t="n"/>
+      <c r="AD97" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="22" t="n"/>
       <c r="B98" s="22" t="n"/>
       <c r="C98" s="22" t="n"/>
       <c r="D98" s="22" t="n"/>
@@ -10140,23 +9016,15 @@
       <c r="V98" s="22" t="n"/>
       <c r="W98" s="22" t="n"/>
       <c r="X98" s="22" t="n"/>
-      <c r="Y98" s="21" t="n"/>
+      <c r="Y98" s="22" t="n"/>
       <c r="Z98" s="22" t="n"/>
       <c r="AA98" s="22" t="n"/>
       <c r="AB98" s="22" t="n"/>
       <c r="AC98" s="22" t="n"/>
-      <c r="AD98" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A99" s="24" t="inlineStr">
-        <is>
-          <t>15.3 Aprobación y rechazo</t>
-        </is>
-      </c>
+      <c r="AD98" s="22" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="22" t="n"/>
       <c r="B99" s="22" t="n"/>
       <c r="C99" s="22" t="n"/>
       <c r="D99" s="22" t="n"/>
@@ -10180,23 +9048,15 @@
       <c r="V99" s="22" t="n"/>
       <c r="W99" s="22" t="n"/>
       <c r="X99" s="22" t="n"/>
-      <c r="Y99" s="25" t="n"/>
+      <c r="Y99" s="22" t="n"/>
       <c r="Z99" s="22" t="n"/>
       <c r="AA99" s="22" t="n"/>
       <c r="AB99" s="22" t="n"/>
       <c r="AC99" s="22" t="n"/>
-      <c r="AD99" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A100" s="24" t="inlineStr">
-        <is>
-          <t>15.4 Testeo</t>
-        </is>
-      </c>
+      <c r="AD99" s="22" t="n"/>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="22" t="n"/>
       <c r="B100" s="22" t="n"/>
       <c r="C100" s="22" t="n"/>
       <c r="D100" s="22" t="n"/>
@@ -10219,24 +9079,16 @@
       <c r="U100" s="22" t="n"/>
       <c r="V100" s="22" t="n"/>
       <c r="W100" s="22" t="n"/>
-      <c r="X100" s="26" t="n"/>
-      <c r="Y100" s="26" t="n"/>
-      <c r="Z100" s="26" t="n"/>
+      <c r="X100" s="22" t="n"/>
+      <c r="Y100" s="22" t="n"/>
+      <c r="Z100" s="22" t="n"/>
       <c r="AA100" s="22" t="n"/>
       <c r="AB100" s="22" t="n"/>
       <c r="AC100" s="22" t="n"/>
-      <c r="AD100" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A101" s="24" t="inlineStr">
-        <is>
-          <t>15.5 Documentación</t>
-        </is>
-      </c>
+      <c r="AD100" s="22" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="22" t="n"/>
       <c r="B101" s="22" t="n"/>
       <c r="C101" s="22" t="n"/>
       <c r="D101" s="22" t="n"/>
@@ -10259,1105 +9111,13 @@
       <c r="U101" s="22" t="n"/>
       <c r="V101" s="22" t="n"/>
       <c r="W101" s="22" t="n"/>
-      <c r="X101" s="27" t="n"/>
-      <c r="Y101" s="27" t="n"/>
-      <c r="Z101" s="27" t="n"/>
+      <c r="X101" s="22" t="n"/>
+      <c r="Y101" s="22" t="n"/>
+      <c r="Z101" s="22" t="n"/>
       <c r="AA101" s="22" t="n"/>
       <c r="AB101" s="22" t="n"/>
       <c r="AC101" s="22" t="n"/>
-      <c r="AD101" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="14" customHeight="1">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>16. Salas y materiales</t>
-        </is>
-      </c>
-      <c r="B102" s="22" t="n"/>
-      <c r="C102" s="22" t="n"/>
-      <c r="D102" s="22" t="n"/>
-      <c r="E102" s="22" t="n"/>
-      <c r="F102" s="22" t="n"/>
-      <c r="G102" s="22" t="n"/>
-      <c r="H102" s="22" t="n"/>
-      <c r="I102" s="22" t="n"/>
-      <c r="J102" s="22" t="n"/>
-      <c r="K102" s="22" t="n"/>
-      <c r="L102" s="22" t="n"/>
-      <c r="M102" s="22" t="n"/>
-      <c r="N102" s="22" t="n"/>
-      <c r="O102" s="22" t="n"/>
-      <c r="P102" s="22" t="n"/>
-      <c r="Q102" s="22" t="n"/>
-      <c r="R102" s="22" t="n"/>
-      <c r="S102" s="22" t="n"/>
-      <c r="T102" s="22" t="n"/>
-      <c r="U102" s="22" t="n"/>
-      <c r="V102" s="22" t="n"/>
-      <c r="W102" s="22" t="n"/>
-      <c r="X102" s="22" t="n"/>
-      <c r="Y102" s="22" t="n"/>
-      <c r="Z102" s="22" t="n"/>
-      <c r="AA102" s="28" t="n"/>
-      <c r="AB102" s="28" t="n"/>
-      <c r="AC102" s="28" t="n"/>
-      <c r="AD102" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A103" s="24" t="inlineStr">
-        <is>
-          <t>16.1 Ficha de salas</t>
-        </is>
-      </c>
-      <c r="B103" s="22" t="n"/>
-      <c r="C103" s="22" t="n"/>
-      <c r="D103" s="22" t="n"/>
-      <c r="E103" s="22" t="n"/>
-      <c r="F103" s="22" t="n"/>
-      <c r="G103" s="22" t="n"/>
-      <c r="H103" s="22" t="n"/>
-      <c r="I103" s="22" t="n"/>
-      <c r="J103" s="22" t="n"/>
-      <c r="K103" s="22" t="n"/>
-      <c r="L103" s="22" t="n"/>
-      <c r="M103" s="22" t="n"/>
-      <c r="N103" s="22" t="n"/>
-      <c r="O103" s="22" t="n"/>
-      <c r="P103" s="22" t="n"/>
-      <c r="Q103" s="22" t="n"/>
-      <c r="R103" s="22" t="n"/>
-      <c r="S103" s="22" t="n"/>
-      <c r="T103" s="22" t="n"/>
-      <c r="U103" s="22" t="n"/>
-      <c r="V103" s="22" t="n"/>
-      <c r="W103" s="22" t="n"/>
-      <c r="X103" s="22" t="n"/>
-      <c r="Y103" s="22" t="n"/>
-      <c r="Z103" s="22" t="n"/>
-      <c r="AA103" s="21" t="n"/>
-      <c r="AB103" s="22" t="n"/>
-      <c r="AC103" s="22" t="n"/>
-      <c r="AD103" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A104" s="24" t="inlineStr">
-        <is>
-          <t>16.2 Inventario de materiales</t>
-        </is>
-      </c>
-      <c r="B104" s="22" t="n"/>
-      <c r="C104" s="22" t="n"/>
-      <c r="D104" s="22" t="n"/>
-      <c r="E104" s="22" t="n"/>
-      <c r="F104" s="22" t="n"/>
-      <c r="G104" s="22" t="n"/>
-      <c r="H104" s="22" t="n"/>
-      <c r="I104" s="22" t="n"/>
-      <c r="J104" s="22" t="n"/>
-      <c r="K104" s="22" t="n"/>
-      <c r="L104" s="22" t="n"/>
-      <c r="M104" s="22" t="n"/>
-      <c r="N104" s="22" t="n"/>
-      <c r="O104" s="22" t="n"/>
-      <c r="P104" s="22" t="n"/>
-      <c r="Q104" s="22" t="n"/>
-      <c r="R104" s="22" t="n"/>
-      <c r="S104" s="22" t="n"/>
-      <c r="T104" s="22" t="n"/>
-      <c r="U104" s="22" t="n"/>
-      <c r="V104" s="22" t="n"/>
-      <c r="W104" s="22" t="n"/>
-      <c r="X104" s="22" t="n"/>
-      <c r="Y104" s="22" t="n"/>
-      <c r="Z104" s="22" t="n"/>
-      <c r="AA104" s="25" t="n"/>
-      <c r="AB104" s="22" t="n"/>
-      <c r="AC104" s="22" t="n"/>
-      <c r="AD104" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A105" s="24" t="inlineStr">
-        <is>
-          <t>16.3 Alta y edición</t>
-        </is>
-      </c>
-      <c r="B105" s="22" t="n"/>
-      <c r="C105" s="22" t="n"/>
-      <c r="D105" s="22" t="n"/>
-      <c r="E105" s="22" t="n"/>
-      <c r="F105" s="22" t="n"/>
-      <c r="G105" s="22" t="n"/>
-      <c r="H105" s="22" t="n"/>
-      <c r="I105" s="22" t="n"/>
-      <c r="J105" s="22" t="n"/>
-      <c r="K105" s="22" t="n"/>
-      <c r="L105" s="22" t="n"/>
-      <c r="M105" s="22" t="n"/>
-      <c r="N105" s="22" t="n"/>
-      <c r="O105" s="22" t="n"/>
-      <c r="P105" s="22" t="n"/>
-      <c r="Q105" s="22" t="n"/>
-      <c r="R105" s="22" t="n"/>
-      <c r="S105" s="22" t="n"/>
-      <c r="T105" s="22" t="n"/>
-      <c r="U105" s="22" t="n"/>
-      <c r="V105" s="22" t="n"/>
-      <c r="W105" s="22" t="n"/>
-      <c r="X105" s="22" t="n"/>
-      <c r="Y105" s="22" t="n"/>
-      <c r="Z105" s="22" t="n"/>
-      <c r="AA105" s="26" t="n"/>
-      <c r="AB105" s="22" t="n"/>
-      <c r="AC105" s="22" t="n"/>
-      <c r="AD105" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A106" s="24" t="inlineStr">
-        <is>
-          <t>16.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B106" s="22" t="n"/>
-      <c r="C106" s="22" t="n"/>
-      <c r="D106" s="22" t="n"/>
-      <c r="E106" s="22" t="n"/>
-      <c r="F106" s="22" t="n"/>
-      <c r="G106" s="22" t="n"/>
-      <c r="H106" s="22" t="n"/>
-      <c r="I106" s="22" t="n"/>
-      <c r="J106" s="22" t="n"/>
-      <c r="K106" s="22" t="n"/>
-      <c r="L106" s="22" t="n"/>
-      <c r="M106" s="22" t="n"/>
-      <c r="N106" s="22" t="n"/>
-      <c r="O106" s="22" t="n"/>
-      <c r="P106" s="22" t="n"/>
-      <c r="Q106" s="22" t="n"/>
-      <c r="R106" s="22" t="n"/>
-      <c r="S106" s="22" t="n"/>
-      <c r="T106" s="22" t="n"/>
-      <c r="U106" s="22" t="n"/>
-      <c r="V106" s="22" t="n"/>
-      <c r="W106" s="22" t="n"/>
-      <c r="X106" s="22" t="n"/>
-      <c r="Y106" s="22" t="n"/>
-      <c r="Z106" s="22" t="n"/>
-      <c r="AA106" s="27" t="n"/>
-      <c r="AB106" s="27" t="n"/>
-      <c r="AC106" s="27" t="n"/>
-      <c r="AD106" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A107" s="24" t="inlineStr">
-        <is>
-          <t>16.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B107" s="22" t="n"/>
-      <c r="C107" s="22" t="n"/>
-      <c r="D107" s="22" t="n"/>
-      <c r="E107" s="22" t="n"/>
-      <c r="F107" s="22" t="n"/>
-      <c r="G107" s="22" t="n"/>
-      <c r="H107" s="22" t="n"/>
-      <c r="I107" s="22" t="n"/>
-      <c r="J107" s="22" t="n"/>
-      <c r="K107" s="22" t="n"/>
-      <c r="L107" s="22" t="n"/>
-      <c r="M107" s="22" t="n"/>
-      <c r="N107" s="22" t="n"/>
-      <c r="O107" s="22" t="n"/>
-      <c r="P107" s="22" t="n"/>
-      <c r="Q107" s="22" t="n"/>
-      <c r="R107" s="22" t="n"/>
-      <c r="S107" s="22" t="n"/>
-      <c r="T107" s="22" t="n"/>
-      <c r="U107" s="22" t="n"/>
-      <c r="V107" s="22" t="n"/>
-      <c r="W107" s="22" t="n"/>
-      <c r="X107" s="22" t="n"/>
-      <c r="Y107" s="22" t="n"/>
-      <c r="Z107" s="22" t="n"/>
-      <c r="AA107" s="28" t="n"/>
-      <c r="AB107" s="28" t="n"/>
-      <c r="AC107" s="28" t="n"/>
-      <c r="AD107" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="14" customHeight="1">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>17. Fisioterapia y citas</t>
-        </is>
-      </c>
-      <c r="B108" s="22" t="n"/>
-      <c r="C108" s="22" t="n"/>
-      <c r="D108" s="22" t="n"/>
-      <c r="E108" s="22" t="n"/>
-      <c r="F108" s="22" t="n"/>
-      <c r="G108" s="22" t="n"/>
-      <c r="H108" s="22" t="n"/>
-      <c r="I108" s="22" t="n"/>
-      <c r="J108" s="22" t="n"/>
-      <c r="K108" s="22" t="n"/>
-      <c r="L108" s="22" t="n"/>
-      <c r="M108" s="22" t="n"/>
-      <c r="N108" s="22" t="n"/>
-      <c r="O108" s="22" t="n"/>
-      <c r="P108" s="22" t="n"/>
-      <c r="Q108" s="22" t="n"/>
-      <c r="R108" s="22" t="n"/>
-      <c r="S108" s="22" t="n"/>
-      <c r="T108" s="22" t="n"/>
-      <c r="U108" s="22" t="n"/>
-      <c r="V108" s="22" t="n"/>
-      <c r="W108" s="22" t="n"/>
-      <c r="X108" s="22" t="n"/>
-      <c r="Y108" s="22" t="n"/>
-      <c r="Z108" s="22" t="n"/>
-      <c r="AA108" s="22" t="n"/>
-      <c r="AB108" s="22" t="n"/>
-      <c r="AC108" s="22" t="n"/>
-      <c r="AD108" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A109" s="24" t="inlineStr">
-        <is>
-          <t>17.1 Solicitud de cita</t>
-        </is>
-      </c>
-      <c r="B109" s="22" t="n"/>
-      <c r="C109" s="22" t="n"/>
-      <c r="D109" s="22" t="n"/>
-      <c r="E109" s="22" t="n"/>
-      <c r="F109" s="22" t="n"/>
-      <c r="G109" s="22" t="n"/>
-      <c r="H109" s="22" t="n"/>
-      <c r="I109" s="22" t="n"/>
-      <c r="J109" s="22" t="n"/>
-      <c r="K109" s="22" t="n"/>
-      <c r="L109" s="22" t="n"/>
-      <c r="M109" s="22" t="n"/>
-      <c r="N109" s="22" t="n"/>
-      <c r="O109" s="22" t="n"/>
-      <c r="P109" s="22" t="n"/>
-      <c r="Q109" s="22" t="n"/>
-      <c r="R109" s="22" t="n"/>
-      <c r="S109" s="22" t="n"/>
-      <c r="T109" s="22" t="n"/>
-      <c r="U109" s="22" t="n"/>
-      <c r="V109" s="22" t="n"/>
-      <c r="W109" s="22" t="n"/>
-      <c r="X109" s="22" t="n"/>
-      <c r="Y109" s="22" t="n"/>
-      <c r="Z109" s="22" t="n"/>
-      <c r="AA109" s="22" t="n"/>
-      <c r="AB109" s="22" t="n"/>
-      <c r="AC109" s="22" t="n"/>
-      <c r="AD109" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A110" s="24" t="inlineStr">
-        <is>
-          <t>17.2 Agenda del fisioterapeuta</t>
-        </is>
-      </c>
-      <c r="B110" s="22" t="n"/>
-      <c r="C110" s="22" t="n"/>
-      <c r="D110" s="22" t="n"/>
-      <c r="E110" s="22" t="n"/>
-      <c r="F110" s="22" t="n"/>
-      <c r="G110" s="22" t="n"/>
-      <c r="H110" s="22" t="n"/>
-      <c r="I110" s="22" t="n"/>
-      <c r="J110" s="22" t="n"/>
-      <c r="K110" s="22" t="n"/>
-      <c r="L110" s="22" t="n"/>
-      <c r="M110" s="22" t="n"/>
-      <c r="N110" s="22" t="n"/>
-      <c r="O110" s="22" t="n"/>
-      <c r="P110" s="22" t="n"/>
-      <c r="Q110" s="22" t="n"/>
-      <c r="R110" s="22" t="n"/>
-      <c r="S110" s="22" t="n"/>
-      <c r="T110" s="22" t="n"/>
-      <c r="U110" s="22" t="n"/>
-      <c r="V110" s="22" t="n"/>
-      <c r="W110" s="22" t="n"/>
-      <c r="X110" s="22" t="n"/>
-      <c r="Y110" s="22" t="n"/>
-      <c r="Z110" s="22" t="n"/>
-      <c r="AA110" s="22" t="n"/>
-      <c r="AB110" s="22" t="n"/>
-      <c r="AC110" s="22" t="n"/>
-      <c r="AD110" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A111" s="24" t="inlineStr">
-        <is>
-          <t>17.3 Panel de citas</t>
-        </is>
-      </c>
-      <c r="B111" s="22" t="n"/>
-      <c r="C111" s="22" t="n"/>
-      <c r="D111" s="22" t="n"/>
-      <c r="E111" s="22" t="n"/>
-      <c r="F111" s="22" t="n"/>
-      <c r="G111" s="22" t="n"/>
-      <c r="H111" s="22" t="n"/>
-      <c r="I111" s="22" t="n"/>
-      <c r="J111" s="22" t="n"/>
-      <c r="K111" s="22" t="n"/>
-      <c r="L111" s="22" t="n"/>
-      <c r="M111" s="22" t="n"/>
-      <c r="N111" s="22" t="n"/>
-      <c r="O111" s="22" t="n"/>
-      <c r="P111" s="22" t="n"/>
-      <c r="Q111" s="22" t="n"/>
-      <c r="R111" s="22" t="n"/>
-      <c r="S111" s="22" t="n"/>
-      <c r="T111" s="22" t="n"/>
-      <c r="U111" s="22" t="n"/>
-      <c r="V111" s="22" t="n"/>
-      <c r="W111" s="22" t="n"/>
-      <c r="X111" s="22" t="n"/>
-      <c r="Y111" s="22" t="n"/>
-      <c r="Z111" s="22" t="n"/>
-      <c r="AA111" s="22" t="n"/>
-      <c r="AB111" s="22" t="n"/>
-      <c r="AC111" s="22" t="n"/>
-      <c r="AD111" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A112" s="24" t="inlineStr">
-        <is>
-          <t>17.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B112" s="22" t="n"/>
-      <c r="C112" s="22" t="n"/>
-      <c r="D112" s="22" t="n"/>
-      <c r="E112" s="22" t="n"/>
-      <c r="F112" s="22" t="n"/>
-      <c r="G112" s="22" t="n"/>
-      <c r="H112" s="22" t="n"/>
-      <c r="I112" s="22" t="n"/>
-      <c r="J112" s="22" t="n"/>
-      <c r="K112" s="22" t="n"/>
-      <c r="L112" s="22" t="n"/>
-      <c r="M112" s="22" t="n"/>
-      <c r="N112" s="22" t="n"/>
-      <c r="O112" s="22" t="n"/>
-      <c r="P112" s="22" t="n"/>
-      <c r="Q112" s="22" t="n"/>
-      <c r="R112" s="22" t="n"/>
-      <c r="S112" s="22" t="n"/>
-      <c r="T112" s="22" t="n"/>
-      <c r="U112" s="22" t="n"/>
-      <c r="V112" s="22" t="n"/>
-      <c r="W112" s="22" t="n"/>
-      <c r="X112" s="22" t="n"/>
-      <c r="Y112" s="22" t="n"/>
-      <c r="Z112" s="22" t="n"/>
-      <c r="AA112" s="22" t="n"/>
-      <c r="AB112" s="22" t="n"/>
-      <c r="AC112" s="22" t="n"/>
-      <c r="AD112" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A113" s="24" t="inlineStr">
-        <is>
-          <t>17.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B113" s="22" t="n"/>
-      <c r="C113" s="22" t="n"/>
-      <c r="D113" s="22" t="n"/>
-      <c r="E113" s="22" t="n"/>
-      <c r="F113" s="22" t="n"/>
-      <c r="G113" s="22" t="n"/>
-      <c r="H113" s="22" t="n"/>
-      <c r="I113" s="22" t="n"/>
-      <c r="J113" s="22" t="n"/>
-      <c r="K113" s="22" t="n"/>
-      <c r="L113" s="22" t="n"/>
-      <c r="M113" s="22" t="n"/>
-      <c r="N113" s="22" t="n"/>
-      <c r="O113" s="22" t="n"/>
-      <c r="P113" s="22" t="n"/>
-      <c r="Q113" s="22" t="n"/>
-      <c r="R113" s="22" t="n"/>
-      <c r="S113" s="22" t="n"/>
-      <c r="T113" s="22" t="n"/>
-      <c r="U113" s="22" t="n"/>
-      <c r="V113" s="22" t="n"/>
-      <c r="W113" s="22" t="n"/>
-      <c r="X113" s="22" t="n"/>
-      <c r="Y113" s="22" t="n"/>
-      <c r="Z113" s="22" t="n"/>
-      <c r="AA113" s="22" t="n"/>
-      <c r="AB113" s="22" t="n"/>
-      <c r="AC113" s="22" t="n"/>
-      <c r="AD113" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="14" customHeight="1">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>18. Comentarios, feedback y seguridad</t>
-        </is>
-      </c>
-      <c r="B114" s="22" t="n"/>
-      <c r="C114" s="22" t="n"/>
-      <c r="D114" s="22" t="n"/>
-      <c r="E114" s="22" t="n"/>
-      <c r="F114" s="22" t="n"/>
-      <c r="G114" s="22" t="n"/>
-      <c r="H114" s="22" t="n"/>
-      <c r="I114" s="22" t="n"/>
-      <c r="J114" s="22" t="n"/>
-      <c r="K114" s="22" t="n"/>
-      <c r="L114" s="22" t="n"/>
-      <c r="M114" s="22" t="n"/>
-      <c r="N114" s="22" t="n"/>
-      <c r="O114" s="22" t="n"/>
-      <c r="P114" s="22" t="n"/>
-      <c r="Q114" s="22" t="n"/>
-      <c r="R114" s="22" t="n"/>
-      <c r="S114" s="22" t="n"/>
-      <c r="T114" s="22" t="n"/>
-      <c r="U114" s="22" t="n"/>
-      <c r="V114" s="22" t="n"/>
-      <c r="W114" s="22" t="n"/>
-      <c r="X114" s="22" t="n"/>
-      <c r="Y114" s="22" t="n"/>
-      <c r="Z114" s="22" t="n"/>
-      <c r="AA114" s="22" t="n"/>
-      <c r="AB114" s="22" t="n"/>
-      <c r="AC114" s="22" t="n"/>
-      <c r="AD114" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A115" s="24" t="inlineStr">
-        <is>
-          <t>18.1 Comentarios de actividad</t>
-        </is>
-      </c>
-      <c r="B115" s="22" t="n"/>
-      <c r="C115" s="22" t="n"/>
-      <c r="D115" s="22" t="n"/>
-      <c r="E115" s="22" t="n"/>
-      <c r="F115" s="22" t="n"/>
-      <c r="G115" s="22" t="n"/>
-      <c r="H115" s="22" t="n"/>
-      <c r="I115" s="22" t="n"/>
-      <c r="J115" s="22" t="n"/>
-      <c r="K115" s="22" t="n"/>
-      <c r="L115" s="22" t="n"/>
-      <c r="M115" s="22" t="n"/>
-      <c r="N115" s="22" t="n"/>
-      <c r="O115" s="22" t="n"/>
-      <c r="P115" s="22" t="n"/>
-      <c r="Q115" s="22" t="n"/>
-      <c r="R115" s="22" t="n"/>
-      <c r="S115" s="22" t="n"/>
-      <c r="T115" s="22" t="n"/>
-      <c r="U115" s="22" t="n"/>
-      <c r="V115" s="22" t="n"/>
-      <c r="W115" s="22" t="n"/>
-      <c r="X115" s="22" t="n"/>
-      <c r="Y115" s="22" t="n"/>
-      <c r="Z115" s="22" t="n"/>
-      <c r="AA115" s="22" t="n"/>
-      <c r="AB115" s="22" t="n"/>
-      <c r="AC115" s="22" t="n"/>
-      <c r="AD115" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A116" s="24" t="inlineStr">
-        <is>
-          <t>18.2 Buzón de feedback</t>
-        </is>
-      </c>
-      <c r="B116" s="22" t="n"/>
-      <c r="C116" s="22" t="n"/>
-      <c r="D116" s="22" t="n"/>
-      <c r="E116" s="22" t="n"/>
-      <c r="F116" s="22" t="n"/>
-      <c r="G116" s="22" t="n"/>
-      <c r="H116" s="22" t="n"/>
-      <c r="I116" s="22" t="n"/>
-      <c r="J116" s="22" t="n"/>
-      <c r="K116" s="22" t="n"/>
-      <c r="L116" s="22" t="n"/>
-      <c r="M116" s="22" t="n"/>
-      <c r="N116" s="22" t="n"/>
-      <c r="O116" s="22" t="n"/>
-      <c r="P116" s="22" t="n"/>
-      <c r="Q116" s="22" t="n"/>
-      <c r="R116" s="22" t="n"/>
-      <c r="S116" s="22" t="n"/>
-      <c r="T116" s="22" t="n"/>
-      <c r="U116" s="22" t="n"/>
-      <c r="V116" s="22" t="n"/>
-      <c r="W116" s="22" t="n"/>
-      <c r="X116" s="22" t="n"/>
-      <c r="Y116" s="22" t="n"/>
-      <c r="Z116" s="22" t="n"/>
-      <c r="AA116" s="22" t="n"/>
-      <c r="AB116" s="22" t="n"/>
-      <c r="AC116" s="22" t="n"/>
-      <c r="AD116" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A117" s="24" t="inlineStr">
-        <is>
-          <t>18.3 Configuración de seguridad</t>
-        </is>
-      </c>
-      <c r="B117" s="22" t="n"/>
-      <c r="C117" s="22" t="n"/>
-      <c r="D117" s="22" t="n"/>
-      <c r="E117" s="22" t="n"/>
-      <c r="F117" s="22" t="n"/>
-      <c r="G117" s="22" t="n"/>
-      <c r="H117" s="22" t="n"/>
-      <c r="I117" s="22" t="n"/>
-      <c r="J117" s="22" t="n"/>
-      <c r="K117" s="22" t="n"/>
-      <c r="L117" s="22" t="n"/>
-      <c r="M117" s="22" t="n"/>
-      <c r="N117" s="22" t="n"/>
-      <c r="O117" s="22" t="n"/>
-      <c r="P117" s="22" t="n"/>
-      <c r="Q117" s="22" t="n"/>
-      <c r="R117" s="22" t="n"/>
-      <c r="S117" s="22" t="n"/>
-      <c r="T117" s="22" t="n"/>
-      <c r="U117" s="22" t="n"/>
-      <c r="V117" s="22" t="n"/>
-      <c r="W117" s="22" t="n"/>
-      <c r="X117" s="22" t="n"/>
-      <c r="Y117" s="22" t="n"/>
-      <c r="Z117" s="22" t="n"/>
-      <c r="AA117" s="22" t="n"/>
-      <c r="AB117" s="22" t="n"/>
-      <c r="AC117" s="22" t="n"/>
-      <c r="AD117" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A118" s="24" t="inlineStr">
-        <is>
-          <t>18.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B118" s="22" t="n"/>
-      <c r="C118" s="22" t="n"/>
-      <c r="D118" s="22" t="n"/>
-      <c r="E118" s="22" t="n"/>
-      <c r="F118" s="22" t="n"/>
-      <c r="G118" s="22" t="n"/>
-      <c r="H118" s="22" t="n"/>
-      <c r="I118" s="22" t="n"/>
-      <c r="J118" s="22" t="n"/>
-      <c r="K118" s="22" t="n"/>
-      <c r="L118" s="22" t="n"/>
-      <c r="M118" s="22" t="n"/>
-      <c r="N118" s="22" t="n"/>
-      <c r="O118" s="22" t="n"/>
-      <c r="P118" s="22" t="n"/>
-      <c r="Q118" s="22" t="n"/>
-      <c r="R118" s="22" t="n"/>
-      <c r="S118" s="22" t="n"/>
-      <c r="T118" s="22" t="n"/>
-      <c r="U118" s="22" t="n"/>
-      <c r="V118" s="22" t="n"/>
-      <c r="W118" s="22" t="n"/>
-      <c r="X118" s="22" t="n"/>
-      <c r="Y118" s="22" t="n"/>
-      <c r="Z118" s="22" t="n"/>
-      <c r="AA118" s="22" t="n"/>
-      <c r="AB118" s="22" t="n"/>
-      <c r="AC118" s="22" t="n"/>
-      <c r="AD118" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A119" s="24" t="inlineStr">
-        <is>
-          <t>18.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B119" s="22" t="n"/>
-      <c r="C119" s="22" t="n"/>
-      <c r="D119" s="22" t="n"/>
-      <c r="E119" s="22" t="n"/>
-      <c r="F119" s="22" t="n"/>
-      <c r="G119" s="22" t="n"/>
-      <c r="H119" s="22" t="n"/>
-      <c r="I119" s="22" t="n"/>
-      <c r="J119" s="22" t="n"/>
-      <c r="K119" s="22" t="n"/>
-      <c r="L119" s="22" t="n"/>
-      <c r="M119" s="22" t="n"/>
-      <c r="N119" s="22" t="n"/>
-      <c r="O119" s="22" t="n"/>
-      <c r="P119" s="22" t="n"/>
-      <c r="Q119" s="22" t="n"/>
-      <c r="R119" s="22" t="n"/>
-      <c r="S119" s="22" t="n"/>
-      <c r="T119" s="22" t="n"/>
-      <c r="U119" s="22" t="n"/>
-      <c r="V119" s="22" t="n"/>
-      <c r="W119" s="22" t="n"/>
-      <c r="X119" s="22" t="n"/>
-      <c r="Y119" s="22" t="n"/>
-      <c r="Z119" s="22" t="n"/>
-      <c r="AA119" s="22" t="n"/>
-      <c r="AB119" s="22" t="n"/>
-      <c r="AC119" s="22" t="n"/>
-      <c r="AD119" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="14" customHeight="1">
-      <c r="A120" s="20" t="inlineStr">
-        <is>
-          <t>19. Interfaz Tailwind y cierre</t>
-        </is>
-      </c>
-      <c r="B120" s="22" t="n"/>
-      <c r="C120" s="22" t="n"/>
-      <c r="D120" s="22" t="n"/>
-      <c r="E120" s="22" t="n"/>
-      <c r="F120" s="22" t="n"/>
-      <c r="G120" s="22" t="n"/>
-      <c r="H120" s="22" t="n"/>
-      <c r="I120" s="22" t="n"/>
-      <c r="J120" s="22" t="n"/>
-      <c r="K120" s="22" t="n"/>
-      <c r="L120" s="22" t="n"/>
-      <c r="M120" s="22" t="n"/>
-      <c r="N120" s="22" t="n"/>
-      <c r="O120" s="22" t="n"/>
-      <c r="P120" s="22" t="n"/>
-      <c r="Q120" s="22" t="n"/>
-      <c r="R120" s="22" t="n"/>
-      <c r="S120" s="22" t="n"/>
-      <c r="T120" s="22" t="n"/>
-      <c r="U120" s="22" t="n"/>
-      <c r="V120" s="22" t="n"/>
-      <c r="W120" s="22" t="n"/>
-      <c r="X120" s="22" t="n"/>
-      <c r="Y120" s="22" t="n"/>
-      <c r="Z120" s="22" t="n"/>
-      <c r="AA120" s="22" t="n"/>
-      <c r="AB120" s="22" t="n"/>
-      <c r="AC120" s="22" t="n"/>
-      <c r="AD120" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A121" s="24" t="inlineStr">
-        <is>
-          <t>19.1 Maquetación con Tailwind</t>
-        </is>
-      </c>
-      <c r="B121" s="22" t="n"/>
-      <c r="C121" s="22" t="n"/>
-      <c r="D121" s="22" t="n"/>
-      <c r="E121" s="22" t="n"/>
-      <c r="F121" s="22" t="n"/>
-      <c r="G121" s="22" t="n"/>
-      <c r="H121" s="22" t="n"/>
-      <c r="I121" s="22" t="n"/>
-      <c r="J121" s="22" t="n"/>
-      <c r="K121" s="22" t="n"/>
-      <c r="L121" s="22" t="n"/>
-      <c r="M121" s="22" t="n"/>
-      <c r="N121" s="22" t="n"/>
-      <c r="O121" s="22" t="n"/>
-      <c r="P121" s="22" t="n"/>
-      <c r="Q121" s="22" t="n"/>
-      <c r="R121" s="22" t="n"/>
-      <c r="S121" s="22" t="n"/>
-      <c r="T121" s="22" t="n"/>
-      <c r="U121" s="22" t="n"/>
-      <c r="V121" s="22" t="n"/>
-      <c r="W121" s="22" t="n"/>
-      <c r="X121" s="22" t="n"/>
-      <c r="Y121" s="22" t="n"/>
-      <c r="Z121" s="22" t="n"/>
-      <c r="AA121" s="22" t="n"/>
-      <c r="AB121" s="22" t="n"/>
-      <c r="AC121" s="22" t="n"/>
-      <c r="AD121" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A122" s="24" t="inlineStr">
-        <is>
-          <t>19.2 Revisión visual</t>
-        </is>
-      </c>
-      <c r="B122" s="22" t="n"/>
-      <c r="C122" s="22" t="n"/>
-      <c r="D122" s="22" t="n"/>
-      <c r="E122" s="22" t="n"/>
-      <c r="F122" s="22" t="n"/>
-      <c r="G122" s="22" t="n"/>
-      <c r="H122" s="22" t="n"/>
-      <c r="I122" s="22" t="n"/>
-      <c r="J122" s="22" t="n"/>
-      <c r="K122" s="22" t="n"/>
-      <c r="L122" s="22" t="n"/>
-      <c r="M122" s="22" t="n"/>
-      <c r="N122" s="22" t="n"/>
-      <c r="O122" s="22" t="n"/>
-      <c r="P122" s="22" t="n"/>
-      <c r="Q122" s="22" t="n"/>
-      <c r="R122" s="22" t="n"/>
-      <c r="S122" s="22" t="n"/>
-      <c r="T122" s="22" t="n"/>
-      <c r="U122" s="22" t="n"/>
-      <c r="V122" s="22" t="n"/>
-      <c r="W122" s="22" t="n"/>
-      <c r="X122" s="22" t="n"/>
-      <c r="Y122" s="22" t="n"/>
-      <c r="Z122" s="22" t="n"/>
-      <c r="AA122" s="22" t="n"/>
-      <c r="AB122" s="22" t="n"/>
-      <c r="AC122" s="22" t="n"/>
-      <c r="AD122" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A123" s="24" t="inlineStr">
-        <is>
-          <t>19.3 Cierre y revisión</t>
-        </is>
-      </c>
-      <c r="B123" s="22" t="n"/>
-      <c r="C123" s="22" t="n"/>
-      <c r="D123" s="22" t="n"/>
-      <c r="E123" s="22" t="n"/>
-      <c r="F123" s="22" t="n"/>
-      <c r="G123" s="22" t="n"/>
-      <c r="H123" s="22" t="n"/>
-      <c r="I123" s="22" t="n"/>
-      <c r="J123" s="22" t="n"/>
-      <c r="K123" s="22" t="n"/>
-      <c r="L123" s="22" t="n"/>
-      <c r="M123" s="22" t="n"/>
-      <c r="N123" s="22" t="n"/>
-      <c r="O123" s="22" t="n"/>
-      <c r="P123" s="22" t="n"/>
-      <c r="Q123" s="22" t="n"/>
-      <c r="R123" s="22" t="n"/>
-      <c r="S123" s="22" t="n"/>
-      <c r="T123" s="22" t="n"/>
-      <c r="U123" s="22" t="n"/>
-      <c r="V123" s="22" t="n"/>
-      <c r="W123" s="22" t="n"/>
-      <c r="X123" s="22" t="n"/>
-      <c r="Y123" s="22" t="n"/>
-      <c r="Z123" s="22" t="n"/>
-      <c r="AA123" s="22" t="n"/>
-      <c r="AB123" s="22" t="n"/>
-      <c r="AC123" s="22" t="n"/>
-      <c r="AD123" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A124" s="24" t="inlineStr">
-        <is>
-          <t>19.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B124" s="22" t="n"/>
-      <c r="C124" s="22" t="n"/>
-      <c r="D124" s="22" t="n"/>
-      <c r="E124" s="22" t="n"/>
-      <c r="F124" s="22" t="n"/>
-      <c r="G124" s="22" t="n"/>
-      <c r="H124" s="22" t="n"/>
-      <c r="I124" s="22" t="n"/>
-      <c r="J124" s="22" t="n"/>
-      <c r="K124" s="22" t="n"/>
-      <c r="L124" s="22" t="n"/>
-      <c r="M124" s="22" t="n"/>
-      <c r="N124" s="22" t="n"/>
-      <c r="O124" s="22" t="n"/>
-      <c r="P124" s="22" t="n"/>
-      <c r="Q124" s="22" t="n"/>
-      <c r="R124" s="22" t="n"/>
-      <c r="S124" s="22" t="n"/>
-      <c r="T124" s="22" t="n"/>
-      <c r="U124" s="22" t="n"/>
-      <c r="V124" s="22" t="n"/>
-      <c r="W124" s="22" t="n"/>
-      <c r="X124" s="22" t="n"/>
-      <c r="Y124" s="22" t="n"/>
-      <c r="Z124" s="22" t="n"/>
-      <c r="AA124" s="22" t="n"/>
-      <c r="AB124" s="22" t="n"/>
-      <c r="AC124" s="22" t="n"/>
-      <c r="AD124" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A125" s="24" t="inlineStr">
-        <is>
-          <t>19.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B125" s="22" t="n"/>
-      <c r="C125" s="22" t="n"/>
-      <c r="D125" s="22" t="n"/>
-      <c r="E125" s="22" t="n"/>
-      <c r="F125" s="22" t="n"/>
-      <c r="G125" s="22" t="n"/>
-      <c r="H125" s="22" t="n"/>
-      <c r="I125" s="22" t="n"/>
-      <c r="J125" s="22" t="n"/>
-      <c r="K125" s="22" t="n"/>
-      <c r="L125" s="22" t="n"/>
-      <c r="M125" s="22" t="n"/>
-      <c r="N125" s="22" t="n"/>
-      <c r="O125" s="22" t="n"/>
-      <c r="P125" s="22" t="n"/>
-      <c r="Q125" s="22" t="n"/>
-      <c r="R125" s="22" t="n"/>
-      <c r="S125" s="22" t="n"/>
-      <c r="T125" s="22" t="n"/>
-      <c r="U125" s="22" t="n"/>
-      <c r="V125" s="22" t="n"/>
-      <c r="W125" s="22" t="n"/>
-      <c r="X125" s="22" t="n"/>
-      <c r="Y125" s="22" t="n"/>
-      <c r="Z125" s="22" t="n"/>
-      <c r="AA125" s="22" t="n"/>
-      <c r="AB125" s="22" t="n"/>
-      <c r="AC125" s="22" t="n"/>
-      <c r="AD125" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="22" t="n"/>
-      <c r="B126" s="22" t="n"/>
-      <c r="C126" s="22" t="n"/>
-      <c r="D126" s="22" t="n"/>
-      <c r="E126" s="22" t="n"/>
-      <c r="F126" s="22" t="n"/>
-      <c r="G126" s="22" t="n"/>
-      <c r="H126" s="22" t="n"/>
-      <c r="I126" s="22" t="n"/>
-      <c r="J126" s="22" t="n"/>
-      <c r="K126" s="22" t="n"/>
-      <c r="L126" s="22" t="n"/>
-      <c r="M126" s="22" t="n"/>
-      <c r="N126" s="22" t="n"/>
-      <c r="O126" s="22" t="n"/>
-      <c r="P126" s="22" t="n"/>
-      <c r="Q126" s="22" t="n"/>
-      <c r="R126" s="22" t="n"/>
-      <c r="S126" s="22" t="n"/>
-      <c r="T126" s="22" t="n"/>
-      <c r="U126" s="22" t="n"/>
-      <c r="V126" s="22" t="n"/>
-      <c r="W126" s="22" t="n"/>
-      <c r="X126" s="22" t="n"/>
-      <c r="Y126" s="22" t="n"/>
-      <c r="Z126" s="22" t="n"/>
-      <c r="AA126" s="22" t="n"/>
-      <c r="AB126" s="22" t="n"/>
-      <c r="AC126" s="22" t="n"/>
-      <c r="AD126" s="22" t="n"/>
-    </row>
-    <row r="127" ht="14" customHeight="1">
-      <c r="A127" s="22" t="n"/>
-      <c r="B127" s="22" t="n"/>
-      <c r="C127" s="22" t="n"/>
-      <c r="D127" s="22" t="n"/>
-      <c r="E127" s="22" t="n"/>
-      <c r="F127" s="22" t="n"/>
-      <c r="G127" s="22" t="n"/>
-      <c r="H127" s="22" t="n"/>
-      <c r="I127" s="22" t="n"/>
-      <c r="J127" s="22" t="n"/>
-      <c r="K127" s="22" t="n"/>
-      <c r="L127" s="22" t="n"/>
-      <c r="M127" s="22" t="n"/>
-      <c r="N127" s="22" t="n"/>
-      <c r="O127" s="22" t="n"/>
-      <c r="P127" s="22" t="n"/>
-      <c r="Q127" s="22" t="n"/>
-      <c r="R127" s="22" t="n"/>
-      <c r="S127" s="22" t="n"/>
-      <c r="T127" s="22" t="n"/>
-      <c r="U127" s="22" t="n"/>
-      <c r="V127" s="22" t="n"/>
-      <c r="W127" s="22" t="n"/>
-      <c r="X127" s="22" t="n"/>
-      <c r="Y127" s="22" t="n"/>
-      <c r="Z127" s="22" t="n"/>
-      <c r="AA127" s="22" t="n"/>
-      <c r="AB127" s="22" t="n"/>
-      <c r="AC127" s="22" t="n"/>
-      <c r="AD127" s="22" t="n"/>
-    </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="22" t="n"/>
-      <c r="B128" s="22" t="n"/>
-      <c r="C128" s="22" t="n"/>
-      <c r="D128" s="22" t="n"/>
-      <c r="E128" s="22" t="n"/>
-      <c r="F128" s="22" t="n"/>
-      <c r="G128" s="22" t="n"/>
-      <c r="H128" s="22" t="n"/>
-      <c r="I128" s="22" t="n"/>
-      <c r="J128" s="22" t="n"/>
-      <c r="K128" s="22" t="n"/>
-      <c r="L128" s="22" t="n"/>
-      <c r="M128" s="22" t="n"/>
-      <c r="N128" s="22" t="n"/>
-      <c r="O128" s="22" t="n"/>
-      <c r="P128" s="22" t="n"/>
-      <c r="Q128" s="22" t="n"/>
-      <c r="R128" s="22" t="n"/>
-      <c r="S128" s="22" t="n"/>
-      <c r="T128" s="22" t="n"/>
-      <c r="U128" s="22" t="n"/>
-      <c r="V128" s="22" t="n"/>
-      <c r="W128" s="22" t="n"/>
-      <c r="X128" s="22" t="n"/>
-      <c r="Y128" s="22" t="n"/>
-      <c r="Z128" s="22" t="n"/>
-      <c r="AA128" s="22" t="n"/>
-      <c r="AB128" s="22" t="n"/>
-      <c r="AC128" s="22" t="n"/>
-      <c r="AD128" s="22" t="n"/>
-    </row>
-    <row r="129" ht="14" customHeight="1">
-      <c r="A129" s="22" t="n"/>
-      <c r="B129" s="22" t="n"/>
-      <c r="C129" s="22" t="n"/>
-      <c r="D129" s="22" t="n"/>
-      <c r="E129" s="22" t="n"/>
-      <c r="F129" s="22" t="n"/>
-      <c r="G129" s="22" t="n"/>
-      <c r="H129" s="22" t="n"/>
-      <c r="I129" s="22" t="n"/>
-      <c r="J129" s="22" t="n"/>
-      <c r="K129" s="22" t="n"/>
-      <c r="L129" s="22" t="n"/>
-      <c r="M129" s="22" t="n"/>
-      <c r="N129" s="22" t="n"/>
-      <c r="O129" s="22" t="n"/>
-      <c r="P129" s="22" t="n"/>
-      <c r="Q129" s="22" t="n"/>
-      <c r="R129" s="22" t="n"/>
-      <c r="S129" s="22" t="n"/>
-      <c r="T129" s="22" t="n"/>
-      <c r="U129" s="22" t="n"/>
-      <c r="V129" s="22" t="n"/>
-      <c r="W129" s="22" t="n"/>
-      <c r="X129" s="22" t="n"/>
-      <c r="Y129" s="22" t="n"/>
-      <c r="Z129" s="22" t="n"/>
-      <c r="AA129" s="22" t="n"/>
-      <c r="AB129" s="22" t="n"/>
-      <c r="AC129" s="22" t="n"/>
-      <c r="AD129" s="22" t="n"/>
+      <c r="AD101" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -11387,10 +9147,10 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W129"/>
+  <dimension ref="A1:W101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
     <col width="3.7" customWidth="1" min="3" max="3"/>
     <col width="3.7" customWidth="1" min="4" max="4"/>
@@ -11979,7 +9739,7 @@
     <row r="16" outlineLevel="1" ht="14" customHeight="1">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>2.2 Creación del formulario</t>
+          <t>2.2 Formulario de alta → correo de registro</t>
         </is>
       </c>
       <c r="B16" s="22" t="n"/>
@@ -12177,7 +9937,7 @@
     <row r="22" outlineLevel="1" ht="14" customHeight="1">
       <c r="A22" s="24" t="inlineStr">
         <is>
-          <t>3.2 Tickets de la cuenta</t>
+          <t>3.2 Ticket de contraseña → usuario</t>
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
@@ -12210,7 +9970,7 @@
     <row r="23" outlineLevel="1" ht="14" customHeight="1">
       <c r="A23" s="24" t="inlineStr">
         <is>
-          <t>3.3 Envío del enlace</t>
+          <t>3.3 Restablecer contraseña → usuario</t>
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
@@ -12531,9 +10291,9 @@
       <c r="T32" s="22" t="n"/>
       <c r="U32" s="22" t="n"/>
       <c r="V32" s="22" t="n"/>
-      <c r="W32" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="W32" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -12573,7 +10333,7 @@
     <row r="34" outlineLevel="1" ht="14" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>5.2 Horario del centro</t>
+          <t>5.2 Horario y avisos → inscritos</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
@@ -12606,7 +10366,7 @@
     <row r="35" outlineLevel="1" ht="14" customHeight="1">
       <c r="A35" s="24" t="inlineStr">
         <is>
-          <t>5.3 Alta y edición</t>
+          <t>5.3 Mínimo de personas para empezar</t>
         </is>
       </c>
       <c r="B35" s="22" t="n"/>
@@ -12630,9 +10390,9 @@
       <c r="T35" s="22" t="n"/>
       <c r="U35" s="22" t="n"/>
       <c r="V35" s="22" t="n"/>
-      <c r="W35" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="W35" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
@@ -12663,9 +10423,9 @@
       <c r="T36" s="22" t="n"/>
       <c r="U36" s="22" t="n"/>
       <c r="V36" s="22" t="n"/>
-      <c r="W36" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="W36" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -12696,16 +10456,16 @@
       <c r="T37" s="22" t="n"/>
       <c r="U37" s="22" t="n"/>
       <c r="V37" s="22" t="n"/>
-      <c r="W37" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="W37" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="38" ht="14" customHeight="1">
       <c r="A38" s="20" t="inlineStr">
         <is>
-          <t>6. Transiciones</t>
+          <t>6. Inscripciones y reservas</t>
         </is>
       </c>
       <c r="B38" s="22" t="n"/>
@@ -12729,16 +10489,16 @@
       <c r="T38" s="22" t="n"/>
       <c r="U38" s="22" t="n"/>
       <c r="V38" s="22" t="n"/>
-      <c r="W38" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="W38" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="39" outlineLevel="1" ht="14" customHeight="1">
       <c r="A39" s="24" t="inlineStr">
         <is>
-          <t>6.1 Transición entre páginas</t>
+          <t>6.1 Formulario de inscripción</t>
         </is>
       </c>
       <c r="B39" s="22" t="n"/>
@@ -12762,16 +10522,16 @@
       <c r="T39" s="22" t="n"/>
       <c r="U39" s="22" t="n"/>
       <c r="V39" s="22" t="n"/>
-      <c r="W39" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="W39" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="40" outlineLevel="1" ht="14" customHeight="1">
       <c r="A40" s="24" t="inlineStr">
         <is>
-          <t>6.2 Transición de los paneles</t>
+          <t>6.2 Control de plazas</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -12795,16 +10555,16 @@
       <c r="T40" s="22" t="n"/>
       <c r="U40" s="22" t="n"/>
       <c r="V40" s="22" t="n"/>
-      <c r="W40" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="W40" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="41" outlineLevel="1" ht="14" customHeight="1">
       <c r="A41" s="24" t="inlineStr">
         <is>
-          <t>6.3 Cierre y revisión visual</t>
+          <t>6.3 Reserva → correo del cliente</t>
         </is>
       </c>
       <c r="B41" s="22" t="n"/>
@@ -12828,9 +10588,9 @@
       <c r="T41" s="22" t="n"/>
       <c r="U41" s="22" t="n"/>
       <c r="V41" s="22" t="n"/>
-      <c r="W41" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="W41" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
@@ -12861,9 +10621,9 @@
       <c r="T42" s="22" t="n"/>
       <c r="U42" s="22" t="n"/>
       <c r="V42" s="22" t="n"/>
-      <c r="W42" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="W42" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
@@ -12894,16 +10654,16 @@
       <c r="T43" s="22" t="n"/>
       <c r="U43" s="22" t="n"/>
       <c r="V43" s="22" t="n"/>
-      <c r="W43" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="W43" s="30" t="inlineStr">
+        <is>
+          <t>sin iniciar</t>
         </is>
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>7. Planes con mejor información</t>
+          <t>7. Suscripciones</t>
         </is>
       </c>
       <c r="B44" s="22" t="n"/>
@@ -12936,7 +10696,7 @@
     <row r="45" outlineLevel="1" ht="14" customHeight="1">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>7.1 Datos que ve el cliente</t>
+          <t>7.1 Planes con mejor información</t>
         </is>
       </c>
       <c r="B45" s="22" t="n"/>
@@ -12969,7 +10729,7 @@
     <row r="46" outlineLevel="1" ht="14" customHeight="1">
       <c r="A46" s="24" t="inlineStr">
         <is>
-          <t>7.2 Detalle de cada plan</t>
+          <t>7.2 Alta del cliente</t>
         </is>
       </c>
       <c r="B46" s="22" t="n"/>
@@ -13002,7 +10762,7 @@
     <row r="47" outlineLevel="1" ht="14" customHeight="1">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>7.3 Textos del alta</t>
+          <t>7.3 Renovación y baja</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -13101,7 +10861,7 @@
     <row r="50" ht="14" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>8. Clases con mínimo de personas</t>
+          <t>8. Pagos con Stripe</t>
         </is>
       </c>
       <c r="B50" s="22" t="n"/>
@@ -13134,7 +10894,7 @@
     <row r="51" outlineLevel="1" ht="14" customHeight="1">
       <c r="A51" s="24" t="inlineStr">
         <is>
-          <t>8.1 Mínimo para abrir la clase</t>
+          <t>8.1 Pasarela de Stripe</t>
         </is>
       </c>
       <c r="B51" s="22" t="n"/>
@@ -13167,7 +10927,7 @@
     <row r="52" outlineLevel="1" ht="14" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>8.2 Aviso si no se llega</t>
+          <t>8.2 Confirmación del pago</t>
         </is>
       </c>
       <c r="B52" s="22" t="n"/>
@@ -13200,7 +10960,7 @@
     <row r="53" outlineLevel="1" ht="14" customHeight="1">
       <c r="A53" s="24" t="inlineStr">
         <is>
-          <t>8.3 Regla al reservar</t>
+          <t>8.3 Pago cancelado</t>
         </is>
       </c>
       <c r="B53" s="22" t="n"/>
@@ -13299,7 +11059,7 @@
     <row r="56" ht="14" customHeight="1">
       <c r="A56" s="20" t="inlineStr">
         <is>
-          <t>9. Correos ya en funcionamiento</t>
+          <t>9. Panel de administración</t>
         </is>
       </c>
       <c r="B56" s="22" t="n"/>
@@ -13332,7 +11092,7 @@
     <row r="57" outlineLevel="1" ht="14" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>9.1 Confirma tu cuenta → registro</t>
+          <t>9.1 Inicio del panel</t>
         </is>
       </c>
       <c r="B57" s="22" t="n"/>
@@ -13365,7 +11125,7 @@
     <row r="58" outlineLevel="1" ht="14" customHeight="1">
       <c r="A58" s="24" t="inlineStr">
         <is>
-          <t>9.2 Restablecer contraseña → usuario</t>
+          <t>9.2 Menú y permisos</t>
         </is>
       </c>
       <c r="B58" s="22" t="n"/>
@@ -13398,7 +11158,7 @@
     <row r="59" outlineLevel="1" ht="14" customHeight="1">
       <c r="A59" s="24" t="inlineStr">
         <is>
-          <t>9.3 Ticket de contraseña → usuario</t>
+          <t>9.3 Listados del panel</t>
         </is>
       </c>
       <c r="B59" s="22" t="n"/>
@@ -13431,7 +11191,7 @@
     <row r="60" outlineLevel="1" ht="14" customHeight="1">
       <c r="A60" s="24" t="inlineStr">
         <is>
-          <t>9.4 Confirmación de reserva → cliente</t>
+          <t>9.4 Testeo</t>
         </is>
       </c>
       <c r="B60" s="22" t="n"/>
@@ -13464,7 +11224,7 @@
     <row r="61" outlineLevel="1" ht="14" customHeight="1">
       <c r="A61" s="24" t="inlineStr">
         <is>
-          <t>9.5 Cambio en tu clase → inscritos</t>
+          <t>9.5 Documentación</t>
         </is>
       </c>
       <c r="B61" s="22" t="n"/>
@@ -13494,10 +11254,10 @@
         </is>
       </c>
     </row>
-    <row r="62" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
-        <is>
-          <t>9.6 Actividad cancelada → inscritos</t>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>10. Gestión de clientes</t>
         </is>
       </c>
       <c r="B62" s="22" t="n"/>
@@ -13530,7 +11290,7 @@
     <row r="63" outlineLevel="1" ht="14" customHeight="1">
       <c r="A63" s="24" t="inlineStr">
         <is>
-          <t>9.7 Respuesta de contacto → remitente</t>
+          <t>10.1 Listado de clientes</t>
         </is>
       </c>
       <c r="B63" s="22" t="n"/>
@@ -13563,7 +11323,7 @@
     <row r="64" outlineLevel="1" ht="14" customHeight="1">
       <c r="A64" s="24" t="inlineStr">
         <is>
-          <t>9.8 Testeo</t>
+          <t>10.2 Ficha del cliente</t>
         </is>
       </c>
       <c r="B64" s="22" t="n"/>
@@ -13596,7 +11356,7 @@
     <row r="65" outlineLevel="1" ht="14" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>9.9 Documentación</t>
+          <t>10.3 Edición de datos</t>
         </is>
       </c>
       <c r="B65" s="22" t="n"/>
@@ -13626,10 +11386,10 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="20" t="inlineStr">
-        <is>
-          <t>10. Inscripciones y reservas</t>
+    <row r="66" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>10.4 Testeo</t>
         </is>
       </c>
       <c r="B66" s="22" t="n"/>
@@ -13662,7 +11422,7 @@
     <row r="67" outlineLevel="1" ht="14" customHeight="1">
       <c r="A67" s="24" t="inlineStr">
         <is>
-          <t>10.1 Formulario de inscripción</t>
+          <t>10.5 Documentación</t>
         </is>
       </c>
       <c r="B67" s="22" t="n"/>
@@ -13692,10 +11452,10 @@
         </is>
       </c>
     </row>
-    <row r="68" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A68" s="24" t="inlineStr">
-        <is>
-          <t>10.2 Control de plazas</t>
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="20" t="inlineStr">
+        <is>
+          <t>11. Monitores y solicitudes</t>
         </is>
       </c>
       <c r="B68" s="22" t="n"/>
@@ -13728,7 +11488,7 @@
     <row r="69" outlineLevel="1" ht="14" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>10.3 Reservas del cliente</t>
+          <t>11.1 Alta de monitores</t>
         </is>
       </c>
       <c r="B69" s="22" t="n"/>
@@ -13761,7 +11521,7 @@
     <row r="70" outlineLevel="1" ht="14" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>10.4 Testeo</t>
+          <t>11.2 Solicitudes de clase</t>
         </is>
       </c>
       <c r="B70" s="22" t="n"/>
@@ -13794,7 +11554,7 @@
     <row r="71" outlineLevel="1" ht="14" customHeight="1">
       <c r="A71" s="24" t="inlineStr">
         <is>
-          <t>10.5 Documentación</t>
+          <t>11.3 Aprobación y rechazo</t>
         </is>
       </c>
       <c r="B71" s="22" t="n"/>
@@ -13824,10 +11584,10 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
-        <is>
-          <t>11. Suscripciones</t>
+    <row r="72" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>11.4 Testeo</t>
         </is>
       </c>
       <c r="B72" s="22" t="n"/>
@@ -13860,7 +11620,7 @@
     <row r="73" outlineLevel="1" ht="14" customHeight="1">
       <c r="A73" s="24" t="inlineStr">
         <is>
-          <t>11.1 Planes de suscripción</t>
+          <t>11.5 Documentación</t>
         </is>
       </c>
       <c r="B73" s="22" t="n"/>
@@ -13890,10 +11650,10 @@
         </is>
       </c>
     </row>
-    <row r="74" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A74" s="24" t="inlineStr">
-        <is>
-          <t>11.2 Alta del cliente</t>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
+        <is>
+          <t>12. Salas y materiales</t>
         </is>
       </c>
       <c r="B74" s="22" t="n"/>
@@ -13926,7 +11686,7 @@
     <row r="75" outlineLevel="1" ht="14" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>11.3 Renovación y baja</t>
+          <t>12.1 Ficha de salas</t>
         </is>
       </c>
       <c r="B75" s="22" t="n"/>
@@ -13959,7 +11719,7 @@
     <row r="76" outlineLevel="1" ht="14" customHeight="1">
       <c r="A76" s="24" t="inlineStr">
         <is>
-          <t>11.4 Testeo</t>
+          <t>12.2 Inventario de materiales</t>
         </is>
       </c>
       <c r="B76" s="22" t="n"/>
@@ -13992,7 +11752,7 @@
     <row r="77" outlineLevel="1" ht="14" customHeight="1">
       <c r="A77" s="24" t="inlineStr">
         <is>
-          <t>11.5 Documentación</t>
+          <t>12.3 Alta y edición</t>
         </is>
       </c>
       <c r="B77" s="22" t="n"/>
@@ -14022,10 +11782,10 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>12. Pagos con Stripe</t>
+    <row r="78" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>12.4 Testeo</t>
         </is>
       </c>
       <c r="B78" s="22" t="n"/>
@@ -14058,7 +11818,7 @@
     <row r="79" outlineLevel="1" ht="14" customHeight="1">
       <c r="A79" s="24" t="inlineStr">
         <is>
-          <t>12.1 Pasarela de Stripe</t>
+          <t>12.5 Documentación</t>
         </is>
       </c>
       <c r="B79" s="22" t="n"/>
@@ -14088,10 +11848,10 @@
         </is>
       </c>
     </row>
-    <row r="80" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A80" s="24" t="inlineStr">
-        <is>
-          <t>12.2 Confirmación del pago</t>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>13. Fisioterapia y citas</t>
         </is>
       </c>
       <c r="B80" s="22" t="n"/>
@@ -14124,7 +11884,7 @@
     <row r="81" outlineLevel="1" ht="14" customHeight="1">
       <c r="A81" s="24" t="inlineStr">
         <is>
-          <t>12.3 Pago cancelado</t>
+          <t>13.1 Solicitud de cita</t>
         </is>
       </c>
       <c r="B81" s="22" t="n"/>
@@ -14157,7 +11917,7 @@
     <row r="82" outlineLevel="1" ht="14" customHeight="1">
       <c r="A82" s="24" t="inlineStr">
         <is>
-          <t>12.4 Testeo</t>
+          <t>13.2 Agenda del fisioterapeuta</t>
         </is>
       </c>
       <c r="B82" s="22" t="n"/>
@@ -14190,7 +11950,7 @@
     <row r="83" outlineLevel="1" ht="14" customHeight="1">
       <c r="A83" s="24" t="inlineStr">
         <is>
-          <t>12.5 Documentación</t>
+          <t>13.3 Panel de citas</t>
         </is>
       </c>
       <c r="B83" s="22" t="n"/>
@@ -14220,10 +11980,10 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>13. Panel de administración</t>
+    <row r="84" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>13.4 Testeo</t>
         </is>
       </c>
       <c r="B84" s="22" t="n"/>
@@ -14256,7 +12016,7 @@
     <row r="85" outlineLevel="1" ht="14" customHeight="1">
       <c r="A85" s="24" t="inlineStr">
         <is>
-          <t>13.1 Inicio del panel</t>
+          <t>13.5 Documentación</t>
         </is>
       </c>
       <c r="B85" s="22" t="n"/>
@@ -14286,17 +12046,17 @@
         </is>
       </c>
     </row>
-    <row r="86" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A86" s="24" t="inlineStr">
-        <is>
-          <t>13.2 Menú y permisos</t>
-        </is>
-      </c>
-      <c r="B86" s="22" t="n"/>
-      <c r="C86" s="22" t="n"/>
-      <c r="D86" s="22" t="n"/>
-      <c r="E86" s="22" t="n"/>
-      <c r="F86" s="22" t="n"/>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="20" t="inlineStr">
+        <is>
+          <t>14. Comentarios, feedback y seguridad</t>
+        </is>
+      </c>
+      <c r="B86" s="27" t="n"/>
+      <c r="C86" s="27" t="n"/>
+      <c r="D86" s="27" t="n"/>
+      <c r="E86" s="27" t="n"/>
+      <c r="F86" s="27" t="n"/>
       <c r="G86" s="22" t="n"/>
       <c r="H86" s="22" t="n"/>
       <c r="I86" s="22" t="n"/>
@@ -14322,10 +12082,10 @@
     <row r="87" outlineLevel="1" ht="14" customHeight="1">
       <c r="A87" s="24" t="inlineStr">
         <is>
-          <t>13.3 Listados del panel</t>
-        </is>
-      </c>
-      <c r="B87" s="22" t="n"/>
+          <t>14.1 Comentarios de actividad</t>
+        </is>
+      </c>
+      <c r="B87" s="28" t="n"/>
       <c r="C87" s="22" t="n"/>
       <c r="D87" s="22" t="n"/>
       <c r="E87" s="22" t="n"/>
@@ -14355,13 +12115,13 @@
     <row r="88" outlineLevel="1" ht="14" customHeight="1">
       <c r="A88" s="24" t="inlineStr">
         <is>
-          <t>13.4 Testeo</t>
+          <t>14.2 Respuesta de contacto → remitente</t>
         </is>
       </c>
       <c r="B88" s="22" t="n"/>
       <c r="C88" s="22" t="n"/>
       <c r="D88" s="22" t="n"/>
-      <c r="E88" s="22" t="n"/>
+      <c r="E88" s="21" t="n"/>
       <c r="F88" s="22" t="n"/>
       <c r="G88" s="22" t="n"/>
       <c r="H88" s="22" t="n"/>
@@ -14388,13 +12148,13 @@
     <row r="89" outlineLevel="1" ht="14" customHeight="1">
       <c r="A89" s="24" t="inlineStr">
         <is>
-          <t>13.5 Documentación</t>
+          <t>14.3 Configuración de seguridad</t>
         </is>
       </c>
       <c r="B89" s="22" t="n"/>
       <c r="C89" s="22" t="n"/>
       <c r="D89" s="22" t="n"/>
-      <c r="E89" s="22" t="n"/>
+      <c r="E89" s="25" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="22" t="n"/>
       <c r="H89" s="22" t="n"/>
@@ -14418,17 +12178,17 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="14" customHeight="1">
-      <c r="A90" s="20" t="inlineStr">
-        <is>
-          <t>14. Gestión de clientes</t>
-        </is>
-      </c>
-      <c r="B90" s="22" t="n"/>
-      <c r="C90" s="22" t="n"/>
-      <c r="D90" s="22" t="n"/>
-      <c r="E90" s="22" t="n"/>
-      <c r="F90" s="22" t="n"/>
+    <row r="90" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>14.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B90" s="26" t="n"/>
+      <c r="C90" s="26" t="n"/>
+      <c r="D90" s="26" t="n"/>
+      <c r="E90" s="26" t="n"/>
+      <c r="F90" s="26" t="n"/>
       <c r="G90" s="22" t="n"/>
       <c r="H90" s="22" t="n"/>
       <c r="I90" s="22" t="n"/>
@@ -14454,14 +12214,14 @@
     <row r="91" outlineLevel="1" ht="14" customHeight="1">
       <c r="A91" s="24" t="inlineStr">
         <is>
-          <t>14.1 Listado de clientes</t>
-        </is>
-      </c>
-      <c r="B91" s="22" t="n"/>
-      <c r="C91" s="22" t="n"/>
-      <c r="D91" s="22" t="n"/>
-      <c r="E91" s="22" t="n"/>
-      <c r="F91" s="22" t="n"/>
+          <t>14.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B91" s="27" t="n"/>
+      <c r="C91" s="27" t="n"/>
+      <c r="D91" s="27" t="n"/>
+      <c r="E91" s="27" t="n"/>
+      <c r="F91" s="27" t="n"/>
       <c r="G91" s="22" t="n"/>
       <c r="H91" s="22" t="n"/>
       <c r="I91" s="22" t="n"/>
@@ -14484,43 +12244,43 @@
         </is>
       </c>
     </row>
-    <row r="92" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A92" s="24" t="inlineStr">
-        <is>
-          <t>14.2 Ficha del cliente</t>
-        </is>
-      </c>
-      <c r="B92" s="22" t="n"/>
-      <c r="C92" s="22" t="n"/>
-      <c r="D92" s="22" t="n"/>
-      <c r="E92" s="22" t="n"/>
-      <c r="F92" s="22" t="n"/>
-      <c r="G92" s="22" t="n"/>
-      <c r="H92" s="22" t="n"/>
-      <c r="I92" s="22" t="n"/>
-      <c r="J92" s="22" t="n"/>
-      <c r="K92" s="22" t="n"/>
-      <c r="L92" s="22" t="n"/>
-      <c r="M92" s="22" t="n"/>
-      <c r="N92" s="22" t="n"/>
-      <c r="O92" s="22" t="n"/>
-      <c r="P92" s="22" t="n"/>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>15. Interfaz Tailwind, correo y cierre</t>
+        </is>
+      </c>
+      <c r="B92" s="28" t="n"/>
+      <c r="C92" s="28" t="n"/>
+      <c r="D92" s="28" t="n"/>
+      <c r="E92" s="28" t="n"/>
+      <c r="F92" s="28" t="n"/>
+      <c r="G92" s="28" t="n"/>
+      <c r="H92" s="28" t="n"/>
+      <c r="I92" s="28" t="n"/>
+      <c r="J92" s="28" t="n"/>
+      <c r="K92" s="28" t="n"/>
+      <c r="L92" s="28" t="n"/>
+      <c r="M92" s="28" t="n"/>
+      <c r="N92" s="28" t="n"/>
+      <c r="O92" s="28" t="n"/>
+      <c r="P92" s="28" t="n"/>
       <c r="Q92" s="22" t="n"/>
       <c r="R92" s="22" t="n"/>
       <c r="S92" s="22" t="n"/>
       <c r="T92" s="22" t="n"/>
       <c r="U92" s="22" t="n"/>
       <c r="V92" s="22" t="n"/>
-      <c r="W92" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W92" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="93" outlineLevel="1" ht="14" customHeight="1">
       <c r="A93" s="24" t="inlineStr">
         <is>
-          <t>14.3 Edición de datos</t>
+          <t>15.1 Transiciones del front</t>
         </is>
       </c>
       <c r="B93" s="22" t="n"/>
@@ -14544,16 +12304,16 @@
       <c r="T93" s="22" t="n"/>
       <c r="U93" s="22" t="n"/>
       <c r="V93" s="22" t="n"/>
-      <c r="W93" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W93" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="94" outlineLevel="1" ht="14" customHeight="1">
       <c r="A94" s="24" t="inlineStr">
         <is>
-          <t>14.4 Testeo</t>
+          <t>15.2 Correos ya en funcionamiento</t>
         </is>
       </c>
       <c r="B94" s="22" t="n"/>
@@ -14586,7 +12346,7 @@
     <row r="95" outlineLevel="1" ht="14" customHeight="1">
       <c r="A95" s="24" t="inlineStr">
         <is>
-          <t>14.5 Documentación</t>
+          <t>15.3 Cierre y revisión</t>
         </is>
       </c>
       <c r="B95" s="22" t="n"/>
@@ -14595,7 +12355,7 @@
       <c r="E95" s="22" t="n"/>
       <c r="F95" s="22" t="n"/>
       <c r="G95" s="22" t="n"/>
-      <c r="H95" s="22" t="n"/>
+      <c r="H95" s="26" t="n"/>
       <c r="I95" s="22" t="n"/>
       <c r="J95" s="22" t="n"/>
       <c r="K95" s="22" t="n"/>
@@ -14616,78 +12376,74 @@
         </is>
       </c>
     </row>
-    <row r="96" ht="14" customHeight="1">
-      <c r="A96" s="20" t="inlineStr">
-        <is>
-          <t>15. Monitores y solicitudes</t>
-        </is>
-      </c>
-      <c r="B96" s="22" t="n"/>
-      <c r="C96" s="22" t="n"/>
-      <c r="D96" s="22" t="n"/>
-      <c r="E96" s="22" t="n"/>
-      <c r="F96" s="22" t="n"/>
-      <c r="G96" s="22" t="n"/>
-      <c r="H96" s="22" t="n"/>
-      <c r="I96" s="22" t="n"/>
-      <c r="J96" s="22" t="n"/>
-      <c r="K96" s="22" t="n"/>
-      <c r="L96" s="22" t="n"/>
-      <c r="M96" s="22" t="n"/>
-      <c r="N96" s="22" t="n"/>
-      <c r="O96" s="22" t="n"/>
-      <c r="P96" s="22" t="n"/>
+    <row r="96" outlineLevel="1" ht="14" customHeight="1">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>15.4 Testeo</t>
+        </is>
+      </c>
+      <c r="B96" s="27" t="n"/>
+      <c r="C96" s="27" t="n"/>
+      <c r="D96" s="27" t="n"/>
+      <c r="E96" s="27" t="n"/>
+      <c r="F96" s="27" t="n"/>
+      <c r="G96" s="27" t="n"/>
+      <c r="H96" s="27" t="n"/>
+      <c r="I96" s="27" t="n"/>
+      <c r="J96" s="27" t="n"/>
+      <c r="K96" s="27" t="n"/>
+      <c r="L96" s="27" t="n"/>
+      <c r="M96" s="27" t="n"/>
+      <c r="N96" s="27" t="n"/>
+      <c r="O96" s="27" t="n"/>
+      <c r="P96" s="27" t="n"/>
       <c r="Q96" s="22" t="n"/>
       <c r="R96" s="22" t="n"/>
       <c r="S96" s="22" t="n"/>
       <c r="T96" s="22" t="n"/>
       <c r="U96" s="22" t="n"/>
       <c r="V96" s="22" t="n"/>
-      <c r="W96" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W96" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="97" outlineLevel="1" ht="14" customHeight="1">
       <c r="A97" s="24" t="inlineStr">
         <is>
-          <t>15.1 Alta de monitores</t>
-        </is>
-      </c>
-      <c r="B97" s="22" t="n"/>
-      <c r="C97" s="22" t="n"/>
-      <c r="D97" s="22" t="n"/>
-      <c r="E97" s="22" t="n"/>
-      <c r="F97" s="22" t="n"/>
-      <c r="G97" s="22" t="n"/>
-      <c r="H97" s="22" t="n"/>
-      <c r="I97" s="22" t="n"/>
-      <c r="J97" s="22" t="n"/>
-      <c r="K97" s="22" t="n"/>
-      <c r="L97" s="22" t="n"/>
-      <c r="M97" s="22" t="n"/>
-      <c r="N97" s="22" t="n"/>
-      <c r="O97" s="22" t="n"/>
-      <c r="P97" s="22" t="n"/>
+          <t>15.5 Documentación</t>
+        </is>
+      </c>
+      <c r="B97" s="28" t="n"/>
+      <c r="C97" s="28" t="n"/>
+      <c r="D97" s="28" t="n"/>
+      <c r="E97" s="28" t="n"/>
+      <c r="F97" s="28" t="n"/>
+      <c r="G97" s="28" t="n"/>
+      <c r="H97" s="28" t="n"/>
+      <c r="I97" s="28" t="n"/>
+      <c r="J97" s="28" t="n"/>
+      <c r="K97" s="28" t="n"/>
+      <c r="L97" s="28" t="n"/>
+      <c r="M97" s="28" t="n"/>
+      <c r="N97" s="28" t="n"/>
+      <c r="O97" s="28" t="n"/>
+      <c r="P97" s="28" t="n"/>
       <c r="Q97" s="22" t="n"/>
       <c r="R97" s="22" t="n"/>
       <c r="S97" s="22" t="n"/>
       <c r="T97" s="22" t="n"/>
       <c r="U97" s="22" t="n"/>
       <c r="V97" s="22" t="n"/>
-      <c r="W97" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A98" s="24" t="inlineStr">
-        <is>
-          <t>15.2 Solicitudes de clase</t>
-        </is>
-      </c>
+      <c r="W97" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="22" t="n"/>
       <c r="B98" s="22" t="n"/>
       <c r="C98" s="22" t="n"/>
       <c r="D98" s="22" t="n"/>
@@ -14709,18 +12465,10 @@
       <c r="T98" s="22" t="n"/>
       <c r="U98" s="22" t="n"/>
       <c r="V98" s="22" t="n"/>
-      <c r="W98" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A99" s="24" t="inlineStr">
-        <is>
-          <t>15.3 Aprobación y rechazo</t>
-        </is>
-      </c>
+      <c r="W98" s="22" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="22" t="n"/>
       <c r="B99" s="22" t="n"/>
       <c r="C99" s="22" t="n"/>
       <c r="D99" s="22" t="n"/>
@@ -14742,18 +12490,10 @@
       <c r="T99" s="22" t="n"/>
       <c r="U99" s="22" t="n"/>
       <c r="V99" s="22" t="n"/>
-      <c r="W99" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A100" s="24" t="inlineStr">
-        <is>
-          <t>15.4 Testeo</t>
-        </is>
-      </c>
+      <c r="W99" s="22" t="n"/>
+    </row>
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="22" t="n"/>
       <c r="B100" s="22" t="n"/>
       <c r="C100" s="22" t="n"/>
       <c r="D100" s="22" t="n"/>
@@ -14775,18 +12515,10 @@
       <c r="T100" s="22" t="n"/>
       <c r="U100" s="22" t="n"/>
       <c r="V100" s="22" t="n"/>
-      <c r="W100" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A101" s="24" t="inlineStr">
-        <is>
-          <t>15.5 Documentación</t>
-        </is>
-      </c>
+      <c r="W100" s="22" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="22" t="n"/>
       <c r="B101" s="22" t="n"/>
       <c r="C101" s="22" t="n"/>
       <c r="D101" s="22" t="n"/>
@@ -14808,903 +12540,7 @@
       <c r="T101" s="22" t="n"/>
       <c r="U101" s="22" t="n"/>
       <c r="V101" s="22" t="n"/>
-      <c r="W101" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="14" customHeight="1">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>16. Salas y materiales</t>
-        </is>
-      </c>
-      <c r="B102" s="28" t="n"/>
-      <c r="C102" s="22" t="n"/>
-      <c r="D102" s="22" t="n"/>
-      <c r="E102" s="22" t="n"/>
-      <c r="F102" s="22" t="n"/>
-      <c r="G102" s="22" t="n"/>
-      <c r="H102" s="22" t="n"/>
-      <c r="I102" s="22" t="n"/>
-      <c r="J102" s="22" t="n"/>
-      <c r="K102" s="22" t="n"/>
-      <c r="L102" s="22" t="n"/>
-      <c r="M102" s="22" t="n"/>
-      <c r="N102" s="22" t="n"/>
-      <c r="O102" s="22" t="n"/>
-      <c r="P102" s="22" t="n"/>
-      <c r="Q102" s="22" t="n"/>
-      <c r="R102" s="22" t="n"/>
-      <c r="S102" s="22" t="n"/>
-      <c r="T102" s="22" t="n"/>
-      <c r="U102" s="22" t="n"/>
-      <c r="V102" s="22" t="n"/>
-      <c r="W102" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A103" s="24" t="inlineStr">
-        <is>
-          <t>16.1 Ficha de salas</t>
-        </is>
-      </c>
-      <c r="B103" s="22" t="n"/>
-      <c r="C103" s="22" t="n"/>
-      <c r="D103" s="22" t="n"/>
-      <c r="E103" s="22" t="n"/>
-      <c r="F103" s="22" t="n"/>
-      <c r="G103" s="22" t="n"/>
-      <c r="H103" s="22" t="n"/>
-      <c r="I103" s="22" t="n"/>
-      <c r="J103" s="22" t="n"/>
-      <c r="K103" s="22" t="n"/>
-      <c r="L103" s="22" t="n"/>
-      <c r="M103" s="22" t="n"/>
-      <c r="N103" s="22" t="n"/>
-      <c r="O103" s="22" t="n"/>
-      <c r="P103" s="22" t="n"/>
-      <c r="Q103" s="22" t="n"/>
-      <c r="R103" s="22" t="n"/>
-      <c r="S103" s="22" t="n"/>
-      <c r="T103" s="22" t="n"/>
-      <c r="U103" s="22" t="n"/>
-      <c r="V103" s="22" t="n"/>
-      <c r="W103" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A104" s="24" t="inlineStr">
-        <is>
-          <t>16.2 Inventario de materiales</t>
-        </is>
-      </c>
-      <c r="B104" s="22" t="n"/>
-      <c r="C104" s="22" t="n"/>
-      <c r="D104" s="22" t="n"/>
-      <c r="E104" s="22" t="n"/>
-      <c r="F104" s="22" t="n"/>
-      <c r="G104" s="22" t="n"/>
-      <c r="H104" s="22" t="n"/>
-      <c r="I104" s="22" t="n"/>
-      <c r="J104" s="22" t="n"/>
-      <c r="K104" s="22" t="n"/>
-      <c r="L104" s="22" t="n"/>
-      <c r="M104" s="22" t="n"/>
-      <c r="N104" s="22" t="n"/>
-      <c r="O104" s="22" t="n"/>
-      <c r="P104" s="22" t="n"/>
-      <c r="Q104" s="22" t="n"/>
-      <c r="R104" s="22" t="n"/>
-      <c r="S104" s="22" t="n"/>
-      <c r="T104" s="22" t="n"/>
-      <c r="U104" s="22" t="n"/>
-      <c r="V104" s="22" t="n"/>
-      <c r="W104" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A105" s="24" t="inlineStr">
-        <is>
-          <t>16.3 Alta y edición</t>
-        </is>
-      </c>
-      <c r="B105" s="22" t="n"/>
-      <c r="C105" s="22" t="n"/>
-      <c r="D105" s="22" t="n"/>
-      <c r="E105" s="22" t="n"/>
-      <c r="F105" s="22" t="n"/>
-      <c r="G105" s="22" t="n"/>
-      <c r="H105" s="22" t="n"/>
-      <c r="I105" s="22" t="n"/>
-      <c r="J105" s="22" t="n"/>
-      <c r="K105" s="22" t="n"/>
-      <c r="L105" s="22" t="n"/>
-      <c r="M105" s="22" t="n"/>
-      <c r="N105" s="22" t="n"/>
-      <c r="O105" s="22" t="n"/>
-      <c r="P105" s="22" t="n"/>
-      <c r="Q105" s="22" t="n"/>
-      <c r="R105" s="22" t="n"/>
-      <c r="S105" s="22" t="n"/>
-      <c r="T105" s="22" t="n"/>
-      <c r="U105" s="22" t="n"/>
-      <c r="V105" s="22" t="n"/>
-      <c r="W105" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A106" s="24" t="inlineStr">
-        <is>
-          <t>16.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B106" s="27" t="n"/>
-      <c r="C106" s="22" t="n"/>
-      <c r="D106" s="22" t="n"/>
-      <c r="E106" s="22" t="n"/>
-      <c r="F106" s="22" t="n"/>
-      <c r="G106" s="22" t="n"/>
-      <c r="H106" s="22" t="n"/>
-      <c r="I106" s="22" t="n"/>
-      <c r="J106" s="22" t="n"/>
-      <c r="K106" s="22" t="n"/>
-      <c r="L106" s="22" t="n"/>
-      <c r="M106" s="22" t="n"/>
-      <c r="N106" s="22" t="n"/>
-      <c r="O106" s="22" t="n"/>
-      <c r="P106" s="22" t="n"/>
-      <c r="Q106" s="22" t="n"/>
-      <c r="R106" s="22" t="n"/>
-      <c r="S106" s="22" t="n"/>
-      <c r="T106" s="22" t="n"/>
-      <c r="U106" s="22" t="n"/>
-      <c r="V106" s="22" t="n"/>
-      <c r="W106" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A107" s="24" t="inlineStr">
-        <is>
-          <t>16.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B107" s="28" t="n"/>
-      <c r="C107" s="22" t="n"/>
-      <c r="D107" s="22" t="n"/>
-      <c r="E107" s="22" t="n"/>
-      <c r="F107" s="22" t="n"/>
-      <c r="G107" s="22" t="n"/>
-      <c r="H107" s="22" t="n"/>
-      <c r="I107" s="22" t="n"/>
-      <c r="J107" s="22" t="n"/>
-      <c r="K107" s="22" t="n"/>
-      <c r="L107" s="22" t="n"/>
-      <c r="M107" s="22" t="n"/>
-      <c r="N107" s="22" t="n"/>
-      <c r="O107" s="22" t="n"/>
-      <c r="P107" s="22" t="n"/>
-      <c r="Q107" s="22" t="n"/>
-      <c r="R107" s="22" t="n"/>
-      <c r="S107" s="22" t="n"/>
-      <c r="T107" s="22" t="n"/>
-      <c r="U107" s="22" t="n"/>
-      <c r="V107" s="22" t="n"/>
-      <c r="W107" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="14" customHeight="1">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>17. Fisioterapia y citas</t>
-        </is>
-      </c>
-      <c r="B108" s="22" t="n"/>
-      <c r="C108" s="21" t="n"/>
-      <c r="D108" s="21" t="n"/>
-      <c r="E108" s="21" t="n"/>
-      <c r="F108" s="22" t="n"/>
-      <c r="G108" s="22" t="n"/>
-      <c r="H108" s="22" t="n"/>
-      <c r="I108" s="22" t="n"/>
-      <c r="J108" s="22" t="n"/>
-      <c r="K108" s="22" t="n"/>
-      <c r="L108" s="22" t="n"/>
-      <c r="M108" s="22" t="n"/>
-      <c r="N108" s="22" t="n"/>
-      <c r="O108" s="22" t="n"/>
-      <c r="P108" s="22" t="n"/>
-      <c r="Q108" s="22" t="n"/>
-      <c r="R108" s="22" t="n"/>
-      <c r="S108" s="22" t="n"/>
-      <c r="T108" s="22" t="n"/>
-      <c r="U108" s="22" t="n"/>
-      <c r="V108" s="22" t="n"/>
-      <c r="W108" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A109" s="24" t="inlineStr">
-        <is>
-          <t>17.1 Solicitud de cita</t>
-        </is>
-      </c>
-      <c r="B109" s="22" t="n"/>
-      <c r="C109" s="25" t="n"/>
-      <c r="D109" s="22" t="n"/>
-      <c r="E109" s="22" t="n"/>
-      <c r="F109" s="22" t="n"/>
-      <c r="G109" s="22" t="n"/>
-      <c r="H109" s="22" t="n"/>
-      <c r="I109" s="22" t="n"/>
-      <c r="J109" s="22" t="n"/>
-      <c r="K109" s="22" t="n"/>
-      <c r="L109" s="22" t="n"/>
-      <c r="M109" s="22" t="n"/>
-      <c r="N109" s="22" t="n"/>
-      <c r="O109" s="22" t="n"/>
-      <c r="P109" s="22" t="n"/>
-      <c r="Q109" s="22" t="n"/>
-      <c r="R109" s="22" t="n"/>
-      <c r="S109" s="22" t="n"/>
-      <c r="T109" s="22" t="n"/>
-      <c r="U109" s="22" t="n"/>
-      <c r="V109" s="22" t="n"/>
-      <c r="W109" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A110" s="24" t="inlineStr">
-        <is>
-          <t>17.2 Agenda del fisioterapeuta</t>
-        </is>
-      </c>
-      <c r="B110" s="22" t="n"/>
-      <c r="C110" s="22" t="n"/>
-      <c r="D110" s="26" t="n"/>
-      <c r="E110" s="22" t="n"/>
-      <c r="F110" s="22" t="n"/>
-      <c r="G110" s="22" t="n"/>
-      <c r="H110" s="22" t="n"/>
-      <c r="I110" s="22" t="n"/>
-      <c r="J110" s="22" t="n"/>
-      <c r="K110" s="22" t="n"/>
-      <c r="L110" s="22" t="n"/>
-      <c r="M110" s="22" t="n"/>
-      <c r="N110" s="22" t="n"/>
-      <c r="O110" s="22" t="n"/>
-      <c r="P110" s="22" t="n"/>
-      <c r="Q110" s="22" t="n"/>
-      <c r="R110" s="22" t="n"/>
-      <c r="S110" s="22" t="n"/>
-      <c r="T110" s="22" t="n"/>
-      <c r="U110" s="22" t="n"/>
-      <c r="V110" s="22" t="n"/>
-      <c r="W110" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A111" s="24" t="inlineStr">
-        <is>
-          <t>17.3 Panel de citas</t>
-        </is>
-      </c>
-      <c r="B111" s="22" t="n"/>
-      <c r="C111" s="22" t="n"/>
-      <c r="D111" s="27" t="n"/>
-      <c r="E111" s="22" t="n"/>
-      <c r="F111" s="22" t="n"/>
-      <c r="G111" s="22" t="n"/>
-      <c r="H111" s="22" t="n"/>
-      <c r="I111" s="22" t="n"/>
-      <c r="J111" s="22" t="n"/>
-      <c r="K111" s="22" t="n"/>
-      <c r="L111" s="22" t="n"/>
-      <c r="M111" s="22" t="n"/>
-      <c r="N111" s="22" t="n"/>
-      <c r="O111" s="22" t="n"/>
-      <c r="P111" s="22" t="n"/>
-      <c r="Q111" s="22" t="n"/>
-      <c r="R111" s="22" t="n"/>
-      <c r="S111" s="22" t="n"/>
-      <c r="T111" s="22" t="n"/>
-      <c r="U111" s="22" t="n"/>
-      <c r="V111" s="22" t="n"/>
-      <c r="W111" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A112" s="24" t="inlineStr">
-        <is>
-          <t>17.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B112" s="22" t="n"/>
-      <c r="C112" s="28" t="n"/>
-      <c r="D112" s="28" t="n"/>
-      <c r="E112" s="28" t="n"/>
-      <c r="F112" s="22" t="n"/>
-      <c r="G112" s="22" t="n"/>
-      <c r="H112" s="22" t="n"/>
-      <c r="I112" s="22" t="n"/>
-      <c r="J112" s="22" t="n"/>
-      <c r="K112" s="22" t="n"/>
-      <c r="L112" s="22" t="n"/>
-      <c r="M112" s="22" t="n"/>
-      <c r="N112" s="22" t="n"/>
-      <c r="O112" s="22" t="n"/>
-      <c r="P112" s="22" t="n"/>
-      <c r="Q112" s="22" t="n"/>
-      <c r="R112" s="22" t="n"/>
-      <c r="S112" s="22" t="n"/>
-      <c r="T112" s="22" t="n"/>
-      <c r="U112" s="22" t="n"/>
-      <c r="V112" s="22" t="n"/>
-      <c r="W112" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A113" s="24" t="inlineStr">
-        <is>
-          <t>17.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B113" s="22" t="n"/>
-      <c r="C113" s="21" t="n"/>
-      <c r="D113" s="21" t="n"/>
-      <c r="E113" s="21" t="n"/>
-      <c r="F113" s="22" t="n"/>
-      <c r="G113" s="22" t="n"/>
-      <c r="H113" s="22" t="n"/>
-      <c r="I113" s="22" t="n"/>
-      <c r="J113" s="22" t="n"/>
-      <c r="K113" s="22" t="n"/>
-      <c r="L113" s="22" t="n"/>
-      <c r="M113" s="22" t="n"/>
-      <c r="N113" s="22" t="n"/>
-      <c r="O113" s="22" t="n"/>
-      <c r="P113" s="22" t="n"/>
-      <c r="Q113" s="22" t="n"/>
-      <c r="R113" s="22" t="n"/>
-      <c r="S113" s="22" t="n"/>
-      <c r="T113" s="22" t="n"/>
-      <c r="U113" s="22" t="n"/>
-      <c r="V113" s="22" t="n"/>
-      <c r="W113" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="14" customHeight="1">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>18. Comentarios, feedback y seguridad</t>
-        </is>
-      </c>
-      <c r="B114" s="22" t="n"/>
-      <c r="C114" s="22" t="n"/>
-      <c r="D114" s="22" t="n"/>
-      <c r="E114" s="22" t="n"/>
-      <c r="F114" s="25" t="n"/>
-      <c r="G114" s="25" t="n"/>
-      <c r="H114" s="25" t="n"/>
-      <c r="I114" s="25" t="n"/>
-      <c r="J114" s="25" t="n"/>
-      <c r="K114" s="22" t="n"/>
-      <c r="L114" s="22" t="n"/>
-      <c r="M114" s="22" t="n"/>
-      <c r="N114" s="22" t="n"/>
-      <c r="O114" s="22" t="n"/>
-      <c r="P114" s="22" t="n"/>
-      <c r="Q114" s="22" t="n"/>
-      <c r="R114" s="22" t="n"/>
-      <c r="S114" s="22" t="n"/>
-      <c r="T114" s="22" t="n"/>
-      <c r="U114" s="22" t="n"/>
-      <c r="V114" s="22" t="n"/>
-      <c r="W114" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A115" s="24" t="inlineStr">
-        <is>
-          <t>18.1 Comentarios de actividad</t>
-        </is>
-      </c>
-      <c r="B115" s="22" t="n"/>
-      <c r="C115" s="22" t="n"/>
-      <c r="D115" s="22" t="n"/>
-      <c r="E115" s="22" t="n"/>
-      <c r="F115" s="26" t="n"/>
-      <c r="G115" s="22" t="n"/>
-      <c r="H115" s="22" t="n"/>
-      <c r="I115" s="22" t="n"/>
-      <c r="J115" s="22" t="n"/>
-      <c r="K115" s="22" t="n"/>
-      <c r="L115" s="22" t="n"/>
-      <c r="M115" s="22" t="n"/>
-      <c r="N115" s="22" t="n"/>
-      <c r="O115" s="22" t="n"/>
-      <c r="P115" s="22" t="n"/>
-      <c r="Q115" s="22" t="n"/>
-      <c r="R115" s="22" t="n"/>
-      <c r="S115" s="22" t="n"/>
-      <c r="T115" s="22" t="n"/>
-      <c r="U115" s="22" t="n"/>
-      <c r="V115" s="22" t="n"/>
-      <c r="W115" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A116" s="24" t="inlineStr">
-        <is>
-          <t>18.2 Buzón de feedback</t>
-        </is>
-      </c>
-      <c r="B116" s="22" t="n"/>
-      <c r="C116" s="22" t="n"/>
-      <c r="D116" s="22" t="n"/>
-      <c r="E116" s="22" t="n"/>
-      <c r="F116" s="22" t="n"/>
-      <c r="G116" s="22" t="n"/>
-      <c r="H116" s="22" t="n"/>
-      <c r="I116" s="27" t="n"/>
-      <c r="J116" s="22" t="n"/>
-      <c r="K116" s="22" t="n"/>
-      <c r="L116" s="22" t="n"/>
-      <c r="M116" s="22" t="n"/>
-      <c r="N116" s="22" t="n"/>
-      <c r="O116" s="22" t="n"/>
-      <c r="P116" s="22" t="n"/>
-      <c r="Q116" s="22" t="n"/>
-      <c r="R116" s="22" t="n"/>
-      <c r="S116" s="22" t="n"/>
-      <c r="T116" s="22" t="n"/>
-      <c r="U116" s="22" t="n"/>
-      <c r="V116" s="22" t="n"/>
-      <c r="W116" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A117" s="24" t="inlineStr">
-        <is>
-          <t>18.3 Configuración de seguridad</t>
-        </is>
-      </c>
-      <c r="B117" s="22" t="n"/>
-      <c r="C117" s="22" t="n"/>
-      <c r="D117" s="22" t="n"/>
-      <c r="E117" s="22" t="n"/>
-      <c r="F117" s="22" t="n"/>
-      <c r="G117" s="22" t="n"/>
-      <c r="H117" s="22" t="n"/>
-      <c r="I117" s="28" t="n"/>
-      <c r="J117" s="22" t="n"/>
-      <c r="K117" s="22" t="n"/>
-      <c r="L117" s="22" t="n"/>
-      <c r="M117" s="22" t="n"/>
-      <c r="N117" s="22" t="n"/>
-      <c r="O117" s="22" t="n"/>
-      <c r="P117" s="22" t="n"/>
-      <c r="Q117" s="22" t="n"/>
-      <c r="R117" s="22" t="n"/>
-      <c r="S117" s="22" t="n"/>
-      <c r="T117" s="22" t="n"/>
-      <c r="U117" s="22" t="n"/>
-      <c r="V117" s="22" t="n"/>
-      <c r="W117" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A118" s="24" t="inlineStr">
-        <is>
-          <t>18.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B118" s="22" t="n"/>
-      <c r="C118" s="22" t="n"/>
-      <c r="D118" s="22" t="n"/>
-      <c r="E118" s="22" t="n"/>
-      <c r="F118" s="21" t="n"/>
-      <c r="G118" s="21" t="n"/>
-      <c r="H118" s="21" t="n"/>
-      <c r="I118" s="21" t="n"/>
-      <c r="J118" s="21" t="n"/>
-      <c r="K118" s="22" t="n"/>
-      <c r="L118" s="22" t="n"/>
-      <c r="M118" s="22" t="n"/>
-      <c r="N118" s="22" t="n"/>
-      <c r="O118" s="22" t="n"/>
-      <c r="P118" s="22" t="n"/>
-      <c r="Q118" s="22" t="n"/>
-      <c r="R118" s="22" t="n"/>
-      <c r="S118" s="22" t="n"/>
-      <c r="T118" s="22" t="n"/>
-      <c r="U118" s="22" t="n"/>
-      <c r="V118" s="22" t="n"/>
-      <c r="W118" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A119" s="24" t="inlineStr">
-        <is>
-          <t>18.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B119" s="22" t="n"/>
-      <c r="C119" s="22" t="n"/>
-      <c r="D119" s="22" t="n"/>
-      <c r="E119" s="22" t="n"/>
-      <c r="F119" s="25" t="n"/>
-      <c r="G119" s="25" t="n"/>
-      <c r="H119" s="25" t="n"/>
-      <c r="I119" s="25" t="n"/>
-      <c r="J119" s="25" t="n"/>
-      <c r="K119" s="22" t="n"/>
-      <c r="L119" s="22" t="n"/>
-      <c r="M119" s="22" t="n"/>
-      <c r="N119" s="22" t="n"/>
-      <c r="O119" s="22" t="n"/>
-      <c r="P119" s="22" t="n"/>
-      <c r="Q119" s="22" t="n"/>
-      <c r="R119" s="22" t="n"/>
-      <c r="S119" s="22" t="n"/>
-      <c r="T119" s="22" t="n"/>
-      <c r="U119" s="22" t="n"/>
-      <c r="V119" s="22" t="n"/>
-      <c r="W119" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="14" customHeight="1">
-      <c r="A120" s="20" t="inlineStr">
-        <is>
-          <t>19. Interfaz Tailwind y cierre</t>
-        </is>
-      </c>
-      <c r="B120" s="22" t="n"/>
-      <c r="C120" s="22" t="n"/>
-      <c r="D120" s="22" t="n"/>
-      <c r="E120" s="22" t="n"/>
-      <c r="F120" s="22" t="n"/>
-      <c r="G120" s="22" t="n"/>
-      <c r="H120" s="22" t="n"/>
-      <c r="I120" s="22" t="n"/>
-      <c r="J120" s="22" t="n"/>
-      <c r="K120" s="26" t="n"/>
-      <c r="L120" s="26" t="n"/>
-      <c r="M120" s="26" t="n"/>
-      <c r="N120" s="26" t="n"/>
-      <c r="O120" s="26" t="n"/>
-      <c r="P120" s="26" t="n"/>
-      <c r="Q120" s="26" t="n"/>
-      <c r="R120" s="26" t="n"/>
-      <c r="S120" s="26" t="n"/>
-      <c r="T120" s="26" t="n"/>
-      <c r="U120" s="22" t="n"/>
-      <c r="V120" s="22" t="n"/>
-      <c r="W120" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A121" s="24" t="inlineStr">
-        <is>
-          <t>19.1 Maquetación con Tailwind</t>
-        </is>
-      </c>
-      <c r="B121" s="22" t="n"/>
-      <c r="C121" s="22" t="n"/>
-      <c r="D121" s="22" t="n"/>
-      <c r="E121" s="22" t="n"/>
-      <c r="F121" s="22" t="n"/>
-      <c r="G121" s="22" t="n"/>
-      <c r="H121" s="22" t="n"/>
-      <c r="I121" s="22" t="n"/>
-      <c r="J121" s="22" t="n"/>
-      <c r="K121" s="27" t="n"/>
-      <c r="L121" s="22" t="n"/>
-      <c r="M121" s="22" t="n"/>
-      <c r="N121" s="22" t="n"/>
-      <c r="O121" s="22" t="n"/>
-      <c r="P121" s="22" t="n"/>
-      <c r="Q121" s="22" t="n"/>
-      <c r="R121" s="22" t="n"/>
-      <c r="S121" s="22" t="n"/>
-      <c r="T121" s="22" t="n"/>
-      <c r="U121" s="22" t="n"/>
-      <c r="V121" s="22" t="n"/>
-      <c r="W121" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A122" s="24" t="inlineStr">
-        <is>
-          <t>19.2 Revisión visual</t>
-        </is>
-      </c>
-      <c r="B122" s="22" t="n"/>
-      <c r="C122" s="22" t="n"/>
-      <c r="D122" s="22" t="n"/>
-      <c r="E122" s="22" t="n"/>
-      <c r="F122" s="22" t="n"/>
-      <c r="G122" s="22" t="n"/>
-      <c r="H122" s="22" t="n"/>
-      <c r="I122" s="22" t="n"/>
-      <c r="J122" s="22" t="n"/>
-      <c r="K122" s="22" t="n"/>
-      <c r="L122" s="28" t="n"/>
-      <c r="M122" s="22" t="n"/>
-      <c r="N122" s="22" t="n"/>
-      <c r="O122" s="22" t="n"/>
-      <c r="P122" s="22" t="n"/>
-      <c r="Q122" s="22" t="n"/>
-      <c r="R122" s="22" t="n"/>
-      <c r="S122" s="22" t="n"/>
-      <c r="T122" s="22" t="n"/>
-      <c r="U122" s="22" t="n"/>
-      <c r="V122" s="22" t="n"/>
-      <c r="W122" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A123" s="24" t="inlineStr">
-        <is>
-          <t>19.3 Cierre y revisión</t>
-        </is>
-      </c>
-      <c r="B123" s="22" t="n"/>
-      <c r="C123" s="22" t="n"/>
-      <c r="D123" s="22" t="n"/>
-      <c r="E123" s="22" t="n"/>
-      <c r="F123" s="22" t="n"/>
-      <c r="G123" s="22" t="n"/>
-      <c r="H123" s="22" t="n"/>
-      <c r="I123" s="22" t="n"/>
-      <c r="J123" s="22" t="n"/>
-      <c r="K123" s="22" t="n"/>
-      <c r="L123" s="21" t="n"/>
-      <c r="M123" s="22" t="n"/>
-      <c r="N123" s="22" t="n"/>
-      <c r="O123" s="22" t="n"/>
-      <c r="P123" s="22" t="n"/>
-      <c r="Q123" s="22" t="n"/>
-      <c r="R123" s="22" t="n"/>
-      <c r="S123" s="22" t="n"/>
-      <c r="T123" s="22" t="n"/>
-      <c r="U123" s="22" t="n"/>
-      <c r="V123" s="22" t="n"/>
-      <c r="W123" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A124" s="24" t="inlineStr">
-        <is>
-          <t>19.4 Testeo</t>
-        </is>
-      </c>
-      <c r="B124" s="22" t="n"/>
-      <c r="C124" s="22" t="n"/>
-      <c r="D124" s="22" t="n"/>
-      <c r="E124" s="22" t="n"/>
-      <c r="F124" s="22" t="n"/>
-      <c r="G124" s="22" t="n"/>
-      <c r="H124" s="22" t="n"/>
-      <c r="I124" s="22" t="n"/>
-      <c r="J124" s="22" t="n"/>
-      <c r="K124" s="25" t="n"/>
-      <c r="L124" s="25" t="n"/>
-      <c r="M124" s="25" t="n"/>
-      <c r="N124" s="25" t="n"/>
-      <c r="O124" s="25" t="n"/>
-      <c r="P124" s="25" t="n"/>
-      <c r="Q124" s="25" t="n"/>
-      <c r="R124" s="25" t="n"/>
-      <c r="S124" s="25" t="n"/>
-      <c r="T124" s="25" t="n"/>
-      <c r="U124" s="22" t="n"/>
-      <c r="V124" s="22" t="n"/>
-      <c r="W124" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" outlineLevel="1" ht="14" customHeight="1">
-      <c r="A125" s="24" t="inlineStr">
-        <is>
-          <t>19.5 Documentación</t>
-        </is>
-      </c>
-      <c r="B125" s="22" t="n"/>
-      <c r="C125" s="22" t="n"/>
-      <c r="D125" s="22" t="n"/>
-      <c r="E125" s="22" t="n"/>
-      <c r="F125" s="22" t="n"/>
-      <c r="G125" s="22" t="n"/>
-      <c r="H125" s="22" t="n"/>
-      <c r="I125" s="22" t="n"/>
-      <c r="J125" s="22" t="n"/>
-      <c r="K125" s="26" t="n"/>
-      <c r="L125" s="26" t="n"/>
-      <c r="M125" s="26" t="n"/>
-      <c r="N125" s="26" t="n"/>
-      <c r="O125" s="26" t="n"/>
-      <c r="P125" s="26" t="n"/>
-      <c r="Q125" s="26" t="n"/>
-      <c r="R125" s="26" t="n"/>
-      <c r="S125" s="26" t="n"/>
-      <c r="T125" s="26" t="n"/>
-      <c r="U125" s="22" t="n"/>
-      <c r="V125" s="22" t="n"/>
-      <c r="W125" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="22" t="n"/>
-      <c r="B126" s="22" t="n"/>
-      <c r="C126" s="22" t="n"/>
-      <c r="D126" s="22" t="n"/>
-      <c r="E126" s="22" t="n"/>
-      <c r="F126" s="22" t="n"/>
-      <c r="G126" s="22" t="n"/>
-      <c r="H126" s="22" t="n"/>
-      <c r="I126" s="22" t="n"/>
-      <c r="J126" s="22" t="n"/>
-      <c r="K126" s="22" t="n"/>
-      <c r="L126" s="22" t="n"/>
-      <c r="M126" s="22" t="n"/>
-      <c r="N126" s="22" t="n"/>
-      <c r="O126" s="22" t="n"/>
-      <c r="P126" s="22" t="n"/>
-      <c r="Q126" s="22" t="n"/>
-      <c r="R126" s="22" t="n"/>
-      <c r="S126" s="22" t="n"/>
-      <c r="T126" s="22" t="n"/>
-      <c r="U126" s="22" t="n"/>
-      <c r="V126" s="22" t="n"/>
-      <c r="W126" s="22" t="n"/>
-    </row>
-    <row r="127" ht="14" customHeight="1">
-      <c r="A127" s="22" t="n"/>
-      <c r="B127" s="22" t="n"/>
-      <c r="C127" s="22" t="n"/>
-      <c r="D127" s="22" t="n"/>
-      <c r="E127" s="22" t="n"/>
-      <c r="F127" s="22" t="n"/>
-      <c r="G127" s="22" t="n"/>
-      <c r="H127" s="22" t="n"/>
-      <c r="I127" s="22" t="n"/>
-      <c r="J127" s="22" t="n"/>
-      <c r="K127" s="22" t="n"/>
-      <c r="L127" s="22" t="n"/>
-      <c r="M127" s="22" t="n"/>
-      <c r="N127" s="22" t="n"/>
-      <c r="O127" s="22" t="n"/>
-      <c r="P127" s="22" t="n"/>
-      <c r="Q127" s="22" t="n"/>
-      <c r="R127" s="22" t="n"/>
-      <c r="S127" s="22" t="n"/>
-      <c r="T127" s="22" t="n"/>
-      <c r="U127" s="22" t="n"/>
-      <c r="V127" s="22" t="n"/>
-      <c r="W127" s="22" t="n"/>
-    </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="22" t="n"/>
-      <c r="B128" s="22" t="n"/>
-      <c r="C128" s="22" t="n"/>
-      <c r="D128" s="22" t="n"/>
-      <c r="E128" s="22" t="n"/>
-      <c r="F128" s="22" t="n"/>
-      <c r="G128" s="22" t="n"/>
-      <c r="H128" s="22" t="n"/>
-      <c r="I128" s="22" t="n"/>
-      <c r="J128" s="22" t="n"/>
-      <c r="K128" s="22" t="n"/>
-      <c r="L128" s="22" t="n"/>
-      <c r="M128" s="22" t="n"/>
-      <c r="N128" s="22" t="n"/>
-      <c r="O128" s="22" t="n"/>
-      <c r="P128" s="22" t="n"/>
-      <c r="Q128" s="22" t="n"/>
-      <c r="R128" s="22" t="n"/>
-      <c r="S128" s="22" t="n"/>
-      <c r="T128" s="22" t="n"/>
-      <c r="U128" s="22" t="n"/>
-      <c r="V128" s="22" t="n"/>
-      <c r="W128" s="22" t="n"/>
-    </row>
-    <row r="129" ht="14" customHeight="1">
-      <c r="A129" s="22" t="n"/>
-      <c r="B129" s="22" t="n"/>
-      <c r="C129" s="22" t="n"/>
-      <c r="D129" s="22" t="n"/>
-      <c r="E129" s="22" t="n"/>
-      <c r="F129" s="22" t="n"/>
-      <c r="G129" s="22" t="n"/>
-      <c r="H129" s="22" t="n"/>
-      <c r="I129" s="22" t="n"/>
-      <c r="J129" s="22" t="n"/>
-      <c r="K129" s="22" t="n"/>
-      <c r="L129" s="22" t="n"/>
-      <c r="M129" s="22" t="n"/>
-      <c r="N129" s="22" t="n"/>
-      <c r="O129" s="22" t="n"/>
-      <c r="P129" s="22" t="n"/>
-      <c r="Q129" s="22" t="n"/>
-      <c r="R129" s="22" t="n"/>
-      <c r="S129" s="22" t="n"/>
-      <c r="T129" s="22" t="n"/>
-      <c r="U129" s="22" t="n"/>
-      <c r="V129" s="22" t="n"/>
-      <c r="W129" s="22" t="n"/>
+      <c r="W101" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/docs/Spartum_Gantt.xlsx
+++ b/docs/Spartum_Gantt.xlsx
@@ -11,11 +11,7 @@
     <sheet name="Planificación Mes 2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Planificación Mes 3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Planificación Mes 1'!$A$1:$AD$101</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Planificación Mes 2'!$A$1:$AD$101</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Planificación Mes 3'!$A$1:$W$101</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,6 +29,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FF0000"/>
       <sz val="22"/>
@@ -42,11 +43,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -95,9 +91,6 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EC5E61"/>
       </patternFill>
@@ -111,6 +104,9 @@
       <patternFill patternType="solid">
         <fgColor rgb="00008000"/>
       </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -201,83 +197,6 @@
       </bottom>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="00F4883C"/>
       </left>
@@ -347,29 +266,106 @@
         <color rgb="00FAE29C"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -379,11 +375,11 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -395,44 +391,44 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -802,7 +798,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AD101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
@@ -1972,9 +1968,9 @@
       <c r="AA26" s="22" t="n"/>
       <c r="AB26" s="22" t="n"/>
       <c r="AC26" s="22" t="n"/>
-      <c r="AD26" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD26" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2057,7 @@
     <row r="29" outlineLevel="1" ht="14" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>4.3 Baja y reactivación</t>
+          <t>4.3 Baja: al redirigir se pierde la sesión</t>
         </is>
       </c>
       <c r="B29" s="22" t="n"/>
@@ -2092,9 +2088,9 @@
       <c r="AA29" s="22" t="n"/>
       <c r="AB29" s="22" t="n"/>
       <c r="AC29" s="22" t="n"/>
-      <c r="AD29" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD29" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -2132,9 +2128,9 @@
       <c r="AA30" s="22" t="n"/>
       <c r="AB30" s="22" t="n"/>
       <c r="AC30" s="22" t="n"/>
-      <c r="AD30" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD30" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -2172,9 +2168,9 @@
       <c r="AA31" s="22" t="n"/>
       <c r="AB31" s="22" t="n"/>
       <c r="AC31" s="22" t="n"/>
-      <c r="AD31" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD31" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2217,7 @@
     <row r="33" outlineLevel="1" ht="14" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>5.1 Listado de actividades</t>
+          <t>5.1 Listado descuadrado</t>
         </is>
       </c>
       <c r="B33" s="22" t="n"/>
@@ -2252,16 +2248,16 @@
       <c r="AA33" s="22" t="n"/>
       <c r="AB33" s="22" t="n"/>
       <c r="AC33" s="22" t="n"/>
-      <c r="AD33" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD33" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="34" outlineLevel="1" ht="14" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>5.2 Horario y avisos → inscritos</t>
+          <t>5.2 Horario con uniformidad</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
@@ -2292,9 +2288,9 @@
       <c r="AA34" s="22" t="n"/>
       <c r="AB34" s="22" t="n"/>
       <c r="AC34" s="22" t="n"/>
-      <c r="AD34" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD34" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -2332,9 +2328,9 @@
       <c r="AA35" s="22" t="n"/>
       <c r="AB35" s="22" t="n"/>
       <c r="AC35" s="22" t="n"/>
-      <c r="AD35" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD35" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -2692,9 +2688,9 @@
       <c r="AA44" s="22" t="n"/>
       <c r="AB44" s="22" t="n"/>
       <c r="AC44" s="22" t="n"/>
-      <c r="AD44" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD44" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -2732,9 +2728,9 @@
       <c r="AA45" s="22" t="n"/>
       <c r="AB45" s="22" t="n"/>
       <c r="AC45" s="22" t="n"/>
-      <c r="AD45" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD45" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -2772,9 +2768,9 @@
       <c r="AA46" s="22" t="n"/>
       <c r="AB46" s="22" t="n"/>
       <c r="AC46" s="22" t="n"/>
-      <c r="AD46" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD46" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -2812,9 +2808,9 @@
       <c r="AA47" s="22" t="n"/>
       <c r="AB47" s="22" t="n"/>
       <c r="AC47" s="22" t="n"/>
-      <c r="AD47" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD47" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -2852,9 +2848,9 @@
       <c r="AA48" s="22" t="n"/>
       <c r="AB48" s="22" t="n"/>
       <c r="AC48" s="22" t="n"/>
-      <c r="AD48" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD48" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -2892,9 +2888,9 @@
       <c r="AA49" s="22" t="n"/>
       <c r="AB49" s="22" t="n"/>
       <c r="AC49" s="22" t="n"/>
-      <c r="AD49" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD49" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2977,7 @@
     <row r="52" outlineLevel="1" ht="14" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>8.2 Confirmación del pago</t>
+          <t>8.2 Guardar el método de pago</t>
         </is>
       </c>
       <c r="B52" s="22" t="n"/>
@@ -3181,7 +3177,7 @@
     <row r="57" outlineLevel="1" ht="14" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>9.1 Inicio del panel</t>
+          <t>9.1 Vista de admin descuadrada</t>
         </is>
       </c>
       <c r="B57" s="22" t="n"/>
@@ -3501,7 +3497,7 @@
     <row r="65" outlineLevel="1" ht="14" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>10.3 Edición de datos</t>
+          <t>10.3 Impersonalidad: usuario1</t>
         </is>
       </c>
       <c r="B65" s="22" t="n"/>
@@ -3621,7 +3617,7 @@
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>11. Monitores y solicitudes</t>
+          <t>11. Monitores y reportes</t>
         </is>
       </c>
       <c r="B68" s="22" t="n"/>
@@ -3661,7 +3657,7 @@
     <row r="69" outlineLevel="1" ht="14" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>11.1 Alta de monitores</t>
+          <t>11.1 Impersonalidad: monitor1</t>
         </is>
       </c>
       <c r="B69" s="22" t="n"/>
@@ -3701,7 +3697,7 @@
     <row r="70" outlineLevel="1" ht="14" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>11.2 Solicitudes de clase</t>
+          <t>11.2 De solicitudes a reportes</t>
         </is>
       </c>
       <c r="B70" s="22" t="n"/>
@@ -3901,7 +3897,7 @@
     <row r="75" outlineLevel="1" ht="14" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>12.1 Ficha de salas</t>
+          <t>12.1 Colores de salas y actividades</t>
         </is>
       </c>
       <c r="B75" s="22" t="n"/>
@@ -4652,9 +4648,9 @@
       <c r="AA93" s="22" t="n"/>
       <c r="AB93" s="22" t="n"/>
       <c r="AC93" s="22" t="n"/>
-      <c r="AD93" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD93" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -4692,9 +4688,9 @@
       <c r="AA94" s="25" t="n"/>
       <c r="AB94" s="22" t="n"/>
       <c r="AC94" s="22" t="n"/>
-      <c r="AD94" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD94" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -4952,12 +4948,12 @@
     <mergeCell ref="I5:O5"/>
     <mergeCell ref="P5:V5"/>
     <mergeCell ref="W4:AC4"/>
+    <mergeCell ref="AD4:AD7"/>
+    <mergeCell ref="B4:H4"/>
     <mergeCell ref="W5:AC5"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="AD4:AD7"/>
     <mergeCell ref="P4:V4"/>
+    <mergeCell ref="A2:AD2"/>
     <mergeCell ref="I4:O4"/>
-    <mergeCell ref="A2:AD2"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="A1:AD1"/>
   </mergeCells>
@@ -4975,7 +4971,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AD101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
@@ -6117,7 +6113,7 @@
           <t>4. Perfil, contraseña y baja</t>
         </is>
       </c>
-      <c r="B26" s="22" t="n"/>
+      <c r="B26" s="27" t="n"/>
       <c r="C26" s="22" t="n"/>
       <c r="D26" s="22" t="n"/>
       <c r="E26" s="22" t="n"/>
@@ -6145,9 +6141,9 @@
       <c r="AA26" s="22" t="n"/>
       <c r="AB26" s="22" t="n"/>
       <c r="AC26" s="22" t="n"/>
-      <c r="AD26" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD26" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -6234,10 +6230,10 @@
     <row r="29" outlineLevel="1" ht="14" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>4.3 Baja y reactivación</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="n"/>
+          <t>4.3 Baja: al redirigir se pierde la sesión</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="n"/>
       <c r="C29" s="22" t="n"/>
       <c r="D29" s="22" t="n"/>
       <c r="E29" s="22" t="n"/>
@@ -6265,9 +6261,9 @@
       <c r="AA29" s="22" t="n"/>
       <c r="AB29" s="22" t="n"/>
       <c r="AC29" s="22" t="n"/>
-      <c r="AD29" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD29" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6273,7 @@
           <t>4.4 Testeo</t>
         </is>
       </c>
-      <c r="B30" s="22" t="n"/>
+      <c r="B30" s="26" t="n"/>
       <c r="C30" s="22" t="n"/>
       <c r="D30" s="22" t="n"/>
       <c r="E30" s="22" t="n"/>
@@ -6305,9 +6301,9 @@
       <c r="AA30" s="22" t="n"/>
       <c r="AB30" s="22" t="n"/>
       <c r="AC30" s="22" t="n"/>
-      <c r="AD30" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD30" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6313,7 @@
           <t>4.5 Documentación</t>
         </is>
       </c>
-      <c r="B31" s="22" t="n"/>
+      <c r="B31" s="27" t="n"/>
       <c r="C31" s="22" t="n"/>
       <c r="D31" s="22" t="n"/>
       <c r="E31" s="22" t="n"/>
@@ -6345,9 +6341,9 @@
       <c r="AA31" s="22" t="n"/>
       <c r="AB31" s="22" t="n"/>
       <c r="AC31" s="22" t="n"/>
-      <c r="AD31" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD31" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -6360,8 +6356,8 @@
       <c r="B32" s="22" t="n"/>
       <c r="C32" s="22" t="n"/>
       <c r="D32" s="22" t="n"/>
-      <c r="E32" s="22" t="n"/>
-      <c r="F32" s="22" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="28" t="n"/>
       <c r="G32" s="22" t="n"/>
       <c r="H32" s="22" t="n"/>
       <c r="I32" s="22" t="n"/>
@@ -6394,13 +6390,13 @@
     <row r="33" outlineLevel="1" ht="14" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>5.1 Listado de actividades</t>
+          <t>5.1 Listado descuadrado</t>
         </is>
       </c>
       <c r="B33" s="22" t="n"/>
       <c r="C33" s="22" t="n"/>
       <c r="D33" s="22" t="n"/>
-      <c r="E33" s="22" t="n"/>
+      <c r="E33" s="21" t="n"/>
       <c r="F33" s="22" t="n"/>
       <c r="G33" s="22" t="n"/>
       <c r="H33" s="22" t="n"/>
@@ -6425,23 +6421,23 @@
       <c r="AA33" s="22" t="n"/>
       <c r="AB33" s="22" t="n"/>
       <c r="AC33" s="22" t="n"/>
-      <c r="AD33" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD33" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="34" outlineLevel="1" ht="14" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>5.2 Horario y avisos → inscritos</t>
+          <t>5.2 Horario con uniformidad</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
       <c r="C34" s="22" t="n"/>
       <c r="D34" s="22" t="n"/>
       <c r="E34" s="22" t="n"/>
-      <c r="F34" s="22" t="n"/>
+      <c r="F34" s="25" t="n"/>
       <c r="G34" s="22" t="n"/>
       <c r="H34" s="22" t="n"/>
       <c r="I34" s="22" t="n"/>
@@ -6465,9 +6461,9 @@
       <c r="AA34" s="22" t="n"/>
       <c r="AB34" s="22" t="n"/>
       <c r="AC34" s="22" t="n"/>
-      <c r="AD34" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="AD34" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -6505,9 +6501,9 @@
       <c r="AA35" s="22" t="n"/>
       <c r="AB35" s="22" t="n"/>
       <c r="AC35" s="22" t="n"/>
-      <c r="AD35" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD35" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -6520,8 +6516,8 @@
       <c r="B36" s="22" t="n"/>
       <c r="C36" s="22" t="n"/>
       <c r="D36" s="22" t="n"/>
-      <c r="E36" s="22" t="n"/>
-      <c r="F36" s="22" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="27" t="n"/>
       <c r="G36" s="22" t="n"/>
       <c r="H36" s="22" t="n"/>
       <c r="I36" s="22" t="n"/>
@@ -6560,8 +6556,8 @@
       <c r="B37" s="22" t="n"/>
       <c r="C37" s="22" t="n"/>
       <c r="D37" s="22" t="n"/>
-      <c r="E37" s="22" t="n"/>
-      <c r="F37" s="22" t="n"/>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="28" t="n"/>
       <c r="G37" s="22" t="n"/>
       <c r="H37" s="22" t="n"/>
       <c r="I37" s="22" t="n"/>
@@ -6597,18 +6593,18 @@
           <t>6. Inscripciones y reservas</t>
         </is>
       </c>
-      <c r="B38" s="21" t="n"/>
-      <c r="C38" s="21" t="n"/>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="21" t="n"/>
+      <c r="B38" s="22" t="n"/>
+      <c r="C38" s="22" t="n"/>
+      <c r="D38" s="22" t="n"/>
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="22" t="n"/>
       <c r="G38" s="22" t="n"/>
       <c r="H38" s="22" t="n"/>
-      <c r="I38" s="22" t="n"/>
-      <c r="J38" s="22" t="n"/>
-      <c r="K38" s="22" t="n"/>
-      <c r="L38" s="22" t="n"/>
-      <c r="M38" s="22" t="n"/>
+      <c r="I38" s="21" t="n"/>
+      <c r="J38" s="21" t="n"/>
+      <c r="K38" s="21" t="n"/>
+      <c r="L38" s="21" t="n"/>
+      <c r="M38" s="21" t="n"/>
       <c r="N38" s="22" t="n"/>
       <c r="O38" s="22" t="n"/>
       <c r="P38" s="22" t="n"/>
@@ -6637,14 +6633,14 @@
           <t>6.1 Formulario de inscripción</t>
         </is>
       </c>
-      <c r="B39" s="25" t="n"/>
+      <c r="B39" s="22" t="n"/>
       <c r="C39" s="22" t="n"/>
       <c r="D39" s="22" t="n"/>
       <c r="E39" s="22" t="n"/>
       <c r="F39" s="22" t="n"/>
       <c r="G39" s="22" t="n"/>
       <c r="H39" s="22" t="n"/>
-      <c r="I39" s="22" t="n"/>
+      <c r="I39" s="25" t="n"/>
       <c r="J39" s="22" t="n"/>
       <c r="K39" s="22" t="n"/>
       <c r="L39" s="22" t="n"/>
@@ -6680,14 +6676,14 @@
       <c r="B40" s="22" t="n"/>
       <c r="C40" s="22" t="n"/>
       <c r="D40" s="22" t="n"/>
-      <c r="E40" s="26" t="n"/>
+      <c r="E40" s="22" t="n"/>
       <c r="F40" s="22" t="n"/>
       <c r="G40" s="22" t="n"/>
       <c r="H40" s="22" t="n"/>
       <c r="I40" s="22" t="n"/>
       <c r="J40" s="22" t="n"/>
       <c r="K40" s="22" t="n"/>
-      <c r="L40" s="22" t="n"/>
+      <c r="L40" s="26" t="n"/>
       <c r="M40" s="22" t="n"/>
       <c r="N40" s="22" t="n"/>
       <c r="O40" s="22" t="n"/>
@@ -6720,14 +6716,14 @@
       <c r="B41" s="22" t="n"/>
       <c r="C41" s="22" t="n"/>
       <c r="D41" s="22" t="n"/>
-      <c r="E41" s="27" t="n"/>
+      <c r="E41" s="22" t="n"/>
       <c r="F41" s="22" t="n"/>
       <c r="G41" s="22" t="n"/>
       <c r="H41" s="22" t="n"/>
       <c r="I41" s="22" t="n"/>
       <c r="J41" s="22" t="n"/>
       <c r="K41" s="22" t="n"/>
-      <c r="L41" s="22" t="n"/>
+      <c r="L41" s="27" t="n"/>
       <c r="M41" s="22" t="n"/>
       <c r="N41" s="22" t="n"/>
       <c r="O41" s="22" t="n"/>
@@ -6757,18 +6753,18 @@
           <t>6.4 Testeo</t>
         </is>
       </c>
-      <c r="B42" s="28" t="n"/>
-      <c r="C42" s="28" t="n"/>
-      <c r="D42" s="28" t="n"/>
-      <c r="E42" s="28" t="n"/>
-      <c r="F42" s="28" t="n"/>
+      <c r="B42" s="22" t="n"/>
+      <c r="C42" s="22" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="22" t="n"/>
       <c r="G42" s="22" t="n"/>
       <c r="H42" s="22" t="n"/>
-      <c r="I42" s="22" t="n"/>
-      <c r="J42" s="22" t="n"/>
-      <c r="K42" s="22" t="n"/>
-      <c r="L42" s="22" t="n"/>
-      <c r="M42" s="22" t="n"/>
+      <c r="I42" s="28" t="n"/>
+      <c r="J42" s="28" t="n"/>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="28" t="n"/>
+      <c r="M42" s="28" t="n"/>
       <c r="N42" s="22" t="n"/>
       <c r="O42" s="22" t="n"/>
       <c r="P42" s="22" t="n"/>
@@ -6797,18 +6793,18 @@
           <t>6.5 Documentación</t>
         </is>
       </c>
-      <c r="B43" s="21" t="n"/>
-      <c r="C43" s="21" t="n"/>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="21" t="n"/>
-      <c r="F43" s="21" t="n"/>
+      <c r="B43" s="22" t="n"/>
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="22" t="n"/>
+      <c r="E43" s="22" t="n"/>
+      <c r="F43" s="22" t="n"/>
       <c r="G43" s="22" t="n"/>
       <c r="H43" s="22" t="n"/>
-      <c r="I43" s="22" t="n"/>
-      <c r="J43" s="22" t="n"/>
-      <c r="K43" s="22" t="n"/>
-      <c r="L43" s="22" t="n"/>
-      <c r="M43" s="22" t="n"/>
+      <c r="I43" s="21" t="n"/>
+      <c r="J43" s="21" t="n"/>
+      <c r="K43" s="21" t="n"/>
+      <c r="L43" s="21" t="n"/>
+      <c r="M43" s="21" t="n"/>
       <c r="N43" s="22" t="n"/>
       <c r="O43" s="22" t="n"/>
       <c r="P43" s="22" t="n"/>
@@ -6865,9 +6861,9 @@
       <c r="AA44" s="22" t="n"/>
       <c r="AB44" s="22" t="n"/>
       <c r="AC44" s="22" t="n"/>
-      <c r="AD44" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD44" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -6905,9 +6901,9 @@
       <c r="AA45" s="22" t="n"/>
       <c r="AB45" s="22" t="n"/>
       <c r="AC45" s="22" t="n"/>
-      <c r="AD45" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD45" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -6945,9 +6941,9 @@
       <c r="AA46" s="22" t="n"/>
       <c r="AB46" s="22" t="n"/>
       <c r="AC46" s="22" t="n"/>
-      <c r="AD46" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD46" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -6985,9 +6981,9 @@
       <c r="AA47" s="22" t="n"/>
       <c r="AB47" s="22" t="n"/>
       <c r="AC47" s="22" t="n"/>
-      <c r="AD47" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD47" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -7025,9 +7021,9 @@
       <c r="AA48" s="22" t="n"/>
       <c r="AB48" s="22" t="n"/>
       <c r="AC48" s="22" t="n"/>
-      <c r="AD48" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD48" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -7065,9 +7061,9 @@
       <c r="AA49" s="22" t="n"/>
       <c r="AB49" s="22" t="n"/>
       <c r="AC49" s="22" t="n"/>
-      <c r="AD49" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD49" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -7078,24 +7074,24 @@
         </is>
       </c>
       <c r="B50" s="22" t="n"/>
-      <c r="C50" s="22" t="n"/>
+      <c r="C50" s="26" t="n"/>
       <c r="D50" s="22" t="n"/>
       <c r="E50" s="22" t="n"/>
       <c r="F50" s="22" t="n"/>
       <c r="G50" s="22" t="n"/>
       <c r="H50" s="22" t="n"/>
-      <c r="I50" s="26" t="n"/>
-      <c r="J50" s="26" t="n"/>
-      <c r="K50" s="26" t="n"/>
-      <c r="L50" s="26" t="n"/>
-      <c r="M50" s="26" t="n"/>
+      <c r="I50" s="22" t="n"/>
+      <c r="J50" s="22" t="n"/>
+      <c r="K50" s="22" t="n"/>
+      <c r="L50" s="22" t="n"/>
+      <c r="M50" s="22" t="n"/>
       <c r="N50" s="22" t="n"/>
       <c r="O50" s="22" t="n"/>
-      <c r="P50" s="22" t="n"/>
-      <c r="Q50" s="22" t="n"/>
-      <c r="R50" s="22" t="n"/>
-      <c r="S50" s="22" t="n"/>
-      <c r="T50" s="22" t="n"/>
+      <c r="P50" s="26" t="n"/>
+      <c r="Q50" s="26" t="n"/>
+      <c r="R50" s="26" t="n"/>
+      <c r="S50" s="26" t="n"/>
+      <c r="T50" s="26" t="n"/>
       <c r="U50" s="22" t="n"/>
       <c r="V50" s="22" t="n"/>
       <c r="W50" s="22" t="n"/>
@@ -7124,14 +7120,14 @@
       <c r="F51" s="22" t="n"/>
       <c r="G51" s="22" t="n"/>
       <c r="H51" s="22" t="n"/>
-      <c r="I51" s="27" t="n"/>
+      <c r="I51" s="22" t="n"/>
       <c r="J51" s="22" t="n"/>
       <c r="K51" s="22" t="n"/>
       <c r="L51" s="22" t="n"/>
       <c r="M51" s="22" t="n"/>
       <c r="N51" s="22" t="n"/>
       <c r="O51" s="22" t="n"/>
-      <c r="P51" s="22" t="n"/>
+      <c r="P51" s="27" t="n"/>
       <c r="Q51" s="22" t="n"/>
       <c r="R51" s="22" t="n"/>
       <c r="S51" s="22" t="n"/>
@@ -7154,11 +7150,11 @@
     <row r="52" outlineLevel="1" ht="14" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>8.2 Confirmación del pago</t>
+          <t>8.2 Guardar el método de pago</t>
         </is>
       </c>
       <c r="B52" s="22" t="n"/>
-      <c r="C52" s="22" t="n"/>
+      <c r="C52" s="28" t="n"/>
       <c r="D52" s="22" t="n"/>
       <c r="E52" s="22" t="n"/>
       <c r="F52" s="22" t="n"/>
@@ -7167,7 +7163,7 @@
       <c r="I52" s="22" t="n"/>
       <c r="J52" s="22" t="n"/>
       <c r="K52" s="22" t="n"/>
-      <c r="L52" s="28" t="n"/>
+      <c r="L52" s="22" t="n"/>
       <c r="M52" s="22" t="n"/>
       <c r="N52" s="22" t="n"/>
       <c r="O52" s="22" t="n"/>
@@ -7207,14 +7203,14 @@
       <c r="I53" s="22" t="n"/>
       <c r="J53" s="22" t="n"/>
       <c r="K53" s="22" t="n"/>
-      <c r="L53" s="21" t="n"/>
+      <c r="L53" s="22" t="n"/>
       <c r="M53" s="22" t="n"/>
       <c r="N53" s="22" t="n"/>
       <c r="O53" s="22" t="n"/>
       <c r="P53" s="22" t="n"/>
       <c r="Q53" s="22" t="n"/>
       <c r="R53" s="22" t="n"/>
-      <c r="S53" s="22" t="n"/>
+      <c r="S53" s="21" t="n"/>
       <c r="T53" s="22" t="n"/>
       <c r="U53" s="22" t="n"/>
       <c r="V53" s="22" t="n"/>
@@ -7238,24 +7234,24 @@
         </is>
       </c>
       <c r="B54" s="22" t="n"/>
-      <c r="C54" s="22" t="n"/>
+      <c r="C54" s="25" t="n"/>
       <c r="D54" s="22" t="n"/>
       <c r="E54" s="22" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="22" t="n"/>
       <c r="H54" s="22" t="n"/>
-      <c r="I54" s="25" t="n"/>
-      <c r="J54" s="25" t="n"/>
-      <c r="K54" s="25" t="n"/>
-      <c r="L54" s="25" t="n"/>
-      <c r="M54" s="25" t="n"/>
+      <c r="I54" s="22" t="n"/>
+      <c r="J54" s="22" t="n"/>
+      <c r="K54" s="22" t="n"/>
+      <c r="L54" s="22" t="n"/>
+      <c r="M54" s="22" t="n"/>
       <c r="N54" s="22" t="n"/>
       <c r="O54" s="22" t="n"/>
-      <c r="P54" s="22" t="n"/>
-      <c r="Q54" s="22" t="n"/>
-      <c r="R54" s="22" t="n"/>
-      <c r="S54" s="22" t="n"/>
-      <c r="T54" s="22" t="n"/>
+      <c r="P54" s="25" t="n"/>
+      <c r="Q54" s="25" t="n"/>
+      <c r="R54" s="25" t="n"/>
+      <c r="S54" s="25" t="n"/>
+      <c r="T54" s="25" t="n"/>
       <c r="U54" s="22" t="n"/>
       <c r="V54" s="22" t="n"/>
       <c r="W54" s="22" t="n"/>
@@ -7278,24 +7274,24 @@
         </is>
       </c>
       <c r="B55" s="22" t="n"/>
-      <c r="C55" s="22" t="n"/>
+      <c r="C55" s="26" t="n"/>
       <c r="D55" s="22" t="n"/>
       <c r="E55" s="22" t="n"/>
       <c r="F55" s="22" t="n"/>
       <c r="G55" s="22" t="n"/>
       <c r="H55" s="22" t="n"/>
-      <c r="I55" s="26" t="n"/>
-      <c r="J55" s="26" t="n"/>
-      <c r="K55" s="26" t="n"/>
-      <c r="L55" s="26" t="n"/>
-      <c r="M55" s="26" t="n"/>
+      <c r="I55" s="22" t="n"/>
+      <c r="J55" s="22" t="n"/>
+      <c r="K55" s="22" t="n"/>
+      <c r="L55" s="22" t="n"/>
+      <c r="M55" s="22" t="n"/>
       <c r="N55" s="22" t="n"/>
       <c r="O55" s="22" t="n"/>
-      <c r="P55" s="22" t="n"/>
-      <c r="Q55" s="22" t="n"/>
-      <c r="R55" s="22" t="n"/>
-      <c r="S55" s="22" t="n"/>
-      <c r="T55" s="22" t="n"/>
+      <c r="P55" s="26" t="n"/>
+      <c r="Q55" s="26" t="n"/>
+      <c r="R55" s="26" t="n"/>
+      <c r="S55" s="26" t="n"/>
+      <c r="T55" s="26" t="n"/>
       <c r="U55" s="22" t="n"/>
       <c r="V55" s="22" t="n"/>
       <c r="W55" s="22" t="n"/>
@@ -7320,7 +7316,7 @@
       <c r="B56" s="22" t="n"/>
       <c r="C56" s="22" t="n"/>
       <c r="D56" s="22" t="n"/>
-      <c r="E56" s="22" t="n"/>
+      <c r="E56" s="27" t="n"/>
       <c r="F56" s="22" t="n"/>
       <c r="G56" s="22" t="n"/>
       <c r="H56" s="22" t="n"/>
@@ -7329,15 +7325,15 @@
       <c r="K56" s="22" t="n"/>
       <c r="L56" s="22" t="n"/>
       <c r="M56" s="22" t="n"/>
-      <c r="N56" s="27" t="n"/>
-      <c r="O56" s="27" t="n"/>
+      <c r="N56" s="22" t="n"/>
+      <c r="O56" s="22" t="n"/>
       <c r="P56" s="22" t="n"/>
       <c r="Q56" s="22" t="n"/>
       <c r="R56" s="22" t="n"/>
       <c r="S56" s="22" t="n"/>
       <c r="T56" s="22" t="n"/>
-      <c r="U56" s="22" t="n"/>
-      <c r="V56" s="22" t="n"/>
+      <c r="U56" s="27" t="n"/>
+      <c r="V56" s="27" t="n"/>
       <c r="W56" s="22" t="n"/>
       <c r="X56" s="22" t="n"/>
       <c r="Y56" s="22" t="n"/>
@@ -7354,13 +7350,13 @@
     <row r="57" outlineLevel="1" ht="14" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>9.1 Inicio del panel</t>
+          <t>9.1 Vista de admin descuadrada</t>
         </is>
       </c>
       <c r="B57" s="22" t="n"/>
       <c r="C57" s="22" t="n"/>
       <c r="D57" s="22" t="n"/>
-      <c r="E57" s="22" t="n"/>
+      <c r="E57" s="28" t="n"/>
       <c r="F57" s="22" t="n"/>
       <c r="G57" s="22" t="n"/>
       <c r="H57" s="22" t="n"/>
@@ -7369,7 +7365,7 @@
       <c r="K57" s="22" t="n"/>
       <c r="L57" s="22" t="n"/>
       <c r="M57" s="22" t="n"/>
-      <c r="N57" s="28" t="n"/>
+      <c r="N57" s="22" t="n"/>
       <c r="O57" s="22" t="n"/>
       <c r="P57" s="22" t="n"/>
       <c r="Q57" s="22" t="n"/>
@@ -7409,14 +7405,14 @@
       <c r="K58" s="22" t="n"/>
       <c r="L58" s="22" t="n"/>
       <c r="M58" s="22" t="n"/>
-      <c r="N58" s="21" t="n"/>
+      <c r="N58" s="22" t="n"/>
       <c r="O58" s="22" t="n"/>
       <c r="P58" s="22" t="n"/>
       <c r="Q58" s="22" t="n"/>
       <c r="R58" s="22" t="n"/>
       <c r="S58" s="22" t="n"/>
       <c r="T58" s="22" t="n"/>
-      <c r="U58" s="22" t="n"/>
+      <c r="U58" s="21" t="n"/>
       <c r="V58" s="22" t="n"/>
       <c r="W58" s="22" t="n"/>
       <c r="X58" s="22" t="n"/>
@@ -7449,14 +7445,14 @@
       <c r="K59" s="22" t="n"/>
       <c r="L59" s="22" t="n"/>
       <c r="M59" s="22" t="n"/>
-      <c r="N59" s="25" t="n"/>
+      <c r="N59" s="22" t="n"/>
       <c r="O59" s="22" t="n"/>
       <c r="P59" s="22" t="n"/>
       <c r="Q59" s="22" t="n"/>
       <c r="R59" s="22" t="n"/>
       <c r="S59" s="22" t="n"/>
       <c r="T59" s="22" t="n"/>
-      <c r="U59" s="22" t="n"/>
+      <c r="U59" s="25" t="n"/>
       <c r="V59" s="22" t="n"/>
       <c r="W59" s="22" t="n"/>
       <c r="X59" s="22" t="n"/>
@@ -7480,7 +7476,7 @@
       <c r="B60" s="22" t="n"/>
       <c r="C60" s="22" t="n"/>
       <c r="D60" s="22" t="n"/>
-      <c r="E60" s="22" t="n"/>
+      <c r="E60" s="26" t="n"/>
       <c r="F60" s="22" t="n"/>
       <c r="G60" s="22" t="n"/>
       <c r="H60" s="22" t="n"/>
@@ -7489,15 +7485,15 @@
       <c r="K60" s="22" t="n"/>
       <c r="L60" s="22" t="n"/>
       <c r="M60" s="22" t="n"/>
-      <c r="N60" s="26" t="n"/>
-      <c r="O60" s="26" t="n"/>
+      <c r="N60" s="22" t="n"/>
+      <c r="O60" s="22" t="n"/>
       <c r="P60" s="22" t="n"/>
       <c r="Q60" s="22" t="n"/>
       <c r="R60" s="22" t="n"/>
       <c r="S60" s="22" t="n"/>
       <c r="T60" s="22" t="n"/>
-      <c r="U60" s="22" t="n"/>
-      <c r="V60" s="22" t="n"/>
+      <c r="U60" s="26" t="n"/>
+      <c r="V60" s="26" t="n"/>
       <c r="W60" s="22" t="n"/>
       <c r="X60" s="22" t="n"/>
       <c r="Y60" s="22" t="n"/>
@@ -7520,7 +7516,7 @@
       <c r="B61" s="22" t="n"/>
       <c r="C61" s="22" t="n"/>
       <c r="D61" s="22" t="n"/>
-      <c r="E61" s="22" t="n"/>
+      <c r="E61" s="27" t="n"/>
       <c r="F61" s="22" t="n"/>
       <c r="G61" s="22" t="n"/>
       <c r="H61" s="22" t="n"/>
@@ -7529,15 +7525,15 @@
       <c r="K61" s="22" t="n"/>
       <c r="L61" s="22" t="n"/>
       <c r="M61" s="22" t="n"/>
-      <c r="N61" s="27" t="n"/>
-      <c r="O61" s="27" t="n"/>
+      <c r="N61" s="22" t="n"/>
+      <c r="O61" s="22" t="n"/>
       <c r="P61" s="22" t="n"/>
       <c r="Q61" s="22" t="n"/>
       <c r="R61" s="22" t="n"/>
       <c r="S61" s="22" t="n"/>
       <c r="T61" s="22" t="n"/>
-      <c r="U61" s="22" t="n"/>
-      <c r="V61" s="22" t="n"/>
+      <c r="U61" s="27" t="n"/>
+      <c r="V61" s="27" t="n"/>
       <c r="W61" s="22" t="n"/>
       <c r="X61" s="22" t="n"/>
       <c r="Y61" s="22" t="n"/>
@@ -7559,7 +7555,7 @@
       </c>
       <c r="B62" s="22" t="n"/>
       <c r="C62" s="22" t="n"/>
-      <c r="D62" s="22" t="n"/>
+      <c r="D62" s="28" t="n"/>
       <c r="E62" s="22" t="n"/>
       <c r="F62" s="22" t="n"/>
       <c r="G62" s="22" t="n"/>
@@ -7571,17 +7567,17 @@
       <c r="M62" s="22" t="n"/>
       <c r="N62" s="22" t="n"/>
       <c r="O62" s="22" t="n"/>
-      <c r="P62" s="28" t="n"/>
-      <c r="Q62" s="28" t="n"/>
-      <c r="R62" s="28" t="n"/>
-      <c r="S62" s="28" t="n"/>
+      <c r="P62" s="22" t="n"/>
+      <c r="Q62" s="22" t="n"/>
+      <c r="R62" s="22" t="n"/>
+      <c r="S62" s="22" t="n"/>
       <c r="T62" s="22" t="n"/>
       <c r="U62" s="22" t="n"/>
       <c r="V62" s="22" t="n"/>
-      <c r="W62" s="22" t="n"/>
-      <c r="X62" s="22" t="n"/>
-      <c r="Y62" s="22" t="n"/>
-      <c r="Z62" s="22" t="n"/>
+      <c r="W62" s="28" t="n"/>
+      <c r="X62" s="28" t="n"/>
+      <c r="Y62" s="28" t="n"/>
+      <c r="Z62" s="28" t="n"/>
       <c r="AA62" s="22" t="n"/>
       <c r="AB62" s="22" t="n"/>
       <c r="AC62" s="22" t="n"/>
@@ -7611,14 +7607,14 @@
       <c r="M63" s="22" t="n"/>
       <c r="N63" s="22" t="n"/>
       <c r="O63" s="22" t="n"/>
-      <c r="P63" s="21" t="n"/>
+      <c r="P63" s="22" t="n"/>
       <c r="Q63" s="22" t="n"/>
       <c r="R63" s="22" t="n"/>
       <c r="S63" s="22" t="n"/>
       <c r="T63" s="22" t="n"/>
       <c r="U63" s="22" t="n"/>
       <c r="V63" s="22" t="n"/>
-      <c r="W63" s="22" t="n"/>
+      <c r="W63" s="21" t="n"/>
       <c r="X63" s="22" t="n"/>
       <c r="Y63" s="22" t="n"/>
       <c r="Z63" s="22" t="n"/>
@@ -7651,14 +7647,14 @@
       <c r="M64" s="22" t="n"/>
       <c r="N64" s="22" t="n"/>
       <c r="O64" s="22" t="n"/>
-      <c r="P64" s="25" t="n"/>
+      <c r="P64" s="22" t="n"/>
       <c r="Q64" s="22" t="n"/>
       <c r="R64" s="22" t="n"/>
       <c r="S64" s="22" t="n"/>
       <c r="T64" s="22" t="n"/>
       <c r="U64" s="22" t="n"/>
       <c r="V64" s="22" t="n"/>
-      <c r="W64" s="22" t="n"/>
+      <c r="W64" s="25" t="n"/>
       <c r="X64" s="22" t="n"/>
       <c r="Y64" s="22" t="n"/>
       <c r="Z64" s="22" t="n"/>
@@ -7674,12 +7670,12 @@
     <row r="65" outlineLevel="1" ht="14" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>10.3 Edición de datos</t>
+          <t>10.3 Impersonalidad: usuario1</t>
         </is>
       </c>
       <c r="B65" s="22" t="n"/>
       <c r="C65" s="22" t="n"/>
-      <c r="D65" s="22" t="n"/>
+      <c r="D65" s="26" t="n"/>
       <c r="E65" s="22" t="n"/>
       <c r="F65" s="22" t="n"/>
       <c r="G65" s="22" t="n"/>
@@ -7691,7 +7687,7 @@
       <c r="M65" s="22" t="n"/>
       <c r="N65" s="22" t="n"/>
       <c r="O65" s="22" t="n"/>
-      <c r="P65" s="26" t="n"/>
+      <c r="P65" s="22" t="n"/>
       <c r="Q65" s="22" t="n"/>
       <c r="R65" s="22" t="n"/>
       <c r="S65" s="22" t="n"/>
@@ -7719,7 +7715,7 @@
       </c>
       <c r="B66" s="22" t="n"/>
       <c r="C66" s="22" t="n"/>
-      <c r="D66" s="22" t="n"/>
+      <c r="D66" s="27" t="n"/>
       <c r="E66" s="22" t="n"/>
       <c r="F66" s="22" t="n"/>
       <c r="G66" s="22" t="n"/>
@@ -7731,17 +7727,17 @@
       <c r="M66" s="22" t="n"/>
       <c r="N66" s="22" t="n"/>
       <c r="O66" s="22" t="n"/>
-      <c r="P66" s="27" t="n"/>
-      <c r="Q66" s="27" t="n"/>
-      <c r="R66" s="27" t="n"/>
-      <c r="S66" s="27" t="n"/>
+      <c r="P66" s="22" t="n"/>
+      <c r="Q66" s="22" t="n"/>
+      <c r="R66" s="22" t="n"/>
+      <c r="S66" s="22" t="n"/>
       <c r="T66" s="22" t="n"/>
       <c r="U66" s="22" t="n"/>
       <c r="V66" s="22" t="n"/>
-      <c r="W66" s="22" t="n"/>
-      <c r="X66" s="22" t="n"/>
-      <c r="Y66" s="22" t="n"/>
-      <c r="Z66" s="22" t="n"/>
+      <c r="W66" s="27" t="n"/>
+      <c r="X66" s="27" t="n"/>
+      <c r="Y66" s="27" t="n"/>
+      <c r="Z66" s="27" t="n"/>
       <c r="AA66" s="22" t="n"/>
       <c r="AB66" s="22" t="n"/>
       <c r="AC66" s="22" t="n"/>
@@ -7759,7 +7755,7 @@
       </c>
       <c r="B67" s="22" t="n"/>
       <c r="C67" s="22" t="n"/>
-      <c r="D67" s="22" t="n"/>
+      <c r="D67" s="28" t="n"/>
       <c r="E67" s="22" t="n"/>
       <c r="F67" s="22" t="n"/>
       <c r="G67" s="22" t="n"/>
@@ -7771,17 +7767,17 @@
       <c r="M67" s="22" t="n"/>
       <c r="N67" s="22" t="n"/>
       <c r="O67" s="22" t="n"/>
-      <c r="P67" s="28" t="n"/>
-      <c r="Q67" s="28" t="n"/>
-      <c r="R67" s="28" t="n"/>
-      <c r="S67" s="28" t="n"/>
+      <c r="P67" s="22" t="n"/>
+      <c r="Q67" s="22" t="n"/>
+      <c r="R67" s="22" t="n"/>
+      <c r="S67" s="22" t="n"/>
       <c r="T67" s="22" t="n"/>
       <c r="U67" s="22" t="n"/>
       <c r="V67" s="22" t="n"/>
-      <c r="W67" s="22" t="n"/>
-      <c r="X67" s="22" t="n"/>
-      <c r="Y67" s="22" t="n"/>
-      <c r="Z67" s="22" t="n"/>
+      <c r="W67" s="28" t="n"/>
+      <c r="X67" s="28" t="n"/>
+      <c r="Y67" s="28" t="n"/>
+      <c r="Z67" s="28" t="n"/>
       <c r="AA67" s="22" t="n"/>
       <c r="AB67" s="22" t="n"/>
       <c r="AC67" s="22" t="n"/>
@@ -7794,14 +7790,14 @@
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>11. Monitores y solicitudes</t>
+          <t>11. Monitores y reportes</t>
         </is>
       </c>
       <c r="B68" s="22" t="n"/>
       <c r="C68" s="22" t="n"/>
-      <c r="D68" s="22" t="n"/>
+      <c r="D68" s="21" t="n"/>
       <c r="E68" s="22" t="n"/>
-      <c r="F68" s="22" t="n"/>
+      <c r="F68" s="21" t="n"/>
       <c r="G68" s="22" t="n"/>
       <c r="H68" s="22" t="n"/>
       <c r="I68" s="22" t="n"/>
@@ -7815,16 +7811,16 @@
       <c r="Q68" s="22" t="n"/>
       <c r="R68" s="22" t="n"/>
       <c r="S68" s="22" t="n"/>
-      <c r="T68" s="21" t="n"/>
-      <c r="U68" s="21" t="n"/>
-      <c r="V68" s="21" t="n"/>
+      <c r="T68" s="22" t="n"/>
+      <c r="U68" s="22" t="n"/>
+      <c r="V68" s="22" t="n"/>
       <c r="W68" s="22" t="n"/>
       <c r="X68" s="22" t="n"/>
       <c r="Y68" s="22" t="n"/>
       <c r="Z68" s="22" t="n"/>
-      <c r="AA68" s="22" t="n"/>
-      <c r="AB68" s="22" t="n"/>
-      <c r="AC68" s="22" t="n"/>
+      <c r="AA68" s="21" t="n"/>
+      <c r="AB68" s="21" t="n"/>
+      <c r="AC68" s="21" t="n"/>
       <c r="AD68" s="30" t="inlineStr">
         <is>
           <t>sin iniciar</t>
@@ -7834,12 +7830,12 @@
     <row r="69" outlineLevel="1" ht="14" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>11.1 Alta de monitores</t>
+          <t>11.1 Impersonalidad: monitor1</t>
         </is>
       </c>
       <c r="B69" s="22" t="n"/>
       <c r="C69" s="22" t="n"/>
-      <c r="D69" s="22" t="n"/>
+      <c r="D69" s="25" t="n"/>
       <c r="E69" s="22" t="n"/>
       <c r="F69" s="22" t="n"/>
       <c r="G69" s="22" t="n"/>
@@ -7855,7 +7851,7 @@
       <c r="Q69" s="22" t="n"/>
       <c r="R69" s="22" t="n"/>
       <c r="S69" s="22" t="n"/>
-      <c r="T69" s="25" t="n"/>
+      <c r="T69" s="22" t="n"/>
       <c r="U69" s="22" t="n"/>
       <c r="V69" s="22" t="n"/>
       <c r="W69" s="22" t="n"/>
@@ -7874,14 +7870,14 @@
     <row r="70" outlineLevel="1" ht="14" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>11.2 Solicitudes de clase</t>
+          <t>11.2 De solicitudes a reportes</t>
         </is>
       </c>
       <c r="B70" s="22" t="n"/>
       <c r="C70" s="22" t="n"/>
       <c r="D70" s="22" t="n"/>
       <c r="E70" s="22" t="n"/>
-      <c r="F70" s="22" t="n"/>
+      <c r="F70" s="26" t="n"/>
       <c r="G70" s="22" t="n"/>
       <c r="H70" s="22" t="n"/>
       <c r="I70" s="22" t="n"/>
@@ -7896,7 +7892,7 @@
       <c r="R70" s="22" t="n"/>
       <c r="S70" s="22" t="n"/>
       <c r="T70" s="22" t="n"/>
-      <c r="U70" s="26" t="n"/>
+      <c r="U70" s="22" t="n"/>
       <c r="V70" s="22" t="n"/>
       <c r="W70" s="22" t="n"/>
       <c r="X70" s="22" t="n"/>
@@ -7936,14 +7932,14 @@
       <c r="R71" s="22" t="n"/>
       <c r="S71" s="22" t="n"/>
       <c r="T71" s="22" t="n"/>
-      <c r="U71" s="27" t="n"/>
+      <c r="U71" s="22" t="n"/>
       <c r="V71" s="22" t="n"/>
       <c r="W71" s="22" t="n"/>
       <c r="X71" s="22" t="n"/>
       <c r="Y71" s="22" t="n"/>
       <c r="Z71" s="22" t="n"/>
       <c r="AA71" s="22" t="n"/>
-      <c r="AB71" s="22" t="n"/>
+      <c r="AB71" s="27" t="n"/>
       <c r="AC71" s="22" t="n"/>
       <c r="AD71" s="30" t="inlineStr">
         <is>
@@ -7959,9 +7955,9 @@
       </c>
       <c r="B72" s="22" t="n"/>
       <c r="C72" s="22" t="n"/>
-      <c r="D72" s="22" t="n"/>
+      <c r="D72" s="28" t="n"/>
       <c r="E72" s="22" t="n"/>
-      <c r="F72" s="22" t="n"/>
+      <c r="F72" s="28" t="n"/>
       <c r="G72" s="22" t="n"/>
       <c r="H72" s="22" t="n"/>
       <c r="I72" s="22" t="n"/>
@@ -7975,16 +7971,16 @@
       <c r="Q72" s="22" t="n"/>
       <c r="R72" s="22" t="n"/>
       <c r="S72" s="22" t="n"/>
-      <c r="T72" s="28" t="n"/>
-      <c r="U72" s="28" t="n"/>
-      <c r="V72" s="28" t="n"/>
+      <c r="T72" s="22" t="n"/>
+      <c r="U72" s="22" t="n"/>
+      <c r="V72" s="22" t="n"/>
       <c r="W72" s="22" t="n"/>
       <c r="X72" s="22" t="n"/>
       <c r="Y72" s="22" t="n"/>
       <c r="Z72" s="22" t="n"/>
-      <c r="AA72" s="22" t="n"/>
-      <c r="AB72" s="22" t="n"/>
-      <c r="AC72" s="22" t="n"/>
+      <c r="AA72" s="28" t="n"/>
+      <c r="AB72" s="28" t="n"/>
+      <c r="AC72" s="28" t="n"/>
       <c r="AD72" s="30" t="inlineStr">
         <is>
           <t>sin iniciar</t>
@@ -7999,9 +7995,9 @@
       </c>
       <c r="B73" s="22" t="n"/>
       <c r="C73" s="22" t="n"/>
-      <c r="D73" s="22" t="n"/>
+      <c r="D73" s="21" t="n"/>
       <c r="E73" s="22" t="n"/>
-      <c r="F73" s="22" t="n"/>
+      <c r="F73" s="21" t="n"/>
       <c r="G73" s="22" t="n"/>
       <c r="H73" s="22" t="n"/>
       <c r="I73" s="22" t="n"/>
@@ -8015,16 +8011,16 @@
       <c r="Q73" s="22" t="n"/>
       <c r="R73" s="22" t="n"/>
       <c r="S73" s="22" t="n"/>
-      <c r="T73" s="21" t="n"/>
-      <c r="U73" s="21" t="n"/>
-      <c r="V73" s="21" t="n"/>
+      <c r="T73" s="22" t="n"/>
+      <c r="U73" s="22" t="n"/>
+      <c r="V73" s="22" t="n"/>
       <c r="W73" s="22" t="n"/>
       <c r="X73" s="22" t="n"/>
       <c r="Y73" s="22" t="n"/>
       <c r="Z73" s="22" t="n"/>
-      <c r="AA73" s="22" t="n"/>
-      <c r="AB73" s="22" t="n"/>
-      <c r="AC73" s="22" t="n"/>
+      <c r="AA73" s="21" t="n"/>
+      <c r="AB73" s="21" t="n"/>
+      <c r="AC73" s="21" t="n"/>
       <c r="AD73" s="30" t="inlineStr">
         <is>
           <t>sin iniciar</t>
@@ -8041,7 +8037,7 @@
       <c r="C74" s="22" t="n"/>
       <c r="D74" s="22" t="n"/>
       <c r="E74" s="22" t="n"/>
-      <c r="F74" s="22" t="n"/>
+      <c r="F74" s="25" t="n"/>
       <c r="G74" s="22" t="n"/>
       <c r="H74" s="22" t="n"/>
       <c r="I74" s="22" t="n"/>
@@ -8058,10 +8054,10 @@
       <c r="T74" s="22" t="n"/>
       <c r="U74" s="22" t="n"/>
       <c r="V74" s="22" t="n"/>
-      <c r="W74" s="25" t="n"/>
-      <c r="X74" s="25" t="n"/>
-      <c r="Y74" s="25" t="n"/>
-      <c r="Z74" s="25" t="n"/>
+      <c r="W74" s="22" t="n"/>
+      <c r="X74" s="22" t="n"/>
+      <c r="Y74" s="22" t="n"/>
+      <c r="Z74" s="22" t="n"/>
       <c r="AA74" s="22" t="n"/>
       <c r="AB74" s="22" t="n"/>
       <c r="AC74" s="22" t="n"/>
@@ -8074,14 +8070,14 @@
     <row r="75" outlineLevel="1" ht="14" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>12.1 Ficha de salas</t>
+          <t>12.1 Colores de salas y actividades</t>
         </is>
       </c>
       <c r="B75" s="22" t="n"/>
       <c r="C75" s="22" t="n"/>
       <c r="D75" s="22" t="n"/>
       <c r="E75" s="22" t="n"/>
-      <c r="F75" s="22" t="n"/>
+      <c r="F75" s="26" t="n"/>
       <c r="G75" s="22" t="n"/>
       <c r="H75" s="22" t="n"/>
       <c r="I75" s="22" t="n"/>
@@ -8098,7 +8094,7 @@
       <c r="T75" s="22" t="n"/>
       <c r="U75" s="22" t="n"/>
       <c r="V75" s="22" t="n"/>
-      <c r="W75" s="26" t="n"/>
+      <c r="W75" s="22" t="n"/>
       <c r="X75" s="22" t="n"/>
       <c r="Y75" s="22" t="n"/>
       <c r="Z75" s="22" t="n"/>
@@ -8138,7 +8134,7 @@
       <c r="T76" s="22" t="n"/>
       <c r="U76" s="22" t="n"/>
       <c r="V76" s="22" t="n"/>
-      <c r="W76" s="27" t="n"/>
+      <c r="W76" s="22" t="n"/>
       <c r="X76" s="22" t="n"/>
       <c r="Y76" s="22" t="n"/>
       <c r="Z76" s="22" t="n"/>
@@ -8178,7 +8174,7 @@
       <c r="T77" s="22" t="n"/>
       <c r="U77" s="22" t="n"/>
       <c r="V77" s="22" t="n"/>
-      <c r="W77" s="28" t="n"/>
+      <c r="W77" s="22" t="n"/>
       <c r="X77" s="22" t="n"/>
       <c r="Y77" s="22" t="n"/>
       <c r="Z77" s="22" t="n"/>
@@ -8201,7 +8197,7 @@
       <c r="C78" s="22" t="n"/>
       <c r="D78" s="22" t="n"/>
       <c r="E78" s="22" t="n"/>
-      <c r="F78" s="22" t="n"/>
+      <c r="F78" s="21" t="n"/>
       <c r="G78" s="22" t="n"/>
       <c r="H78" s="22" t="n"/>
       <c r="I78" s="22" t="n"/>
@@ -8218,10 +8214,10 @@
       <c r="T78" s="22" t="n"/>
       <c r="U78" s="22" t="n"/>
       <c r="V78" s="22" t="n"/>
-      <c r="W78" s="21" t="n"/>
-      <c r="X78" s="21" t="n"/>
-      <c r="Y78" s="21" t="n"/>
-      <c r="Z78" s="21" t="n"/>
+      <c r="W78" s="22" t="n"/>
+      <c r="X78" s="22" t="n"/>
+      <c r="Y78" s="22" t="n"/>
+      <c r="Z78" s="22" t="n"/>
       <c r="AA78" s="22" t="n"/>
       <c r="AB78" s="22" t="n"/>
       <c r="AC78" s="22" t="n"/>
@@ -8241,7 +8237,7 @@
       <c r="C79" s="22" t="n"/>
       <c r="D79" s="22" t="n"/>
       <c r="E79" s="22" t="n"/>
-      <c r="F79" s="22" t="n"/>
+      <c r="F79" s="25" t="n"/>
       <c r="G79" s="22" t="n"/>
       <c r="H79" s="22" t="n"/>
       <c r="I79" s="22" t="n"/>
@@ -8258,10 +8254,10 @@
       <c r="T79" s="22" t="n"/>
       <c r="U79" s="22" t="n"/>
       <c r="V79" s="22" t="n"/>
-      <c r="W79" s="25" t="n"/>
-      <c r="X79" s="25" t="n"/>
-      <c r="Y79" s="25" t="n"/>
-      <c r="Z79" s="25" t="n"/>
+      <c r="W79" s="22" t="n"/>
+      <c r="X79" s="22" t="n"/>
+      <c r="Y79" s="22" t="n"/>
+      <c r="Z79" s="22" t="n"/>
       <c r="AA79" s="22" t="n"/>
       <c r="AB79" s="22" t="n"/>
       <c r="AC79" s="22" t="n"/>
@@ -8302,9 +8298,9 @@
       <c r="X80" s="22" t="n"/>
       <c r="Y80" s="22" t="n"/>
       <c r="Z80" s="22" t="n"/>
-      <c r="AA80" s="26" t="n"/>
-      <c r="AB80" s="26" t="n"/>
-      <c r="AC80" s="26" t="n"/>
+      <c r="AA80" s="22" t="n"/>
+      <c r="AB80" s="22" t="n"/>
+      <c r="AC80" s="22" t="n"/>
       <c r="AD80" s="30" t="inlineStr">
         <is>
           <t>sin iniciar</t>
@@ -8342,7 +8338,7 @@
       <c r="X81" s="22" t="n"/>
       <c r="Y81" s="22" t="n"/>
       <c r="Z81" s="22" t="n"/>
-      <c r="AA81" s="27" t="n"/>
+      <c r="AA81" s="22" t="n"/>
       <c r="AB81" s="22" t="n"/>
       <c r="AC81" s="22" t="n"/>
       <c r="AD81" s="30" t="inlineStr">
@@ -8383,7 +8379,7 @@
       <c r="Y82" s="22" t="n"/>
       <c r="Z82" s="22" t="n"/>
       <c r="AA82" s="22" t="n"/>
-      <c r="AB82" s="28" t="n"/>
+      <c r="AB82" s="22" t="n"/>
       <c r="AC82" s="22" t="n"/>
       <c r="AD82" s="30" t="inlineStr">
         <is>
@@ -8423,7 +8419,7 @@
       <c r="Y83" s="22" t="n"/>
       <c r="Z83" s="22" t="n"/>
       <c r="AA83" s="22" t="n"/>
-      <c r="AB83" s="21" t="n"/>
+      <c r="AB83" s="22" t="n"/>
       <c r="AC83" s="22" t="n"/>
       <c r="AD83" s="30" t="inlineStr">
         <is>
@@ -8462,9 +8458,9 @@
       <c r="X84" s="22" t="n"/>
       <c r="Y84" s="22" t="n"/>
       <c r="Z84" s="22" t="n"/>
-      <c r="AA84" s="25" t="n"/>
-      <c r="AB84" s="25" t="n"/>
-      <c r="AC84" s="25" t="n"/>
+      <c r="AA84" s="22" t="n"/>
+      <c r="AB84" s="22" t="n"/>
+      <c r="AC84" s="22" t="n"/>
       <c r="AD84" s="30" t="inlineStr">
         <is>
           <t>sin iniciar</t>
@@ -8502,9 +8498,9 @@
       <c r="X85" s="22" t="n"/>
       <c r="Y85" s="22" t="n"/>
       <c r="Z85" s="22" t="n"/>
-      <c r="AA85" s="26" t="n"/>
-      <c r="AB85" s="26" t="n"/>
-      <c r="AC85" s="26" t="n"/>
+      <c r="AA85" s="22" t="n"/>
+      <c r="AB85" s="22" t="n"/>
+      <c r="AC85" s="22" t="n"/>
       <c r="AD85" s="30" t="inlineStr">
         <is>
           <t>sin iniciar</t>
@@ -8825,9 +8821,9 @@
       <c r="AA93" s="22" t="n"/>
       <c r="AB93" s="22" t="n"/>
       <c r="AC93" s="22" t="n"/>
-      <c r="AD93" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="AD93" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -8865,9 +8861,9 @@
       <c r="AA94" s="22" t="n"/>
       <c r="AB94" s="22" t="n"/>
       <c r="AC94" s="22" t="n"/>
-      <c r="AD94" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="AD94" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -9125,12 +9121,12 @@
     <mergeCell ref="I5:O5"/>
     <mergeCell ref="P5:V5"/>
     <mergeCell ref="W4:AC4"/>
+    <mergeCell ref="AD4:AD7"/>
+    <mergeCell ref="B4:H4"/>
     <mergeCell ref="W5:AC5"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="AD4:AD7"/>
     <mergeCell ref="P4:V4"/>
+    <mergeCell ref="A2:AD2"/>
     <mergeCell ref="I4:O4"/>
-    <mergeCell ref="A2:AD2"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="A1:AD1"/>
   </mergeCells>
@@ -9148,7 +9144,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="3.7" customWidth="1" min="2" max="2"/>
@@ -10093,9 +10089,9 @@
       <c r="T26" s="22" t="n"/>
       <c r="U26" s="22" t="n"/>
       <c r="V26" s="22" t="n"/>
-      <c r="W26" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="W26" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10164,7 @@
     <row r="29" outlineLevel="1" ht="14" customHeight="1">
       <c r="A29" s="24" t="inlineStr">
         <is>
-          <t>4.3 Baja y reactivación</t>
+          <t>4.3 Baja: al redirigir se pierde la sesión</t>
         </is>
       </c>
       <c r="B29" s="22" t="n"/>
@@ -10192,9 +10188,9 @@
       <c r="T29" s="22" t="n"/>
       <c r="U29" s="22" t="n"/>
       <c r="V29" s="22" t="n"/>
-      <c r="W29" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="W29" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -10225,9 +10221,9 @@
       <c r="T30" s="22" t="n"/>
       <c r="U30" s="22" t="n"/>
       <c r="V30" s="22" t="n"/>
-      <c r="W30" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="W30" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -10258,9 +10254,9 @@
       <c r="T31" s="22" t="n"/>
       <c r="U31" s="22" t="n"/>
       <c r="V31" s="22" t="n"/>
-      <c r="W31" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="W31" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10296,7 @@
     <row r="33" outlineLevel="1" ht="14" customHeight="1">
       <c r="A33" s="24" t="inlineStr">
         <is>
-          <t>5.1 Listado de actividades</t>
+          <t>5.1 Listado descuadrado</t>
         </is>
       </c>
       <c r="B33" s="22" t="n"/>
@@ -10324,16 +10320,16 @@
       <c r="T33" s="22" t="n"/>
       <c r="U33" s="22" t="n"/>
       <c r="V33" s="22" t="n"/>
-      <c r="W33" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="W33" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
     <row r="34" outlineLevel="1" ht="14" customHeight="1">
       <c r="A34" s="24" t="inlineStr">
         <is>
-          <t>5.2 Horario y avisos → inscritos</t>
+          <t>5.2 Horario con uniformidad</t>
         </is>
       </c>
       <c r="B34" s="22" t="n"/>
@@ -10357,9 +10353,9 @@
       <c r="T34" s="22" t="n"/>
       <c r="U34" s="22" t="n"/>
       <c r="V34" s="22" t="n"/>
-      <c r="W34" s="23" t="inlineStr">
-        <is>
-          <t>completado</t>
+      <c r="W34" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -10390,9 +10386,9 @@
       <c r="T35" s="22" t="n"/>
       <c r="U35" s="22" t="n"/>
       <c r="V35" s="22" t="n"/>
-      <c r="W35" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W35" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -10687,9 +10683,9 @@
       <c r="T44" s="22" t="n"/>
       <c r="U44" s="22" t="n"/>
       <c r="V44" s="22" t="n"/>
-      <c r="W44" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W44" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -10720,9 +10716,9 @@
       <c r="T45" s="22" t="n"/>
       <c r="U45" s="22" t="n"/>
       <c r="V45" s="22" t="n"/>
-      <c r="W45" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W45" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -10753,9 +10749,9 @@
       <c r="T46" s="22" t="n"/>
       <c r="U46" s="22" t="n"/>
       <c r="V46" s="22" t="n"/>
-      <c r="W46" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W46" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -10786,9 +10782,9 @@
       <c r="T47" s="22" t="n"/>
       <c r="U47" s="22" t="n"/>
       <c r="V47" s="22" t="n"/>
-      <c r="W47" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W47" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -10819,9 +10815,9 @@
       <c r="T48" s="22" t="n"/>
       <c r="U48" s="22" t="n"/>
       <c r="V48" s="22" t="n"/>
-      <c r="W48" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W48" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -10852,9 +10848,9 @@
       <c r="T49" s="22" t="n"/>
       <c r="U49" s="22" t="n"/>
       <c r="V49" s="22" t="n"/>
-      <c r="W49" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W49" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -10927,7 +10923,7 @@
     <row r="52" outlineLevel="1" ht="14" customHeight="1">
       <c r="A52" s="24" t="inlineStr">
         <is>
-          <t>8.2 Confirmación del pago</t>
+          <t>8.2 Guardar el método de pago</t>
         </is>
       </c>
       <c r="B52" s="22" t="n"/>
@@ -11092,7 +11088,7 @@
     <row r="57" outlineLevel="1" ht="14" customHeight="1">
       <c r="A57" s="24" t="inlineStr">
         <is>
-          <t>9.1 Inicio del panel</t>
+          <t>9.1 Vista de admin descuadrada</t>
         </is>
       </c>
       <c r="B57" s="22" t="n"/>
@@ -11356,7 +11352,7 @@
     <row r="65" outlineLevel="1" ht="14" customHeight="1">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>10.3 Edición de datos</t>
+          <t>10.3 Impersonalidad: usuario1</t>
         </is>
       </c>
       <c r="B65" s="22" t="n"/>
@@ -11455,7 +11451,7 @@
     <row r="68" ht="14" customHeight="1">
       <c r="A68" s="20" t="inlineStr">
         <is>
-          <t>11. Monitores y solicitudes</t>
+          <t>11. Monitores y reportes</t>
         </is>
       </c>
       <c r="B68" s="22" t="n"/>
@@ -11488,7 +11484,7 @@
     <row r="69" outlineLevel="1" ht="14" customHeight="1">
       <c r="A69" s="24" t="inlineStr">
         <is>
-          <t>11.1 Alta de monitores</t>
+          <t>11.1 Impersonalidad: monitor1</t>
         </is>
       </c>
       <c r="B69" s="22" t="n"/>
@@ -11521,7 +11517,7 @@
     <row r="70" outlineLevel="1" ht="14" customHeight="1">
       <c r="A70" s="24" t="inlineStr">
         <is>
-          <t>11.2 Solicitudes de clase</t>
+          <t>11.2 De solicitudes a reportes</t>
         </is>
       </c>
       <c r="B70" s="22" t="n"/>
@@ -11656,10 +11652,10 @@
           <t>12. Salas y materiales</t>
         </is>
       </c>
-      <c r="B74" s="22" t="n"/>
-      <c r="C74" s="22" t="n"/>
-      <c r="D74" s="22" t="n"/>
-      <c r="E74" s="22" t="n"/>
+      <c r="B74" s="25" t="n"/>
+      <c r="C74" s="25" t="n"/>
+      <c r="D74" s="25" t="n"/>
+      <c r="E74" s="25" t="n"/>
       <c r="F74" s="22" t="n"/>
       <c r="G74" s="22" t="n"/>
       <c r="H74" s="22" t="n"/>
@@ -11686,7 +11682,7 @@
     <row r="75" outlineLevel="1" ht="14" customHeight="1">
       <c r="A75" s="24" t="inlineStr">
         <is>
-          <t>12.1 Ficha de salas</t>
+          <t>12.1 Colores de salas y actividades</t>
         </is>
       </c>
       <c r="B75" s="22" t="n"/>
@@ -11722,7 +11718,7 @@
           <t>12.2 Inventario de materiales</t>
         </is>
       </c>
-      <c r="B76" s="22" t="n"/>
+      <c r="B76" s="27" t="n"/>
       <c r="C76" s="22" t="n"/>
       <c r="D76" s="22" t="n"/>
       <c r="E76" s="22" t="n"/>
@@ -11755,7 +11751,7 @@
           <t>12.3 Alta y edición</t>
         </is>
       </c>
-      <c r="B77" s="22" t="n"/>
+      <c r="B77" s="28" t="n"/>
       <c r="C77" s="22" t="n"/>
       <c r="D77" s="22" t="n"/>
       <c r="E77" s="22" t="n"/>
@@ -11788,10 +11784,10 @@
           <t>12.4 Testeo</t>
         </is>
       </c>
-      <c r="B78" s="22" t="n"/>
-      <c r="C78" s="22" t="n"/>
-      <c r="D78" s="22" t="n"/>
-      <c r="E78" s="22" t="n"/>
+      <c r="B78" s="21" t="n"/>
+      <c r="C78" s="21" t="n"/>
+      <c r="D78" s="21" t="n"/>
+      <c r="E78" s="21" t="n"/>
       <c r="F78" s="22" t="n"/>
       <c r="G78" s="22" t="n"/>
       <c r="H78" s="22" t="n"/>
@@ -11821,10 +11817,10 @@
           <t>12.5 Documentación</t>
         </is>
       </c>
-      <c r="B79" s="22" t="n"/>
-      <c r="C79" s="22" t="n"/>
-      <c r="D79" s="22" t="n"/>
-      <c r="E79" s="22" t="n"/>
+      <c r="B79" s="25" t="n"/>
+      <c r="C79" s="25" t="n"/>
+      <c r="D79" s="25" t="n"/>
+      <c r="E79" s="25" t="n"/>
       <c r="F79" s="22" t="n"/>
       <c r="G79" s="22" t="n"/>
       <c r="H79" s="22" t="n"/>
@@ -11858,9 +11854,9 @@
       <c r="C80" s="22" t="n"/>
       <c r="D80" s="22" t="n"/>
       <c r="E80" s="22" t="n"/>
-      <c r="F80" s="22" t="n"/>
-      <c r="G80" s="22" t="n"/>
-      <c r="H80" s="22" t="n"/>
+      <c r="F80" s="26" t="n"/>
+      <c r="G80" s="26" t="n"/>
+      <c r="H80" s="26" t="n"/>
       <c r="I80" s="22" t="n"/>
       <c r="J80" s="22" t="n"/>
       <c r="K80" s="22" t="n"/>
@@ -11891,7 +11887,7 @@
       <c r="C81" s="22" t="n"/>
       <c r="D81" s="22" t="n"/>
       <c r="E81" s="22" t="n"/>
-      <c r="F81" s="22" t="n"/>
+      <c r="F81" s="27" t="n"/>
       <c r="G81" s="22" t="n"/>
       <c r="H81" s="22" t="n"/>
       <c r="I81" s="22" t="n"/>
@@ -11925,7 +11921,7 @@
       <c r="D82" s="22" t="n"/>
       <c r="E82" s="22" t="n"/>
       <c r="F82" s="22" t="n"/>
-      <c r="G82" s="22" t="n"/>
+      <c r="G82" s="28" t="n"/>
       <c r="H82" s="22" t="n"/>
       <c r="I82" s="22" t="n"/>
       <c r="J82" s="22" t="n"/>
@@ -11958,7 +11954,7 @@
       <c r="D83" s="22" t="n"/>
       <c r="E83" s="22" t="n"/>
       <c r="F83" s="22" t="n"/>
-      <c r="G83" s="22" t="n"/>
+      <c r="G83" s="21" t="n"/>
       <c r="H83" s="22" t="n"/>
       <c r="I83" s="22" t="n"/>
       <c r="J83" s="22" t="n"/>
@@ -11990,9 +11986,9 @@
       <c r="C84" s="22" t="n"/>
       <c r="D84" s="22" t="n"/>
       <c r="E84" s="22" t="n"/>
-      <c r="F84" s="22" t="n"/>
-      <c r="G84" s="22" t="n"/>
-      <c r="H84" s="22" t="n"/>
+      <c r="F84" s="25" t="n"/>
+      <c r="G84" s="25" t="n"/>
+      <c r="H84" s="25" t="n"/>
       <c r="I84" s="22" t="n"/>
       <c r="J84" s="22" t="n"/>
       <c r="K84" s="22" t="n"/>
@@ -12023,9 +12019,9 @@
       <c r="C85" s="22" t="n"/>
       <c r="D85" s="22" t="n"/>
       <c r="E85" s="22" t="n"/>
-      <c r="F85" s="22" t="n"/>
-      <c r="G85" s="22" t="n"/>
-      <c r="H85" s="22" t="n"/>
+      <c r="F85" s="26" t="n"/>
+      <c r="G85" s="26" t="n"/>
+      <c r="H85" s="26" t="n"/>
       <c r="I85" s="22" t="n"/>
       <c r="J85" s="22" t="n"/>
       <c r="K85" s="22" t="n"/>
@@ -12052,18 +12048,18 @@
           <t>14. Comentarios, feedback y seguridad</t>
         </is>
       </c>
-      <c r="B86" s="27" t="n"/>
-      <c r="C86" s="27" t="n"/>
-      <c r="D86" s="27" t="n"/>
-      <c r="E86" s="27" t="n"/>
-      <c r="F86" s="27" t="n"/>
+      <c r="B86" s="22" t="n"/>
+      <c r="C86" s="22" t="n"/>
+      <c r="D86" s="22" t="n"/>
+      <c r="E86" s="22" t="n"/>
+      <c r="F86" s="22" t="n"/>
       <c r="G86" s="22" t="n"/>
       <c r="H86" s="22" t="n"/>
-      <c r="I86" s="22" t="n"/>
-      <c r="J86" s="22" t="n"/>
-      <c r="K86" s="22" t="n"/>
-      <c r="L86" s="22" t="n"/>
-      <c r="M86" s="22" t="n"/>
+      <c r="I86" s="27" t="n"/>
+      <c r="J86" s="27" t="n"/>
+      <c r="K86" s="27" t="n"/>
+      <c r="L86" s="27" t="n"/>
+      <c r="M86" s="27" t="n"/>
       <c r="N86" s="22" t="n"/>
       <c r="O86" s="22" t="n"/>
       <c r="P86" s="22" t="n"/>
@@ -12085,14 +12081,14 @@
           <t>14.1 Comentarios de actividad</t>
         </is>
       </c>
-      <c r="B87" s="28" t="n"/>
+      <c r="B87" s="22" t="n"/>
       <c r="C87" s="22" t="n"/>
       <c r="D87" s="22" t="n"/>
       <c r="E87" s="22" t="n"/>
       <c r="F87" s="22" t="n"/>
       <c r="G87" s="22" t="n"/>
       <c r="H87" s="22" t="n"/>
-      <c r="I87" s="22" t="n"/>
+      <c r="I87" s="28" t="n"/>
       <c r="J87" s="22" t="n"/>
       <c r="K87" s="22" t="n"/>
       <c r="L87" s="22" t="n"/>
@@ -12121,14 +12117,14 @@
       <c r="B88" s="22" t="n"/>
       <c r="C88" s="22" t="n"/>
       <c r="D88" s="22" t="n"/>
-      <c r="E88" s="21" t="n"/>
+      <c r="E88" s="22" t="n"/>
       <c r="F88" s="22" t="n"/>
       <c r="G88" s="22" t="n"/>
       <c r="H88" s="22" t="n"/>
       <c r="I88" s="22" t="n"/>
       <c r="J88" s="22" t="n"/>
       <c r="K88" s="22" t="n"/>
-      <c r="L88" s="22" t="n"/>
+      <c r="L88" s="21" t="n"/>
       <c r="M88" s="22" t="n"/>
       <c r="N88" s="22" t="n"/>
       <c r="O88" s="22" t="n"/>
@@ -12154,14 +12150,14 @@
       <c r="B89" s="22" t="n"/>
       <c r="C89" s="22" t="n"/>
       <c r="D89" s="22" t="n"/>
-      <c r="E89" s="25" t="n"/>
+      <c r="E89" s="22" t="n"/>
       <c r="F89" s="22" t="n"/>
       <c r="G89" s="22" t="n"/>
       <c r="H89" s="22" t="n"/>
       <c r="I89" s="22" t="n"/>
       <c r="J89" s="22" t="n"/>
       <c r="K89" s="22" t="n"/>
-      <c r="L89" s="22" t="n"/>
+      <c r="L89" s="25" t="n"/>
       <c r="M89" s="22" t="n"/>
       <c r="N89" s="22" t="n"/>
       <c r="O89" s="22" t="n"/>
@@ -12184,18 +12180,18 @@
           <t>14.4 Testeo</t>
         </is>
       </c>
-      <c r="B90" s="26" t="n"/>
-      <c r="C90" s="26" t="n"/>
-      <c r="D90" s="26" t="n"/>
-      <c r="E90" s="26" t="n"/>
-      <c r="F90" s="26" t="n"/>
+      <c r="B90" s="22" t="n"/>
+      <c r="C90" s="22" t="n"/>
+      <c r="D90" s="22" t="n"/>
+      <c r="E90" s="22" t="n"/>
+      <c r="F90" s="22" t="n"/>
       <c r="G90" s="22" t="n"/>
       <c r="H90" s="22" t="n"/>
-      <c r="I90" s="22" t="n"/>
-      <c r="J90" s="22" t="n"/>
-      <c r="K90" s="22" t="n"/>
-      <c r="L90" s="22" t="n"/>
-      <c r="M90" s="22" t="n"/>
+      <c r="I90" s="26" t="n"/>
+      <c r="J90" s="26" t="n"/>
+      <c r="K90" s="26" t="n"/>
+      <c r="L90" s="26" t="n"/>
+      <c r="M90" s="26" t="n"/>
       <c r="N90" s="22" t="n"/>
       <c r="O90" s="22" t="n"/>
       <c r="P90" s="22" t="n"/>
@@ -12217,18 +12213,18 @@
           <t>14.5 Documentación</t>
         </is>
       </c>
-      <c r="B91" s="27" t="n"/>
-      <c r="C91" s="27" t="n"/>
-      <c r="D91" s="27" t="n"/>
-      <c r="E91" s="27" t="n"/>
-      <c r="F91" s="27" t="n"/>
+      <c r="B91" s="22" t="n"/>
+      <c r="C91" s="22" t="n"/>
+      <c r="D91" s="22" t="n"/>
+      <c r="E91" s="22" t="n"/>
+      <c r="F91" s="22" t="n"/>
       <c r="G91" s="22" t="n"/>
       <c r="H91" s="22" t="n"/>
-      <c r="I91" s="22" t="n"/>
-      <c r="J91" s="22" t="n"/>
-      <c r="K91" s="22" t="n"/>
-      <c r="L91" s="22" t="n"/>
-      <c r="M91" s="22" t="n"/>
+      <c r="I91" s="27" t="n"/>
+      <c r="J91" s="27" t="n"/>
+      <c r="K91" s="27" t="n"/>
+      <c r="L91" s="27" t="n"/>
+      <c r="M91" s="27" t="n"/>
       <c r="N91" s="22" t="n"/>
       <c r="O91" s="22" t="n"/>
       <c r="P91" s="22" t="n"/>
@@ -12304,9 +12300,9 @@
       <c r="T93" s="22" t="n"/>
       <c r="U93" s="22" t="n"/>
       <c r="V93" s="22" t="n"/>
-      <c r="W93" s="29" t="inlineStr">
-        <is>
-          <t>en curso</t>
+      <c r="W93" s="23" t="inlineStr">
+        <is>
+          <t>completado</t>
         </is>
       </c>
     </row>
@@ -12337,9 +12333,9 @@
       <c r="T94" s="22" t="n"/>
       <c r="U94" s="22" t="n"/>
       <c r="V94" s="22" t="n"/>
-      <c r="W94" s="30" t="inlineStr">
-        <is>
-          <t>sin iniciar</t>
+      <c r="W94" s="29" t="inlineStr">
+        <is>
+          <t>en curso</t>
         </is>
       </c>
     </row>
@@ -12549,8 +12545,8 @@
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="P5:V5"/>
     <mergeCell ref="B4:H4"/>
+    <mergeCell ref="W4:W7"/>
     <mergeCell ref="P4:V4"/>
-    <mergeCell ref="W4:W7"/>
     <mergeCell ref="I4:O4"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="B5:H5"/>
